--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="255">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -548,6 +548,9 @@
   </si>
   <si>
     <t>['5', '63']</t>
+  </si>
+  <si>
+    <t>['11', '82']</t>
   </si>
   <si>
     <t>['12', '22', '45+1', '45+4', '90+1', '90+8']</t>
@@ -1137,7 +1140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP153"/>
+  <dimension ref="A1:BP154"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2011,7 +2014,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q5">
         <v>7.5</v>
@@ -2217,7 +2220,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2629,7 +2632,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q8">
         <v>4</v>
@@ -2710,7 +2713,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ8">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2835,7 +2838,7 @@
         <v>86</v>
       </c>
       <c r="P9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3119,7 +3122,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ10">
         <v>1</v>
@@ -3659,7 +3662,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3740,7 +3743,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ13">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3865,7 +3868,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q14">
         <v>2.4</v>
@@ -4689,7 +4692,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -5101,7 +5104,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -5307,7 +5310,7 @@
         <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5513,7 +5516,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5719,7 +5722,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -5925,7 +5928,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q24">
         <v>3.25</v>
@@ -6006,7 +6009,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ24">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -6131,7 +6134,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q25">
         <v>2.05</v>
@@ -6209,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ25">
         <v>0.22</v>
@@ -6337,7 +6340,7 @@
         <v>86</v>
       </c>
       <c r="P26" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6955,7 +6958,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7367,7 +7370,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7573,7 +7576,7 @@
         <v>86</v>
       </c>
       <c r="P32" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q32">
         <v>2.05</v>
@@ -8191,7 +8194,7 @@
         <v>86</v>
       </c>
       <c r="P35" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q35">
         <v>8.800000000000001</v>
@@ -8603,7 +8606,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -9299,7 +9302,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ40">
         <v>1.22</v>
@@ -9427,7 +9430,7 @@
         <v>86</v>
       </c>
       <c r="P41" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q41">
         <v>2.38</v>
@@ -9508,7 +9511,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ41">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR41">
         <v>1.88</v>
@@ -9839,7 +9842,7 @@
         <v>86</v>
       </c>
       <c r="P43" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q43">
         <v>7.5</v>
@@ -10045,7 +10048,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10457,7 +10460,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q46">
         <v>2.5</v>
@@ -10663,7 +10666,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q47">
         <v>4.33</v>
@@ -10869,7 +10872,7 @@
         <v>86</v>
       </c>
       <c r="P48" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q48">
         <v>2.4</v>
@@ -11487,7 +11490,7 @@
         <v>116</v>
       </c>
       <c r="P51" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11693,7 +11696,7 @@
         <v>118</v>
       </c>
       <c r="P52" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q52">
         <v>5.5</v>
@@ -12105,7 +12108,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -12392,7 +12395,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ55">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR55">
         <v>1.49</v>
@@ -12517,7 +12520,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q56">
         <v>5.5</v>
@@ -12723,7 +12726,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q57">
         <v>5</v>
@@ -12929,7 +12932,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13135,7 +13138,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13341,7 +13344,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13547,7 +13550,7 @@
         <v>86</v>
       </c>
       <c r="P61" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q61">
         <v>6.5</v>
@@ -13753,7 +13756,7 @@
         <v>86</v>
       </c>
       <c r="P62" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q62">
         <v>7</v>
@@ -13959,7 +13962,7 @@
         <v>86</v>
       </c>
       <c r="P63" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q63">
         <v>3.5</v>
@@ -14165,7 +14168,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14783,7 +14786,7 @@
         <v>86</v>
       </c>
       <c r="P67" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q67">
         <v>6.5</v>
@@ -14989,7 +14992,7 @@
         <v>86</v>
       </c>
       <c r="P68" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q68">
         <v>4.75</v>
@@ -15479,7 +15482,7 @@
         <v>3</v>
       </c>
       <c r="AP70">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ70">
         <v>2.1</v>
@@ -15607,7 +15610,7 @@
         <v>92</v>
       </c>
       <c r="P71" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q71">
         <v>9.5</v>
@@ -16225,7 +16228,7 @@
         <v>86</v>
       </c>
       <c r="P74" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16843,7 +16846,7 @@
         <v>130</v>
       </c>
       <c r="P77" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q77">
         <v>1.83</v>
@@ -17049,7 +17052,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q78">
         <v>12</v>
@@ -17255,7 +17258,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q79">
         <v>3.75</v>
@@ -17336,7 +17339,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ79">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR79">
         <v>1.25</v>
@@ -17461,7 +17464,7 @@
         <v>131</v>
       </c>
       <c r="P80" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17667,7 +17670,7 @@
         <v>132</v>
       </c>
       <c r="P81" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -17745,7 +17748,7 @@
         <v>1.8</v>
       </c>
       <c r="AP81">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ81">
         <v>1.7</v>
@@ -18079,7 +18082,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q83">
         <v>1.67</v>
@@ -18697,7 +18700,7 @@
         <v>134</v>
       </c>
       <c r="P86" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q86">
         <v>2.63</v>
@@ -19190,7 +19193,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ88">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR88">
         <v>1.18</v>
@@ -20345,7 +20348,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q94">
         <v>13</v>
@@ -20551,7 +20554,7 @@
         <v>139</v>
       </c>
       <c r="P95" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -20963,7 +20966,7 @@
         <v>140</v>
       </c>
       <c r="P97" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q97">
         <v>2.4</v>
@@ -21453,7 +21456,7 @@
         <v>1.2</v>
       </c>
       <c r="AP99">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ99">
         <v>1.2</v>
@@ -21787,7 +21790,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22405,7 +22408,7 @@
         <v>145</v>
       </c>
       <c r="P104" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22611,7 +22614,7 @@
         <v>86</v>
       </c>
       <c r="P105" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -22817,7 +22820,7 @@
         <v>146</v>
       </c>
       <c r="P106" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q106">
         <v>6</v>
@@ -23104,7 +23107,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ107">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR107">
         <v>1.46</v>
@@ -23229,7 +23232,7 @@
         <v>147</v>
       </c>
       <c r="P108" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23641,7 +23644,7 @@
         <v>149</v>
       </c>
       <c r="P110" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -24053,7 +24056,7 @@
         <v>143</v>
       </c>
       <c r="P112" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q112">
         <v>4.75</v>
@@ -24337,7 +24340,7 @@
         <v>0.67</v>
       </c>
       <c r="AP113">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ113">
         <v>0.44</v>
@@ -24877,7 +24880,7 @@
         <v>86</v>
       </c>
       <c r="P116" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q116">
         <v>4.5</v>
@@ -25083,7 +25086,7 @@
         <v>153</v>
       </c>
       <c r="P117" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q117">
         <v>1.53</v>
@@ -25289,7 +25292,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25495,7 +25498,7 @@
         <v>154</v>
       </c>
       <c r="P119" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q119">
         <v>1.8</v>
@@ -25701,7 +25704,7 @@
         <v>155</v>
       </c>
       <c r="P120" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q120">
         <v>7.5</v>
@@ -26113,7 +26116,7 @@
         <v>157</v>
       </c>
       <c r="P122" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q122">
         <v>2.63</v>
@@ -26191,7 +26194,7 @@
         <v>1.14</v>
       </c>
       <c r="AP122">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ122">
         <v>0.89</v>
@@ -26319,7 +26322,7 @@
         <v>158</v>
       </c>
       <c r="P123" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q123">
         <v>1.73</v>
@@ -26937,7 +26940,7 @@
         <v>86</v>
       </c>
       <c r="P126" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27143,7 +27146,7 @@
         <v>161</v>
       </c>
       <c r="P127" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27349,7 +27352,7 @@
         <v>86</v>
       </c>
       <c r="P128" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q128">
         <v>2.4</v>
@@ -27555,7 +27558,7 @@
         <v>138</v>
       </c>
       <c r="P129" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27761,7 +27764,7 @@
         <v>98</v>
       </c>
       <c r="P130" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q130">
         <v>6.5</v>
@@ -27967,7 +27970,7 @@
         <v>162</v>
       </c>
       <c r="P131" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q131">
         <v>4.33</v>
@@ -28173,7 +28176,7 @@
         <v>86</v>
       </c>
       <c r="P132" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q132">
         <v>8</v>
@@ -29696,7 +29699,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ139">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR139">
         <v>1.95</v>
@@ -29821,7 +29824,7 @@
         <v>167</v>
       </c>
       <c r="P140" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q140">
         <v>2.3</v>
@@ -30027,7 +30030,7 @@
         <v>86</v>
       </c>
       <c r="P141" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q141">
         <v>7.5</v>
@@ -30105,7 +30108,7 @@
         <v>2.71</v>
       </c>
       <c r="AP141">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ141">
         <v>2.78</v>
@@ -30233,7 +30236,7 @@
         <v>168</v>
       </c>
       <c r="P142" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30439,7 +30442,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30851,7 +30854,7 @@
         <v>171</v>
       </c>
       <c r="P145" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q145">
         <v>3.75</v>
@@ -31057,7 +31060,7 @@
         <v>172</v>
       </c>
       <c r="P146" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q146">
         <v>7.5</v>
@@ -31263,7 +31266,7 @@
         <v>173</v>
       </c>
       <c r="P147" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31469,7 +31472,7 @@
         <v>174</v>
       </c>
       <c r="P148" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q148">
         <v>2.75</v>
@@ -31675,7 +31678,7 @@
         <v>86</v>
       </c>
       <c r="P149" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q149">
         <v>7.5</v>
@@ -32087,7 +32090,7 @@
         <v>86</v>
       </c>
       <c r="P151" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q151">
         <v>6.5</v>
@@ -32293,7 +32296,7 @@
         <v>176</v>
       </c>
       <c r="P152" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q152">
         <v>2.75</v>
@@ -32499,7 +32502,7 @@
         <v>177</v>
       </c>
       <c r="P153" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q153">
         <v>4.75</v>
@@ -32655,6 +32658,212 @@
         <v>0</v>
       </c>
       <c r="BP153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:68">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154">
+        <v>7762752</v>
+      </c>
+      <c r="C154" t="s">
+        <v>68</v>
+      </c>
+      <c r="D154" t="s">
+        <v>69</v>
+      </c>
+      <c r="E154" s="2">
+        <v>45695.52083333334</v>
+      </c>
+      <c r="F154">
+        <v>20</v>
+      </c>
+      <c r="G154" t="s">
+        <v>78</v>
+      </c>
+      <c r="H154" t="s">
+        <v>84</v>
+      </c>
+      <c r="I154">
+        <v>1</v>
+      </c>
+      <c r="J154">
+        <v>1</v>
+      </c>
+      <c r="K154">
+        <v>2</v>
+      </c>
+      <c r="L154">
+        <v>2</v>
+      </c>
+      <c r="M154">
+        <v>2</v>
+      </c>
+      <c r="N154">
+        <v>4</v>
+      </c>
+      <c r="O154" t="s">
+        <v>178</v>
+      </c>
+      <c r="P154" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q154">
+        <v>2.75</v>
+      </c>
+      <c r="R154">
+        <v>1.95</v>
+      </c>
+      <c r="S154">
+        <v>4.75</v>
+      </c>
+      <c r="T154">
+        <v>1.44</v>
+      </c>
+      <c r="U154">
+        <v>2.63</v>
+      </c>
+      <c r="V154">
+        <v>3.25</v>
+      </c>
+      <c r="W154">
+        <v>1.33</v>
+      </c>
+      <c r="X154">
+        <v>10</v>
+      </c>
+      <c r="Y154">
+        <v>1.06</v>
+      </c>
+      <c r="Z154">
+        <v>1.85</v>
+      </c>
+      <c r="AA154">
+        <v>3.25</v>
+      </c>
+      <c r="AB154">
+        <v>3.7</v>
+      </c>
+      <c r="AC154">
+        <v>1.04</v>
+      </c>
+      <c r="AD154">
+        <v>7.2</v>
+      </c>
+      <c r="AE154">
+        <v>1.48</v>
+      </c>
+      <c r="AF154">
+        <v>2.48</v>
+      </c>
+      <c r="AG154">
+        <v>2.05</v>
+      </c>
+      <c r="AH154">
+        <v>1.61</v>
+      </c>
+      <c r="AI154">
+        <v>2.1</v>
+      </c>
+      <c r="AJ154">
+        <v>1.67</v>
+      </c>
+      <c r="AK154">
+        <v>1.2</v>
+      </c>
+      <c r="AL154">
+        <v>1.29</v>
+      </c>
+      <c r="AM154">
+        <v>1.83</v>
+      </c>
+      <c r="AN154">
+        <v>2.44</v>
+      </c>
+      <c r="AO154">
+        <v>1.56</v>
+      </c>
+      <c r="AP154">
+        <v>2.3</v>
+      </c>
+      <c r="AQ154">
+        <v>1.5</v>
+      </c>
+      <c r="AR154">
+        <v>1.41</v>
+      </c>
+      <c r="AS154">
+        <v>1.14</v>
+      </c>
+      <c r="AT154">
+        <v>2.55</v>
+      </c>
+      <c r="AU154">
+        <v>6</v>
+      </c>
+      <c r="AV154">
+        <v>7</v>
+      </c>
+      <c r="AW154">
+        <v>5</v>
+      </c>
+      <c r="AX154">
+        <v>4</v>
+      </c>
+      <c r="AY154">
+        <v>11</v>
+      </c>
+      <c r="AZ154">
+        <v>11</v>
+      </c>
+      <c r="BA154">
+        <v>4</v>
+      </c>
+      <c r="BB154">
+        <v>3</v>
+      </c>
+      <c r="BC154">
+        <v>7</v>
+      </c>
+      <c r="BD154">
+        <v>0</v>
+      </c>
+      <c r="BE154">
+        <v>0</v>
+      </c>
+      <c r="BF154">
+        <v>0</v>
+      </c>
+      <c r="BG154">
+        <v>0</v>
+      </c>
+      <c r="BH154">
+        <v>0</v>
+      </c>
+      <c r="BI154">
+        <v>0</v>
+      </c>
+      <c r="BJ154">
+        <v>0</v>
+      </c>
+      <c r="BK154">
+        <v>0</v>
+      </c>
+      <c r="BL154">
+        <v>0</v>
+      </c>
+      <c r="BM154">
+        <v>0</v>
+      </c>
+      <c r="BN154">
+        <v>0</v>
+      </c>
+      <c r="BO154">
+        <v>0</v>
+      </c>
+      <c r="BP154">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="257">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -553,6 +553,9 @@
     <t>['11', '82']</t>
   </si>
   <si>
+    <t>['23', '75']</t>
+  </si>
+  <si>
     <t>['12', '22', '45+1', '45+4', '90+1', '90+8']</t>
   </si>
   <si>
@@ -779,6 +782,9 @@
   </si>
   <si>
     <t>['20', '40', '45+1', '55']</t>
+  </si>
+  <si>
+    <t>['46', '50']</t>
   </si>
 </sst>
 </file>
@@ -1140,7 +1146,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP154"/>
+  <dimension ref="A1:BP155"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2014,7 +2020,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q5">
         <v>7.5</v>
@@ -2220,7 +2226,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2632,7 +2638,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q8">
         <v>4</v>
@@ -2838,7 +2844,7 @@
         <v>86</v>
       </c>
       <c r="P9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2916,7 +2922,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ9">
         <v>1.7</v>
@@ -3331,7 +3337,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ11">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3662,7 +3668,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3868,7 +3874,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q14">
         <v>2.4</v>
@@ -4692,7 +4698,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -5104,7 +5110,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -5310,7 +5316,7 @@
         <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5516,7 +5522,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5722,7 +5728,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -5928,7 +5934,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q24">
         <v>3.25</v>
@@ -6134,7 +6140,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q25">
         <v>2.05</v>
@@ -6340,7 +6346,7 @@
         <v>86</v>
       </c>
       <c r="P26" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6830,7 +6836,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ28">
         <v>0.5600000000000001</v>
@@ -6958,7 +6964,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7039,7 +7045,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ29">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR29">
         <v>2.25</v>
@@ -7370,7 +7376,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7576,7 +7582,7 @@
         <v>86</v>
       </c>
       <c r="P32" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q32">
         <v>2.05</v>
@@ -8194,7 +8200,7 @@
         <v>86</v>
       </c>
       <c r="P35" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q35">
         <v>8.800000000000001</v>
@@ -8606,7 +8612,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -8893,7 +8899,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ38">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR38">
         <v>0.86</v>
@@ -9430,7 +9436,7 @@
         <v>86</v>
       </c>
       <c r="P41" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q41">
         <v>2.38</v>
@@ -9842,7 +9848,7 @@
         <v>86</v>
       </c>
       <c r="P43" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q43">
         <v>7.5</v>
@@ -10048,7 +10054,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10126,7 +10132,7 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ44">
         <v>0.89</v>
@@ -10460,7 +10466,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q46">
         <v>2.5</v>
@@ -10666,7 +10672,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q47">
         <v>4.33</v>
@@ -10872,7 +10878,7 @@
         <v>86</v>
       </c>
       <c r="P48" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q48">
         <v>2.4</v>
@@ -11490,7 +11496,7 @@
         <v>116</v>
       </c>
       <c r="P51" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11696,7 +11702,7 @@
         <v>118</v>
       </c>
       <c r="P52" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q52">
         <v>5.5</v>
@@ -12108,7 +12114,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -12520,7 +12526,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q56">
         <v>5.5</v>
@@ -12598,7 +12604,7 @@
         <v>1</v>
       </c>
       <c r="AP56">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ56">
         <v>0.7</v>
@@ -12726,7 +12732,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q57">
         <v>5</v>
@@ -12932,7 +12938,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13138,7 +13144,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13344,7 +13350,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13550,7 +13556,7 @@
         <v>86</v>
       </c>
       <c r="P61" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q61">
         <v>6.5</v>
@@ -13756,7 +13762,7 @@
         <v>86</v>
       </c>
       <c r="P62" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q62">
         <v>7</v>
@@ -13962,7 +13968,7 @@
         <v>86</v>
       </c>
       <c r="P63" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q63">
         <v>3.5</v>
@@ -14168,7 +14174,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14786,7 +14792,7 @@
         <v>86</v>
       </c>
       <c r="P67" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q67">
         <v>6.5</v>
@@ -14992,7 +14998,7 @@
         <v>86</v>
       </c>
       <c r="P68" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q68">
         <v>4.75</v>
@@ -15279,7 +15285,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ69">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR69">
         <v>1.44</v>
@@ -15610,7 +15616,7 @@
         <v>92</v>
       </c>
       <c r="P71" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q71">
         <v>9.5</v>
@@ -15688,7 +15694,7 @@
         <v>2</v>
       </c>
       <c r="AP71">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ71">
         <v>1.3</v>
@@ -16228,7 +16234,7 @@
         <v>86</v>
       </c>
       <c r="P74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16846,7 +16852,7 @@
         <v>130</v>
       </c>
       <c r="P77" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q77">
         <v>1.83</v>
@@ -17052,7 +17058,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q78">
         <v>12</v>
@@ -17258,7 +17264,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q79">
         <v>3.75</v>
@@ -17336,7 +17342,7 @@
         <v>1.6</v>
       </c>
       <c r="AP79">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ79">
         <v>1.5</v>
@@ -17464,7 +17470,7 @@
         <v>131</v>
       </c>
       <c r="P80" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17670,7 +17676,7 @@
         <v>132</v>
       </c>
       <c r="P81" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -18082,7 +18088,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q83">
         <v>1.67</v>
@@ -18575,7 +18581,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ85">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR85">
         <v>0.85</v>
@@ -18700,7 +18706,7 @@
         <v>134</v>
       </c>
       <c r="P86" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q86">
         <v>2.63</v>
@@ -20348,7 +20354,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q94">
         <v>13</v>
@@ -20426,7 +20432,7 @@
         <v>3</v>
       </c>
       <c r="AP94">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ94">
         <v>2.78</v>
@@ -20554,7 +20560,7 @@
         <v>139</v>
       </c>
       <c r="P95" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -20966,7 +20972,7 @@
         <v>140</v>
       </c>
       <c r="P97" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q97">
         <v>2.4</v>
@@ -21253,7 +21259,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ98">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR98">
         <v>1.84</v>
@@ -21790,7 +21796,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22408,7 +22414,7 @@
         <v>145</v>
       </c>
       <c r="P104" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22614,7 +22620,7 @@
         <v>86</v>
       </c>
       <c r="P105" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -22820,7 +22826,7 @@
         <v>146</v>
       </c>
       <c r="P106" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q106">
         <v>6</v>
@@ -23232,7 +23238,7 @@
         <v>147</v>
       </c>
       <c r="P108" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23644,7 +23650,7 @@
         <v>149</v>
       </c>
       <c r="P110" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23928,7 +23934,7 @@
         <v>2.57</v>
       </c>
       <c r="AP111">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ111">
         <v>2.1</v>
@@ -24056,7 +24062,7 @@
         <v>143</v>
       </c>
       <c r="P112" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q112">
         <v>4.75</v>
@@ -24343,7 +24349,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ113">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR113">
         <v>1.41</v>
@@ -24880,7 +24886,7 @@
         <v>86</v>
       </c>
       <c r="P116" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q116">
         <v>4.5</v>
@@ -25086,7 +25092,7 @@
         <v>153</v>
       </c>
       <c r="P117" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q117">
         <v>1.53</v>
@@ -25292,7 +25298,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25498,7 +25504,7 @@
         <v>154</v>
       </c>
       <c r="P119" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q119">
         <v>1.8</v>
@@ -25704,7 +25710,7 @@
         <v>155</v>
       </c>
       <c r="P120" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q120">
         <v>7.5</v>
@@ -26116,7 +26122,7 @@
         <v>157</v>
       </c>
       <c r="P122" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q122">
         <v>2.63</v>
@@ -26322,7 +26328,7 @@
         <v>158</v>
       </c>
       <c r="P123" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q123">
         <v>1.73</v>
@@ -26403,7 +26409,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ123">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR123">
         <v>1.29</v>
@@ -26940,7 +26946,7 @@
         <v>86</v>
       </c>
       <c r="P126" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27146,7 +27152,7 @@
         <v>161</v>
       </c>
       <c r="P127" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27352,7 +27358,7 @@
         <v>86</v>
       </c>
       <c r="P128" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q128">
         <v>2.4</v>
@@ -27558,7 +27564,7 @@
         <v>138</v>
       </c>
       <c r="P129" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27764,7 +27770,7 @@
         <v>98</v>
       </c>
       <c r="P130" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q130">
         <v>6.5</v>
@@ -27842,7 +27848,7 @@
         <v>1.63</v>
       </c>
       <c r="AP130">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ130">
         <v>1.9</v>
@@ -27970,7 +27976,7 @@
         <v>162</v>
       </c>
       <c r="P131" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q131">
         <v>4.33</v>
@@ -28176,7 +28182,7 @@
         <v>86</v>
       </c>
       <c r="P132" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q132">
         <v>8</v>
@@ -29824,7 +29830,7 @@
         <v>167</v>
       </c>
       <c r="P140" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q140">
         <v>2.3</v>
@@ -29905,7 +29911,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ140">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR140">
         <v>1.34</v>
@@ -30030,7 +30036,7 @@
         <v>86</v>
       </c>
       <c r="P141" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q141">
         <v>7.5</v>
@@ -30236,7 +30242,7 @@
         <v>168</v>
       </c>
       <c r="P142" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30442,7 +30448,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30854,7 +30860,7 @@
         <v>171</v>
       </c>
       <c r="P145" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q145">
         <v>3.75</v>
@@ -31060,7 +31066,7 @@
         <v>172</v>
       </c>
       <c r="P146" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q146">
         <v>7.5</v>
@@ -31266,7 +31272,7 @@
         <v>173</v>
       </c>
       <c r="P147" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31472,7 +31478,7 @@
         <v>174</v>
       </c>
       <c r="P148" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q148">
         <v>2.75</v>
@@ -31678,7 +31684,7 @@
         <v>86</v>
       </c>
       <c r="P149" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q149">
         <v>7.5</v>
@@ -32090,7 +32096,7 @@
         <v>86</v>
       </c>
       <c r="P151" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q151">
         <v>6.5</v>
@@ -32296,7 +32302,7 @@
         <v>176</v>
       </c>
       <c r="P152" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q152">
         <v>2.75</v>
@@ -32502,7 +32508,7 @@
         <v>177</v>
       </c>
       <c r="P153" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q153">
         <v>4.75</v>
@@ -32864,6 +32870,212 @@
         <v>0</v>
       </c>
       <c r="BP154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:68">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155">
+        <v>7762747</v>
+      </c>
+      <c r="C155" t="s">
+        <v>68</v>
+      </c>
+      <c r="D155" t="s">
+        <v>69</v>
+      </c>
+      <c r="E155" s="2">
+        <v>45696.3125</v>
+      </c>
+      <c r="F155">
+        <v>20</v>
+      </c>
+      <c r="G155" t="s">
+        <v>77</v>
+      </c>
+      <c r="H155" t="s">
+        <v>74</v>
+      </c>
+      <c r="I155">
+        <v>1</v>
+      </c>
+      <c r="J155">
+        <v>0</v>
+      </c>
+      <c r="K155">
+        <v>1</v>
+      </c>
+      <c r="L155">
+        <v>2</v>
+      </c>
+      <c r="M155">
+        <v>2</v>
+      </c>
+      <c r="N155">
+        <v>4</v>
+      </c>
+      <c r="O155" t="s">
+        <v>179</v>
+      </c>
+      <c r="P155" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q155">
+        <v>3</v>
+      </c>
+      <c r="R155">
+        <v>2</v>
+      </c>
+      <c r="S155">
+        <v>4</v>
+      </c>
+      <c r="T155">
+        <v>1.5</v>
+      </c>
+      <c r="U155">
+        <v>2.5</v>
+      </c>
+      <c r="V155">
+        <v>3.5</v>
+      </c>
+      <c r="W155">
+        <v>1.29</v>
+      </c>
+      <c r="X155">
+        <v>11</v>
+      </c>
+      <c r="Y155">
+        <v>1.05</v>
+      </c>
+      <c r="Z155">
+        <v>2.12</v>
+      </c>
+      <c r="AA155">
+        <v>3.23</v>
+      </c>
+      <c r="AB155">
+        <v>3.45</v>
+      </c>
+      <c r="AC155">
+        <v>1.03</v>
+      </c>
+      <c r="AD155">
+        <v>7.6</v>
+      </c>
+      <c r="AE155">
+        <v>1.4</v>
+      </c>
+      <c r="AF155">
+        <v>2.85</v>
+      </c>
+      <c r="AG155">
+        <v>2.15</v>
+      </c>
+      <c r="AH155">
+        <v>1.57</v>
+      </c>
+      <c r="AI155">
+        <v>2</v>
+      </c>
+      <c r="AJ155">
+        <v>1.73</v>
+      </c>
+      <c r="AK155">
+        <v>1.29</v>
+      </c>
+      <c r="AL155">
+        <v>1.32</v>
+      </c>
+      <c r="AM155">
+        <v>1.62</v>
+      </c>
+      <c r="AN155">
+        <v>0.78</v>
+      </c>
+      <c r="AO155">
+        <v>0.44</v>
+      </c>
+      <c r="AP155">
+        <v>0.8</v>
+      </c>
+      <c r="AQ155">
+        <v>0.5</v>
+      </c>
+      <c r="AR155">
+        <v>1.02</v>
+      </c>
+      <c r="AS155">
+        <v>0.86</v>
+      </c>
+      <c r="AT155">
+        <v>1.88</v>
+      </c>
+      <c r="AU155">
+        <v>5</v>
+      </c>
+      <c r="AV155">
+        <v>7</v>
+      </c>
+      <c r="AW155">
+        <v>6</v>
+      </c>
+      <c r="AX155">
+        <v>3</v>
+      </c>
+      <c r="AY155">
+        <v>11</v>
+      </c>
+      <c r="AZ155">
+        <v>10</v>
+      </c>
+      <c r="BA155">
+        <v>5</v>
+      </c>
+      <c r="BB155">
+        <v>3</v>
+      </c>
+      <c r="BC155">
+        <v>8</v>
+      </c>
+      <c r="BD155">
+        <v>0</v>
+      </c>
+      <c r="BE155">
+        <v>0</v>
+      </c>
+      <c r="BF155">
+        <v>0</v>
+      </c>
+      <c r="BG155">
+        <v>0</v>
+      </c>
+      <c r="BH155">
+        <v>0</v>
+      </c>
+      <c r="BI155">
+        <v>0</v>
+      </c>
+      <c r="BJ155">
+        <v>0</v>
+      </c>
+      <c r="BK155">
+        <v>0</v>
+      </c>
+      <c r="BL155">
+        <v>0</v>
+      </c>
+      <c r="BM155">
+        <v>0</v>
+      </c>
+      <c r="BN155">
+        <v>0</v>
+      </c>
+      <c r="BO155">
+        <v>0</v>
+      </c>
+      <c r="BP155">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="259">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -550,10 +550,13 @@
     <t>['5', '63']</t>
   </si>
   <si>
-    <t>['11', '82']</t>
+    <t>['11', '81']</t>
   </si>
   <si>
     <t>['23', '75']</t>
+  </si>
+  <si>
+    <t>['63']</t>
   </si>
   <si>
     <t>['12', '22', '45+1', '45+4', '90+1', '90+8']</t>
@@ -785,6 +788,9 @@
   </si>
   <si>
     <t>['46', '50']</t>
+  </si>
+  <si>
+    <t>['21', '23']</t>
   </si>
 </sst>
 </file>
@@ -1146,7 +1152,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP155"/>
+  <dimension ref="A1:BP157"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1480,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AQ2">
         <v>1.3</v>
@@ -2020,7 +2026,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q5">
         <v>7.5</v>
@@ -2226,7 +2232,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2513,7 +2519,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ7">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2638,7 +2644,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q8">
         <v>4</v>
@@ -2844,7 +2850,7 @@
         <v>86</v>
       </c>
       <c r="P9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3668,7 +3674,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3874,7 +3880,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q14">
         <v>2.4</v>
@@ -3955,7 +3961,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ14">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4364,7 +4370,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AQ16">
         <v>1.2</v>
@@ -4698,7 +4704,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -4985,7 +4991,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ19">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5110,7 +5116,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -5316,7 +5322,7 @@
         <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5522,7 +5528,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5728,7 +5734,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -5934,7 +5940,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q24">
         <v>3.25</v>
@@ -6012,7 +6018,7 @@
         <v>2</v>
       </c>
       <c r="AP24">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ24">
         <v>1.5</v>
@@ -6140,7 +6146,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q25">
         <v>2.05</v>
@@ -6346,7 +6352,7 @@
         <v>86</v>
       </c>
       <c r="P26" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6427,7 +6433,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ26">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AR26">
         <v>1.84</v>
@@ -6964,7 +6970,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7042,7 +7048,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AQ29">
         <v>0.5</v>
@@ -7376,7 +7382,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7582,7 +7588,7 @@
         <v>86</v>
       </c>
       <c r="P32" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q32">
         <v>2.05</v>
@@ -8200,7 +8206,7 @@
         <v>86</v>
       </c>
       <c r="P35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q35">
         <v>8.800000000000001</v>
@@ -8612,7 +8618,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -9311,7 +9317,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ40">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR40">
         <v>1.4</v>
@@ -9436,7 +9442,7 @@
         <v>86</v>
       </c>
       <c r="P41" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q41">
         <v>2.38</v>
@@ -9848,7 +9854,7 @@
         <v>86</v>
       </c>
       <c r="P43" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q43">
         <v>7.5</v>
@@ -10054,7 +10060,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10135,7 +10141,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ44">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AR44">
         <v>0.95</v>
@@ -10338,7 +10344,7 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AQ45">
         <v>1</v>
@@ -10466,7 +10472,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q46">
         <v>2.5</v>
@@ -10544,7 +10550,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ46">
         <v>1.2</v>
@@ -10672,7 +10678,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q47">
         <v>4.33</v>
@@ -10878,7 +10884,7 @@
         <v>86</v>
       </c>
       <c r="P48" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q48">
         <v>2.4</v>
@@ -11496,7 +11502,7 @@
         <v>116</v>
       </c>
       <c r="P51" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11702,7 +11708,7 @@
         <v>118</v>
       </c>
       <c r="P52" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q52">
         <v>5.5</v>
@@ -12114,7 +12120,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -12526,7 +12532,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q56">
         <v>5.5</v>
@@ -12732,7 +12738,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q57">
         <v>5</v>
@@ -12938,7 +12944,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13016,7 +13022,7 @@
         <v>0.25</v>
       </c>
       <c r="AP58">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AQ58">
         <v>1.2</v>
@@ -13144,7 +13150,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13350,7 +13356,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13556,7 +13562,7 @@
         <v>86</v>
       </c>
       <c r="P61" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q61">
         <v>6.5</v>
@@ -13637,7 +13643,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ61">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR61">
         <v>1.06</v>
@@ -13762,7 +13768,7 @@
         <v>86</v>
       </c>
       <c r="P62" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q62">
         <v>7</v>
@@ -13840,7 +13846,7 @@
         <v>3</v>
       </c>
       <c r="AP62">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ62">
         <v>2.78</v>
@@ -13968,7 +13974,7 @@
         <v>86</v>
       </c>
       <c r="P63" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q63">
         <v>3.5</v>
@@ -14174,7 +14180,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14792,7 +14798,7 @@
         <v>86</v>
       </c>
       <c r="P67" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q67">
         <v>6.5</v>
@@ -14870,7 +14876,7 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ67">
         <v>1.9</v>
@@ -14998,7 +15004,7 @@
         <v>86</v>
       </c>
       <c r="P68" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q68">
         <v>4.75</v>
@@ -15616,7 +15622,7 @@
         <v>92</v>
       </c>
       <c r="P71" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q71">
         <v>9.5</v>
@@ -16234,7 +16240,7 @@
         <v>86</v>
       </c>
       <c r="P74" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16518,10 +16524,10 @@
         <v>0.75</v>
       </c>
       <c r="AP75">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AQ75">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR75">
         <v>1.99</v>
@@ -16852,7 +16858,7 @@
         <v>130</v>
       </c>
       <c r="P77" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q77">
         <v>1.83</v>
@@ -17058,7 +17064,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q78">
         <v>12</v>
@@ -17264,7 +17270,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q79">
         <v>3.75</v>
@@ -17470,7 +17476,7 @@
         <v>131</v>
       </c>
       <c r="P80" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17676,7 +17682,7 @@
         <v>132</v>
       </c>
       <c r="P81" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -17960,7 +17966,7 @@
         <v>1.75</v>
       </c>
       <c r="AP82">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ82">
         <v>1.9</v>
@@ -18088,7 +18094,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q83">
         <v>1.67</v>
@@ -18706,7 +18712,7 @@
         <v>134</v>
       </c>
       <c r="P86" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q86">
         <v>2.63</v>
@@ -18993,7 +18999,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ87">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AR87">
         <v>1.66</v>
@@ -19405,7 +19411,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ89">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AR89">
         <v>1.32</v>
@@ -19817,7 +19823,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ91">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR91">
         <v>1.91</v>
@@ -20226,7 +20232,7 @@
         <v>0.4</v>
       </c>
       <c r="AP93">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AQ93">
         <v>0.22</v>
@@ -20354,7 +20360,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q94">
         <v>13</v>
@@ -20560,7 +20566,7 @@
         <v>139</v>
       </c>
       <c r="P95" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -20847,7 +20853,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ96">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AR96">
         <v>1.46</v>
@@ -20972,7 +20978,7 @@
         <v>140</v>
       </c>
       <c r="P97" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q97">
         <v>2.4</v>
@@ -21050,7 +21056,7 @@
         <v>1</v>
       </c>
       <c r="AP97">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ97">
         <v>0.5600000000000001</v>
@@ -21796,7 +21802,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22414,7 +22420,7 @@
         <v>145</v>
       </c>
       <c r="P104" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22620,7 +22626,7 @@
         <v>86</v>
       </c>
       <c r="P105" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -22826,7 +22832,7 @@
         <v>146</v>
       </c>
       <c r="P106" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q106">
         <v>6</v>
@@ -22907,7 +22913,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ106">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR106">
         <v>1.32</v>
@@ -23238,7 +23244,7 @@
         <v>147</v>
       </c>
       <c r="P108" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23650,7 +23656,7 @@
         <v>149</v>
       </c>
       <c r="P110" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23728,7 +23734,7 @@
         <v>1.86</v>
       </c>
       <c r="AP110">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AQ110">
         <v>1.9</v>
@@ -24062,7 +24068,7 @@
         <v>143</v>
       </c>
       <c r="P112" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q112">
         <v>4.75</v>
@@ -24143,7 +24149,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ112">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR112">
         <v>1.48</v>
@@ -24758,10 +24764,10 @@
         <v>1.33</v>
       </c>
       <c r="AP115">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ115">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AR115">
         <v>1.42</v>
@@ -24886,7 +24892,7 @@
         <v>86</v>
       </c>
       <c r="P116" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q116">
         <v>4.5</v>
@@ -25092,7 +25098,7 @@
         <v>153</v>
       </c>
       <c r="P117" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q117">
         <v>1.53</v>
@@ -25298,7 +25304,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25504,7 +25510,7 @@
         <v>154</v>
       </c>
       <c r="P119" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q119">
         <v>1.8</v>
@@ -25710,7 +25716,7 @@
         <v>155</v>
       </c>
       <c r="P120" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q120">
         <v>7.5</v>
@@ -26122,7 +26128,7 @@
         <v>157</v>
       </c>
       <c r="P122" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q122">
         <v>2.63</v>
@@ -26203,7 +26209,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ122">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AR122">
         <v>1.43</v>
@@ -26328,7 +26334,7 @@
         <v>158</v>
       </c>
       <c r="P123" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q123">
         <v>1.73</v>
@@ -26946,7 +26952,7 @@
         <v>86</v>
       </c>
       <c r="P126" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27152,7 +27158,7 @@
         <v>161</v>
       </c>
       <c r="P127" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27358,7 +27364,7 @@
         <v>86</v>
       </c>
       <c r="P128" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q128">
         <v>2.4</v>
@@ -27436,7 +27442,7 @@
         <v>0.86</v>
       </c>
       <c r="AP128">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ128">
         <v>1</v>
@@ -27564,7 +27570,7 @@
         <v>138</v>
       </c>
       <c r="P129" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27770,7 +27776,7 @@
         <v>98</v>
       </c>
       <c r="P130" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q130">
         <v>6.5</v>
@@ -27976,7 +27982,7 @@
         <v>162</v>
       </c>
       <c r="P131" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q131">
         <v>4.33</v>
@@ -28182,7 +28188,7 @@
         <v>86</v>
       </c>
       <c r="P132" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q132">
         <v>8</v>
@@ -28469,7 +28475,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ133">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR133">
         <v>0.99</v>
@@ -29496,7 +29502,7 @@
         <v>0.63</v>
       </c>
       <c r="AP138">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AQ138">
         <v>0.5600000000000001</v>
@@ -29830,7 +29836,7 @@
         <v>167</v>
       </c>
       <c r="P140" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q140">
         <v>2.3</v>
@@ -30036,7 +30042,7 @@
         <v>86</v>
       </c>
       <c r="P141" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q141">
         <v>7.5</v>
@@ -30242,7 +30248,7 @@
         <v>168</v>
       </c>
       <c r="P142" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30323,7 +30329,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ142">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AR142">
         <v>2.2</v>
@@ -30448,7 +30454,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30526,7 +30532,7 @@
         <v>0.25</v>
       </c>
       <c r="AP143">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ143">
         <v>0.22</v>
@@ -30860,7 +30866,7 @@
         <v>171</v>
       </c>
       <c r="P145" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q145">
         <v>3.75</v>
@@ -31066,7 +31072,7 @@
         <v>172</v>
       </c>
       <c r="P146" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q146">
         <v>7.5</v>
@@ -31272,7 +31278,7 @@
         <v>173</v>
       </c>
       <c r="P147" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31478,7 +31484,7 @@
         <v>174</v>
       </c>
       <c r="P148" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q148">
         <v>2.75</v>
@@ -31684,7 +31690,7 @@
         <v>86</v>
       </c>
       <c r="P149" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q149">
         <v>7.5</v>
@@ -32096,7 +32102,7 @@
         <v>86</v>
       </c>
       <c r="P151" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q151">
         <v>6.5</v>
@@ -32302,7 +32308,7 @@
         <v>176</v>
       </c>
       <c r="P152" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q152">
         <v>2.75</v>
@@ -32508,7 +32514,7 @@
         <v>177</v>
       </c>
       <c r="P153" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q153">
         <v>4.75</v>
@@ -32920,7 +32926,7 @@
         <v>179</v>
       </c>
       <c r="P155" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33077,6 +33083,418 @@
       </c>
       <c r="BP155">
         <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:68">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156">
+        <v>7762748</v>
+      </c>
+      <c r="C156" t="s">
+        <v>68</v>
+      </c>
+      <c r="D156" t="s">
+        <v>69</v>
+      </c>
+      <c r="E156" s="2">
+        <v>45696.41666666666</v>
+      </c>
+      <c r="F156">
+        <v>20</v>
+      </c>
+      <c r="G156" t="s">
+        <v>70</v>
+      </c>
+      <c r="H156" t="s">
+        <v>72</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="J156">
+        <v>2</v>
+      </c>
+      <c r="K156">
+        <v>2</v>
+      </c>
+      <c r="L156">
+        <v>1</v>
+      </c>
+      <c r="M156">
+        <v>2</v>
+      </c>
+      <c r="N156">
+        <v>3</v>
+      </c>
+      <c r="O156" t="s">
+        <v>176</v>
+      </c>
+      <c r="P156" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q156">
+        <v>2.2</v>
+      </c>
+      <c r="R156">
+        <v>2.1</v>
+      </c>
+      <c r="S156">
+        <v>7</v>
+      </c>
+      <c r="T156">
+        <v>1.44</v>
+      </c>
+      <c r="U156">
+        <v>2.63</v>
+      </c>
+      <c r="V156">
+        <v>3.4</v>
+      </c>
+      <c r="W156">
+        <v>1.3</v>
+      </c>
+      <c r="X156">
+        <v>10</v>
+      </c>
+      <c r="Y156">
+        <v>1.06</v>
+      </c>
+      <c r="Z156">
+        <v>1.42</v>
+      </c>
+      <c r="AA156">
+        <v>3.98</v>
+      </c>
+      <c r="AB156">
+        <v>8.9</v>
+      </c>
+      <c r="AC156">
+        <v>1.01</v>
+      </c>
+      <c r="AD156">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE156">
+        <v>1.34</v>
+      </c>
+      <c r="AF156">
+        <v>3.1</v>
+      </c>
+      <c r="AG156">
+        <v>2.05</v>
+      </c>
+      <c r="AH156">
+        <v>1.61</v>
+      </c>
+      <c r="AI156">
+        <v>2.25</v>
+      </c>
+      <c r="AJ156">
+        <v>1.57</v>
+      </c>
+      <c r="AK156">
+        <v>1.09</v>
+      </c>
+      <c r="AL156">
+        <v>1.18</v>
+      </c>
+      <c r="AM156">
+        <v>2.6</v>
+      </c>
+      <c r="AN156">
+        <v>2.33</v>
+      </c>
+      <c r="AO156">
+        <v>0.89</v>
+      </c>
+      <c r="AP156">
+        <v>2.1</v>
+      </c>
+      <c r="AQ156">
+        <v>1.1</v>
+      </c>
+      <c r="AR156">
+        <v>1.7</v>
+      </c>
+      <c r="AS156">
+        <v>1.25</v>
+      </c>
+      <c r="AT156">
+        <v>2.95</v>
+      </c>
+      <c r="AU156">
+        <v>5</v>
+      </c>
+      <c r="AV156">
+        <v>6</v>
+      </c>
+      <c r="AW156">
+        <v>7</v>
+      </c>
+      <c r="AX156">
+        <v>4</v>
+      </c>
+      <c r="AY156">
+        <v>12</v>
+      </c>
+      <c r="AZ156">
+        <v>10</v>
+      </c>
+      <c r="BA156">
+        <v>11</v>
+      </c>
+      <c r="BB156">
+        <v>6</v>
+      </c>
+      <c r="BC156">
+        <v>17</v>
+      </c>
+      <c r="BD156">
+        <v>1.34</v>
+      </c>
+      <c r="BE156">
+        <v>7</v>
+      </c>
+      <c r="BF156">
+        <v>3.65</v>
+      </c>
+      <c r="BG156">
+        <v>1.38</v>
+      </c>
+      <c r="BH156">
+        <v>2.8</v>
+      </c>
+      <c r="BI156">
+        <v>1.64</v>
+      </c>
+      <c r="BJ156">
+        <v>2.1</v>
+      </c>
+      <c r="BK156">
+        <v>2.05</v>
+      </c>
+      <c r="BL156">
+        <v>1.68</v>
+      </c>
+      <c r="BM156">
+        <v>2.65</v>
+      </c>
+      <c r="BN156">
+        <v>1.42</v>
+      </c>
+      <c r="BO156">
+        <v>3.55</v>
+      </c>
+      <c r="BP156">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="157" spans="1:68">
+      <c r="A157" s="1">
+        <v>156</v>
+      </c>
+      <c r="B157">
+        <v>7762753</v>
+      </c>
+      <c r="C157" t="s">
+        <v>68</v>
+      </c>
+      <c r="D157" t="s">
+        <v>69</v>
+      </c>
+      <c r="E157" s="2">
+        <v>45696.52083333334</v>
+      </c>
+      <c r="F157">
+        <v>20</v>
+      </c>
+      <c r="G157" t="s">
+        <v>85</v>
+      </c>
+      <c r="H157" t="s">
+        <v>80</v>
+      </c>
+      <c r="I157">
+        <v>0</v>
+      </c>
+      <c r="J157">
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <v>0</v>
+      </c>
+      <c r="L157">
+        <v>1</v>
+      </c>
+      <c r="M157">
+        <v>0</v>
+      </c>
+      <c r="N157">
+        <v>1</v>
+      </c>
+      <c r="O157" t="s">
+        <v>180</v>
+      </c>
+      <c r="P157" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q157">
+        <v>5</v>
+      </c>
+      <c r="R157">
+        <v>2.2</v>
+      </c>
+      <c r="S157">
+        <v>2.38</v>
+      </c>
+      <c r="T157">
+        <v>1.4</v>
+      </c>
+      <c r="U157">
+        <v>2.75</v>
+      </c>
+      <c r="V157">
+        <v>3</v>
+      </c>
+      <c r="W157">
+        <v>1.36</v>
+      </c>
+      <c r="X157">
+        <v>8</v>
+      </c>
+      <c r="Y157">
+        <v>1.08</v>
+      </c>
+      <c r="Z157">
+        <v>4.5</v>
+      </c>
+      <c r="AA157">
+        <v>3.71</v>
+      </c>
+      <c r="AB157">
+        <v>1.73</v>
+      </c>
+      <c r="AC157">
+        <v>1.03</v>
+      </c>
+      <c r="AD157">
+        <v>9</v>
+      </c>
+      <c r="AE157">
+        <v>1.3</v>
+      </c>
+      <c r="AF157">
+        <v>3.3</v>
+      </c>
+      <c r="AG157">
+        <v>1.92</v>
+      </c>
+      <c r="AH157">
+        <v>1.82</v>
+      </c>
+      <c r="AI157">
+        <v>1.83</v>
+      </c>
+      <c r="AJ157">
+        <v>1.83</v>
+      </c>
+      <c r="AK157">
+        <v>2.04</v>
+      </c>
+      <c r="AL157">
+        <v>1.24</v>
+      </c>
+      <c r="AM157">
+        <v>1.18</v>
+      </c>
+      <c r="AN157">
+        <v>1.78</v>
+      </c>
+      <c r="AO157">
+        <v>1.22</v>
+      </c>
+      <c r="AP157">
+        <v>1.9</v>
+      </c>
+      <c r="AQ157">
+        <v>1.1</v>
+      </c>
+      <c r="AR157">
+        <v>1.48</v>
+      </c>
+      <c r="AS157">
+        <v>1.68</v>
+      </c>
+      <c r="AT157">
+        <v>3.16</v>
+      </c>
+      <c r="AU157">
+        <v>4</v>
+      </c>
+      <c r="AV157">
+        <v>5</v>
+      </c>
+      <c r="AW157">
+        <v>5</v>
+      </c>
+      <c r="AX157">
+        <v>1</v>
+      </c>
+      <c r="AY157">
+        <v>9</v>
+      </c>
+      <c r="AZ157">
+        <v>6</v>
+      </c>
+      <c r="BA157">
+        <v>1</v>
+      </c>
+      <c r="BB157">
+        <v>3</v>
+      </c>
+      <c r="BC157">
+        <v>4</v>
+      </c>
+      <c r="BD157">
+        <v>3.2</v>
+      </c>
+      <c r="BE157">
+        <v>7</v>
+      </c>
+      <c r="BF157">
+        <v>1.42</v>
+      </c>
+      <c r="BG157">
+        <v>1.26</v>
+      </c>
+      <c r="BH157">
+        <v>3.4</v>
+      </c>
+      <c r="BI157">
+        <v>1.47</v>
+      </c>
+      <c r="BJ157">
+        <v>2.48</v>
+      </c>
+      <c r="BK157">
+        <v>1.75</v>
+      </c>
+      <c r="BL157">
+        <v>1.95</v>
+      </c>
+      <c r="BM157">
+        <v>2.18</v>
+      </c>
+      <c r="BN157">
+        <v>1.58</v>
+      </c>
+      <c r="BO157">
+        <v>2.8</v>
+      </c>
+      <c r="BP157">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="262">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -559,6 +559,12 @@
     <t>['63']</t>
   </si>
   <si>
+    <t>['55']</t>
+  </si>
+  <si>
+    <t>['45']</t>
+  </si>
+  <si>
     <t>['12', '22', '45+1', '45+4', '90+1', '90+8']</t>
   </si>
   <si>
@@ -791,6 +797,9 @@
   </si>
   <si>
     <t>['21', '23']</t>
+  </si>
+  <si>
+    <t>['1', '19', '44', '60']</t>
   </si>
 </sst>
 </file>
@@ -1152,7 +1161,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP157"/>
+  <dimension ref="A1:BP159"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2026,7 +2035,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q5">
         <v>7.5</v>
@@ -2232,7 +2241,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2644,7 +2653,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q8">
         <v>4</v>
@@ -2850,7 +2859,7 @@
         <v>86</v>
       </c>
       <c r="P9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3549,7 +3558,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ12">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3674,7 +3683,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3752,7 +3761,7 @@
         <v>3</v>
       </c>
       <c r="AP13">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ13">
         <v>1.5</v>
@@ -3880,7 +3889,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q14">
         <v>2.4</v>
@@ -3958,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ14">
         <v>1.1</v>
@@ -4167,7 +4176,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ15">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4704,7 +4713,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -5116,7 +5125,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -5322,7 +5331,7 @@
         <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5528,7 +5537,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5734,7 +5743,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -5940,7 +5949,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q24">
         <v>3.25</v>
@@ -6146,7 +6155,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q25">
         <v>2.05</v>
@@ -6227,7 +6236,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ25">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR25">
         <v>1.06</v>
@@ -6352,7 +6361,7 @@
         <v>86</v>
       </c>
       <c r="P26" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6845,7 +6854,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ28">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR28">
         <v>0.91</v>
@@ -6970,7 +6979,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7382,7 +7391,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7588,7 +7597,7 @@
         <v>86</v>
       </c>
       <c r="P32" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q32">
         <v>2.05</v>
@@ -8206,7 +8215,7 @@
         <v>86</v>
       </c>
       <c r="P35" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q35">
         <v>8.800000000000001</v>
@@ -8618,7 +8627,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -9111,7 +9120,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ39">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR39">
         <v>1.98</v>
@@ -9442,7 +9451,7 @@
         <v>86</v>
       </c>
       <c r="P41" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q41">
         <v>2.38</v>
@@ -9520,7 +9529,7 @@
         <v>1.33</v>
       </c>
       <c r="AP41">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ41">
         <v>1.5</v>
@@ -9726,7 +9735,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ42">
         <v>0.7</v>
@@ -9854,7 +9863,7 @@
         <v>86</v>
       </c>
       <c r="P43" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q43">
         <v>7.5</v>
@@ -10060,7 +10069,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10472,7 +10481,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q46">
         <v>2.5</v>
@@ -10678,7 +10687,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q47">
         <v>4.33</v>
@@ -10884,7 +10893,7 @@
         <v>86</v>
       </c>
       <c r="P48" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q48">
         <v>2.4</v>
@@ -11502,7 +11511,7 @@
         <v>116</v>
       </c>
       <c r="P51" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11583,7 +11592,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ51">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR51">
         <v>1.13</v>
@@ -11708,7 +11717,7 @@
         <v>118</v>
       </c>
       <c r="P52" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q52">
         <v>5.5</v>
@@ -12120,7 +12129,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -12201,7 +12210,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ54">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR54">
         <v>1.14</v>
@@ -12532,7 +12541,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q56">
         <v>5.5</v>
@@ -12738,7 +12747,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q57">
         <v>5</v>
@@ -12944,7 +12953,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13150,7 +13159,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13228,7 +13237,7 @@
         <v>1.75</v>
       </c>
       <c r="AP59">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ59">
         <v>1.9</v>
@@ -13356,7 +13365,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13562,7 +13571,7 @@
         <v>86</v>
       </c>
       <c r="P61" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q61">
         <v>6.5</v>
@@ -13768,7 +13777,7 @@
         <v>86</v>
       </c>
       <c r="P62" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q62">
         <v>7</v>
@@ -13974,7 +13983,7 @@
         <v>86</v>
       </c>
       <c r="P63" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q63">
         <v>3.5</v>
@@ -14180,7 +14189,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14673,7 +14682,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ66">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR66">
         <v>1.61</v>
@@ -14798,7 +14807,7 @@
         <v>86</v>
       </c>
       <c r="P67" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q67">
         <v>6.5</v>
@@ -15004,7 +15013,7 @@
         <v>86</v>
       </c>
       <c r="P68" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q68">
         <v>4.75</v>
@@ -15622,7 +15631,7 @@
         <v>92</v>
       </c>
       <c r="P71" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q71">
         <v>9.5</v>
@@ -15909,7 +15918,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ72">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR72">
         <v>1.09</v>
@@ -16240,7 +16249,7 @@
         <v>86</v>
       </c>
       <c r="P74" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16730,7 +16739,7 @@
         <v>2.5</v>
       </c>
       <c r="AP76">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ76">
         <v>2.1</v>
@@ -16858,7 +16867,7 @@
         <v>130</v>
       </c>
       <c r="P77" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q77">
         <v>1.83</v>
@@ -17064,7 +17073,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q78">
         <v>12</v>
@@ -17270,7 +17279,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q79">
         <v>3.75</v>
@@ -17476,7 +17485,7 @@
         <v>131</v>
       </c>
       <c r="P80" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17682,7 +17691,7 @@
         <v>132</v>
       </c>
       <c r="P81" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -18094,7 +18103,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q83">
         <v>1.67</v>
@@ -18378,7 +18387,7 @@
         <v>2.17</v>
       </c>
       <c r="AP84">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ84">
         <v>1.9</v>
@@ -18712,7 +18721,7 @@
         <v>134</v>
       </c>
       <c r="P86" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q86">
         <v>2.63</v>
@@ -18793,7 +18802,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ86">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR86">
         <v>1.23</v>
@@ -20026,7 +20035,7 @@
         <v>0.67</v>
       </c>
       <c r="AP92">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ92">
         <v>0.7</v>
@@ -20235,7 +20244,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ93">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR93">
         <v>1.8</v>
@@ -20360,7 +20369,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q94">
         <v>13</v>
@@ -20566,7 +20575,7 @@
         <v>139</v>
       </c>
       <c r="P95" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -20644,7 +20653,7 @@
         <v>0.33</v>
       </c>
       <c r="AP95">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ95">
         <v>1.2</v>
@@ -20978,7 +20987,7 @@
         <v>140</v>
       </c>
       <c r="P97" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q97">
         <v>2.4</v>
@@ -21059,7 +21068,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ97">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR97">
         <v>1.31</v>
@@ -21674,7 +21683,7 @@
         <v>1.4</v>
       </c>
       <c r="AP100">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ100">
         <v>1.9</v>
@@ -21802,7 +21811,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22420,7 +22429,7 @@
         <v>145</v>
       </c>
       <c r="P104" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22626,7 +22635,7 @@
         <v>86</v>
       </c>
       <c r="P105" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -22832,7 +22841,7 @@
         <v>146</v>
       </c>
       <c r="P106" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q106">
         <v>6</v>
@@ -23244,7 +23253,7 @@
         <v>147</v>
       </c>
       <c r="P108" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23322,7 +23331,7 @@
         <v>1.86</v>
       </c>
       <c r="AP108">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ108">
         <v>1.7</v>
@@ -23531,7 +23540,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ109">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR109">
         <v>1.64</v>
@@ -23656,7 +23665,7 @@
         <v>149</v>
       </c>
       <c r="P110" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -24068,7 +24077,7 @@
         <v>143</v>
       </c>
       <c r="P112" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q112">
         <v>4.75</v>
@@ -24146,7 +24155,7 @@
         <v>0.71</v>
       </c>
       <c r="AP112">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ112">
         <v>1.1</v>
@@ -24558,10 +24567,10 @@
         <v>0.83</v>
       </c>
       <c r="AP114">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ114">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR114">
         <v>1.09</v>
@@ -24892,7 +24901,7 @@
         <v>86</v>
       </c>
       <c r="P116" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q116">
         <v>4.5</v>
@@ -25098,7 +25107,7 @@
         <v>153</v>
       </c>
       <c r="P117" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q117">
         <v>1.53</v>
@@ -25304,7 +25313,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25510,7 +25519,7 @@
         <v>154</v>
       </c>
       <c r="P119" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q119">
         <v>1.8</v>
@@ -25716,7 +25725,7 @@
         <v>155</v>
       </c>
       <c r="P120" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q120">
         <v>7.5</v>
@@ -26003,7 +26012,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ121">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR121">
         <v>1.4</v>
@@ -26128,7 +26137,7 @@
         <v>157</v>
       </c>
       <c r="P122" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q122">
         <v>2.63</v>
@@ -26334,7 +26343,7 @@
         <v>158</v>
       </c>
       <c r="P123" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q123">
         <v>1.73</v>
@@ -26412,7 +26421,7 @@
         <v>0.57</v>
       </c>
       <c r="AP123">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ123">
         <v>0.5</v>
@@ -26621,7 +26630,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ124">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR124">
         <v>2.17</v>
@@ -26952,7 +26961,7 @@
         <v>86</v>
       </c>
       <c r="P126" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27030,7 +27039,7 @@
         <v>1.43</v>
       </c>
       <c r="AP126">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ126">
         <v>1.9</v>
@@ -27158,7 +27167,7 @@
         <v>161</v>
       </c>
       <c r="P127" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27364,7 +27373,7 @@
         <v>86</v>
       </c>
       <c r="P128" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q128">
         <v>2.4</v>
@@ -27570,7 +27579,7 @@
         <v>138</v>
       </c>
       <c r="P129" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27776,7 +27785,7 @@
         <v>98</v>
       </c>
       <c r="P130" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q130">
         <v>6.5</v>
@@ -27982,7 +27991,7 @@
         <v>162</v>
       </c>
       <c r="P131" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q131">
         <v>4.33</v>
@@ -28188,7 +28197,7 @@
         <v>86</v>
       </c>
       <c r="P132" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q132">
         <v>8</v>
@@ -29296,7 +29305,7 @@
         <v>1.13</v>
       </c>
       <c r="AP137">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ137">
         <v>1.2</v>
@@ -29505,7 +29514,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ138">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR138">
         <v>1.67</v>
@@ -29836,7 +29845,7 @@
         <v>167</v>
       </c>
       <c r="P140" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q140">
         <v>2.3</v>
@@ -30042,7 +30051,7 @@
         <v>86</v>
       </c>
       <c r="P141" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q141">
         <v>7.5</v>
@@ -30248,7 +30257,7 @@
         <v>168</v>
       </c>
       <c r="P142" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30454,7 +30463,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30535,7 +30544,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ143">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR143">
         <v>1.42</v>
@@ -30738,7 +30747,7 @@
         <v>1.13</v>
       </c>
       <c r="AP144">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ144">
         <v>1</v>
@@ -30866,7 +30875,7 @@
         <v>171</v>
       </c>
       <c r="P145" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q145">
         <v>3.75</v>
@@ -31072,7 +31081,7 @@
         <v>172</v>
       </c>
       <c r="P146" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q146">
         <v>7.5</v>
@@ -31278,7 +31287,7 @@
         <v>173</v>
       </c>
       <c r="P147" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31484,7 +31493,7 @@
         <v>174</v>
       </c>
       <c r="P148" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q148">
         <v>2.75</v>
@@ -31690,7 +31699,7 @@
         <v>86</v>
       </c>
       <c r="P149" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q149">
         <v>7.5</v>
@@ -32102,7 +32111,7 @@
         <v>86</v>
       </c>
       <c r="P151" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q151">
         <v>6.5</v>
@@ -32308,7 +32317,7 @@
         <v>176</v>
       </c>
       <c r="P152" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q152">
         <v>2.75</v>
@@ -32514,7 +32523,7 @@
         <v>177</v>
       </c>
       <c r="P153" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q153">
         <v>4.75</v>
@@ -32592,7 +32601,7 @@
         <v>2.75</v>
       </c>
       <c r="AP153">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ153">
         <v>2.78</v>
@@ -32926,7 +32935,7 @@
         <v>179</v>
       </c>
       <c r="P155" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33132,7 +33141,7 @@
         <v>176</v>
       </c>
       <c r="P156" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q156">
         <v>2.2</v>
@@ -33495,6 +33504,418 @@
       </c>
       <c r="BP157">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="158" spans="1:68">
+      <c r="A158" s="1">
+        <v>157</v>
+      </c>
+      <c r="B158">
+        <v>7762746</v>
+      </c>
+      <c r="C158" t="s">
+        <v>68</v>
+      </c>
+      <c r="D158" t="s">
+        <v>69</v>
+      </c>
+      <c r="E158" s="2">
+        <v>45697.29166666666</v>
+      </c>
+      <c r="F158">
+        <v>20</v>
+      </c>
+      <c r="G158" t="s">
+        <v>81</v>
+      </c>
+      <c r="H158" t="s">
+        <v>73</v>
+      </c>
+      <c r="I158">
+        <v>0</v>
+      </c>
+      <c r="J158">
+        <v>3</v>
+      </c>
+      <c r="K158">
+        <v>3</v>
+      </c>
+      <c r="L158">
+        <v>1</v>
+      </c>
+      <c r="M158">
+        <v>4</v>
+      </c>
+      <c r="N158">
+        <v>5</v>
+      </c>
+      <c r="O158" t="s">
+        <v>181</v>
+      </c>
+      <c r="P158" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q158">
+        <v>2.2</v>
+      </c>
+      <c r="R158">
+        <v>2.2</v>
+      </c>
+      <c r="S158">
+        <v>6</v>
+      </c>
+      <c r="T158">
+        <v>1.4</v>
+      </c>
+      <c r="U158">
+        <v>2.75</v>
+      </c>
+      <c r="V158">
+        <v>3</v>
+      </c>
+      <c r="W158">
+        <v>1.36</v>
+      </c>
+      <c r="X158">
+        <v>8</v>
+      </c>
+      <c r="Y158">
+        <v>1.08</v>
+      </c>
+      <c r="Z158">
+        <v>1.52</v>
+      </c>
+      <c r="AA158">
+        <v>4</v>
+      </c>
+      <c r="AB158">
+        <v>6.2</v>
+      </c>
+      <c r="AC158">
+        <v>1.03</v>
+      </c>
+      <c r="AD158">
+        <v>9</v>
+      </c>
+      <c r="AE158">
+        <v>1.32</v>
+      </c>
+      <c r="AF158">
+        <v>3.2</v>
+      </c>
+      <c r="AG158">
+        <v>1.95</v>
+      </c>
+      <c r="AH158">
+        <v>1.79</v>
+      </c>
+      <c r="AI158">
+        <v>2</v>
+      </c>
+      <c r="AJ158">
+        <v>1.73</v>
+      </c>
+      <c r="AK158">
+        <v>1.15</v>
+      </c>
+      <c r="AL158">
+        <v>1.22</v>
+      </c>
+      <c r="AM158">
+        <v>2.19</v>
+      </c>
+      <c r="AN158">
+        <v>0.89</v>
+      </c>
+      <c r="AO158">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP158">
+        <v>0.8</v>
+      </c>
+      <c r="AQ158">
+        <v>0.8</v>
+      </c>
+      <c r="AR158">
+        <v>1.62</v>
+      </c>
+      <c r="AS158">
+        <v>1.22</v>
+      </c>
+      <c r="AT158">
+        <v>2.84</v>
+      </c>
+      <c r="AU158">
+        <v>6</v>
+      </c>
+      <c r="AV158">
+        <v>9</v>
+      </c>
+      <c r="AW158">
+        <v>16</v>
+      </c>
+      <c r="AX158">
+        <v>4</v>
+      </c>
+      <c r="AY158">
+        <v>22</v>
+      </c>
+      <c r="AZ158">
+        <v>13</v>
+      </c>
+      <c r="BA158">
+        <v>7</v>
+      </c>
+      <c r="BB158">
+        <v>5</v>
+      </c>
+      <c r="BC158">
+        <v>12</v>
+      </c>
+      <c r="BD158">
+        <v>0</v>
+      </c>
+      <c r="BE158">
+        <v>0</v>
+      </c>
+      <c r="BF158">
+        <v>0</v>
+      </c>
+      <c r="BG158">
+        <v>0</v>
+      </c>
+      <c r="BH158">
+        <v>0</v>
+      </c>
+      <c r="BI158">
+        <v>0</v>
+      </c>
+      <c r="BJ158">
+        <v>0</v>
+      </c>
+      <c r="BK158">
+        <v>0</v>
+      </c>
+      <c r="BL158">
+        <v>0</v>
+      </c>
+      <c r="BM158">
+        <v>0</v>
+      </c>
+      <c r="BN158">
+        <v>0</v>
+      </c>
+      <c r="BO158">
+        <v>0</v>
+      </c>
+      <c r="BP158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:68">
+      <c r="A159" s="1">
+        <v>158</v>
+      </c>
+      <c r="B159">
+        <v>7762751</v>
+      </c>
+      <c r="C159" t="s">
+        <v>68</v>
+      </c>
+      <c r="D159" t="s">
+        <v>69</v>
+      </c>
+      <c r="E159" s="2">
+        <v>45697.39583333334</v>
+      </c>
+      <c r="F159">
+        <v>20</v>
+      </c>
+      <c r="G159" t="s">
+        <v>82</v>
+      </c>
+      <c r="H159" t="s">
+        <v>76</v>
+      </c>
+      <c r="I159">
+        <v>1</v>
+      </c>
+      <c r="J159">
+        <v>1</v>
+      </c>
+      <c r="K159">
+        <v>2</v>
+      </c>
+      <c r="L159">
+        <v>1</v>
+      </c>
+      <c r="M159">
+        <v>1</v>
+      </c>
+      <c r="N159">
+        <v>2</v>
+      </c>
+      <c r="O159" t="s">
+        <v>182</v>
+      </c>
+      <c r="P159" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q159">
+        <v>1.8</v>
+      </c>
+      <c r="R159">
+        <v>2.4</v>
+      </c>
+      <c r="S159">
+        <v>9.5</v>
+      </c>
+      <c r="T159">
+        <v>1.36</v>
+      </c>
+      <c r="U159">
+        <v>3</v>
+      </c>
+      <c r="V159">
+        <v>2.63</v>
+      </c>
+      <c r="W159">
+        <v>1.44</v>
+      </c>
+      <c r="X159">
+        <v>7</v>
+      </c>
+      <c r="Y159">
+        <v>1.1</v>
+      </c>
+      <c r="Z159">
+        <v>1.23</v>
+      </c>
+      <c r="AA159">
+        <v>5.4</v>
+      </c>
+      <c r="AB159">
+        <v>14</v>
+      </c>
+      <c r="AC159">
+        <v>1.01</v>
+      </c>
+      <c r="AD159">
+        <v>11</v>
+      </c>
+      <c r="AE159">
+        <v>1.25</v>
+      </c>
+      <c r="AF159">
+        <v>3.7</v>
+      </c>
+      <c r="AG159">
+        <v>1.77</v>
+      </c>
+      <c r="AH159">
+        <v>1.98</v>
+      </c>
+      <c r="AI159">
+        <v>2.5</v>
+      </c>
+      <c r="AJ159">
+        <v>1.5</v>
+      </c>
+      <c r="AK159">
+        <v>1.06</v>
+      </c>
+      <c r="AL159">
+        <v>1.13</v>
+      </c>
+      <c r="AM159">
+        <v>3.3</v>
+      </c>
+      <c r="AN159">
+        <v>2.11</v>
+      </c>
+      <c r="AO159">
+        <v>0.22</v>
+      </c>
+      <c r="AP159">
+        <v>2</v>
+      </c>
+      <c r="AQ159">
+        <v>0.3</v>
+      </c>
+      <c r="AR159">
+        <v>1.57</v>
+      </c>
+      <c r="AS159">
+        <v>0.93</v>
+      </c>
+      <c r="AT159">
+        <v>2.5</v>
+      </c>
+      <c r="AU159">
+        <v>5</v>
+      </c>
+      <c r="AV159">
+        <v>2</v>
+      </c>
+      <c r="AW159">
+        <v>8</v>
+      </c>
+      <c r="AX159">
+        <v>6</v>
+      </c>
+      <c r="AY159">
+        <v>13</v>
+      </c>
+      <c r="AZ159">
+        <v>8</v>
+      </c>
+      <c r="BA159">
+        <v>18</v>
+      </c>
+      <c r="BB159">
+        <v>3</v>
+      </c>
+      <c r="BC159">
+        <v>21</v>
+      </c>
+      <c r="BD159">
+        <v>0</v>
+      </c>
+      <c r="BE159">
+        <v>0</v>
+      </c>
+      <c r="BF159">
+        <v>0</v>
+      </c>
+      <c r="BG159">
+        <v>0</v>
+      </c>
+      <c r="BH159">
+        <v>0</v>
+      </c>
+      <c r="BI159">
+        <v>0</v>
+      </c>
+      <c r="BJ159">
+        <v>0</v>
+      </c>
+      <c r="BK159">
+        <v>0</v>
+      </c>
+      <c r="BL159">
+        <v>0</v>
+      </c>
+      <c r="BM159">
+        <v>0</v>
+      </c>
+      <c r="BN159">
+        <v>0</v>
+      </c>
+      <c r="BO159">
+        <v>0</v>
+      </c>
+      <c r="BP159">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="263">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -563,6 +563,9 @@
   </si>
   <si>
     <t>['45']</t>
+  </si>
+  <si>
+    <t>['34', '62']</t>
   </si>
   <si>
     <t>['12', '22', '45+1', '45+4', '90+1', '90+8']</t>
@@ -1161,7 +1164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP159"/>
+  <dimension ref="A1:BP160"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2035,7 +2038,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q5">
         <v>7.5</v>
@@ -2241,7 +2244,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2653,7 +2656,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q8">
         <v>4</v>
@@ -2859,7 +2862,7 @@
         <v>86</v>
       </c>
       <c r="P9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3349,7 +3352,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ11">
         <v>0.5</v>
@@ -3683,7 +3686,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3889,7 +3892,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q14">
         <v>2.4</v>
@@ -4713,7 +4716,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -5125,7 +5128,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -5331,7 +5334,7 @@
         <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5537,7 +5540,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5743,7 +5746,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -5949,7 +5952,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q24">
         <v>3.25</v>
@@ -6155,7 +6158,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q25">
         <v>2.05</v>
@@ -6361,7 +6364,7 @@
         <v>86</v>
       </c>
       <c r="P26" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6645,7 +6648,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ27">
         <v>1</v>
@@ -6979,7 +6982,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7391,7 +7394,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7597,7 +7600,7 @@
         <v>86</v>
       </c>
       <c r="P32" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q32">
         <v>2.05</v>
@@ -8215,7 +8218,7 @@
         <v>86</v>
       </c>
       <c r="P35" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q35">
         <v>8.800000000000001</v>
@@ -8627,7 +8630,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -9117,7 +9120,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ39">
         <v>0.3</v>
@@ -9451,7 +9454,7 @@
         <v>86</v>
       </c>
       <c r="P41" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q41">
         <v>2.38</v>
@@ -9863,7 +9866,7 @@
         <v>86</v>
       </c>
       <c r="P43" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q43">
         <v>7.5</v>
@@ -9944,7 +9947,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ43">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AR43">
         <v>1.51</v>
@@ -10069,7 +10072,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10481,7 +10484,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q46">
         <v>2.5</v>
@@ -10687,7 +10690,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q47">
         <v>4.33</v>
@@ -10893,7 +10896,7 @@
         <v>86</v>
       </c>
       <c r="P48" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q48">
         <v>2.4</v>
@@ -11511,7 +11514,7 @@
         <v>116</v>
       </c>
       <c r="P51" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11717,7 +11720,7 @@
         <v>118</v>
       </c>
       <c r="P52" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q52">
         <v>5.5</v>
@@ -12129,7 +12132,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -12541,7 +12544,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q56">
         <v>5.5</v>
@@ -12747,7 +12750,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q57">
         <v>5</v>
@@ -12953,7 +12956,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13159,7 +13162,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13365,7 +13368,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13446,7 +13449,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ60">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AR60">
         <v>1.59</v>
@@ -13571,7 +13574,7 @@
         <v>86</v>
       </c>
       <c r="P61" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q61">
         <v>6.5</v>
@@ -13777,7 +13780,7 @@
         <v>86</v>
       </c>
       <c r="P62" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q62">
         <v>7</v>
@@ -13858,7 +13861,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ62">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AR62">
         <v>1.3</v>
@@ -13983,7 +13986,7 @@
         <v>86</v>
       </c>
       <c r="P63" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q63">
         <v>3.5</v>
@@ -14189,7 +14192,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14807,7 +14810,7 @@
         <v>86</v>
       </c>
       <c r="P67" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q67">
         <v>6.5</v>
@@ -15013,7 +15016,7 @@
         <v>86</v>
       </c>
       <c r="P68" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q68">
         <v>4.75</v>
@@ -15631,7 +15634,7 @@
         <v>92</v>
       </c>
       <c r="P71" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q71">
         <v>9.5</v>
@@ -16249,7 +16252,7 @@
         <v>86</v>
       </c>
       <c r="P74" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16867,7 +16870,7 @@
         <v>130</v>
       </c>
       <c r="P77" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q77">
         <v>1.83</v>
@@ -16945,7 +16948,7 @@
         <v>0.4</v>
       </c>
       <c r="AP77">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ77">
         <v>1.2</v>
@@ -17073,7 +17076,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q78">
         <v>12</v>
@@ -17154,7 +17157,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ78">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AR78">
         <v>1.46</v>
@@ -17279,7 +17282,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q79">
         <v>3.75</v>
@@ -17485,7 +17488,7 @@
         <v>131</v>
       </c>
       <c r="P80" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17691,7 +17694,7 @@
         <v>132</v>
       </c>
       <c r="P81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -18103,7 +18106,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q83">
         <v>1.67</v>
@@ -18721,7 +18724,7 @@
         <v>134</v>
       </c>
       <c r="P86" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q86">
         <v>2.63</v>
@@ -19829,7 +19832,7 @@
         <v>0.8</v>
       </c>
       <c r="AP91">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ91">
         <v>1.1</v>
@@ -20369,7 +20372,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q94">
         <v>13</v>
@@ -20450,7 +20453,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ94">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AR94">
         <v>1.21</v>
@@ -20575,7 +20578,7 @@
         <v>139</v>
       </c>
       <c r="P95" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -20987,7 +20990,7 @@
         <v>140</v>
       </c>
       <c r="P97" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q97">
         <v>2.4</v>
@@ -21811,7 +21814,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -21889,7 +21892,7 @@
         <v>1.67</v>
       </c>
       <c r="AP101">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ101">
         <v>1.7</v>
@@ -22429,7 +22432,7 @@
         <v>145</v>
       </c>
       <c r="P104" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22635,7 +22638,7 @@
         <v>86</v>
       </c>
       <c r="P105" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -22841,7 +22844,7 @@
         <v>146</v>
       </c>
       <c r="P106" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q106">
         <v>6</v>
@@ -23253,7 +23256,7 @@
         <v>147</v>
       </c>
       <c r="P108" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23665,7 +23668,7 @@
         <v>149</v>
       </c>
       <c r="P110" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -24077,7 +24080,7 @@
         <v>143</v>
       </c>
       <c r="P112" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q112">
         <v>4.75</v>
@@ -24901,7 +24904,7 @@
         <v>86</v>
       </c>
       <c r="P116" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q116">
         <v>4.5</v>
@@ -25107,7 +25110,7 @@
         <v>153</v>
       </c>
       <c r="P117" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q117">
         <v>1.53</v>
@@ -25185,7 +25188,7 @@
         <v>1</v>
       </c>
       <c r="AP117">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ117">
         <v>1.2</v>
@@ -25313,7 +25316,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25519,7 +25522,7 @@
         <v>154</v>
       </c>
       <c r="P119" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q119">
         <v>1.8</v>
@@ -25725,7 +25728,7 @@
         <v>155</v>
       </c>
       <c r="P120" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q120">
         <v>7.5</v>
@@ -25806,7 +25809,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ120">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AR120">
         <v>1.46</v>
@@ -26137,7 +26140,7 @@
         <v>157</v>
       </c>
       <c r="P122" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q122">
         <v>2.63</v>
@@ -26343,7 +26346,7 @@
         <v>158</v>
       </c>
       <c r="P123" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q123">
         <v>1.73</v>
@@ -26627,7 +26630,7 @@
         <v>0.71</v>
       </c>
       <c r="AP124">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ124">
         <v>0.8</v>
@@ -26961,7 +26964,7 @@
         <v>86</v>
       </c>
       <c r="P126" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27167,7 +27170,7 @@
         <v>161</v>
       </c>
       <c r="P127" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27248,7 +27251,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ127">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AR127">
         <v>2.03</v>
@@ -27373,7 +27376,7 @@
         <v>86</v>
       </c>
       <c r="P128" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q128">
         <v>2.4</v>
@@ -27579,7 +27582,7 @@
         <v>138</v>
       </c>
       <c r="P129" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27785,7 +27788,7 @@
         <v>98</v>
       </c>
       <c r="P130" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q130">
         <v>6.5</v>
@@ -27991,7 +27994,7 @@
         <v>162</v>
       </c>
       <c r="P131" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q131">
         <v>4.33</v>
@@ -28197,7 +28200,7 @@
         <v>86</v>
       </c>
       <c r="P132" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q132">
         <v>8</v>
@@ -29845,7 +29848,7 @@
         <v>167</v>
       </c>
       <c r="P140" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q140">
         <v>2.3</v>
@@ -30051,7 +30054,7 @@
         <v>86</v>
       </c>
       <c r="P141" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q141">
         <v>7.5</v>
@@ -30132,7 +30135,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ141">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AR141">
         <v>1.45</v>
@@ -30257,7 +30260,7 @@
         <v>168</v>
       </c>
       <c r="P142" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30335,7 +30338,7 @@
         <v>1</v>
       </c>
       <c r="AP142">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ142">
         <v>1.1</v>
@@ -30463,7 +30466,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30875,7 +30878,7 @@
         <v>171</v>
       </c>
       <c r="P145" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q145">
         <v>3.75</v>
@@ -31081,7 +31084,7 @@
         <v>172</v>
       </c>
       <c r="P146" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q146">
         <v>7.5</v>
@@ -31287,7 +31290,7 @@
         <v>173</v>
       </c>
       <c r="P147" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31493,7 +31496,7 @@
         <v>174</v>
       </c>
       <c r="P148" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q148">
         <v>2.75</v>
@@ -31699,7 +31702,7 @@
         <v>86</v>
       </c>
       <c r="P149" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q149">
         <v>7.5</v>
@@ -32111,7 +32114,7 @@
         <v>86</v>
       </c>
       <c r="P151" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q151">
         <v>6.5</v>
@@ -32317,7 +32320,7 @@
         <v>176</v>
       </c>
       <c r="P152" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q152">
         <v>2.75</v>
@@ -32523,7 +32526,7 @@
         <v>177</v>
       </c>
       <c r="P153" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q153">
         <v>4.75</v>
@@ -32604,7 +32607,7 @@
         <v>2</v>
       </c>
       <c r="AQ153">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AR153">
         <v>1.54</v>
@@ -32935,7 +32938,7 @@
         <v>179</v>
       </c>
       <c r="P155" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33141,7 +33144,7 @@
         <v>176</v>
       </c>
       <c r="P156" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q156">
         <v>2.2</v>
@@ -33553,7 +33556,7 @@
         <v>181</v>
       </c>
       <c r="P158" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33759,7 +33762,7 @@
         <v>182</v>
       </c>
       <c r="P159" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q159">
         <v>1.8</v>
@@ -33915,6 +33918,212 @@
         <v>0</v>
       </c>
       <c r="BP159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:68">
+      <c r="A160" s="1">
+        <v>159</v>
+      </c>
+      <c r="B160">
+        <v>7762750</v>
+      </c>
+      <c r="C160" t="s">
+        <v>68</v>
+      </c>
+      <c r="D160" t="s">
+        <v>69</v>
+      </c>
+      <c r="E160" s="2">
+        <v>45697.51041666666</v>
+      </c>
+      <c r="F160">
+        <v>20</v>
+      </c>
+      <c r="G160" t="s">
+        <v>79</v>
+      </c>
+      <c r="H160" t="s">
+        <v>75</v>
+      </c>
+      <c r="I160">
+        <v>1</v>
+      </c>
+      <c r="J160">
+        <v>0</v>
+      </c>
+      <c r="K160">
+        <v>1</v>
+      </c>
+      <c r="L160">
+        <v>2</v>
+      </c>
+      <c r="M160">
+        <v>1</v>
+      </c>
+      <c r="N160">
+        <v>3</v>
+      </c>
+      <c r="O160" t="s">
+        <v>183</v>
+      </c>
+      <c r="P160" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q160">
+        <v>4.75</v>
+      </c>
+      <c r="R160">
+        <v>1.95</v>
+      </c>
+      <c r="S160">
+        <v>2.75</v>
+      </c>
+      <c r="T160">
+        <v>1.53</v>
+      </c>
+      <c r="U160">
+        <v>2.38</v>
+      </c>
+      <c r="V160">
+        <v>3.5</v>
+      </c>
+      <c r="W160">
+        <v>1.29</v>
+      </c>
+      <c r="X160">
+        <v>11</v>
+      </c>
+      <c r="Y160">
+        <v>1.05</v>
+      </c>
+      <c r="Z160">
+        <v>3.45</v>
+      </c>
+      <c r="AA160">
+        <v>3.29</v>
+      </c>
+      <c r="AB160">
+        <v>2.1</v>
+      </c>
+      <c r="AC160">
+        <v>1.05</v>
+      </c>
+      <c r="AD160">
+        <v>6.7</v>
+      </c>
+      <c r="AE160">
+        <v>1.46</v>
+      </c>
+      <c r="AF160">
+        <v>2.6</v>
+      </c>
+      <c r="AG160">
+        <v>2.25</v>
+      </c>
+      <c r="AH160">
+        <v>1.5</v>
+      </c>
+      <c r="AI160">
+        <v>2.1</v>
+      </c>
+      <c r="AJ160">
+        <v>1.67</v>
+      </c>
+      <c r="AK160">
+        <v>1.74</v>
+      </c>
+      <c r="AL160">
+        <v>1.3</v>
+      </c>
+      <c r="AM160">
+        <v>1.24</v>
+      </c>
+      <c r="AN160">
+        <v>2.33</v>
+      </c>
+      <c r="AO160">
+        <v>2.78</v>
+      </c>
+      <c r="AP160">
+        <v>2.4</v>
+      </c>
+      <c r="AQ160">
+        <v>2.5</v>
+      </c>
+      <c r="AR160">
+        <v>2.11</v>
+      </c>
+      <c r="AS160">
+        <v>1.65</v>
+      </c>
+      <c r="AT160">
+        <v>3.76</v>
+      </c>
+      <c r="AU160">
+        <v>6</v>
+      </c>
+      <c r="AV160">
+        <v>2</v>
+      </c>
+      <c r="AW160">
+        <v>1</v>
+      </c>
+      <c r="AX160">
+        <v>3</v>
+      </c>
+      <c r="AY160">
+        <v>7</v>
+      </c>
+      <c r="AZ160">
+        <v>5</v>
+      </c>
+      <c r="BA160">
+        <v>5</v>
+      </c>
+      <c r="BB160">
+        <v>10</v>
+      </c>
+      <c r="BC160">
+        <v>15</v>
+      </c>
+      <c r="BD160">
+        <v>0</v>
+      </c>
+      <c r="BE160">
+        <v>0</v>
+      </c>
+      <c r="BF160">
+        <v>0</v>
+      </c>
+      <c r="BG160">
+        <v>0</v>
+      </c>
+      <c r="BH160">
+        <v>0</v>
+      </c>
+      <c r="BI160">
+        <v>0</v>
+      </c>
+      <c r="BJ160">
+        <v>0</v>
+      </c>
+      <c r="BK160">
+        <v>0</v>
+      </c>
+      <c r="BL160">
+        <v>0</v>
+      </c>
+      <c r="BM160">
+        <v>0</v>
+      </c>
+      <c r="BN160">
+        <v>0</v>
+      </c>
+      <c r="BO160">
+        <v>0</v>
+      </c>
+      <c r="BP160">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="263">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1164,7 +1164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP160"/>
+  <dimension ref="A1:BP161"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -4176,7 +4176,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ15">
         <v>0.8</v>
@@ -6442,7 +6442,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ26">
         <v>1.1</v>
@@ -9944,7 +9944,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ43">
         <v>2.5</v>
@@ -12828,7 +12828,7 @@
         <v>3</v>
       </c>
       <c r="AP57">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ57">
         <v>2.1</v>
@@ -16124,7 +16124,7 @@
         <v>0.8</v>
       </c>
       <c r="AP73">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ73">
         <v>0.7</v>
@@ -19214,7 +19214,7 @@
         <v>1.83</v>
       </c>
       <c r="AP88">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ88">
         <v>1.5</v>
@@ -24982,7 +24982,7 @@
         <v>1.17</v>
       </c>
       <c r="AP116">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ116">
         <v>1.9</v>
@@ -26836,7 +26836,7 @@
         <v>1.29</v>
       </c>
       <c r="AP125">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ125">
         <v>1.2</v>
@@ -29926,7 +29926,7 @@
         <v>0.5</v>
       </c>
       <c r="AP140">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ140">
         <v>0.5</v>
@@ -34125,6 +34125,212 @@
       </c>
       <c r="BP160">
         <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:68">
+      <c r="A161" s="1">
+        <v>160</v>
+      </c>
+      <c r="B161">
+        <v>7762749</v>
+      </c>
+      <c r="C161" t="s">
+        <v>68</v>
+      </c>
+      <c r="D161" t="s">
+        <v>69</v>
+      </c>
+      <c r="E161" s="2">
+        <v>45698.52083333334</v>
+      </c>
+      <c r="F161">
+        <v>20</v>
+      </c>
+      <c r="G161" t="s">
+        <v>83</v>
+      </c>
+      <c r="H161" t="s">
+        <v>71</v>
+      </c>
+      <c r="I161">
+        <v>0</v>
+      </c>
+      <c r="J161">
+        <v>0</v>
+      </c>
+      <c r="K161">
+        <v>0</v>
+      </c>
+      <c r="L161">
+        <v>0</v>
+      </c>
+      <c r="M161">
+        <v>0</v>
+      </c>
+      <c r="N161">
+        <v>0</v>
+      </c>
+      <c r="O161" t="s">
+        <v>86</v>
+      </c>
+      <c r="P161" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q161">
+        <v>2.6</v>
+      </c>
+      <c r="R161">
+        <v>2</v>
+      </c>
+      <c r="S161">
+        <v>5</v>
+      </c>
+      <c r="T161">
+        <v>1.53</v>
+      </c>
+      <c r="U161">
+        <v>2.38</v>
+      </c>
+      <c r="V161">
+        <v>3.5</v>
+      </c>
+      <c r="W161">
+        <v>1.29</v>
+      </c>
+      <c r="X161">
+        <v>11</v>
+      </c>
+      <c r="Y161">
+        <v>1.05</v>
+      </c>
+      <c r="Z161">
+        <v>1.72</v>
+      </c>
+      <c r="AA161">
+        <v>3.47</v>
+      </c>
+      <c r="AB161">
+        <v>5</v>
+      </c>
+      <c r="AC161">
+        <v>1.04</v>
+      </c>
+      <c r="AD161">
+        <v>6.9</v>
+      </c>
+      <c r="AE161">
+        <v>1.5</v>
+      </c>
+      <c r="AF161">
+        <v>2.4</v>
+      </c>
+      <c r="AG161">
+        <v>2.25</v>
+      </c>
+      <c r="AH161">
+        <v>1.53</v>
+      </c>
+      <c r="AI161">
+        <v>2.2</v>
+      </c>
+      <c r="AJ161">
+        <v>1.62</v>
+      </c>
+      <c r="AK161">
+        <v>1.17</v>
+      </c>
+      <c r="AL161">
+        <v>1.26</v>
+      </c>
+      <c r="AM161">
+        <v>2.01</v>
+      </c>
+      <c r="AN161">
+        <v>1.44</v>
+      </c>
+      <c r="AO161">
+        <v>1</v>
+      </c>
+      <c r="AP161">
+        <v>1.4</v>
+      </c>
+      <c r="AQ161">
+        <v>1</v>
+      </c>
+      <c r="AR161">
+        <v>1.48</v>
+      </c>
+      <c r="AS161">
+        <v>0.96</v>
+      </c>
+      <c r="AT161">
+        <v>2.44</v>
+      </c>
+      <c r="AU161">
+        <v>8</v>
+      </c>
+      <c r="AV161">
+        <v>3</v>
+      </c>
+      <c r="AW161">
+        <v>9</v>
+      </c>
+      <c r="AX161">
+        <v>3</v>
+      </c>
+      <c r="AY161">
+        <v>17</v>
+      </c>
+      <c r="AZ161">
+        <v>6</v>
+      </c>
+      <c r="BA161">
+        <v>8</v>
+      </c>
+      <c r="BB161">
+        <v>2</v>
+      </c>
+      <c r="BC161">
+        <v>10</v>
+      </c>
+      <c r="BD161">
+        <v>1.46</v>
+      </c>
+      <c r="BE161">
+        <v>7</v>
+      </c>
+      <c r="BF161">
+        <v>3.05</v>
+      </c>
+      <c r="BG161">
+        <v>1.38</v>
+      </c>
+      <c r="BH161">
+        <v>2.8</v>
+      </c>
+      <c r="BI161">
+        <v>1.64</v>
+      </c>
+      <c r="BJ161">
+        <v>2.1</v>
+      </c>
+      <c r="BK161">
+        <v>2.02</v>
+      </c>
+      <c r="BL161">
+        <v>1.7</v>
+      </c>
+      <c r="BM161">
+        <v>2.55</v>
+      </c>
+      <c r="BN161">
+        <v>1.43</v>
+      </c>
+      <c r="BO161">
+        <v>3.4</v>
+      </c>
+      <c r="BP161">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="264">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -804,6 +804,9 @@
   <si>
     <t>['1', '19', '44', '60']</t>
   </si>
+  <si>
+    <t>['58', '61', '84']</t>
+  </si>
 </sst>
 </file>
 
@@ -1164,7 +1167,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP161"/>
+  <dimension ref="A1:BP162"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2322,7 +2325,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ6">
         <v>2.1</v>
@@ -4179,7 +4182,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ15">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -5824,7 +5827,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ23">
         <v>1.7</v>
@@ -6857,7 +6860,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ28">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR28">
         <v>0.91</v>
@@ -8502,7 +8505,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ36">
         <v>1.2</v>
@@ -10768,7 +10771,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ47">
         <v>1.3</v>
@@ -11595,7 +11598,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ51">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR51">
         <v>1.13</v>
@@ -12416,7 +12419,7 @@
         <v>1.75</v>
       </c>
       <c r="AP55">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ55">
         <v>1.5</v>
@@ -14685,7 +14688,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ66">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR66">
         <v>1.61</v>
@@ -17154,7 +17157,7 @@
         <v>3</v>
       </c>
       <c r="AP78">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ78">
         <v>2.5</v>
@@ -18805,7 +18808,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ86">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR86">
         <v>1.23</v>
@@ -19420,7 +19423,7 @@
         <v>1.75</v>
       </c>
       <c r="AP89">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ89">
         <v>1.1</v>
@@ -21071,7 +21074,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ97">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR97">
         <v>1.31</v>
@@ -22510,7 +22513,7 @@
         <v>0.57</v>
       </c>
       <c r="AP104">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ104">
         <v>0.7</v>
@@ -24573,7 +24576,7 @@
         <v>2</v>
       </c>
       <c r="AQ114">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR114">
         <v>1.09</v>
@@ -26633,7 +26636,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ124">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR124">
         <v>2.17</v>
@@ -28278,7 +28281,7 @@
         <v>1.63</v>
       </c>
       <c r="AP132">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ132">
         <v>1.9</v>
@@ -29517,7 +29520,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ138">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR138">
         <v>1.67</v>
@@ -31162,7 +31165,7 @@
         <v>1.78</v>
       </c>
       <c r="AP146">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ146">
         <v>1.9</v>
@@ -33637,7 +33640,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ158">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR158">
         <v>1.62</v>
@@ -34331,6 +34334,212 @@
       </c>
       <c r="BP161">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="162" spans="1:68">
+      <c r="A162" s="1">
+        <v>161</v>
+      </c>
+      <c r="B162">
+        <v>7762761</v>
+      </c>
+      <c r="C162" t="s">
+        <v>68</v>
+      </c>
+      <c r="D162" t="s">
+        <v>69</v>
+      </c>
+      <c r="E162" s="2">
+        <v>45702.52083333334</v>
+      </c>
+      <c r="F162">
+        <v>21</v>
+      </c>
+      <c r="G162" t="s">
+        <v>74</v>
+      </c>
+      <c r="H162" t="s">
+        <v>73</v>
+      </c>
+      <c r="I162">
+        <v>0</v>
+      </c>
+      <c r="J162">
+        <v>0</v>
+      </c>
+      <c r="K162">
+        <v>0</v>
+      </c>
+      <c r="L162">
+        <v>0</v>
+      </c>
+      <c r="M162">
+        <v>3</v>
+      </c>
+      <c r="N162">
+        <v>3</v>
+      </c>
+      <c r="O162" t="s">
+        <v>86</v>
+      </c>
+      <c r="P162" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q162">
+        <v>3.5</v>
+      </c>
+      <c r="R162">
+        <v>1.95</v>
+      </c>
+      <c r="S162">
+        <v>3.6</v>
+      </c>
+      <c r="T162">
+        <v>1.53</v>
+      </c>
+      <c r="U162">
+        <v>2.38</v>
+      </c>
+      <c r="V162">
+        <v>3.5</v>
+      </c>
+      <c r="W162">
+        <v>1.29</v>
+      </c>
+      <c r="X162">
+        <v>11</v>
+      </c>
+      <c r="Y162">
+        <v>1.05</v>
+      </c>
+      <c r="Z162">
+        <v>2.14</v>
+      </c>
+      <c r="AA162">
+        <v>3.09</v>
+      </c>
+      <c r="AB162">
+        <v>3.58</v>
+      </c>
+      <c r="AC162">
+        <v>1.03</v>
+      </c>
+      <c r="AD162">
+        <v>7.6</v>
+      </c>
+      <c r="AE162">
+        <v>1.43</v>
+      </c>
+      <c r="AF162">
+        <v>2.7</v>
+      </c>
+      <c r="AG162">
+        <v>1.94</v>
+      </c>
+      <c r="AH162">
+        <v>1.8</v>
+      </c>
+      <c r="AI162">
+        <v>2</v>
+      </c>
+      <c r="AJ162">
+        <v>1.73</v>
+      </c>
+      <c r="AK162">
+        <v>1.37</v>
+      </c>
+      <c r="AL162">
+        <v>1.34</v>
+      </c>
+      <c r="AM162">
+        <v>1.48</v>
+      </c>
+      <c r="AN162">
+        <v>0.8</v>
+      </c>
+      <c r="AO162">
+        <v>0.8</v>
+      </c>
+      <c r="AP162">
+        <v>0.73</v>
+      </c>
+      <c r="AQ162">
+        <v>1</v>
+      </c>
+      <c r="AR162">
+        <v>1.31</v>
+      </c>
+      <c r="AS162">
+        <v>1.29</v>
+      </c>
+      <c r="AT162">
+        <v>2.6</v>
+      </c>
+      <c r="AU162">
+        <v>4</v>
+      </c>
+      <c r="AV162">
+        <v>7</v>
+      </c>
+      <c r="AW162">
+        <v>1</v>
+      </c>
+      <c r="AX162">
+        <v>2</v>
+      </c>
+      <c r="AY162">
+        <v>5</v>
+      </c>
+      <c r="AZ162">
+        <v>9</v>
+      </c>
+      <c r="BA162">
+        <v>1</v>
+      </c>
+      <c r="BB162">
+        <v>1</v>
+      </c>
+      <c r="BC162">
+        <v>2</v>
+      </c>
+      <c r="BD162">
+        <v>1.82</v>
+      </c>
+      <c r="BE162">
+        <v>6.8</v>
+      </c>
+      <c r="BF162">
+        <v>2.3</v>
+      </c>
+      <c r="BG162">
+        <v>0</v>
+      </c>
+      <c r="BH162">
+        <v>0</v>
+      </c>
+      <c r="BI162">
+        <v>0</v>
+      </c>
+      <c r="BJ162">
+        <v>0</v>
+      </c>
+      <c r="BK162">
+        <v>0</v>
+      </c>
+      <c r="BL162">
+        <v>0</v>
+      </c>
+      <c r="BM162">
+        <v>0</v>
+      </c>
+      <c r="BN162">
+        <v>0</v>
+      </c>
+      <c r="BO162">
+        <v>0</v>
+      </c>
+      <c r="BP162">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="267">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -568,6 +568,12 @@
     <t>['34', '62']</t>
   </si>
   <si>
+    <t>['51']</t>
+  </si>
+  <si>
+    <t>['81']</t>
+  </si>
+  <si>
     <t>['12', '22', '45+1', '45+4', '90+1', '90+8']</t>
   </si>
   <si>
@@ -575,9 +581,6 @@
   </si>
   <si>
     <t>['45+2', '90+4']</t>
-  </si>
-  <si>
-    <t>['51']</t>
   </si>
   <si>
     <t>['41', '72']</t>
@@ -806,6 +809,12 @@
   </si>
   <si>
     <t>['58', '61', '84']</t>
+  </si>
+  <si>
+    <t>['40']</t>
+  </si>
+  <si>
+    <t>['12', '21', '58', '60']</t>
   </si>
 </sst>
 </file>
@@ -1167,7 +1176,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP162"/>
+  <dimension ref="A1:BP165"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1707,7 +1716,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ3">
         <v>0.7</v>
@@ -2041,7 +2050,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q5">
         <v>7.5</v>
@@ -2122,7 +2131,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ5">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2247,7 +2256,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2328,7 +2337,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ6">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2659,7 +2668,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q8">
         <v>4</v>
@@ -2737,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ8">
         <v>1.5</v>
@@ -2865,7 +2874,7 @@
         <v>86</v>
       </c>
       <c r="P9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3689,7 +3698,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3895,7 +3904,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q14">
         <v>2.4</v>
@@ -4591,7 +4600,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ17">
         <v>0.7</v>
@@ -4719,7 +4728,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -4800,7 +4809,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ18">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AR18">
         <v>1.14</v>
@@ -5003,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ19">
         <v>1.1</v>
@@ -5131,7 +5140,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -5337,7 +5346,7 @@
         <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5418,7 +5427,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ21">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR21">
         <v>0.9</v>
@@ -5543,7 +5552,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5621,10 +5630,10 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ22">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AR22">
         <v>1.34</v>
@@ -5749,7 +5758,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -5955,7 +5964,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q24">
         <v>3.25</v>
@@ -6161,7 +6170,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q25">
         <v>2.05</v>
@@ -6367,7 +6376,7 @@
         <v>86</v>
       </c>
       <c r="P26" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6985,7 +6994,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7269,7 +7278,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ30">
         <v>1.2</v>
@@ -7397,7 +7406,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7475,7 +7484,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ31">
         <v>1.7</v>
@@ -7603,7 +7612,7 @@
         <v>86</v>
       </c>
       <c r="P32" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q32">
         <v>2.05</v>
@@ -7890,7 +7899,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ33">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AR33">
         <v>1.4</v>
@@ -8221,7 +8230,7 @@
         <v>86</v>
       </c>
       <c r="P35" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="Q35">
         <v>8.800000000000001</v>
@@ -8299,10 +8308,10 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ35">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AR35">
         <v>0.9399999999999999</v>
@@ -8633,7 +8642,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -8714,7 +8723,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ37">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR37">
         <v>1.15</v>
@@ -9457,7 +9466,7 @@
         <v>86</v>
       </c>
       <c r="P41" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q41">
         <v>2.38</v>
@@ -9869,7 +9878,7 @@
         <v>86</v>
       </c>
       <c r="P43" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q43">
         <v>7.5</v>
@@ -10075,7 +10084,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10487,7 +10496,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q46">
         <v>2.5</v>
@@ -10693,7 +10702,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q47">
         <v>4.33</v>
@@ -10899,7 +10908,7 @@
         <v>86</v>
       </c>
       <c r="P48" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q48">
         <v>2.4</v>
@@ -10980,7 +10989,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ48">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AR48">
         <v>2.19</v>
@@ -11183,10 +11192,10 @@
         <v>2</v>
       </c>
       <c r="AP49">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ49">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AR49">
         <v>1.37</v>
@@ -11389,7 +11398,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ50">
         <v>1.2</v>
@@ -11517,7 +11526,7 @@
         <v>116</v>
       </c>
       <c r="P51" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11723,7 +11732,7 @@
         <v>118</v>
       </c>
       <c r="P52" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q52">
         <v>5.5</v>
@@ -11801,7 +11810,7 @@
         <v>3</v>
       </c>
       <c r="AP52">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ52">
         <v>1.7</v>
@@ -12010,7 +12019,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ53">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR53">
         <v>1.4</v>
@@ -12135,7 +12144,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -12547,7 +12556,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q56">
         <v>5.5</v>
@@ -12753,7 +12762,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q57">
         <v>5</v>
@@ -12834,7 +12843,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ57">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AR57">
         <v>1.15</v>
@@ -12959,7 +12968,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13165,7 +13174,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13246,7 +13255,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ59">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AR59">
         <v>1.61</v>
@@ -13371,7 +13380,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13449,7 +13458,7 @@
         <v>3</v>
       </c>
       <c r="AP60">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ60">
         <v>2.5</v>
@@ -13577,7 +13586,7 @@
         <v>86</v>
       </c>
       <c r="P61" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q61">
         <v>6.5</v>
@@ -13783,7 +13792,7 @@
         <v>86</v>
       </c>
       <c r="P62" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q62">
         <v>7</v>
@@ -13989,7 +13998,7 @@
         <v>86</v>
       </c>
       <c r="P63" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q63">
         <v>3.5</v>
@@ -14195,7 +14204,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14273,7 +14282,7 @@
         <v>0</v>
       </c>
       <c r="AP64">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ64">
         <v>1.2</v>
@@ -14813,7 +14822,7 @@
         <v>86</v>
       </c>
       <c r="P67" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q67">
         <v>6.5</v>
@@ -14894,7 +14903,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ67">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AR67">
         <v>1.17</v>
@@ -15019,7 +15028,7 @@
         <v>86</v>
       </c>
       <c r="P68" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q68">
         <v>4.75</v>
@@ -15097,10 +15106,10 @@
         <v>1.33</v>
       </c>
       <c r="AP68">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ68">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR68">
         <v>1.26</v>
@@ -15303,7 +15312,7 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ69">
         <v>0.5</v>
@@ -15512,7 +15521,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ70">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AR70">
         <v>1.49</v>
@@ -15637,7 +15646,7 @@
         <v>92</v>
       </c>
       <c r="P71" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q71">
         <v>9.5</v>
@@ -16255,7 +16264,7 @@
         <v>86</v>
       </c>
       <c r="P74" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16748,7 +16757,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ76">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AR76">
         <v>1.63</v>
@@ -16873,7 +16882,7 @@
         <v>130</v>
       </c>
       <c r="P77" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q77">
         <v>1.83</v>
@@ -17079,7 +17088,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q78">
         <v>12</v>
@@ -17285,7 +17294,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q79">
         <v>3.75</v>
@@ -17491,7 +17500,7 @@
         <v>131</v>
       </c>
       <c r="P80" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17569,7 +17578,7 @@
         <v>1.8</v>
       </c>
       <c r="AP80">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ80">
         <v>1.3</v>
@@ -17697,7 +17706,7 @@
         <v>132</v>
       </c>
       <c r="P81" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -17984,7 +17993,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ82">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR82">
         <v>1.21</v>
@@ -18109,7 +18118,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q83">
         <v>1.67</v>
@@ -18396,7 +18405,7 @@
         <v>2</v>
       </c>
       <c r="AQ84">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AR84">
         <v>1.5</v>
@@ -18599,7 +18608,7 @@
         <v>0.75</v>
       </c>
       <c r="AP85">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ85">
         <v>0.5</v>
@@ -18727,7 +18736,7 @@
         <v>134</v>
       </c>
       <c r="P86" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q86">
         <v>2.63</v>
@@ -18805,7 +18814,7 @@
         <v>1.25</v>
       </c>
       <c r="AP86">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ86">
         <v>1</v>
@@ -20375,7 +20384,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q94">
         <v>13</v>
@@ -20581,7 +20590,7 @@
         <v>139</v>
       </c>
       <c r="P95" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -20865,7 +20874,7 @@
         <v>1.6</v>
       </c>
       <c r="AP96">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ96">
         <v>1.1</v>
@@ -20993,7 +21002,7 @@
         <v>140</v>
       </c>
       <c r="P97" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q97">
         <v>2.4</v>
@@ -21692,7 +21701,7 @@
         <v>2</v>
       </c>
       <c r="AQ100">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR100">
         <v>1.22</v>
@@ -21817,7 +21826,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22101,7 +22110,7 @@
         <v>0.8</v>
       </c>
       <c r="AP102">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ102">
         <v>1</v>
@@ -22435,7 +22444,7 @@
         <v>145</v>
       </c>
       <c r="P104" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22641,7 +22650,7 @@
         <v>86</v>
       </c>
       <c r="P105" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -22847,7 +22856,7 @@
         <v>146</v>
       </c>
       <c r="P106" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q106">
         <v>6</v>
@@ -23131,7 +23140,7 @@
         <v>1.57</v>
       </c>
       <c r="AP107">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ107">
         <v>1.5</v>
@@ -23259,7 +23268,7 @@
         <v>147</v>
       </c>
       <c r="P108" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23671,7 +23680,7 @@
         <v>149</v>
       </c>
       <c r="P110" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23752,7 +23761,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ110">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AR110">
         <v>1.77</v>
@@ -23958,7 +23967,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ111">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AR111">
         <v>1.08</v>
@@ -24083,7 +24092,7 @@
         <v>143</v>
       </c>
       <c r="P112" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q112">
         <v>4.75</v>
@@ -24907,7 +24916,7 @@
         <v>86</v>
       </c>
       <c r="P116" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q116">
         <v>4.5</v>
@@ -24988,7 +24997,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ116">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR116">
         <v>1.24</v>
@@ -25113,7 +25122,7 @@
         <v>153</v>
       </c>
       <c r="P117" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q117">
         <v>1.53</v>
@@ -25319,7 +25328,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25397,7 +25406,7 @@
         <v>1.43</v>
       </c>
       <c r="AP118">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ118">
         <v>1.3</v>
@@ -25525,7 +25534,7 @@
         <v>154</v>
       </c>
       <c r="P119" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q119">
         <v>1.8</v>
@@ -25731,7 +25740,7 @@
         <v>155</v>
       </c>
       <c r="P120" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q120">
         <v>7.5</v>
@@ -25809,7 +25818,7 @@
         <v>3</v>
       </c>
       <c r="AP120">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ120">
         <v>2.5</v>
@@ -26015,7 +26024,7 @@
         <v>0.29</v>
       </c>
       <c r="AP121">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ121">
         <v>0.3</v>
@@ -26143,7 +26152,7 @@
         <v>157</v>
       </c>
       <c r="P122" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q122">
         <v>2.63</v>
@@ -26349,7 +26358,7 @@
         <v>158</v>
       </c>
       <c r="P123" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q123">
         <v>1.73</v>
@@ -26967,7 +26976,7 @@
         <v>86</v>
       </c>
       <c r="P126" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27048,7 +27057,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ126">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR126">
         <v>1.5</v>
@@ -27173,7 +27182,7 @@
         <v>161</v>
       </c>
       <c r="P127" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27379,7 +27388,7 @@
         <v>86</v>
       </c>
       <c r="P128" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q128">
         <v>2.4</v>
@@ -27585,7 +27594,7 @@
         <v>138</v>
       </c>
       <c r="P129" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27663,7 +27672,7 @@
         <v>1.38</v>
       </c>
       <c r="AP129">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ129">
         <v>1.3</v>
@@ -27791,7 +27800,7 @@
         <v>98</v>
       </c>
       <c r="P130" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q130">
         <v>6.5</v>
@@ -27872,7 +27881,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ130">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR130">
         <v>1.03</v>
@@ -27997,7 +28006,7 @@
         <v>162</v>
       </c>
       <c r="P131" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q131">
         <v>4.33</v>
@@ -28203,7 +28212,7 @@
         <v>86</v>
       </c>
       <c r="P132" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q132">
         <v>8</v>
@@ -28284,7 +28293,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ132">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AR132">
         <v>1.32</v>
@@ -28487,7 +28496,7 @@
         <v>1</v>
       </c>
       <c r="AP133">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ133">
         <v>1.1</v>
@@ -28696,7 +28705,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ134">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AR134">
         <v>1.33</v>
@@ -28899,7 +28908,7 @@
         <v>1</v>
       </c>
       <c r="AP135">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ135">
         <v>1.2</v>
@@ -29851,7 +29860,7 @@
         <v>167</v>
       </c>
       <c r="P140" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q140">
         <v>2.3</v>
@@ -30057,7 +30066,7 @@
         <v>86</v>
       </c>
       <c r="P141" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q141">
         <v>7.5</v>
@@ -30263,7 +30272,7 @@
         <v>168</v>
       </c>
       <c r="P142" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30469,7 +30478,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30881,7 +30890,7 @@
         <v>171</v>
       </c>
       <c r="P145" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q145">
         <v>3.75</v>
@@ -31087,7 +31096,7 @@
         <v>172</v>
       </c>
       <c r="P146" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q146">
         <v>7.5</v>
@@ -31168,7 +31177,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ146">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR146">
         <v>1.29</v>
@@ -31293,7 +31302,7 @@
         <v>173</v>
       </c>
       <c r="P147" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31499,7 +31508,7 @@
         <v>174</v>
       </c>
       <c r="P148" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q148">
         <v>2.75</v>
@@ -31705,7 +31714,7 @@
         <v>86</v>
       </c>
       <c r="P149" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q149">
         <v>7.5</v>
@@ -31783,10 +31792,10 @@
         <v>1.78</v>
       </c>
       <c r="AP149">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ149">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AR149">
         <v>1.37</v>
@@ -31992,7 +32001,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ150">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AR150">
         <v>1.74</v>
@@ -32117,7 +32126,7 @@
         <v>86</v>
       </c>
       <c r="P151" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q151">
         <v>6.5</v>
@@ -32195,7 +32204,7 @@
         <v>1</v>
       </c>
       <c r="AP151">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ151">
         <v>1.2</v>
@@ -32323,7 +32332,7 @@
         <v>176</v>
       </c>
       <c r="P152" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q152">
         <v>2.75</v>
@@ -32401,7 +32410,7 @@
         <v>0.44</v>
       </c>
       <c r="AP152">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ152">
         <v>0.7</v>
@@ -32529,7 +32538,7 @@
         <v>177</v>
       </c>
       <c r="P153" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q153">
         <v>4.75</v>
@@ -32941,7 +32950,7 @@
         <v>179</v>
       </c>
       <c r="P155" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33147,7 +33156,7 @@
         <v>176</v>
       </c>
       <c r="P156" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q156">
         <v>2.2</v>
@@ -33559,7 +33568,7 @@
         <v>181</v>
       </c>
       <c r="P158" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33765,7 +33774,7 @@
         <v>182</v>
       </c>
       <c r="P159" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q159">
         <v>1.8</v>
@@ -34383,7 +34392,7 @@
         <v>86</v>
       </c>
       <c r="P162" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q162">
         <v>3.5</v>
@@ -34512,34 +34521,652 @@
         <v>2.3</v>
       </c>
       <c r="BG162">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BH162">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BI162">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BJ162">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BK162">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BL162">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BM162">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BN162">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BO162">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BP162">
-        <v>0</v>
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="163" spans="1:68">
+      <c r="A163" s="1">
+        <v>162</v>
+      </c>
+      <c r="B163">
+        <v>7762759</v>
+      </c>
+      <c r="C163" t="s">
+        <v>68</v>
+      </c>
+      <c r="D163" t="s">
+        <v>69</v>
+      </c>
+      <c r="E163" s="2">
+        <v>45703.3125</v>
+      </c>
+      <c r="F163">
+        <v>21</v>
+      </c>
+      <c r="G163" t="s">
+        <v>71</v>
+      </c>
+      <c r="H163" t="s">
+        <v>70</v>
+      </c>
+      <c r="I163">
+        <v>0</v>
+      </c>
+      <c r="J163">
+        <v>1</v>
+      </c>
+      <c r="K163">
+        <v>1</v>
+      </c>
+      <c r="L163">
+        <v>1</v>
+      </c>
+      <c r="M163">
+        <v>1</v>
+      </c>
+      <c r="N163">
+        <v>2</v>
+      </c>
+      <c r="O163" t="s">
+        <v>184</v>
+      </c>
+      <c r="P163" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q163">
+        <v>5.5</v>
+      </c>
+      <c r="R163">
+        <v>1.95</v>
+      </c>
+      <c r="S163">
+        <v>2.5</v>
+      </c>
+      <c r="T163">
+        <v>1.53</v>
+      </c>
+      <c r="U163">
+        <v>2.38</v>
+      </c>
+      <c r="V163">
+        <v>3.75</v>
+      </c>
+      <c r="W163">
+        <v>1.25</v>
+      </c>
+      <c r="X163">
+        <v>11</v>
+      </c>
+      <c r="Y163">
+        <v>1.05</v>
+      </c>
+      <c r="Z163">
+        <v>5.5</v>
+      </c>
+      <c r="AA163">
+        <v>3.5</v>
+      </c>
+      <c r="AB163">
+        <v>1.66</v>
+      </c>
+      <c r="AC163">
+        <v>1.05</v>
+      </c>
+      <c r="AD163">
+        <v>6.55</v>
+      </c>
+      <c r="AE163">
+        <v>1.47</v>
+      </c>
+      <c r="AF163">
+        <v>2.55</v>
+      </c>
+      <c r="AG163">
+        <v>2.23</v>
+      </c>
+      <c r="AH163">
+        <v>1.58</v>
+      </c>
+      <c r="AI163">
+        <v>2.25</v>
+      </c>
+      <c r="AJ163">
+        <v>1.57</v>
+      </c>
+      <c r="AK163">
+        <v>1.96</v>
+      </c>
+      <c r="AL163">
+        <v>1.27</v>
+      </c>
+      <c r="AM163">
+        <v>1.17</v>
+      </c>
+      <c r="AN163">
+        <v>1.1</v>
+      </c>
+      <c r="AO163">
+        <v>1.9</v>
+      </c>
+      <c r="AP163">
+        <v>1.09</v>
+      </c>
+      <c r="AQ163">
+        <v>1.82</v>
+      </c>
+      <c r="AR163">
+        <v>1.34</v>
+      </c>
+      <c r="AS163">
+        <v>1.37</v>
+      </c>
+      <c r="AT163">
+        <v>2.71</v>
+      </c>
+      <c r="AU163">
+        <v>3</v>
+      </c>
+      <c r="AV163">
+        <v>4</v>
+      </c>
+      <c r="AW163">
+        <v>1</v>
+      </c>
+      <c r="AX163">
+        <v>8</v>
+      </c>
+      <c r="AY163">
+        <v>4</v>
+      </c>
+      <c r="AZ163">
+        <v>12</v>
+      </c>
+      <c r="BA163">
+        <v>2</v>
+      </c>
+      <c r="BB163">
+        <v>7</v>
+      </c>
+      <c r="BC163">
+        <v>9</v>
+      </c>
+      <c r="BD163">
+        <v>2.8</v>
+      </c>
+      <c r="BE163">
+        <v>6.5</v>
+      </c>
+      <c r="BF163">
+        <v>1.52</v>
+      </c>
+      <c r="BG163">
+        <v>1.5</v>
+      </c>
+      <c r="BH163">
+        <v>2.35</v>
+      </c>
+      <c r="BI163">
+        <v>1.85</v>
+      </c>
+      <c r="BJ163">
+        <v>1.83</v>
+      </c>
+      <c r="BK163">
+        <v>2.35</v>
+      </c>
+      <c r="BL163">
+        <v>1.5</v>
+      </c>
+      <c r="BM163">
+        <v>3.05</v>
+      </c>
+      <c r="BN163">
+        <v>1.3</v>
+      </c>
+      <c r="BO163">
+        <v>4.1</v>
+      </c>
+      <c r="BP163">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="164" spans="1:68">
+      <c r="A164" s="1">
+        <v>163</v>
+      </c>
+      <c r="B164">
+        <v>7762756</v>
+      </c>
+      <c r="C164" t="s">
+        <v>68</v>
+      </c>
+      <c r="D164" t="s">
+        <v>69</v>
+      </c>
+      <c r="E164" s="2">
+        <v>45703.41666666666</v>
+      </c>
+      <c r="F164">
+        <v>21</v>
+      </c>
+      <c r="G164" t="s">
+        <v>84</v>
+      </c>
+      <c r="H164" t="s">
+        <v>82</v>
+      </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <v>0</v>
+      </c>
+      <c r="L164">
+        <v>1</v>
+      </c>
+      <c r="M164">
+        <v>0</v>
+      </c>
+      <c r="N164">
+        <v>1</v>
+      </c>
+      <c r="O164" t="s">
+        <v>181</v>
+      </c>
+      <c r="P164" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q164">
+        <v>3.75</v>
+      </c>
+      <c r="R164">
+        <v>2.05</v>
+      </c>
+      <c r="S164">
+        <v>3</v>
+      </c>
+      <c r="T164">
+        <v>1.44</v>
+      </c>
+      <c r="U164">
+        <v>2.63</v>
+      </c>
+      <c r="V164">
+        <v>3.25</v>
+      </c>
+      <c r="W164">
+        <v>1.33</v>
+      </c>
+      <c r="X164">
+        <v>10</v>
+      </c>
+      <c r="Y164">
+        <v>1.06</v>
+      </c>
+      <c r="Z164">
+        <v>2.98</v>
+      </c>
+      <c r="AA164">
+        <v>3.18</v>
+      </c>
+      <c r="AB164">
+        <v>2.38</v>
+      </c>
+      <c r="AC164">
+        <v>1.01</v>
+      </c>
+      <c r="AD164">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE164">
+        <v>1.35</v>
+      </c>
+      <c r="AF164">
+        <v>3.05</v>
+      </c>
+      <c r="AG164">
+        <v>1.92</v>
+      </c>
+      <c r="AH164">
+        <v>1.82</v>
+      </c>
+      <c r="AI164">
+        <v>1.83</v>
+      </c>
+      <c r="AJ164">
+        <v>1.83</v>
+      </c>
+      <c r="AK164">
+        <v>1.58</v>
+      </c>
+      <c r="AL164">
+        <v>1.31</v>
+      </c>
+      <c r="AM164">
+        <v>1.32</v>
+      </c>
+      <c r="AN164">
+        <v>1.7</v>
+      </c>
+      <c r="AO164">
+        <v>2.1</v>
+      </c>
+      <c r="AP164">
+        <v>1.82</v>
+      </c>
+      <c r="AQ164">
+        <v>1.91</v>
+      </c>
+      <c r="AR164">
+        <v>1.55</v>
+      </c>
+      <c r="AS164">
+        <v>1.39</v>
+      </c>
+      <c r="AT164">
+        <v>2.94</v>
+      </c>
+      <c r="AU164">
+        <v>4</v>
+      </c>
+      <c r="AV164">
+        <v>8</v>
+      </c>
+      <c r="AW164">
+        <v>11</v>
+      </c>
+      <c r="AX164">
+        <v>8</v>
+      </c>
+      <c r="AY164">
+        <v>15</v>
+      </c>
+      <c r="AZ164">
+        <v>16</v>
+      </c>
+      <c r="BA164">
+        <v>2</v>
+      </c>
+      <c r="BB164">
+        <v>9</v>
+      </c>
+      <c r="BC164">
+        <v>11</v>
+      </c>
+      <c r="BD164">
+        <v>2.42</v>
+      </c>
+      <c r="BE164">
+        <v>6.45</v>
+      </c>
+      <c r="BF164">
+        <v>1.86</v>
+      </c>
+      <c r="BG164">
+        <v>1.22</v>
+      </c>
+      <c r="BH164">
+        <v>3.5</v>
+      </c>
+      <c r="BI164">
+        <v>1.44</v>
+      </c>
+      <c r="BJ164">
+        <v>2.5</v>
+      </c>
+      <c r="BK164">
+        <v>1.8</v>
+      </c>
+      <c r="BL164">
+        <v>1.9</v>
+      </c>
+      <c r="BM164">
+        <v>2.28</v>
+      </c>
+      <c r="BN164">
+        <v>1.53</v>
+      </c>
+      <c r="BO164">
+        <v>3.04</v>
+      </c>
+      <c r="BP164">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="165" spans="1:68">
+      <c r="A165" s="1">
+        <v>164</v>
+      </c>
+      <c r="B165">
+        <v>7762757</v>
+      </c>
+      <c r="C165" t="s">
+        <v>68</v>
+      </c>
+      <c r="D165" t="s">
+        <v>69</v>
+      </c>
+      <c r="E165" s="2">
+        <v>45703.52083333334</v>
+      </c>
+      <c r="F165">
+        <v>21</v>
+      </c>
+      <c r="G165" t="s">
+        <v>76</v>
+      </c>
+      <c r="H165" t="s">
+        <v>79</v>
+      </c>
+      <c r="I165">
+        <v>0</v>
+      </c>
+      <c r="J165">
+        <v>2</v>
+      </c>
+      <c r="K165">
+        <v>2</v>
+      </c>
+      <c r="L165">
+        <v>1</v>
+      </c>
+      <c r="M165">
+        <v>4</v>
+      </c>
+      <c r="N165">
+        <v>5</v>
+      </c>
+      <c r="O165" t="s">
+        <v>185</v>
+      </c>
+      <c r="P165" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q165">
+        <v>9.5</v>
+      </c>
+      <c r="R165">
+        <v>2.38</v>
+      </c>
+      <c r="S165">
+        <v>1.8</v>
+      </c>
+      <c r="T165">
+        <v>1.4</v>
+      </c>
+      <c r="U165">
+        <v>2.75</v>
+      </c>
+      <c r="V165">
+        <v>2.75</v>
+      </c>
+      <c r="W165">
+        <v>1.4</v>
+      </c>
+      <c r="X165">
+        <v>8</v>
+      </c>
+      <c r="Y165">
+        <v>1.08</v>
+      </c>
+      <c r="Z165">
+        <v>7.9</v>
+      </c>
+      <c r="AA165">
+        <v>4.4</v>
+      </c>
+      <c r="AB165">
+        <v>1.39</v>
+      </c>
+      <c r="AC165">
+        <v>1</v>
+      </c>
+      <c r="AD165">
+        <v>9.5</v>
+      </c>
+      <c r="AE165">
+        <v>1.29</v>
+      </c>
+      <c r="AF165">
+        <v>3.4</v>
+      </c>
+      <c r="AG165">
+        <v>1.94</v>
+      </c>
+      <c r="AH165">
+        <v>1.8</v>
+      </c>
+      <c r="AI165">
+        <v>2.5</v>
+      </c>
+      <c r="AJ165">
+        <v>1.5</v>
+      </c>
+      <c r="AK165">
+        <v>3.1</v>
+      </c>
+      <c r="AL165">
+        <v>1.14</v>
+      </c>
+      <c r="AM165">
+        <v>1.06</v>
+      </c>
+      <c r="AN165">
+        <v>0.7</v>
+      </c>
+      <c r="AO165">
+        <v>1.9</v>
+      </c>
+      <c r="AP165">
+        <v>0.64</v>
+      </c>
+      <c r="AQ165">
+        <v>2</v>
+      </c>
+      <c r="AR165">
+        <v>1.02</v>
+      </c>
+      <c r="AS165">
+        <v>1.79</v>
+      </c>
+      <c r="AT165">
+        <v>2.81</v>
+      </c>
+      <c r="AU165">
+        <v>4</v>
+      </c>
+      <c r="AV165">
+        <v>7</v>
+      </c>
+      <c r="AW165">
+        <v>0</v>
+      </c>
+      <c r="AX165">
+        <v>6</v>
+      </c>
+      <c r="AY165">
+        <v>4</v>
+      </c>
+      <c r="AZ165">
+        <v>13</v>
+      </c>
+      <c r="BA165">
+        <v>1</v>
+      </c>
+      <c r="BB165">
+        <v>5</v>
+      </c>
+      <c r="BC165">
+        <v>6</v>
+      </c>
+      <c r="BD165">
+        <v>13.5</v>
+      </c>
+      <c r="BE165">
+        <v>15.5</v>
+      </c>
+      <c r="BF165">
+        <v>1.01</v>
+      </c>
+      <c r="BG165">
+        <v>1.33</v>
+      </c>
+      <c r="BH165">
+        <v>2.98</v>
+      </c>
+      <c r="BI165">
+        <v>1.65</v>
+      </c>
+      <c r="BJ165">
+        <v>2.08</v>
+      </c>
+      <c r="BK165">
+        <v>2.12</v>
+      </c>
+      <c r="BL165">
+        <v>1.62</v>
+      </c>
+      <c r="BM165">
+        <v>2.98</v>
+      </c>
+      <c r="BN165">
+        <v>1.34</v>
+      </c>
+      <c r="BO165">
+        <v>4.35</v>
+      </c>
+      <c r="BP165">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="269">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -572,6 +572,12 @@
   </si>
   <si>
     <t>['81']</t>
+  </si>
+  <si>
+    <t>['46', '70']</t>
+  </si>
+  <si>
+    <t>['9', '63']</t>
   </si>
   <si>
     <t>['12', '22', '45+1', '45+4', '90+1', '90+8']</t>
@@ -1176,7 +1182,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP165"/>
+  <dimension ref="A1:BP168"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1922,10 +1928,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ4">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2050,7 +2056,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q5">
         <v>7.5</v>
@@ -2256,7 +2262,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2540,7 +2546,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ7">
         <v>1.1</v>
@@ -2668,7 +2674,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q8">
         <v>4</v>
@@ -2955,7 +2961,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ9">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3570,7 +3576,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ12">
         <v>0.3</v>
@@ -3698,7 +3704,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3904,7 +3910,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q14">
         <v>2.4</v>
@@ -4397,7 +4403,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ16">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR16">
         <v>2.14</v>
@@ -4728,7 +4734,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -4806,7 +4812,7 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ18">
         <v>2</v>
@@ -5140,7 +5146,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -5218,10 +5224,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ20">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR20">
         <v>0.96</v>
@@ -5346,7 +5352,7 @@
         <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5552,7 +5558,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5758,7 +5764,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -5839,7 +5845,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ23">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR23">
         <v>0.91</v>
@@ -5964,7 +5970,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q24">
         <v>3.25</v>
@@ -6170,7 +6176,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q25">
         <v>2.05</v>
@@ -6376,7 +6382,7 @@
         <v>86</v>
       </c>
       <c r="P26" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6994,7 +7000,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7281,7 +7287,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ30">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR30">
         <v>1.68</v>
@@ -7406,7 +7412,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7487,7 +7493,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ31">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR31">
         <v>1.36</v>
@@ -7612,7 +7618,7 @@
         <v>86</v>
       </c>
       <c r="P32" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q32">
         <v>2.05</v>
@@ -7690,7 +7696,7 @@
         <v>0.5</v>
       </c>
       <c r="AP32">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ32">
         <v>0.7</v>
@@ -7896,7 +7902,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ33">
         <v>2</v>
@@ -8517,7 +8523,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ36">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR36">
         <v>1.19</v>
@@ -8642,7 +8648,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -8720,7 +8726,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ37">
         <v>1.82</v>
@@ -9466,7 +9472,7 @@
         <v>86</v>
       </c>
       <c r="P41" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q41">
         <v>2.38</v>
@@ -9878,7 +9884,7 @@
         <v>86</v>
       </c>
       <c r="P43" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q43">
         <v>7.5</v>
@@ -10084,7 +10090,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10496,7 +10502,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q46">
         <v>2.5</v>
@@ -10577,7 +10583,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ46">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR46">
         <v>1.81</v>
@@ -10702,7 +10708,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q47">
         <v>4.33</v>
@@ -10908,7 +10914,7 @@
         <v>86</v>
       </c>
       <c r="P48" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q48">
         <v>2.4</v>
@@ -10986,7 +10992,7 @@
         <v>3</v>
       </c>
       <c r="AP48">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ48">
         <v>1.91</v>
@@ -11401,7 +11407,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ50">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR50">
         <v>1.44</v>
@@ -11526,7 +11532,7 @@
         <v>116</v>
       </c>
       <c r="P51" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11604,7 +11610,7 @@
         <v>2</v>
       </c>
       <c r="AP51">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ51">
         <v>1</v>
@@ -11732,7 +11738,7 @@
         <v>118</v>
       </c>
       <c r="P52" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q52">
         <v>5.5</v>
@@ -11813,7 +11819,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ52">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR52">
         <v>0.93</v>
@@ -12016,7 +12022,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ53">
         <v>1.82</v>
@@ -12144,7 +12150,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -12222,7 +12228,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ54">
         <v>0.3</v>
@@ -12556,7 +12562,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q56">
         <v>5.5</v>
@@ -12762,7 +12768,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q57">
         <v>5</v>
@@ -12968,7 +12974,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13049,7 +13055,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ58">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR58">
         <v>1.97</v>
@@ -13174,7 +13180,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13380,7 +13386,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13586,7 +13592,7 @@
         <v>86</v>
       </c>
       <c r="P61" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q61">
         <v>6.5</v>
@@ -13792,7 +13798,7 @@
         <v>86</v>
       </c>
       <c r="P62" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q62">
         <v>7</v>
@@ -13998,7 +14004,7 @@
         <v>86</v>
       </c>
       <c r="P63" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q63">
         <v>3.5</v>
@@ -14076,7 +14082,7 @@
         <v>1.67</v>
       </c>
       <c r="AP63">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ63">
         <v>1.3</v>
@@ -14204,7 +14210,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14285,7 +14291,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ64">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR64">
         <v>0.92</v>
@@ -14488,10 +14494,10 @@
         <v>2.25</v>
       </c>
       <c r="AP65">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ65">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR65">
         <v>1.93</v>
@@ -14694,7 +14700,7 @@
         <v>1.67</v>
       </c>
       <c r="AP66">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ66">
         <v>1</v>
@@ -14822,7 +14828,7 @@
         <v>86</v>
       </c>
       <c r="P67" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q67">
         <v>6.5</v>
@@ -15028,7 +15034,7 @@
         <v>86</v>
       </c>
       <c r="P68" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q68">
         <v>4.75</v>
@@ -15646,7 +15652,7 @@
         <v>92</v>
       </c>
       <c r="P71" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q71">
         <v>9.5</v>
@@ -16264,7 +16270,7 @@
         <v>86</v>
       </c>
       <c r="P74" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16342,7 +16348,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ74">
         <v>1</v>
@@ -16882,7 +16888,7 @@
         <v>130</v>
       </c>
       <c r="P77" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q77">
         <v>1.83</v>
@@ -16963,7 +16969,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ77">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR77">
         <v>1.79</v>
@@ -17088,7 +17094,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q78">
         <v>12</v>
@@ -17294,7 +17300,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q79">
         <v>3.75</v>
@@ -17500,7 +17506,7 @@
         <v>131</v>
       </c>
       <c r="P80" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17706,7 +17712,7 @@
         <v>132</v>
       </c>
       <c r="P81" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -17787,7 +17793,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ81">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR81">
         <v>1.3</v>
@@ -18118,7 +18124,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q83">
         <v>1.67</v>
@@ -18196,10 +18202,10 @@
         <v>0.75</v>
       </c>
       <c r="AP83">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ83">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR83">
         <v>1.8</v>
@@ -18736,7 +18742,7 @@
         <v>134</v>
       </c>
       <c r="P86" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q86">
         <v>2.63</v>
@@ -19020,7 +19026,7 @@
         <v>2.33</v>
       </c>
       <c r="AP87">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ87">
         <v>1.1</v>
@@ -20384,7 +20390,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q94">
         <v>13</v>
@@ -20590,7 +20596,7 @@
         <v>139</v>
       </c>
       <c r="P95" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -20671,7 +20677,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ95">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR95">
         <v>1.49</v>
@@ -21002,7 +21008,7 @@
         <v>140</v>
       </c>
       <c r="P97" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q97">
         <v>2.4</v>
@@ -21286,7 +21292,7 @@
         <v>0.8</v>
       </c>
       <c r="AP98">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ98">
         <v>0.5</v>
@@ -21495,7 +21501,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ99">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR99">
         <v>1.34</v>
@@ -21826,7 +21832,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -21907,7 +21913,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ101">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR101">
         <v>1.85</v>
@@ -22316,7 +22322,7 @@
         <v>1.67</v>
       </c>
       <c r="AP103">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ103">
         <v>1.3</v>
@@ -22444,7 +22450,7 @@
         <v>145</v>
       </c>
       <c r="P104" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22650,7 +22656,7 @@
         <v>86</v>
       </c>
       <c r="P105" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -22731,7 +22737,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ105">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR105">
         <v>1.16</v>
@@ -22856,7 +22862,7 @@
         <v>146</v>
       </c>
       <c r="P106" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q106">
         <v>6</v>
@@ -22934,7 +22940,7 @@
         <v>0.67</v>
       </c>
       <c r="AP106">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ106">
         <v>1.1</v>
@@ -23268,7 +23274,7 @@
         <v>147</v>
       </c>
       <c r="P108" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23349,7 +23355,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ108">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR108">
         <v>1.48</v>
@@ -23552,7 +23558,7 @@
         <v>0.33</v>
       </c>
       <c r="AP109">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ109">
         <v>0.3</v>
@@ -23680,7 +23686,7 @@
         <v>149</v>
       </c>
       <c r="P110" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -24092,7 +24098,7 @@
         <v>143</v>
       </c>
       <c r="P112" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q112">
         <v>4.75</v>
@@ -24916,7 +24922,7 @@
         <v>86</v>
       </c>
       <c r="P116" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q116">
         <v>4.5</v>
@@ -25122,7 +25128,7 @@
         <v>153</v>
       </c>
       <c r="P117" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q117">
         <v>1.53</v>
@@ -25203,7 +25209,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ117">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR117">
         <v>1.99</v>
@@ -25328,7 +25334,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25534,7 +25540,7 @@
         <v>154</v>
       </c>
       <c r="P119" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q119">
         <v>1.8</v>
@@ -25612,7 +25618,7 @@
         <v>0.83</v>
       </c>
       <c r="AP119">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ119">
         <v>1</v>
@@ -25740,7 +25746,7 @@
         <v>155</v>
       </c>
       <c r="P120" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q120">
         <v>7.5</v>
@@ -26152,7 +26158,7 @@
         <v>157</v>
       </c>
       <c r="P122" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q122">
         <v>2.63</v>
@@ -26358,7 +26364,7 @@
         <v>158</v>
       </c>
       <c r="P123" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q123">
         <v>1.73</v>
@@ -26851,7 +26857,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ125">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR125">
         <v>1.25</v>
@@ -26976,7 +26982,7 @@
         <v>86</v>
       </c>
       <c r="P126" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27182,7 +27188,7 @@
         <v>161</v>
       </c>
       <c r="P127" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27260,7 +27266,7 @@
         <v>3</v>
       </c>
       <c r="AP127">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ127">
         <v>2.5</v>
@@ -27388,7 +27394,7 @@
         <v>86</v>
       </c>
       <c r="P128" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q128">
         <v>2.4</v>
@@ -27594,7 +27600,7 @@
         <v>138</v>
       </c>
       <c r="P129" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27800,7 +27806,7 @@
         <v>98</v>
       </c>
       <c r="P130" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q130">
         <v>6.5</v>
@@ -28006,7 +28012,7 @@
         <v>162</v>
       </c>
       <c r="P131" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q131">
         <v>4.33</v>
@@ -28087,7 +28093,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ131">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR131">
         <v>1.16</v>
@@ -28212,7 +28218,7 @@
         <v>86</v>
       </c>
       <c r="P132" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q132">
         <v>8</v>
@@ -28702,7 +28708,7 @@
         <v>2.25</v>
       </c>
       <c r="AP134">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ134">
         <v>1.91</v>
@@ -28911,7 +28917,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ135">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR135">
         <v>1.42</v>
@@ -29114,7 +29120,7 @@
         <v>0.5</v>
       </c>
       <c r="AP136">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ136">
         <v>0.7</v>
@@ -29323,7 +29329,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ137">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR137">
         <v>1.54</v>
@@ -29732,7 +29738,7 @@
         <v>1.75</v>
       </c>
       <c r="AP139">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ139">
         <v>1.5</v>
@@ -29860,7 +29866,7 @@
         <v>167</v>
       </c>
       <c r="P140" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q140">
         <v>2.3</v>
@@ -30066,7 +30072,7 @@
         <v>86</v>
       </c>
       <c r="P141" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q141">
         <v>7.5</v>
@@ -30272,7 +30278,7 @@
         <v>168</v>
       </c>
       <c r="P142" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30478,7 +30484,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30890,7 +30896,7 @@
         <v>171</v>
       </c>
       <c r="P145" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q145">
         <v>3.75</v>
@@ -30968,10 +30974,10 @@
         <v>1.56</v>
       </c>
       <c r="AP145">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ145">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR145">
         <v>1.27</v>
@@ -31096,7 +31102,7 @@
         <v>172</v>
       </c>
       <c r="P146" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q146">
         <v>7.5</v>
@@ -31302,7 +31308,7 @@
         <v>173</v>
       </c>
       <c r="P147" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31380,7 +31386,7 @@
         <v>1.33</v>
       </c>
       <c r="AP147">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ147">
         <v>1.3</v>
@@ -31508,7 +31514,7 @@
         <v>174</v>
       </c>
       <c r="P148" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q148">
         <v>2.75</v>
@@ -31589,7 +31595,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ148">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR148">
         <v>1.13</v>
@@ -31714,7 +31720,7 @@
         <v>86</v>
       </c>
       <c r="P149" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q149">
         <v>7.5</v>
@@ -31998,7 +32004,7 @@
         <v>2.33</v>
       </c>
       <c r="AP150">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ150">
         <v>1.91</v>
@@ -32126,7 +32132,7 @@
         <v>86</v>
       </c>
       <c r="P151" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q151">
         <v>6.5</v>
@@ -32207,7 +32213,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ151">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR151">
         <v>0.99</v>
@@ -32332,7 +32338,7 @@
         <v>176</v>
       </c>
       <c r="P152" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q152">
         <v>2.75</v>
@@ -32538,7 +32544,7 @@
         <v>177</v>
       </c>
       <c r="P153" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q153">
         <v>4.75</v>
@@ -32950,7 +32956,7 @@
         <v>179</v>
       </c>
       <c r="P155" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33156,7 +33162,7 @@
         <v>176</v>
       </c>
       <c r="P156" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q156">
         <v>2.2</v>
@@ -33568,7 +33574,7 @@
         <v>181</v>
       </c>
       <c r="P158" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33774,7 +33780,7 @@
         <v>182</v>
       </c>
       <c r="P159" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q159">
         <v>1.8</v>
@@ -34392,7 +34398,7 @@
         <v>86</v>
       </c>
       <c r="P162" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q162">
         <v>3.5</v>
@@ -34598,7 +34604,7 @@
         <v>184</v>
       </c>
       <c r="P163" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35010,7 +35016,7 @@
         <v>185</v>
       </c>
       <c r="P165" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q165">
         <v>9.5</v>
@@ -35167,6 +35173,624 @@
       </c>
       <c r="BP165">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="166" spans="1:68">
+      <c r="A166" s="1">
+        <v>165</v>
+      </c>
+      <c r="B166">
+        <v>7762760</v>
+      </c>
+      <c r="C166" t="s">
+        <v>68</v>
+      </c>
+      <c r="D166" t="s">
+        <v>69</v>
+      </c>
+      <c r="E166" s="2">
+        <v>45704.3125</v>
+      </c>
+      <c r="F166">
+        <v>21</v>
+      </c>
+      <c r="G166" t="s">
+        <v>72</v>
+      </c>
+      <c r="H166" t="s">
+        <v>77</v>
+      </c>
+      <c r="I166">
+        <v>0</v>
+      </c>
+      <c r="J166">
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <v>0</v>
+      </c>
+      <c r="L166">
+        <v>0</v>
+      </c>
+      <c r="M166">
+        <v>1</v>
+      </c>
+      <c r="N166">
+        <v>1</v>
+      </c>
+      <c r="O166" t="s">
+        <v>86</v>
+      </c>
+      <c r="P166" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q166">
+        <v>2.4</v>
+      </c>
+      <c r="R166">
+        <v>2.1</v>
+      </c>
+      <c r="S166">
+        <v>5</v>
+      </c>
+      <c r="T166">
+        <v>1.44</v>
+      </c>
+      <c r="U166">
+        <v>2.63</v>
+      </c>
+      <c r="V166">
+        <v>3.25</v>
+      </c>
+      <c r="W166">
+        <v>1.33</v>
+      </c>
+      <c r="X166">
+        <v>9</v>
+      </c>
+      <c r="Y166">
+        <v>1.07</v>
+      </c>
+      <c r="Z166">
+        <v>1.81</v>
+      </c>
+      <c r="AA166">
+        <v>3.47</v>
+      </c>
+      <c r="AB166">
+        <v>4.33</v>
+      </c>
+      <c r="AC166">
+        <v>1</v>
+      </c>
+      <c r="AD166">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE166">
+        <v>1.35</v>
+      </c>
+      <c r="AF166">
+        <v>3</v>
+      </c>
+      <c r="AG166">
+        <v>2</v>
+      </c>
+      <c r="AH166">
+        <v>1.75</v>
+      </c>
+      <c r="AI166">
+        <v>2</v>
+      </c>
+      <c r="AJ166">
+        <v>1.73</v>
+      </c>
+      <c r="AK166">
+        <v>1.2</v>
+      </c>
+      <c r="AL166">
+        <v>1.27</v>
+      </c>
+      <c r="AM166">
+        <v>1.89</v>
+      </c>
+      <c r="AN166">
+        <v>0.6</v>
+      </c>
+      <c r="AO166">
+        <v>1.2</v>
+      </c>
+      <c r="AP166">
+        <v>0.55</v>
+      </c>
+      <c r="AQ166">
+        <v>1.36</v>
+      </c>
+      <c r="AR166">
+        <v>1.31</v>
+      </c>
+      <c r="AS166">
+        <v>1.11</v>
+      </c>
+      <c r="AT166">
+        <v>2.42</v>
+      </c>
+      <c r="AU166">
+        <v>4</v>
+      </c>
+      <c r="AV166">
+        <v>6</v>
+      </c>
+      <c r="AW166">
+        <v>5</v>
+      </c>
+      <c r="AX166">
+        <v>6</v>
+      </c>
+      <c r="AY166">
+        <v>9</v>
+      </c>
+      <c r="AZ166">
+        <v>12</v>
+      </c>
+      <c r="BA166">
+        <v>5</v>
+      </c>
+      <c r="BB166">
+        <v>3</v>
+      </c>
+      <c r="BC166">
+        <v>8</v>
+      </c>
+      <c r="BD166">
+        <v>1.52</v>
+      </c>
+      <c r="BE166">
+        <v>7</v>
+      </c>
+      <c r="BF166">
+        <v>2.8</v>
+      </c>
+      <c r="BG166">
+        <v>1.3</v>
+      </c>
+      <c r="BH166">
+        <v>3.15</v>
+      </c>
+      <c r="BI166">
+        <v>1.52</v>
+      </c>
+      <c r="BJ166">
+        <v>2.33</v>
+      </c>
+      <c r="BK166">
+        <v>1.83</v>
+      </c>
+      <c r="BL166">
+        <v>1.85</v>
+      </c>
+      <c r="BM166">
+        <v>2.3</v>
+      </c>
+      <c r="BN166">
+        <v>1.54</v>
+      </c>
+      <c r="BO166">
+        <v>2.9</v>
+      </c>
+      <c r="BP166">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="167" spans="1:68">
+      <c r="A167" s="1">
+        <v>166</v>
+      </c>
+      <c r="B167">
+        <v>7762758</v>
+      </c>
+      <c r="C167" t="s">
+        <v>68</v>
+      </c>
+      <c r="D167" t="s">
+        <v>69</v>
+      </c>
+      <c r="E167" s="2">
+        <v>45704.41666666666</v>
+      </c>
+      <c r="F167">
+        <v>21</v>
+      </c>
+      <c r="G167" t="s">
+        <v>75</v>
+      </c>
+      <c r="H167" t="s">
+        <v>83</v>
+      </c>
+      <c r="I167">
+        <v>0</v>
+      </c>
+      <c r="J167">
+        <v>0</v>
+      </c>
+      <c r="K167">
+        <v>0</v>
+      </c>
+      <c r="L167">
+        <v>2</v>
+      </c>
+      <c r="M167">
+        <v>1</v>
+      </c>
+      <c r="N167">
+        <v>3</v>
+      </c>
+      <c r="O167" t="s">
+        <v>186</v>
+      </c>
+      <c r="P167" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q167">
+        <v>1.73</v>
+      </c>
+      <c r="R167">
+        <v>2.5</v>
+      </c>
+      <c r="S167">
+        <v>11</v>
+      </c>
+      <c r="T167">
+        <v>1.36</v>
+      </c>
+      <c r="U167">
+        <v>3</v>
+      </c>
+      <c r="V167">
+        <v>2.63</v>
+      </c>
+      <c r="W167">
+        <v>1.44</v>
+      </c>
+      <c r="X167">
+        <v>7</v>
+      </c>
+      <c r="Y167">
+        <v>1.1</v>
+      </c>
+      <c r="Z167">
+        <v>1.33</v>
+      </c>
+      <c r="AA167">
+        <v>4.6</v>
+      </c>
+      <c r="AB167">
+        <v>10</v>
+      </c>
+      <c r="AC167">
+        <v>1</v>
+      </c>
+      <c r="AD167">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE167">
+        <v>1.25</v>
+      </c>
+      <c r="AF167">
+        <v>3.65</v>
+      </c>
+      <c r="AG167">
+        <v>1.92</v>
+      </c>
+      <c r="AH167">
+        <v>1.82</v>
+      </c>
+      <c r="AI167">
+        <v>2.63</v>
+      </c>
+      <c r="AJ167">
+        <v>1.44</v>
+      </c>
+      <c r="AK167">
+        <v>1.04</v>
+      </c>
+      <c r="AL167">
+        <v>1.11</v>
+      </c>
+      <c r="AM167">
+        <v>3.55</v>
+      </c>
+      <c r="AN167">
+        <v>2.8</v>
+      </c>
+      <c r="AO167">
+        <v>1.7</v>
+      </c>
+      <c r="AP167">
+        <v>2.82</v>
+      </c>
+      <c r="AQ167">
+        <v>1.55</v>
+      </c>
+      <c r="AR167">
+        <v>1.7</v>
+      </c>
+      <c r="AS167">
+        <v>1.23</v>
+      </c>
+      <c r="AT167">
+        <v>2.93</v>
+      </c>
+      <c r="AU167">
+        <v>6</v>
+      </c>
+      <c r="AV167">
+        <v>3</v>
+      </c>
+      <c r="AW167">
+        <v>9</v>
+      </c>
+      <c r="AX167">
+        <v>1</v>
+      </c>
+      <c r="AY167">
+        <v>15</v>
+      </c>
+      <c r="AZ167">
+        <v>4</v>
+      </c>
+      <c r="BA167">
+        <v>5</v>
+      </c>
+      <c r="BB167">
+        <v>2</v>
+      </c>
+      <c r="BC167">
+        <v>7</v>
+      </c>
+      <c r="BD167">
+        <v>1.24</v>
+      </c>
+      <c r="BE167">
+        <v>7.5</v>
+      </c>
+      <c r="BF167">
+        <v>4.6</v>
+      </c>
+      <c r="BG167">
+        <v>1.53</v>
+      </c>
+      <c r="BH167">
+        <v>2.32</v>
+      </c>
+      <c r="BI167">
+        <v>1.9</v>
+      </c>
+      <c r="BJ167">
+        <v>1.79</v>
+      </c>
+      <c r="BK167">
+        <v>2.4</v>
+      </c>
+      <c r="BL167">
+        <v>1.49</v>
+      </c>
+      <c r="BM167">
+        <v>3.15</v>
+      </c>
+      <c r="BN167">
+        <v>1.3</v>
+      </c>
+      <c r="BO167">
+        <v>4.1</v>
+      </c>
+      <c r="BP167">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="168" spans="1:68">
+      <c r="A168" s="1">
+        <v>167</v>
+      </c>
+      <c r="B168">
+        <v>7762755</v>
+      </c>
+      <c r="C168" t="s">
+        <v>68</v>
+      </c>
+      <c r="D168" t="s">
+        <v>69</v>
+      </c>
+      <c r="E168" s="2">
+        <v>45704.52083333334</v>
+      </c>
+      <c r="F168">
+        <v>21</v>
+      </c>
+      <c r="G168" t="s">
+        <v>80</v>
+      </c>
+      <c r="H168" t="s">
+        <v>78</v>
+      </c>
+      <c r="I168">
+        <v>1</v>
+      </c>
+      <c r="J168">
+        <v>0</v>
+      </c>
+      <c r="K168">
+        <v>1</v>
+      </c>
+      <c r="L168">
+        <v>2</v>
+      </c>
+      <c r="M168">
+        <v>0</v>
+      </c>
+      <c r="N168">
+        <v>2</v>
+      </c>
+      <c r="O168" t="s">
+        <v>187</v>
+      </c>
+      <c r="P168" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q168">
+        <v>2.1</v>
+      </c>
+      <c r="R168">
+        <v>2.25</v>
+      </c>
+      <c r="S168">
+        <v>6.5</v>
+      </c>
+      <c r="T168">
+        <v>1.4</v>
+      </c>
+      <c r="U168">
+        <v>2.75</v>
+      </c>
+      <c r="V168">
+        <v>3</v>
+      </c>
+      <c r="W168">
+        <v>1.36</v>
+      </c>
+      <c r="X168">
+        <v>8</v>
+      </c>
+      <c r="Y168">
+        <v>1.08</v>
+      </c>
+      <c r="Z168">
+        <v>1.39</v>
+      </c>
+      <c r="AA168">
+        <v>4.3</v>
+      </c>
+      <c r="AB168">
+        <v>8.5</v>
+      </c>
+      <c r="AC168">
+        <v>1</v>
+      </c>
+      <c r="AD168">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE168">
+        <v>1.31</v>
+      </c>
+      <c r="AF168">
+        <v>3.3</v>
+      </c>
+      <c r="AG168">
+        <v>1.98</v>
+      </c>
+      <c r="AH168">
+        <v>1.77</v>
+      </c>
+      <c r="AI168">
+        <v>2.1</v>
+      </c>
+      <c r="AJ168">
+        <v>1.67</v>
+      </c>
+      <c r="AK168">
+        <v>1.11</v>
+      </c>
+      <c r="AL168">
+        <v>1.2</v>
+      </c>
+      <c r="AM168">
+        <v>2.4</v>
+      </c>
+      <c r="AN168">
+        <v>1.5</v>
+      </c>
+      <c r="AO168">
+        <v>1.2</v>
+      </c>
+      <c r="AP168">
+        <v>1.64</v>
+      </c>
+      <c r="AQ168">
+        <v>1.09</v>
+      </c>
+      <c r="AR168">
+        <v>2.21</v>
+      </c>
+      <c r="AS168">
+        <v>1.28</v>
+      </c>
+      <c r="AT168">
+        <v>3.49</v>
+      </c>
+      <c r="AU168">
+        <v>5</v>
+      </c>
+      <c r="AV168">
+        <v>2</v>
+      </c>
+      <c r="AW168">
+        <v>6</v>
+      </c>
+      <c r="AX168">
+        <v>3</v>
+      </c>
+      <c r="AY168">
+        <v>11</v>
+      </c>
+      <c r="AZ168">
+        <v>5</v>
+      </c>
+      <c r="BA168">
+        <v>3</v>
+      </c>
+      <c r="BB168">
+        <v>1</v>
+      </c>
+      <c r="BC168">
+        <v>4</v>
+      </c>
+      <c r="BD168">
+        <v>1.3</v>
+      </c>
+      <c r="BE168">
+        <v>7.5</v>
+      </c>
+      <c r="BF168">
+        <v>3.8</v>
+      </c>
+      <c r="BG168">
+        <v>1.38</v>
+      </c>
+      <c r="BH168">
+        <v>2.7</v>
+      </c>
+      <c r="BI168">
+        <v>1.67</v>
+      </c>
+      <c r="BJ168">
+        <v>2.07</v>
+      </c>
+      <c r="BK168">
+        <v>2.07</v>
+      </c>
+      <c r="BL168">
+        <v>1.67</v>
+      </c>
+      <c r="BM168">
+        <v>2.65</v>
+      </c>
+      <c r="BN168">
+        <v>1.42</v>
+      </c>
+      <c r="BO168">
+        <v>3.4</v>
+      </c>
+      <c r="BP168">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="270">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -578,6 +578,9 @@
   </si>
   <si>
     <t>['9', '63']</t>
+  </si>
+  <si>
+    <t>['-1']</t>
   </si>
   <si>
     <t>['12', '22', '45+1', '45+4', '90+1', '90+8']</t>
@@ -1182,7 +1185,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP168"/>
+  <dimension ref="A1:BP169"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1519,7 +1522,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ2">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2056,7 +2059,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q5">
         <v>7.5</v>
@@ -2262,7 +2265,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2674,7 +2677,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q8">
         <v>4</v>
@@ -3704,7 +3707,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3910,7 +3913,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q14">
         <v>2.4</v>
@@ -4734,7 +4737,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -5146,7 +5149,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -5352,7 +5355,7 @@
         <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5558,7 +5561,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5764,7 +5767,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -5970,7 +5973,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q24">
         <v>3.25</v>
@@ -6048,7 +6051,7 @@
         <v>2</v>
       </c>
       <c r="AP24">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ24">
         <v>1.5</v>
@@ -6176,7 +6179,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q25">
         <v>2.05</v>
@@ -6382,7 +6385,7 @@
         <v>86</v>
       </c>
       <c r="P26" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -7000,7 +7003,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7412,7 +7415,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7618,7 +7621,7 @@
         <v>86</v>
       </c>
       <c r="P32" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q32">
         <v>2.05</v>
@@ -8111,7 +8114,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ34">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR34">
         <v>0.89</v>
@@ -8648,7 +8651,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -9472,7 +9475,7 @@
         <v>86</v>
       </c>
       <c r="P41" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q41">
         <v>2.38</v>
@@ -9884,7 +9887,7 @@
         <v>86</v>
       </c>
       <c r="P43" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q43">
         <v>7.5</v>
@@ -10090,7 +10093,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10502,7 +10505,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q46">
         <v>2.5</v>
@@ -10580,7 +10583,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ46">
         <v>1.09</v>
@@ -10708,7 +10711,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q47">
         <v>4.33</v>
@@ -10789,7 +10792,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ47">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR47">
         <v>1.32</v>
@@ -10914,7 +10917,7 @@
         <v>86</v>
       </c>
       <c r="P48" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q48">
         <v>2.4</v>
@@ -11532,7 +11535,7 @@
         <v>116</v>
       </c>
       <c r="P51" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11738,7 +11741,7 @@
         <v>118</v>
       </c>
       <c r="P52" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q52">
         <v>5.5</v>
@@ -12150,7 +12153,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -12562,7 +12565,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q56">
         <v>5.5</v>
@@ -12768,7 +12771,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q57">
         <v>5</v>
@@ -12974,7 +12977,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13180,7 +13183,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13386,7 +13389,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13592,7 +13595,7 @@
         <v>86</v>
       </c>
       <c r="P61" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q61">
         <v>6.5</v>
@@ -13798,7 +13801,7 @@
         <v>86</v>
       </c>
       <c r="P62" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q62">
         <v>7</v>
@@ -13876,7 +13879,7 @@
         <v>3</v>
       </c>
       <c r="AP62">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ62">
         <v>2.5</v>
@@ -14004,7 +14007,7 @@
         <v>86</v>
       </c>
       <c r="P63" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q63">
         <v>3.5</v>
@@ -14085,7 +14088,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ63">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR63">
         <v>1.29</v>
@@ -14210,7 +14213,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14828,7 +14831,7 @@
         <v>86</v>
       </c>
       <c r="P67" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q67">
         <v>6.5</v>
@@ -14906,7 +14909,7 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ67">
         <v>2</v>
@@ -15034,7 +15037,7 @@
         <v>86</v>
       </c>
       <c r="P68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q68">
         <v>4.75</v>
@@ -15652,7 +15655,7 @@
         <v>92</v>
       </c>
       <c r="P71" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q71">
         <v>9.5</v>
@@ -15733,7 +15736,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ71">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR71">
         <v>1.26</v>
@@ -16270,7 +16273,7 @@
         <v>86</v>
       </c>
       <c r="P74" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16888,7 +16891,7 @@
         <v>130</v>
       </c>
       <c r="P77" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q77">
         <v>1.83</v>
@@ -17094,7 +17097,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q78">
         <v>12</v>
@@ -17300,7 +17303,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q79">
         <v>3.75</v>
@@ -17506,7 +17509,7 @@
         <v>131</v>
       </c>
       <c r="P80" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17587,7 +17590,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ80">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR80">
         <v>1.54</v>
@@ -17712,7 +17715,7 @@
         <v>132</v>
       </c>
       <c r="P81" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -17996,7 +17999,7 @@
         <v>1.75</v>
       </c>
       <c r="AP82">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ82">
         <v>1.82</v>
@@ -18124,7 +18127,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q83">
         <v>1.67</v>
@@ -18742,7 +18745,7 @@
         <v>134</v>
       </c>
       <c r="P86" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q86">
         <v>2.63</v>
@@ -20390,7 +20393,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q94">
         <v>13</v>
@@ -20596,7 +20599,7 @@
         <v>139</v>
       </c>
       <c r="P95" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -21008,7 +21011,7 @@
         <v>140</v>
       </c>
       <c r="P97" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q97">
         <v>2.4</v>
@@ -21086,7 +21089,7 @@
         <v>1</v>
       </c>
       <c r="AP97">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ97">
         <v>1</v>
@@ -21832,7 +21835,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22325,7 +22328,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ103">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR103">
         <v>1.72</v>
@@ -22450,7 +22453,7 @@
         <v>145</v>
       </c>
       <c r="P104" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22656,7 +22659,7 @@
         <v>86</v>
       </c>
       <c r="P105" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -22862,7 +22865,7 @@
         <v>146</v>
       </c>
       <c r="P106" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q106">
         <v>6</v>
@@ -23274,7 +23277,7 @@
         <v>147</v>
       </c>
       <c r="P108" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23686,7 +23689,7 @@
         <v>149</v>
       </c>
       <c r="P110" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -24098,7 +24101,7 @@
         <v>143</v>
       </c>
       <c r="P112" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q112">
         <v>4.75</v>
@@ -24794,7 +24797,7 @@
         <v>1.33</v>
       </c>
       <c r="AP115">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ115">
         <v>1.1</v>
@@ -24922,7 +24925,7 @@
         <v>86</v>
       </c>
       <c r="P116" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q116">
         <v>4.5</v>
@@ -25128,7 +25131,7 @@
         <v>153</v>
       </c>
       <c r="P117" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q117">
         <v>1.53</v>
@@ -25334,7 +25337,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25415,7 +25418,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ118">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR118">
         <v>0.95</v>
@@ -25540,7 +25543,7 @@
         <v>154</v>
       </c>
       <c r="P119" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q119">
         <v>1.8</v>
@@ -25746,7 +25749,7 @@
         <v>155</v>
       </c>
       <c r="P120" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q120">
         <v>7.5</v>
@@ -26158,7 +26161,7 @@
         <v>157</v>
       </c>
       <c r="P122" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q122">
         <v>2.63</v>
@@ -26364,7 +26367,7 @@
         <v>158</v>
       </c>
       <c r="P123" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q123">
         <v>1.73</v>
@@ -26982,7 +26985,7 @@
         <v>86</v>
       </c>
       <c r="P126" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27188,7 +27191,7 @@
         <v>161</v>
       </c>
       <c r="P127" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27394,7 +27397,7 @@
         <v>86</v>
       </c>
       <c r="P128" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q128">
         <v>2.4</v>
@@ -27472,7 +27475,7 @@
         <v>0.86</v>
       </c>
       <c r="AP128">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ128">
         <v>1</v>
@@ -27600,7 +27603,7 @@
         <v>138</v>
       </c>
       <c r="P129" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27681,7 +27684,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ129">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR129">
         <v>1.45</v>
@@ -27806,7 +27809,7 @@
         <v>98</v>
       </c>
       <c r="P130" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q130">
         <v>6.5</v>
@@ -28012,7 +28015,7 @@
         <v>162</v>
       </c>
       <c r="P131" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q131">
         <v>4.33</v>
@@ -28218,7 +28221,7 @@
         <v>86</v>
       </c>
       <c r="P132" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q132">
         <v>8</v>
@@ -29866,7 +29869,7 @@
         <v>167</v>
       </c>
       <c r="P140" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q140">
         <v>2.3</v>
@@ -30072,7 +30075,7 @@
         <v>86</v>
       </c>
       <c r="P141" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q141">
         <v>7.5</v>
@@ -30278,7 +30281,7 @@
         <v>168</v>
       </c>
       <c r="P142" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30484,7 +30487,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30562,7 +30565,7 @@
         <v>0.25</v>
       </c>
       <c r="AP143">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ143">
         <v>0.3</v>
@@ -30896,7 +30899,7 @@
         <v>171</v>
       </c>
       <c r="P145" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q145">
         <v>3.75</v>
@@ -31102,7 +31105,7 @@
         <v>172</v>
       </c>
       <c r="P146" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q146">
         <v>7.5</v>
@@ -31308,7 +31311,7 @@
         <v>173</v>
       </c>
       <c r="P147" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31389,7 +31392,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ147">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR147">
         <v>2.12</v>
@@ -31514,7 +31517,7 @@
         <v>174</v>
       </c>
       <c r="P148" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q148">
         <v>2.75</v>
@@ -31720,7 +31723,7 @@
         <v>86</v>
       </c>
       <c r="P149" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q149">
         <v>7.5</v>
@@ -32132,7 +32135,7 @@
         <v>86</v>
       </c>
       <c r="P151" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q151">
         <v>6.5</v>
@@ -32338,7 +32341,7 @@
         <v>176</v>
       </c>
       <c r="P152" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q152">
         <v>2.75</v>
@@ -32544,7 +32547,7 @@
         <v>177</v>
       </c>
       <c r="P153" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q153">
         <v>4.75</v>
@@ -32956,7 +32959,7 @@
         <v>179</v>
       </c>
       <c r="P155" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33162,7 +33165,7 @@
         <v>176</v>
       </c>
       <c r="P156" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q156">
         <v>2.2</v>
@@ -33446,7 +33449,7 @@
         <v>1.22</v>
       </c>
       <c r="AP157">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ157">
         <v>1.1</v>
@@ -33574,7 +33577,7 @@
         <v>181</v>
       </c>
       <c r="P158" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33780,7 +33783,7 @@
         <v>182</v>
       </c>
       <c r="P159" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q159">
         <v>1.8</v>
@@ -34398,7 +34401,7 @@
         <v>86</v>
       </c>
       <c r="P162" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q162">
         <v>3.5</v>
@@ -34604,7 +34607,7 @@
         <v>184</v>
       </c>
       <c r="P163" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35016,7 +35019,7 @@
         <v>185</v>
       </c>
       <c r="P165" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q165">
         <v>9.5</v>
@@ -35791,6 +35794,212 @@
       </c>
       <c r="BP168">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="169" spans="1:68">
+      <c r="A169" s="1">
+        <v>168</v>
+      </c>
+      <c r="B169">
+        <v>7762754</v>
+      </c>
+      <c r="C169" t="s">
+        <v>68</v>
+      </c>
+      <c r="D169" t="s">
+        <v>69</v>
+      </c>
+      <c r="E169" s="2">
+        <v>45705.52083333334</v>
+      </c>
+      <c r="F169">
+        <v>21</v>
+      </c>
+      <c r="G169" t="s">
+        <v>85</v>
+      </c>
+      <c r="H169" t="s">
+        <v>81</v>
+      </c>
+      <c r="I169">
+        <v>0</v>
+      </c>
+      <c r="J169">
+        <v>0</v>
+      </c>
+      <c r="K169">
+        <v>0</v>
+      </c>
+      <c r="L169">
+        <v>1</v>
+      </c>
+      <c r="M169">
+        <v>1</v>
+      </c>
+      <c r="N169">
+        <v>2</v>
+      </c>
+      <c r="O169" t="s">
+        <v>188</v>
+      </c>
+      <c r="P169" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q169">
+        <v>2.88</v>
+      </c>
+      <c r="R169">
+        <v>2.1</v>
+      </c>
+      <c r="S169">
+        <v>3.75</v>
+      </c>
+      <c r="T169">
+        <v>1.4</v>
+      </c>
+      <c r="U169">
+        <v>2.75</v>
+      </c>
+      <c r="V169">
+        <v>3</v>
+      </c>
+      <c r="W169">
+        <v>1.36</v>
+      </c>
+      <c r="X169">
+        <v>9</v>
+      </c>
+      <c r="Y169">
+        <v>1.07</v>
+      </c>
+      <c r="Z169">
+        <v>2.2</v>
+      </c>
+      <c r="AA169">
+        <v>3.19</v>
+      </c>
+      <c r="AB169">
+        <v>3.32</v>
+      </c>
+      <c r="AC169">
+        <v>1.01</v>
+      </c>
+      <c r="AD169">
+        <v>8.9</v>
+      </c>
+      <c r="AE169">
+        <v>1.29</v>
+      </c>
+      <c r="AF169">
+        <v>3.4</v>
+      </c>
+      <c r="AG169">
+        <v>1.94</v>
+      </c>
+      <c r="AH169">
+        <v>1.8</v>
+      </c>
+      <c r="AI169">
+        <v>1.8</v>
+      </c>
+      <c r="AJ169">
+        <v>1.91</v>
+      </c>
+      <c r="AK169">
+        <v>1.31</v>
+      </c>
+      <c r="AL169">
+        <v>1.29</v>
+      </c>
+      <c r="AM169">
+        <v>1.63</v>
+      </c>
+      <c r="AN169">
+        <v>1.9</v>
+      </c>
+      <c r="AO169">
+        <v>1.3</v>
+      </c>
+      <c r="AP169">
+        <v>1.82</v>
+      </c>
+      <c r="AQ169">
+        <v>1.27</v>
+      </c>
+      <c r="AR169">
+        <v>1.46</v>
+      </c>
+      <c r="AS169">
+        <v>1.5</v>
+      </c>
+      <c r="AT169">
+        <v>2.96</v>
+      </c>
+      <c r="AU169">
+        <v>3</v>
+      </c>
+      <c r="AV169">
+        <v>7</v>
+      </c>
+      <c r="AW169">
+        <v>4</v>
+      </c>
+      <c r="AX169">
+        <v>5</v>
+      </c>
+      <c r="AY169">
+        <v>7</v>
+      </c>
+      <c r="AZ169">
+        <v>12</v>
+      </c>
+      <c r="BA169">
+        <v>4</v>
+      </c>
+      <c r="BB169">
+        <v>6</v>
+      </c>
+      <c r="BC169">
+        <v>10</v>
+      </c>
+      <c r="BD169">
+        <v>1.81</v>
+      </c>
+      <c r="BE169">
+        <v>6.4</v>
+      </c>
+      <c r="BF169">
+        <v>2.2</v>
+      </c>
+      <c r="BG169">
+        <v>1.34</v>
+      </c>
+      <c r="BH169">
+        <v>2.9</v>
+      </c>
+      <c r="BI169">
+        <v>1.58</v>
+      </c>
+      <c r="BJ169">
+        <v>2.18</v>
+      </c>
+      <c r="BK169">
+        <v>1.95</v>
+      </c>
+      <c r="BL169">
+        <v>1.75</v>
+      </c>
+      <c r="BM169">
+        <v>2.48</v>
+      </c>
+      <c r="BN169">
+        <v>1.48</v>
+      </c>
+      <c r="BO169">
+        <v>3.2</v>
+      </c>
+      <c r="BP169">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="271">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -580,7 +580,7 @@
     <t>['9', '63']</t>
   </si>
   <si>
-    <t>['-1']</t>
+    <t>['73']</t>
   </si>
   <si>
     <t>['12', '22', '45+1', '45+4', '90+1', '90+8']</t>
@@ -824,6 +824,9 @@
   </si>
   <si>
     <t>['12', '21', '58', '60']</t>
+  </si>
+  <si>
+    <t>['27']</t>
   </si>
 </sst>
 </file>
@@ -35825,10 +35828,10 @@
         <v>0</v>
       </c>
       <c r="J169">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K169">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L169">
         <v>1</v>
@@ -35843,7 +35846,7 @@
         <v>188</v>
       </c>
       <c r="P169" t="s">
-        <v>188</v>
+        <v>270</v>
       </c>
       <c r="Q169">
         <v>2.88</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="273">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -580,7 +580,16 @@
     <t>['9', '63']</t>
   </si>
   <si>
-    <t>['73']</t>
+    <t>['-1']</t>
+  </si>
+  <si>
+    <t>['78']</t>
+  </si>
+  <si>
+    <t>['25', '78']</t>
+  </si>
+  <si>
+    <t>['17', '90+4']</t>
   </si>
   <si>
     <t>['12', '22', '45+1', '45+4', '90+1', '90+8']</t>
@@ -824,9 +833,6 @@
   </si>
   <si>
     <t>['12', '21', '58', '60']</t>
-  </si>
-  <si>
-    <t>['27']</t>
   </si>
 </sst>
 </file>
@@ -1188,7 +1194,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP169"/>
+  <dimension ref="A1:BP172"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2062,7 +2068,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q5">
         <v>7.5</v>
@@ -2268,7 +2274,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2680,7 +2686,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q8">
         <v>4</v>
@@ -2761,7 +2767,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ8">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3376,10 +3382,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ11">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3585,7 +3591,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ12">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3710,7 +3716,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3788,10 +3794,10 @@
         <v>3</v>
       </c>
       <c r="AP13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ13">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3916,7 +3922,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q14">
         <v>2.4</v>
@@ -4200,7 +4206,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ15">
         <v>1</v>
@@ -4740,7 +4746,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -5152,7 +5158,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -5358,7 +5364,7 @@
         <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5564,7 +5570,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5770,7 +5776,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -5976,7 +5982,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q24">
         <v>3.25</v>
@@ -6057,7 +6063,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ24">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -6182,7 +6188,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q25">
         <v>2.05</v>
@@ -6263,7 +6269,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ25">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR25">
         <v>1.06</v>
@@ -6388,7 +6394,7 @@
         <v>86</v>
       </c>
       <c r="P26" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6466,7 +6472,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ26">
         <v>1.1</v>
@@ -6672,7 +6678,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ27">
         <v>1</v>
@@ -7006,7 +7012,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7087,7 +7093,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ29">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR29">
         <v>2.25</v>
@@ -7418,7 +7424,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7624,7 +7630,7 @@
         <v>86</v>
       </c>
       <c r="P32" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q32">
         <v>2.05</v>
@@ -8654,7 +8660,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -8941,7 +8947,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ38">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR38">
         <v>0.86</v>
@@ -9144,10 +9150,10 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ39">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR39">
         <v>1.98</v>
@@ -9478,7 +9484,7 @@
         <v>86</v>
       </c>
       <c r="P41" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q41">
         <v>2.38</v>
@@ -9559,7 +9565,7 @@
         <v>2</v>
       </c>
       <c r="AQ41">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR41">
         <v>1.88</v>
@@ -9762,7 +9768,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ42">
         <v>0.7</v>
@@ -9890,7 +9896,7 @@
         <v>86</v>
       </c>
       <c r="P43" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q43">
         <v>7.5</v>
@@ -9968,7 +9974,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ43">
         <v>2.5</v>
@@ -10096,7 +10102,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10508,7 +10514,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q46">
         <v>2.5</v>
@@ -10714,7 +10720,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q47">
         <v>4.33</v>
@@ -10920,7 +10926,7 @@
         <v>86</v>
       </c>
       <c r="P48" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q48">
         <v>2.4</v>
@@ -11538,7 +11544,7 @@
         <v>116</v>
       </c>
       <c r="P51" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11744,7 +11750,7 @@
         <v>118</v>
       </c>
       <c r="P52" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q52">
         <v>5.5</v>
@@ -12156,7 +12162,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -12237,7 +12243,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ54">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR54">
         <v>1.14</v>
@@ -12443,7 +12449,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ55">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR55">
         <v>1.49</v>
@@ -12568,7 +12574,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q56">
         <v>5.5</v>
@@ -12774,7 +12780,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q57">
         <v>5</v>
@@ -12852,7 +12858,7 @@
         <v>3</v>
       </c>
       <c r="AP57">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ57">
         <v>1.91</v>
@@ -12980,7 +12986,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13186,7 +13192,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13264,7 +13270,7 @@
         <v>1.75</v>
       </c>
       <c r="AP59">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ59">
         <v>2</v>
@@ -13392,7 +13398,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13598,7 +13604,7 @@
         <v>86</v>
       </c>
       <c r="P61" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q61">
         <v>6.5</v>
@@ -13804,7 +13810,7 @@
         <v>86</v>
       </c>
       <c r="P62" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q62">
         <v>7</v>
@@ -14010,7 +14016,7 @@
         <v>86</v>
       </c>
       <c r="P63" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q63">
         <v>3.5</v>
@@ -14216,7 +14222,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14834,7 +14840,7 @@
         <v>86</v>
       </c>
       <c r="P67" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q67">
         <v>6.5</v>
@@ -15040,7 +15046,7 @@
         <v>86</v>
       </c>
       <c r="P68" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q68">
         <v>4.75</v>
@@ -15327,7 +15333,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ69">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR69">
         <v>1.44</v>
@@ -15658,7 +15664,7 @@
         <v>92</v>
       </c>
       <c r="P71" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q71">
         <v>9.5</v>
@@ -15945,7 +15951,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ72">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR72">
         <v>1.09</v>
@@ -16148,7 +16154,7 @@
         <v>0.8</v>
       </c>
       <c r="AP73">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ73">
         <v>0.7</v>
@@ -16276,7 +16282,7 @@
         <v>86</v>
       </c>
       <c r="P74" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16766,7 +16772,7 @@
         <v>2.5</v>
       </c>
       <c r="AP76">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ76">
         <v>1.91</v>
@@ -16894,7 +16900,7 @@
         <v>130</v>
       </c>
       <c r="P77" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q77">
         <v>1.83</v>
@@ -16972,7 +16978,7 @@
         <v>0.4</v>
       </c>
       <c r="AP77">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ77">
         <v>1.09</v>
@@ -17100,7 +17106,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q78">
         <v>12</v>
@@ -17306,7 +17312,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q79">
         <v>3.75</v>
@@ -17387,7 +17393,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ79">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR79">
         <v>1.25</v>
@@ -17512,7 +17518,7 @@
         <v>131</v>
       </c>
       <c r="P80" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17718,7 +17724,7 @@
         <v>132</v>
       </c>
       <c r="P81" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -18130,7 +18136,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q83">
         <v>1.67</v>
@@ -18623,7 +18629,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ85">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR85">
         <v>0.85</v>
@@ -18748,7 +18754,7 @@
         <v>134</v>
       </c>
       <c r="P86" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q86">
         <v>2.63</v>
@@ -19238,10 +19244,10 @@
         <v>1.83</v>
       </c>
       <c r="AP88">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ88">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR88">
         <v>1.18</v>
@@ -19856,7 +19862,7 @@
         <v>0.8</v>
       </c>
       <c r="AP91">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ91">
         <v>1.1</v>
@@ -20271,7 +20277,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ93">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR93">
         <v>1.8</v>
@@ -20396,7 +20402,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q94">
         <v>13</v>
@@ -20602,7 +20608,7 @@
         <v>139</v>
       </c>
       <c r="P95" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -20680,7 +20686,7 @@
         <v>0.33</v>
       </c>
       <c r="AP95">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ95">
         <v>1.09</v>
@@ -21014,7 +21020,7 @@
         <v>140</v>
       </c>
       <c r="P97" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q97">
         <v>2.4</v>
@@ -21301,7 +21307,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ98">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR98">
         <v>1.84</v>
@@ -21838,7 +21844,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -21916,7 +21922,7 @@
         <v>1.67</v>
       </c>
       <c r="AP101">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ101">
         <v>1.55</v>
@@ -22456,7 +22462,7 @@
         <v>145</v>
       </c>
       <c r="P104" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22662,7 +22668,7 @@
         <v>86</v>
       </c>
       <c r="P105" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -22868,7 +22874,7 @@
         <v>146</v>
       </c>
       <c r="P106" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q106">
         <v>6</v>
@@ -23155,7 +23161,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ107">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR107">
         <v>1.46</v>
@@ -23280,7 +23286,7 @@
         <v>147</v>
       </c>
       <c r="P108" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23358,7 +23364,7 @@
         <v>1.86</v>
       </c>
       <c r="AP108">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ108">
         <v>1.55</v>
@@ -23567,7 +23573,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ109">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR109">
         <v>1.64</v>
@@ -23692,7 +23698,7 @@
         <v>149</v>
       </c>
       <c r="P110" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -24104,7 +24110,7 @@
         <v>143</v>
       </c>
       <c r="P112" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q112">
         <v>4.75</v>
@@ -24182,7 +24188,7 @@
         <v>0.71</v>
       </c>
       <c r="AP112">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ112">
         <v>1.1</v>
@@ -24391,7 +24397,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ113">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR113">
         <v>1.41</v>
@@ -24928,7 +24934,7 @@
         <v>86</v>
       </c>
       <c r="P116" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q116">
         <v>4.5</v>
@@ -25006,7 +25012,7 @@
         <v>1.17</v>
       </c>
       <c r="AP116">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ116">
         <v>1.82</v>
@@ -25134,7 +25140,7 @@
         <v>153</v>
       </c>
       <c r="P117" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q117">
         <v>1.53</v>
@@ -25212,7 +25218,7 @@
         <v>1</v>
       </c>
       <c r="AP117">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ117">
         <v>1.36</v>
@@ -25340,7 +25346,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25546,7 +25552,7 @@
         <v>154</v>
       </c>
       <c r="P119" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q119">
         <v>1.8</v>
@@ -25752,7 +25758,7 @@
         <v>155</v>
       </c>
       <c r="P120" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q120">
         <v>7.5</v>
@@ -26039,7 +26045,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ121">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR121">
         <v>1.4</v>
@@ -26164,7 +26170,7 @@
         <v>157</v>
       </c>
       <c r="P122" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q122">
         <v>2.63</v>
@@ -26370,7 +26376,7 @@
         <v>158</v>
       </c>
       <c r="P123" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q123">
         <v>1.73</v>
@@ -26451,7 +26457,7 @@
         <v>2</v>
       </c>
       <c r="AQ123">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR123">
         <v>1.29</v>
@@ -26654,7 +26660,7 @@
         <v>0.71</v>
       </c>
       <c r="AP124">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ124">
         <v>1</v>
@@ -26860,7 +26866,7 @@
         <v>1.29</v>
       </c>
       <c r="AP125">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ125">
         <v>1.36</v>
@@ -26988,7 +26994,7 @@
         <v>86</v>
       </c>
       <c r="P126" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27066,7 +27072,7 @@
         <v>1.43</v>
       </c>
       <c r="AP126">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ126">
         <v>1.82</v>
@@ -27194,7 +27200,7 @@
         <v>161</v>
       </c>
       <c r="P127" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27400,7 +27406,7 @@
         <v>86</v>
       </c>
       <c r="P128" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q128">
         <v>2.4</v>
@@ -27606,7 +27612,7 @@
         <v>138</v>
       </c>
       <c r="P129" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27812,7 +27818,7 @@
         <v>98</v>
       </c>
       <c r="P130" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q130">
         <v>6.5</v>
@@ -28018,7 +28024,7 @@
         <v>162</v>
       </c>
       <c r="P131" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q131">
         <v>4.33</v>
@@ -28224,7 +28230,7 @@
         <v>86</v>
       </c>
       <c r="P132" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q132">
         <v>8</v>
@@ -29332,7 +29338,7 @@
         <v>1.13</v>
       </c>
       <c r="AP137">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ137">
         <v>1.36</v>
@@ -29747,7 +29753,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ139">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR139">
         <v>1.95</v>
@@ -29872,7 +29878,7 @@
         <v>167</v>
       </c>
       <c r="P140" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q140">
         <v>2.3</v>
@@ -29950,10 +29956,10 @@
         <v>0.5</v>
       </c>
       <c r="AP140">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ140">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR140">
         <v>1.34</v>
@@ -30078,7 +30084,7 @@
         <v>86</v>
       </c>
       <c r="P141" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q141">
         <v>7.5</v>
@@ -30284,7 +30290,7 @@
         <v>168</v>
       </c>
       <c r="P142" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30362,7 +30368,7 @@
         <v>1</v>
       </c>
       <c r="AP142">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ142">
         <v>1.1</v>
@@ -30490,7 +30496,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30571,7 +30577,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ143">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR143">
         <v>1.42</v>
@@ -30902,7 +30908,7 @@
         <v>171</v>
       </c>
       <c r="P145" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q145">
         <v>3.75</v>
@@ -31108,7 +31114,7 @@
         <v>172</v>
       </c>
       <c r="P146" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q146">
         <v>7.5</v>
@@ -31314,7 +31320,7 @@
         <v>173</v>
       </c>
       <c r="P147" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31520,7 +31526,7 @@
         <v>174</v>
       </c>
       <c r="P148" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q148">
         <v>2.75</v>
@@ -31726,7 +31732,7 @@
         <v>86</v>
       </c>
       <c r="P149" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q149">
         <v>7.5</v>
@@ -32138,7 +32144,7 @@
         <v>86</v>
       </c>
       <c r="P151" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q151">
         <v>6.5</v>
@@ -32344,7 +32350,7 @@
         <v>176</v>
       </c>
       <c r="P152" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q152">
         <v>2.75</v>
@@ -32550,7 +32556,7 @@
         <v>177</v>
       </c>
       <c r="P153" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q153">
         <v>4.75</v>
@@ -32837,7 +32843,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ154">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR154">
         <v>1.41</v>
@@ -32962,7 +32968,7 @@
         <v>179</v>
       </c>
       <c r="P155" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33043,7 +33049,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ155">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR155">
         <v>1.02</v>
@@ -33168,7 +33174,7 @@
         <v>176</v>
       </c>
       <c r="P156" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q156">
         <v>2.2</v>
@@ -33580,7 +33586,7 @@
         <v>181</v>
       </c>
       <c r="P158" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33658,7 +33664,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP158">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ158">
         <v>1</v>
@@ -33786,7 +33792,7 @@
         <v>182</v>
       </c>
       <c r="P159" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q159">
         <v>1.8</v>
@@ -33867,7 +33873,7 @@
         <v>2</v>
       </c>
       <c r="AQ159">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR159">
         <v>1.57</v>
@@ -34070,7 +34076,7 @@
         <v>2.78</v>
       </c>
       <c r="AP160">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ160">
         <v>2.5</v>
@@ -34276,7 +34282,7 @@
         <v>1</v>
       </c>
       <c r="AP161">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ161">
         <v>1</v>
@@ -34404,7 +34410,7 @@
         <v>86</v>
       </c>
       <c r="P162" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q162">
         <v>3.5</v>
@@ -34610,7 +34616,7 @@
         <v>184</v>
       </c>
       <c r="P163" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35022,7 +35028,7 @@
         <v>185</v>
       </c>
       <c r="P165" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q165">
         <v>9.5</v>
@@ -35813,7 +35819,7 @@
         <v>69</v>
       </c>
       <c r="E169" s="2">
-        <v>45705.52083333334</v>
+        <v>45705.54166666666</v>
       </c>
       <c r="F169">
         <v>21</v>
@@ -35828,10 +35834,10 @@
         <v>0</v>
       </c>
       <c r="J169">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K169">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L169">
         <v>1</v>
@@ -35846,7 +35852,7 @@
         <v>188</v>
       </c>
       <c r="P169" t="s">
-        <v>270</v>
+        <v>188</v>
       </c>
       <c r="Q169">
         <v>2.88</v>
@@ -36003,6 +36009,624 @@
       </c>
       <c r="BP169">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="170" spans="1:68">
+      <c r="A170" s="1">
+        <v>169</v>
+      </c>
+      <c r="B170">
+        <v>7762762</v>
+      </c>
+      <c r="C170" t="s">
+        <v>68</v>
+      </c>
+      <c r="D170" t="s">
+        <v>69</v>
+      </c>
+      <c r="E170" s="2">
+        <v>45709.32291666666</v>
+      </c>
+      <c r="F170">
+        <v>22</v>
+      </c>
+      <c r="G170" t="s">
+        <v>81</v>
+      </c>
+      <c r="H170" t="s">
+        <v>74</v>
+      </c>
+      <c r="I170">
+        <v>0</v>
+      </c>
+      <c r="J170">
+        <v>0</v>
+      </c>
+      <c r="K170">
+        <v>0</v>
+      </c>
+      <c r="L170">
+        <v>1</v>
+      </c>
+      <c r="M170">
+        <v>0</v>
+      </c>
+      <c r="N170">
+        <v>1</v>
+      </c>
+      <c r="O170" t="s">
+        <v>189</v>
+      </c>
+      <c r="P170" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q170">
+        <v>2.05</v>
+      </c>
+      <c r="R170">
+        <v>2.25</v>
+      </c>
+      <c r="S170">
+        <v>6.5</v>
+      </c>
+      <c r="T170">
+        <v>1.4</v>
+      </c>
+      <c r="U170">
+        <v>2.75</v>
+      </c>
+      <c r="V170">
+        <v>2.75</v>
+      </c>
+      <c r="W170">
+        <v>1.4</v>
+      </c>
+      <c r="X170">
+        <v>8</v>
+      </c>
+      <c r="Y170">
+        <v>1.08</v>
+      </c>
+      <c r="Z170">
+        <v>1.49</v>
+      </c>
+      <c r="AA170">
+        <v>4.3</v>
+      </c>
+      <c r="AB170">
+        <v>5.9</v>
+      </c>
+      <c r="AC170">
+        <v>1.03</v>
+      </c>
+      <c r="AD170">
+        <v>9</v>
+      </c>
+      <c r="AE170">
+        <v>1.28</v>
+      </c>
+      <c r="AF170">
+        <v>3.45</v>
+      </c>
+      <c r="AG170">
+        <v>1.87</v>
+      </c>
+      <c r="AH170">
+        <v>1.87</v>
+      </c>
+      <c r="AI170">
+        <v>2</v>
+      </c>
+      <c r="AJ170">
+        <v>1.73</v>
+      </c>
+      <c r="AK170">
+        <v>1.12</v>
+      </c>
+      <c r="AL170">
+        <v>1.19</v>
+      </c>
+      <c r="AM170">
+        <v>2.42</v>
+      </c>
+      <c r="AN170">
+        <v>0.8</v>
+      </c>
+      <c r="AO170">
+        <v>0.5</v>
+      </c>
+      <c r="AP170">
+        <v>1</v>
+      </c>
+      <c r="AQ170">
+        <v>0.45</v>
+      </c>
+      <c r="AR170">
+        <v>1.7</v>
+      </c>
+      <c r="AS170">
+        <v>0.93</v>
+      </c>
+      <c r="AT170">
+        <v>2.63</v>
+      </c>
+      <c r="AU170">
+        <v>8</v>
+      </c>
+      <c r="AV170">
+        <v>3</v>
+      </c>
+      <c r="AW170">
+        <v>6</v>
+      </c>
+      <c r="AX170">
+        <v>6</v>
+      </c>
+      <c r="AY170">
+        <v>14</v>
+      </c>
+      <c r="AZ170">
+        <v>9</v>
+      </c>
+      <c r="BA170">
+        <v>11</v>
+      </c>
+      <c r="BB170">
+        <v>6</v>
+      </c>
+      <c r="BC170">
+        <v>17</v>
+      </c>
+      <c r="BD170">
+        <v>1.38</v>
+      </c>
+      <c r="BE170">
+        <v>7.5</v>
+      </c>
+      <c r="BF170">
+        <v>3.4</v>
+      </c>
+      <c r="BG170">
+        <v>1.29</v>
+      </c>
+      <c r="BH170">
+        <v>3.15</v>
+      </c>
+      <c r="BI170">
+        <v>1.5</v>
+      </c>
+      <c r="BJ170">
+        <v>2.38</v>
+      </c>
+      <c r="BK170">
+        <v>1.82</v>
+      </c>
+      <c r="BL170">
+        <v>1.86</v>
+      </c>
+      <c r="BM170">
+        <v>2.3</v>
+      </c>
+      <c r="BN170">
+        <v>1.53</v>
+      </c>
+      <c r="BO170">
+        <v>2.95</v>
+      </c>
+      <c r="BP170">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="171" spans="1:68">
+      <c r="A171" s="1">
+        <v>170</v>
+      </c>
+      <c r="B171">
+        <v>7762766</v>
+      </c>
+      <c r="C171" t="s">
+        <v>68</v>
+      </c>
+      <c r="D171" t="s">
+        <v>69</v>
+      </c>
+      <c r="E171" s="2">
+        <v>45709.42708333334</v>
+      </c>
+      <c r="F171">
+        <v>22</v>
+      </c>
+      <c r="G171" t="s">
+        <v>83</v>
+      </c>
+      <c r="H171" t="s">
+        <v>76</v>
+      </c>
+      <c r="I171">
+        <v>1</v>
+      </c>
+      <c r="J171">
+        <v>1</v>
+      </c>
+      <c r="K171">
+        <v>2</v>
+      </c>
+      <c r="L171">
+        <v>2</v>
+      </c>
+      <c r="M171">
+        <v>1</v>
+      </c>
+      <c r="N171">
+        <v>3</v>
+      </c>
+      <c r="O171" t="s">
+        <v>190</v>
+      </c>
+      <c r="P171" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q171">
+        <v>2.25</v>
+      </c>
+      <c r="R171">
+        <v>2.1</v>
+      </c>
+      <c r="S171">
+        <v>6.5</v>
+      </c>
+      <c r="T171">
+        <v>1.5</v>
+      </c>
+      <c r="U171">
+        <v>2.5</v>
+      </c>
+      <c r="V171">
+        <v>3.4</v>
+      </c>
+      <c r="W171">
+        <v>1.3</v>
+      </c>
+      <c r="X171">
+        <v>10</v>
+      </c>
+      <c r="Y171">
+        <v>1.06</v>
+      </c>
+      <c r="Z171">
+        <v>1.53</v>
+      </c>
+      <c r="AA171">
+        <v>4.2</v>
+      </c>
+      <c r="AB171">
+        <v>5.7</v>
+      </c>
+      <c r="AC171">
+        <v>1.01</v>
+      </c>
+      <c r="AD171">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE171">
+        <v>1.41</v>
+      </c>
+      <c r="AF171">
+        <v>2.8</v>
+      </c>
+      <c r="AG171">
+        <v>2.1</v>
+      </c>
+      <c r="AH171">
+        <v>1.6</v>
+      </c>
+      <c r="AI171">
+        <v>2.25</v>
+      </c>
+      <c r="AJ171">
+        <v>1.57</v>
+      </c>
+      <c r="AK171">
+        <v>1.13</v>
+      </c>
+      <c r="AL171">
+        <v>1.23</v>
+      </c>
+      <c r="AM171">
+        <v>2.2</v>
+      </c>
+      <c r="AN171">
+        <v>1.4</v>
+      </c>
+      <c r="AO171">
+        <v>0.3</v>
+      </c>
+      <c r="AP171">
+        <v>1.55</v>
+      </c>
+      <c r="AQ171">
+        <v>0.27</v>
+      </c>
+      <c r="AR171">
+        <v>1.57</v>
+      </c>
+      <c r="AS171">
+        <v>0.93</v>
+      </c>
+      <c r="AT171">
+        <v>2.5</v>
+      </c>
+      <c r="AU171">
+        <v>9</v>
+      </c>
+      <c r="AV171">
+        <v>5</v>
+      </c>
+      <c r="AW171">
+        <v>5</v>
+      </c>
+      <c r="AX171">
+        <v>4</v>
+      </c>
+      <c r="AY171">
+        <v>14</v>
+      </c>
+      <c r="AZ171">
+        <v>9</v>
+      </c>
+      <c r="BA171">
+        <v>10</v>
+      </c>
+      <c r="BB171">
+        <v>3</v>
+      </c>
+      <c r="BC171">
+        <v>13</v>
+      </c>
+      <c r="BD171">
+        <v>1.3</v>
+      </c>
+      <c r="BE171">
+        <v>7</v>
+      </c>
+      <c r="BF171">
+        <v>3.9</v>
+      </c>
+      <c r="BG171">
+        <v>1.5</v>
+      </c>
+      <c r="BH171">
+        <v>2.35</v>
+      </c>
+      <c r="BI171">
+        <v>1.83</v>
+      </c>
+      <c r="BJ171">
+        <v>1.85</v>
+      </c>
+      <c r="BK171">
+        <v>2.33</v>
+      </c>
+      <c r="BL171">
+        <v>1.52</v>
+      </c>
+      <c r="BM171">
+        <v>3.05</v>
+      </c>
+      <c r="BN171">
+        <v>1.32</v>
+      </c>
+      <c r="BO171">
+        <v>4.1</v>
+      </c>
+      <c r="BP171">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="172" spans="1:68">
+      <c r="A172" s="1">
+        <v>171</v>
+      </c>
+      <c r="B172">
+        <v>7762767</v>
+      </c>
+      <c r="C172" t="s">
+        <v>68</v>
+      </c>
+      <c r="D172" t="s">
+        <v>69</v>
+      </c>
+      <c r="E172" s="2">
+        <v>45709.53125</v>
+      </c>
+      <c r="F172">
+        <v>22</v>
+      </c>
+      <c r="G172" t="s">
+        <v>79</v>
+      </c>
+      <c r="H172" t="s">
+        <v>84</v>
+      </c>
+      <c r="I172">
+        <v>1</v>
+      </c>
+      <c r="J172">
+        <v>0</v>
+      </c>
+      <c r="K172">
+        <v>1</v>
+      </c>
+      <c r="L172">
+        <v>2</v>
+      </c>
+      <c r="M172">
+        <v>0</v>
+      </c>
+      <c r="N172">
+        <v>2</v>
+      </c>
+      <c r="O172" t="s">
+        <v>191</v>
+      </c>
+      <c r="P172" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q172">
+        <v>1.83</v>
+      </c>
+      <c r="R172">
+        <v>2.38</v>
+      </c>
+      <c r="S172">
+        <v>9</v>
+      </c>
+      <c r="T172">
+        <v>1.4</v>
+      </c>
+      <c r="U172">
+        <v>2.75</v>
+      </c>
+      <c r="V172">
+        <v>2.75</v>
+      </c>
+      <c r="W172">
+        <v>1.4</v>
+      </c>
+      <c r="X172">
+        <v>8</v>
+      </c>
+      <c r="Y172">
+        <v>1.08</v>
+      </c>
+      <c r="Z172">
+        <v>1.3</v>
+      </c>
+      <c r="AA172">
+        <v>5</v>
+      </c>
+      <c r="AB172">
+        <v>10</v>
+      </c>
+      <c r="AC172">
+        <v>1.01</v>
+      </c>
+      <c r="AD172">
+        <v>9</v>
+      </c>
+      <c r="AE172">
+        <v>1.28</v>
+      </c>
+      <c r="AF172">
+        <v>3.45</v>
+      </c>
+      <c r="AG172">
+        <v>1.82</v>
+      </c>
+      <c r="AH172">
+        <v>1.92</v>
+      </c>
+      <c r="AI172">
+        <v>2.38</v>
+      </c>
+      <c r="AJ172">
+        <v>1.53</v>
+      </c>
+      <c r="AK172">
+        <v>1.07</v>
+      </c>
+      <c r="AL172">
+        <v>1.15</v>
+      </c>
+      <c r="AM172">
+        <v>2.9</v>
+      </c>
+      <c r="AN172">
+        <v>2.4</v>
+      </c>
+      <c r="AO172">
+        <v>1.5</v>
+      </c>
+      <c r="AP172">
+        <v>2.45</v>
+      </c>
+      <c r="AQ172">
+        <v>1.36</v>
+      </c>
+      <c r="AR172">
+        <v>2.02</v>
+      </c>
+      <c r="AS172">
+        <v>1.19</v>
+      </c>
+      <c r="AT172">
+        <v>3.21</v>
+      </c>
+      <c r="AU172">
+        <v>11</v>
+      </c>
+      <c r="AV172">
+        <v>2</v>
+      </c>
+      <c r="AW172">
+        <v>8</v>
+      </c>
+      <c r="AX172">
+        <v>4</v>
+      </c>
+      <c r="AY172">
+        <v>19</v>
+      </c>
+      <c r="AZ172">
+        <v>6</v>
+      </c>
+      <c r="BA172">
+        <v>8</v>
+      </c>
+      <c r="BB172">
+        <v>3</v>
+      </c>
+      <c r="BC172">
+        <v>11</v>
+      </c>
+      <c r="BD172">
+        <v>1.3</v>
+      </c>
+      <c r="BE172">
+        <v>7.5</v>
+      </c>
+      <c r="BF172">
+        <v>3.9</v>
+      </c>
+      <c r="BG172">
+        <v>1.43</v>
+      </c>
+      <c r="BH172">
+        <v>2.6</v>
+      </c>
+      <c r="BI172">
+        <v>1.72</v>
+      </c>
+      <c r="BJ172">
+        <v>1.98</v>
+      </c>
+      <c r="BK172">
+        <v>2.15</v>
+      </c>
+      <c r="BL172">
+        <v>1.61</v>
+      </c>
+      <c r="BM172">
+        <v>2.75</v>
+      </c>
+      <c r="BN172">
+        <v>1.38</v>
+      </c>
+      <c r="BO172">
+        <v>3.65</v>
+      </c>
+      <c r="BP172">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="275">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -592,6 +592,9 @@
     <t>['17', '90+4']</t>
   </si>
   <si>
+    <t>['43']</t>
+  </si>
+  <si>
     <t>['12', '22', '45+1', '45+4', '90+1', '90+8']</t>
   </si>
   <si>
@@ -833,6 +836,9 @@
   </si>
   <si>
     <t>['12', '21', '58', '60']</t>
+  </si>
+  <si>
+    <t>['8', '47', '60']</t>
   </si>
 </sst>
 </file>
@@ -1194,7 +1200,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP172"/>
+  <dimension ref="A1:BP175"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1528,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ2">
         <v>1.27</v>
@@ -1737,7 +1743,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ3">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2068,7 +2074,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q5">
         <v>7.5</v>
@@ -2274,7 +2280,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2561,7 +2567,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ7">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2686,7 +2692,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q8">
         <v>4</v>
@@ -3176,7 +3182,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ10">
         <v>1</v>
@@ -3716,7 +3722,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3922,7 +3928,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q14">
         <v>2.4</v>
@@ -4000,7 +4006,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ14">
         <v>1.1</v>
@@ -4412,7 +4418,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
         <v>1.36</v>
@@ -4621,7 +4627,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ17">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR17">
         <v>1.12</v>
@@ -4746,7 +4752,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -5033,7 +5039,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ19">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5158,7 +5164,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -5364,7 +5370,7 @@
         <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5570,7 +5576,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5776,7 +5782,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -5982,7 +5988,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q24">
         <v>3.25</v>
@@ -6188,7 +6194,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q25">
         <v>2.05</v>
@@ -6266,7 +6272,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ25">
         <v>0.27</v>
@@ -6394,7 +6400,7 @@
         <v>86</v>
       </c>
       <c r="P26" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -7012,7 +7018,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7090,7 +7096,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ29">
         <v>0.45</v>
@@ -7424,7 +7430,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7630,7 +7636,7 @@
         <v>86</v>
       </c>
       <c r="P32" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q32">
         <v>2.05</v>
@@ -7711,7 +7717,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ32">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR32">
         <v>2.55</v>
@@ -8660,7 +8666,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -9356,10 +9362,10 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ40">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR40">
         <v>1.4</v>
@@ -9484,7 +9490,7 @@
         <v>86</v>
       </c>
       <c r="P41" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q41">
         <v>2.38</v>
@@ -9562,7 +9568,7 @@
         <v>1.33</v>
       </c>
       <c r="AP41">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ41">
         <v>1.36</v>
@@ -9771,7 +9777,7 @@
         <v>1</v>
       </c>
       <c r="AQ42">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR42">
         <v>1.54</v>
@@ -9896,7 +9902,7 @@
         <v>86</v>
       </c>
       <c r="P43" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q43">
         <v>7.5</v>
@@ -9977,7 +9983,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ43">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR43">
         <v>1.51</v>
@@ -10102,7 +10108,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10386,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ45">
         <v>1</v>
@@ -10514,7 +10520,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q46">
         <v>2.5</v>
@@ -10720,7 +10726,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q47">
         <v>4.33</v>
@@ -10926,7 +10932,7 @@
         <v>86</v>
       </c>
       <c r="P48" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q48">
         <v>2.4</v>
@@ -11544,7 +11550,7 @@
         <v>116</v>
       </c>
       <c r="P51" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11750,7 +11756,7 @@
         <v>118</v>
       </c>
       <c r="P52" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q52">
         <v>5.5</v>
@@ -12162,7 +12168,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -12574,7 +12580,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q56">
         <v>5.5</v>
@@ -12655,7 +12661,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ56">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR56">
         <v>1.1</v>
@@ -12780,7 +12786,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q57">
         <v>5</v>
@@ -12986,7 +12992,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13064,7 +13070,7 @@
         <v>0.25</v>
       </c>
       <c r="AP58">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ58">
         <v>1.09</v>
@@ -13192,7 +13198,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13398,7 +13404,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13479,7 +13485,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ60">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR60">
         <v>1.59</v>
@@ -13604,7 +13610,7 @@
         <v>86</v>
       </c>
       <c r="P61" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q61">
         <v>6.5</v>
@@ -13685,7 +13691,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ61">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR61">
         <v>1.06</v>
@@ -13810,7 +13816,7 @@
         <v>86</v>
       </c>
       <c r="P62" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q62">
         <v>7</v>
@@ -13891,7 +13897,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ62">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR62">
         <v>1.3</v>
@@ -14016,7 +14022,7 @@
         <v>86</v>
       </c>
       <c r="P63" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q63">
         <v>3.5</v>
@@ -14222,7 +14228,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14840,7 +14846,7 @@
         <v>86</v>
       </c>
       <c r="P67" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q67">
         <v>6.5</v>
@@ -15046,7 +15052,7 @@
         <v>86</v>
       </c>
       <c r="P68" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q68">
         <v>4.75</v>
@@ -15536,7 +15542,7 @@
         <v>3</v>
       </c>
       <c r="AP70">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ70">
         <v>1.91</v>
@@ -15664,7 +15670,7 @@
         <v>92</v>
       </c>
       <c r="P71" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q71">
         <v>9.5</v>
@@ -16157,7 +16163,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ73">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR73">
         <v>1.15</v>
@@ -16282,7 +16288,7 @@
         <v>86</v>
       </c>
       <c r="P74" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16566,10 +16572,10 @@
         <v>0.75</v>
       </c>
       <c r="AP75">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ75">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR75">
         <v>1.99</v>
@@ -16900,7 +16906,7 @@
         <v>130</v>
       </c>
       <c r="P77" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q77">
         <v>1.83</v>
@@ -17106,7 +17112,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q78">
         <v>12</v>
@@ -17187,7 +17193,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ78">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR78">
         <v>1.46</v>
@@ -17312,7 +17318,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q79">
         <v>3.75</v>
@@ -17518,7 +17524,7 @@
         <v>131</v>
       </c>
       <c r="P80" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17724,7 +17730,7 @@
         <v>132</v>
       </c>
       <c r="P81" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -17802,7 +17808,7 @@
         <v>1.8</v>
       </c>
       <c r="AP81">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ81">
         <v>1.55</v>
@@ -18136,7 +18142,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q83">
         <v>1.67</v>
@@ -18420,7 +18426,7 @@
         <v>2.17</v>
       </c>
       <c r="AP84">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ84">
         <v>2</v>
@@ -18754,7 +18760,7 @@
         <v>134</v>
       </c>
       <c r="P86" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q86">
         <v>2.63</v>
@@ -19865,7 +19871,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ91">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR91">
         <v>1.91</v>
@@ -20068,10 +20074,10 @@
         <v>0.67</v>
       </c>
       <c r="AP92">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ92">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR92">
         <v>1.22</v>
@@ -20274,7 +20280,7 @@
         <v>0.4</v>
       </c>
       <c r="AP93">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ93">
         <v>0.27</v>
@@ -20402,7 +20408,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q94">
         <v>13</v>
@@ -20483,7 +20489,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ94">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR94">
         <v>1.21</v>
@@ -20608,7 +20614,7 @@
         <v>139</v>
       </c>
       <c r="P95" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -21020,7 +21026,7 @@
         <v>140</v>
       </c>
       <c r="P97" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q97">
         <v>2.4</v>
@@ -21510,7 +21516,7 @@
         <v>1.2</v>
       </c>
       <c r="AP99">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ99">
         <v>1.36</v>
@@ -21716,7 +21722,7 @@
         <v>1.4</v>
       </c>
       <c r="AP100">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ100">
         <v>1.82</v>
@@ -21844,7 +21850,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22462,7 +22468,7 @@
         <v>145</v>
       </c>
       <c r="P104" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22543,7 +22549,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ104">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR104">
         <v>1.26</v>
@@ -22668,7 +22674,7 @@
         <v>86</v>
       </c>
       <c r="P105" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -22874,7 +22880,7 @@
         <v>146</v>
       </c>
       <c r="P106" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q106">
         <v>6</v>
@@ -22955,7 +22961,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ106">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR106">
         <v>1.32</v>
@@ -23286,7 +23292,7 @@
         <v>147</v>
       </c>
       <c r="P108" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23698,7 +23704,7 @@
         <v>149</v>
       </c>
       <c r="P110" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23776,7 +23782,7 @@
         <v>1.86</v>
       </c>
       <c r="AP110">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ110">
         <v>2</v>
@@ -24110,7 +24116,7 @@
         <v>143</v>
       </c>
       <c r="P112" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q112">
         <v>4.75</v>
@@ -24191,7 +24197,7 @@
         <v>1</v>
       </c>
       <c r="AQ112">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR112">
         <v>1.48</v>
@@ -24394,7 +24400,7 @@
         <v>0.67</v>
       </c>
       <c r="AP113">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ113">
         <v>0.45</v>
@@ -24600,7 +24606,7 @@
         <v>0.83</v>
       </c>
       <c r="AP114">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ114">
         <v>1</v>
@@ -24934,7 +24940,7 @@
         <v>86</v>
       </c>
       <c r="P116" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q116">
         <v>4.5</v>
@@ -25140,7 +25146,7 @@
         <v>153</v>
       </c>
       <c r="P117" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q117">
         <v>1.53</v>
@@ -25346,7 +25352,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25552,7 +25558,7 @@
         <v>154</v>
       </c>
       <c r="P119" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q119">
         <v>1.8</v>
@@ -25758,7 +25764,7 @@
         <v>155</v>
       </c>
       <c r="P120" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q120">
         <v>7.5</v>
@@ -25839,7 +25845,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ120">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR120">
         <v>1.46</v>
@@ -26170,7 +26176,7 @@
         <v>157</v>
       </c>
       <c r="P122" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q122">
         <v>2.63</v>
@@ -26248,7 +26254,7 @@
         <v>1.14</v>
       </c>
       <c r="AP122">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ122">
         <v>1.1</v>
@@ -26376,7 +26382,7 @@
         <v>158</v>
       </c>
       <c r="P123" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q123">
         <v>1.73</v>
@@ -26454,7 +26460,7 @@
         <v>0.57</v>
       </c>
       <c r="AP123">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ123">
         <v>0.45</v>
@@ -26994,7 +27000,7 @@
         <v>86</v>
       </c>
       <c r="P126" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27200,7 +27206,7 @@
         <v>161</v>
       </c>
       <c r="P127" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27281,7 +27287,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ127">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR127">
         <v>2.03</v>
@@ -27406,7 +27412,7 @@
         <v>86</v>
       </c>
       <c r="P128" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q128">
         <v>2.4</v>
@@ -27612,7 +27618,7 @@
         <v>138</v>
       </c>
       <c r="P129" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27818,7 +27824,7 @@
         <v>98</v>
       </c>
       <c r="P130" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q130">
         <v>6.5</v>
@@ -28024,7 +28030,7 @@
         <v>162</v>
       </c>
       <c r="P131" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q131">
         <v>4.33</v>
@@ -28230,7 +28236,7 @@
         <v>86</v>
       </c>
       <c r="P132" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q132">
         <v>8</v>
@@ -28517,7 +28523,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ133">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR133">
         <v>0.99</v>
@@ -29135,7 +29141,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ136">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR136">
         <v>1.69</v>
@@ -29544,7 +29550,7 @@
         <v>0.63</v>
       </c>
       <c r="AP138">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ138">
         <v>1</v>
@@ -29878,7 +29884,7 @@
         <v>167</v>
       </c>
       <c r="P140" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q140">
         <v>2.3</v>
@@ -30084,7 +30090,7 @@
         <v>86</v>
       </c>
       <c r="P141" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q141">
         <v>7.5</v>
@@ -30162,10 +30168,10 @@
         <v>2.71</v>
       </c>
       <c r="AP141">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ141">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR141">
         <v>1.45</v>
@@ -30290,7 +30296,7 @@
         <v>168</v>
       </c>
       <c r="P142" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30496,7 +30502,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30780,7 +30786,7 @@
         <v>1.13</v>
       </c>
       <c r="AP144">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ144">
         <v>1</v>
@@ -30908,7 +30914,7 @@
         <v>171</v>
       </c>
       <c r="P145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q145">
         <v>3.75</v>
@@ -31114,7 +31120,7 @@
         <v>172</v>
       </c>
       <c r="P146" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q146">
         <v>7.5</v>
@@ -31320,7 +31326,7 @@
         <v>173</v>
       </c>
       <c r="P147" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31526,7 +31532,7 @@
         <v>174</v>
       </c>
       <c r="P148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q148">
         <v>2.75</v>
@@ -31732,7 +31738,7 @@
         <v>86</v>
       </c>
       <c r="P149" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q149">
         <v>7.5</v>
@@ -32144,7 +32150,7 @@
         <v>86</v>
       </c>
       <c r="P151" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q151">
         <v>6.5</v>
@@ -32350,7 +32356,7 @@
         <v>176</v>
       </c>
       <c r="P152" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q152">
         <v>2.75</v>
@@ -32431,7 +32437,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ152">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR152">
         <v>1.47</v>
@@ -32556,7 +32562,7 @@
         <v>177</v>
       </c>
       <c r="P153" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q153">
         <v>4.75</v>
@@ -32634,10 +32640,10 @@
         <v>2.75</v>
       </c>
       <c r="AP153">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ153">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR153">
         <v>1.54</v>
@@ -32840,7 +32846,7 @@
         <v>1.56</v>
       </c>
       <c r="AP154">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ154">
         <v>1.36</v>
@@ -32968,7 +32974,7 @@
         <v>179</v>
       </c>
       <c r="P155" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33174,7 +33180,7 @@
         <v>176</v>
       </c>
       <c r="P156" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q156">
         <v>2.2</v>
@@ -33252,7 +33258,7 @@
         <v>0.89</v>
       </c>
       <c r="AP156">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ156">
         <v>1.1</v>
@@ -33461,7 +33467,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ157">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR157">
         <v>1.48</v>
@@ -33586,7 +33592,7 @@
         <v>181</v>
       </c>
       <c r="P158" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33792,7 +33798,7 @@
         <v>182</v>
       </c>
       <c r="P159" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q159">
         <v>1.8</v>
@@ -33870,7 +33876,7 @@
         <v>0.22</v>
       </c>
       <c r="AP159">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ159">
         <v>0.27</v>
@@ -34079,7 +34085,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ160">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AR160">
         <v>2.11</v>
@@ -34410,7 +34416,7 @@
         <v>86</v>
       </c>
       <c r="P162" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q162">
         <v>3.5</v>
@@ -34616,7 +34622,7 @@
         <v>184</v>
       </c>
       <c r="P163" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35028,7 +35034,7 @@
         <v>185</v>
       </c>
       <c r="P165" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q165">
         <v>9.5</v>
@@ -36627,6 +36633,624 @@
       </c>
       <c r="BP172">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="173" spans="1:68">
+      <c r="A173" s="1">
+        <v>172</v>
+      </c>
+      <c r="B173">
+        <v>7762769</v>
+      </c>
+      <c r="C173" t="s">
+        <v>68</v>
+      </c>
+      <c r="D173" t="s">
+        <v>69</v>
+      </c>
+      <c r="E173" s="2">
+        <v>45710.3125</v>
+      </c>
+      <c r="F173">
+        <v>22</v>
+      </c>
+      <c r="G173" t="s">
+        <v>78</v>
+      </c>
+      <c r="H173" t="s">
+        <v>85</v>
+      </c>
+      <c r="I173">
+        <v>1</v>
+      </c>
+      <c r="J173">
+        <v>0</v>
+      </c>
+      <c r="K173">
+        <v>1</v>
+      </c>
+      <c r="L173">
+        <v>1</v>
+      </c>
+      <c r="M173">
+        <v>1</v>
+      </c>
+      <c r="N173">
+        <v>2</v>
+      </c>
+      <c r="O173" t="s">
+        <v>192</v>
+      </c>
+      <c r="P173" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q173">
+        <v>2.63</v>
+      </c>
+      <c r="R173">
+        <v>2.05</v>
+      </c>
+      <c r="S173">
+        <v>4.75</v>
+      </c>
+      <c r="T173">
+        <v>1.5</v>
+      </c>
+      <c r="U173">
+        <v>2.5</v>
+      </c>
+      <c r="V173">
+        <v>3.4</v>
+      </c>
+      <c r="W173">
+        <v>1.3</v>
+      </c>
+      <c r="X173">
+        <v>10</v>
+      </c>
+      <c r="Y173">
+        <v>1.06</v>
+      </c>
+      <c r="Z173">
+        <v>2</v>
+      </c>
+      <c r="AA173">
+        <v>3.3</v>
+      </c>
+      <c r="AB173">
+        <v>3.75</v>
+      </c>
+      <c r="AC173">
+        <v>1.03</v>
+      </c>
+      <c r="AD173">
+        <v>7.7</v>
+      </c>
+      <c r="AE173">
+        <v>1.4</v>
+      </c>
+      <c r="AF173">
+        <v>2.8</v>
+      </c>
+      <c r="AG173">
+        <v>2.15</v>
+      </c>
+      <c r="AH173">
+        <v>1.6</v>
+      </c>
+      <c r="AI173">
+        <v>2</v>
+      </c>
+      <c r="AJ173">
+        <v>1.73</v>
+      </c>
+      <c r="AK173">
+        <v>1.25</v>
+      </c>
+      <c r="AL173">
+        <v>1.29</v>
+      </c>
+      <c r="AM173">
+        <v>1.73</v>
+      </c>
+      <c r="AN173">
+        <v>2.3</v>
+      </c>
+      <c r="AO173">
+        <v>0.7</v>
+      </c>
+      <c r="AP173">
+        <v>2.18</v>
+      </c>
+      <c r="AQ173">
+        <v>0.73</v>
+      </c>
+      <c r="AR173">
+        <v>1.43</v>
+      </c>
+      <c r="AS173">
+        <v>1.51</v>
+      </c>
+      <c r="AT173">
+        <v>2.94</v>
+      </c>
+      <c r="AU173">
+        <v>5</v>
+      </c>
+      <c r="AV173">
+        <v>3</v>
+      </c>
+      <c r="AW173">
+        <v>12</v>
+      </c>
+      <c r="AX173">
+        <v>2</v>
+      </c>
+      <c r="AY173">
+        <v>17</v>
+      </c>
+      <c r="AZ173">
+        <v>5</v>
+      </c>
+      <c r="BA173">
+        <v>4</v>
+      </c>
+      <c r="BB173">
+        <v>4</v>
+      </c>
+      <c r="BC173">
+        <v>8</v>
+      </c>
+      <c r="BD173">
+        <v>1.61</v>
+      </c>
+      <c r="BE173">
+        <v>6.5</v>
+      </c>
+      <c r="BF173">
+        <v>2.55</v>
+      </c>
+      <c r="BG173">
+        <v>1.47</v>
+      </c>
+      <c r="BH173">
+        <v>2.48</v>
+      </c>
+      <c r="BI173">
+        <v>1.77</v>
+      </c>
+      <c r="BJ173">
+        <v>1.92</v>
+      </c>
+      <c r="BK173">
+        <v>2.23</v>
+      </c>
+      <c r="BL173">
+        <v>1.56</v>
+      </c>
+      <c r="BM173">
+        <v>2.9</v>
+      </c>
+      <c r="BN173">
+        <v>1.34</v>
+      </c>
+      <c r="BO173">
+        <v>3.9</v>
+      </c>
+      <c r="BP173">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="174" spans="1:68">
+      <c r="A174" s="1">
+        <v>173</v>
+      </c>
+      <c r="B174">
+        <v>7762768</v>
+      </c>
+      <c r="C174" t="s">
+        <v>68</v>
+      </c>
+      <c r="D174" t="s">
+        <v>69</v>
+      </c>
+      <c r="E174" s="2">
+        <v>45710.41666666666</v>
+      </c>
+      <c r="F174">
+        <v>22</v>
+      </c>
+      <c r="G174" t="s">
+        <v>82</v>
+      </c>
+      <c r="H174" t="s">
+        <v>80</v>
+      </c>
+      <c r="I174">
+        <v>0</v>
+      </c>
+      <c r="J174">
+        <v>1</v>
+      </c>
+      <c r="K174">
+        <v>1</v>
+      </c>
+      <c r="L174">
+        <v>0</v>
+      </c>
+      <c r="M174">
+        <v>3</v>
+      </c>
+      <c r="N174">
+        <v>3</v>
+      </c>
+      <c r="O174" t="s">
+        <v>86</v>
+      </c>
+      <c r="P174" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q174">
+        <v>3.75</v>
+      </c>
+      <c r="R174">
+        <v>2.05</v>
+      </c>
+      <c r="S174">
+        <v>3.1</v>
+      </c>
+      <c r="T174">
+        <v>1.44</v>
+      </c>
+      <c r="U174">
+        <v>2.63</v>
+      </c>
+      <c r="V174">
+        <v>3.4</v>
+      </c>
+      <c r="W174">
+        <v>1.3</v>
+      </c>
+      <c r="X174">
+        <v>10</v>
+      </c>
+      <c r="Y174">
+        <v>1.06</v>
+      </c>
+      <c r="Z174">
+        <v>2.68</v>
+      </c>
+      <c r="AA174">
+        <v>3.08</v>
+      </c>
+      <c r="AB174">
+        <v>2.68</v>
+      </c>
+      <c r="AC174">
+        <v>1.02</v>
+      </c>
+      <c r="AD174">
+        <v>7.7</v>
+      </c>
+      <c r="AE174">
+        <v>1.4</v>
+      </c>
+      <c r="AF174">
+        <v>2.8</v>
+      </c>
+      <c r="AG174">
+        <v>2.1</v>
+      </c>
+      <c r="AH174">
+        <v>1.61</v>
+      </c>
+      <c r="AI174">
+        <v>1.83</v>
+      </c>
+      <c r="AJ174">
+        <v>1.83</v>
+      </c>
+      <c r="AK174">
+        <v>1.53</v>
+      </c>
+      <c r="AL174">
+        <v>1.3</v>
+      </c>
+      <c r="AM174">
+        <v>1.37</v>
+      </c>
+      <c r="AN174">
+        <v>2</v>
+      </c>
+      <c r="AO174">
+        <v>1.1</v>
+      </c>
+      <c r="AP174">
+        <v>1.82</v>
+      </c>
+      <c r="AQ174">
+        <v>1.27</v>
+      </c>
+      <c r="AR174">
+        <v>1.58</v>
+      </c>
+      <c r="AS174">
+        <v>1.63</v>
+      </c>
+      <c r="AT174">
+        <v>3.21</v>
+      </c>
+      <c r="AU174">
+        <v>6</v>
+      </c>
+      <c r="AV174">
+        <v>7</v>
+      </c>
+      <c r="AW174">
+        <v>2</v>
+      </c>
+      <c r="AX174">
+        <v>9</v>
+      </c>
+      <c r="AY174">
+        <v>8</v>
+      </c>
+      <c r="AZ174">
+        <v>16</v>
+      </c>
+      <c r="BA174">
+        <v>4</v>
+      </c>
+      <c r="BB174">
+        <v>5</v>
+      </c>
+      <c r="BC174">
+        <v>9</v>
+      </c>
+      <c r="BD174">
+        <v>1.98</v>
+      </c>
+      <c r="BE174">
+        <v>6.4</v>
+      </c>
+      <c r="BF174">
+        <v>1.98</v>
+      </c>
+      <c r="BG174">
+        <v>1.34</v>
+      </c>
+      <c r="BH174">
+        <v>2.9</v>
+      </c>
+      <c r="BI174">
+        <v>1.58</v>
+      </c>
+      <c r="BJ174">
+        <v>2.18</v>
+      </c>
+      <c r="BK174">
+        <v>1.95</v>
+      </c>
+      <c r="BL174">
+        <v>1.74</v>
+      </c>
+      <c r="BM174">
+        <v>2.45</v>
+      </c>
+      <c r="BN174">
+        <v>1.48</v>
+      </c>
+      <c r="BO174">
+        <v>3.2</v>
+      </c>
+      <c r="BP174">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="175" spans="1:68">
+      <c r="A175" s="1">
+        <v>174</v>
+      </c>
+      <c r="B175">
+        <v>7762765</v>
+      </c>
+      <c r="C175" t="s">
+        <v>68</v>
+      </c>
+      <c r="D175" t="s">
+        <v>69</v>
+      </c>
+      <c r="E175" s="2">
+        <v>45710.52083333334</v>
+      </c>
+      <c r="F175">
+        <v>22</v>
+      </c>
+      <c r="G175" t="s">
+        <v>70</v>
+      </c>
+      <c r="H175" t="s">
+        <v>75</v>
+      </c>
+      <c r="I175">
+        <v>1</v>
+      </c>
+      <c r="J175">
+        <v>1</v>
+      </c>
+      <c r="K175">
+        <v>2</v>
+      </c>
+      <c r="L175">
+        <v>1</v>
+      </c>
+      <c r="M175">
+        <v>1</v>
+      </c>
+      <c r="N175">
+        <v>2</v>
+      </c>
+      <c r="O175" t="s">
+        <v>124</v>
+      </c>
+      <c r="P175" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q175">
+        <v>5.5</v>
+      </c>
+      <c r="R175">
+        <v>1.95</v>
+      </c>
+      <c r="S175">
+        <v>2.63</v>
+      </c>
+      <c r="T175">
+        <v>1.53</v>
+      </c>
+      <c r="U175">
+        <v>2.38</v>
+      </c>
+      <c r="V175">
+        <v>3.75</v>
+      </c>
+      <c r="W175">
+        <v>1.25</v>
+      </c>
+      <c r="X175">
+        <v>11</v>
+      </c>
+      <c r="Y175">
+        <v>1.05</v>
+      </c>
+      <c r="Z175">
+        <v>3.71</v>
+      </c>
+      <c r="AA175">
+        <v>3.37</v>
+      </c>
+      <c r="AB175">
+        <v>1.99</v>
+      </c>
+      <c r="AC175">
+        <v>1.05</v>
+      </c>
+      <c r="AD175">
+        <v>6.55</v>
+      </c>
+      <c r="AE175">
+        <v>1.46</v>
+      </c>
+      <c r="AF175">
+        <v>2.6</v>
+      </c>
+      <c r="AG175">
+        <v>2.37</v>
+      </c>
+      <c r="AH175">
+        <v>1.48</v>
+      </c>
+      <c r="AI175">
+        <v>2.2</v>
+      </c>
+      <c r="AJ175">
+        <v>1.62</v>
+      </c>
+      <c r="AK175">
+        <v>1.82</v>
+      </c>
+      <c r="AL175">
+        <v>1.3</v>
+      </c>
+      <c r="AM175">
+        <v>1.2</v>
+      </c>
+      <c r="AN175">
+        <v>2.1</v>
+      </c>
+      <c r="AO175">
+        <v>2.5</v>
+      </c>
+      <c r="AP175">
+        <v>2</v>
+      </c>
+      <c r="AQ175">
+        <v>2.36</v>
+      </c>
+      <c r="AR175">
+        <v>1.71</v>
+      </c>
+      <c r="AS175">
+        <v>1.59</v>
+      </c>
+      <c r="AT175">
+        <v>3.3</v>
+      </c>
+      <c r="AU175">
+        <v>4</v>
+      </c>
+      <c r="AV175">
+        <v>8</v>
+      </c>
+      <c r="AW175">
+        <v>2</v>
+      </c>
+      <c r="AX175">
+        <v>7</v>
+      </c>
+      <c r="AY175">
+        <v>6</v>
+      </c>
+      <c r="AZ175">
+        <v>15</v>
+      </c>
+      <c r="BA175">
+        <v>0</v>
+      </c>
+      <c r="BB175">
+        <v>5</v>
+      </c>
+      <c r="BC175">
+        <v>5</v>
+      </c>
+      <c r="BD175">
+        <v>2.7</v>
+      </c>
+      <c r="BE175">
+        <v>6.25</v>
+      </c>
+      <c r="BF175">
+        <v>1.58</v>
+      </c>
+      <c r="BG175">
+        <v>1.66</v>
+      </c>
+      <c r="BH175">
+        <v>2.08</v>
+      </c>
+      <c r="BI175">
+        <v>2.08</v>
+      </c>
+      <c r="BJ175">
+        <v>1.66</v>
+      </c>
+      <c r="BK175">
+        <v>2.7</v>
+      </c>
+      <c r="BL175">
+        <v>1.4</v>
+      </c>
+      <c r="BM175">
+        <v>3.65</v>
+      </c>
+      <c r="BN175">
+        <v>1.24</v>
+      </c>
+      <c r="BO175">
+        <v>5.1</v>
+      </c>
+      <c r="BP175">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="275">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1200,7 +1200,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP175"/>
+  <dimension ref="A1:BP176"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2152,7 +2152,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ5">
         <v>2</v>
@@ -4009,7 +4009,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ14">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -5448,7 +5448,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ21">
         <v>1.82</v>
@@ -6481,7 +6481,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ26">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR26">
         <v>1.84</v>
@@ -8126,7 +8126,7 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ34">
         <v>1.27</v>
@@ -8950,7 +8950,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ38">
         <v>0.45</v>
@@ -10189,7 +10189,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ44">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR44">
         <v>0.95</v>
@@ -13688,7 +13688,7 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ61">
         <v>1.27</v>
@@ -15954,7 +15954,7 @@
         <v>0.25</v>
       </c>
       <c r="AP72">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ72">
         <v>0.27</v>
@@ -19047,7 +19047,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ87">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR87">
         <v>1.66</v>
@@ -19459,7 +19459,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ89">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR89">
         <v>1.32</v>
@@ -19662,7 +19662,7 @@
         <v>0.75</v>
       </c>
       <c r="AP90">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ90">
         <v>1</v>
@@ -20901,7 +20901,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ96">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR96">
         <v>1.46</v>
@@ -22752,7 +22752,7 @@
         <v>0.71</v>
       </c>
       <c r="AP105">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ105">
         <v>1.09</v>
@@ -24815,7 +24815,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ115">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR115">
         <v>1.42</v>
@@ -26257,7 +26257,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ122">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR122">
         <v>1.43</v>
@@ -28108,7 +28108,7 @@
         <v>1.75</v>
       </c>
       <c r="AP131">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ131">
         <v>1.55</v>
@@ -30377,7 +30377,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ142">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR142">
         <v>2.2</v>
@@ -31610,7 +31610,7 @@
         <v>1</v>
       </c>
       <c r="AP148">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ148">
         <v>1.36</v>
@@ -33261,7 +33261,7 @@
         <v>2</v>
       </c>
       <c r="AQ156">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR156">
         <v>1.7</v>
@@ -37251,6 +37251,212 @@
       </c>
       <c r="BP175">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="176" spans="1:68">
+      <c r="A176" s="1">
+        <v>175</v>
+      </c>
+      <c r="B176">
+        <v>7762763</v>
+      </c>
+      <c r="C176" t="s">
+        <v>68</v>
+      </c>
+      <c r="D176" t="s">
+        <v>69</v>
+      </c>
+      <c r="E176" s="2">
+        <v>45711.5</v>
+      </c>
+      <c r="F176">
+        <v>22</v>
+      </c>
+      <c r="G176" t="s">
+        <v>73</v>
+      </c>
+      <c r="H176" t="s">
+        <v>72</v>
+      </c>
+      <c r="I176">
+        <v>0</v>
+      </c>
+      <c r="J176">
+        <v>0</v>
+      </c>
+      <c r="K176">
+        <v>0</v>
+      </c>
+      <c r="L176">
+        <v>0</v>
+      </c>
+      <c r="M176">
+        <v>1</v>
+      </c>
+      <c r="N176">
+        <v>1</v>
+      </c>
+      <c r="O176" t="s">
+        <v>86</v>
+      </c>
+      <c r="P176" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q176">
+        <v>3.1</v>
+      </c>
+      <c r="R176">
+        <v>2.05</v>
+      </c>
+      <c r="S176">
+        <v>3.75</v>
+      </c>
+      <c r="T176">
+        <v>1.44</v>
+      </c>
+      <c r="U176">
+        <v>2.63</v>
+      </c>
+      <c r="V176">
+        <v>3.4</v>
+      </c>
+      <c r="W176">
+        <v>1.3</v>
+      </c>
+      <c r="X176">
+        <v>10</v>
+      </c>
+      <c r="Y176">
+        <v>1.06</v>
+      </c>
+      <c r="Z176">
+        <v>2.32</v>
+      </c>
+      <c r="AA176">
+        <v>3.21</v>
+      </c>
+      <c r="AB176">
+        <v>3.04</v>
+      </c>
+      <c r="AC176">
+        <v>1.01</v>
+      </c>
+      <c r="AD176">
+        <v>8.6</v>
+      </c>
+      <c r="AE176">
+        <v>1.37</v>
+      </c>
+      <c r="AF176">
+        <v>2.95</v>
+      </c>
+      <c r="AG176">
+        <v>2.05</v>
+      </c>
+      <c r="AH176">
+        <v>1.61</v>
+      </c>
+      <c r="AI176">
+        <v>1.83</v>
+      </c>
+      <c r="AJ176">
+        <v>1.83</v>
+      </c>
+      <c r="AK176">
+        <v>1.35</v>
+      </c>
+      <c r="AL176">
+        <v>1.3</v>
+      </c>
+      <c r="AM176">
+        <v>1.56</v>
+      </c>
+      <c r="AN176">
+        <v>0.9</v>
+      </c>
+      <c r="AO176">
+        <v>1.1</v>
+      </c>
+      <c r="AP176">
+        <v>0.82</v>
+      </c>
+      <c r="AQ176">
+        <v>1.27</v>
+      </c>
+      <c r="AR176">
+        <v>1.29</v>
+      </c>
+      <c r="AS176">
+        <v>1.26</v>
+      </c>
+      <c r="AT176">
+        <v>2.55</v>
+      </c>
+      <c r="AU176">
+        <v>6</v>
+      </c>
+      <c r="AV176">
+        <v>7</v>
+      </c>
+      <c r="AW176">
+        <v>9</v>
+      </c>
+      <c r="AX176">
+        <v>2</v>
+      </c>
+      <c r="AY176">
+        <v>15</v>
+      </c>
+      <c r="AZ176">
+        <v>9</v>
+      </c>
+      <c r="BA176">
+        <v>9</v>
+      </c>
+      <c r="BB176">
+        <v>3</v>
+      </c>
+      <c r="BC176">
+        <v>12</v>
+      </c>
+      <c r="BD176">
+        <v>1.79</v>
+      </c>
+      <c r="BE176">
+        <v>6.4</v>
+      </c>
+      <c r="BF176">
+        <v>2.23</v>
+      </c>
+      <c r="BG176">
+        <v>1.43</v>
+      </c>
+      <c r="BH176">
+        <v>2.55</v>
+      </c>
+      <c r="BI176">
+        <v>1.74</v>
+      </c>
+      <c r="BJ176">
+        <v>1.97</v>
+      </c>
+      <c r="BK176">
+        <v>2.18</v>
+      </c>
+      <c r="BL176">
+        <v>1.58</v>
+      </c>
+      <c r="BM176">
+        <v>2.8</v>
+      </c>
+      <c r="BN176">
+        <v>1.36</v>
+      </c>
+      <c r="BO176">
+        <v>3.7</v>
+      </c>
+      <c r="BP176">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="275">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -595,6 +595,9 @@
     <t>['43']</t>
   </si>
   <si>
+    <t>['32']</t>
+  </si>
+  <si>
     <t>['12', '22', '45+1', '45+4', '90+1', '90+8']</t>
   </si>
   <si>
@@ -689,9 +692,6 @@
   </si>
   <si>
     <t>['9', '17', '59']</t>
-  </si>
-  <si>
-    <t>['32']</t>
   </si>
   <si>
     <t>['71', '78']</t>
@@ -1200,7 +1200,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP176"/>
+  <dimension ref="A1:BP177"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2074,7 +2074,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q5">
         <v>7.5</v>
@@ -2280,7 +2280,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2692,7 +2692,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q8">
         <v>4</v>
@@ -2976,7 +2976,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ9">
         <v>1.55</v>
@@ -3185,7 +3185,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ10">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3722,7 +3722,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3928,7 +3928,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q14">
         <v>2.4</v>
@@ -4752,7 +4752,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -5164,7 +5164,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -5370,7 +5370,7 @@
         <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5576,7 +5576,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5782,7 +5782,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -5988,7 +5988,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q24">
         <v>3.25</v>
@@ -6194,7 +6194,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q25">
         <v>2.05</v>
@@ -6400,7 +6400,7 @@
         <v>86</v>
       </c>
       <c r="P26" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6687,7 +6687,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ27">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR27">
         <v>1.64</v>
@@ -6890,7 +6890,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ28">
         <v>1</v>
@@ -7018,7 +7018,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7430,7 +7430,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7636,7 +7636,7 @@
         <v>86</v>
       </c>
       <c r="P32" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q32">
         <v>2.05</v>
@@ -8666,7 +8666,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -9490,7 +9490,7 @@
         <v>86</v>
       </c>
       <c r="P41" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q41">
         <v>2.38</v>
@@ -9902,7 +9902,7 @@
         <v>86</v>
       </c>
       <c r="P43" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q43">
         <v>7.5</v>
@@ -10108,7 +10108,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10186,7 +10186,7 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ44">
         <v>1.27</v>
@@ -10395,7 +10395,7 @@
         <v>2</v>
       </c>
       <c r="AQ45">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR45">
         <v>2.07</v>
@@ -10520,7 +10520,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q46">
         <v>2.5</v>
@@ -10726,7 +10726,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q47">
         <v>4.33</v>
@@ -10932,7 +10932,7 @@
         <v>86</v>
       </c>
       <c r="P48" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q48">
         <v>2.4</v>
@@ -11550,7 +11550,7 @@
         <v>116</v>
       </c>
       <c r="P51" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11756,7 +11756,7 @@
         <v>118</v>
       </c>
       <c r="P52" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q52">
         <v>5.5</v>
@@ -12168,7 +12168,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -12580,7 +12580,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q56">
         <v>5.5</v>
@@ -12658,7 +12658,7 @@
         <v>1</v>
       </c>
       <c r="AP56">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ56">
         <v>0.73</v>
@@ -12786,7 +12786,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q57">
         <v>5</v>
@@ -12992,7 +12992,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13198,7 +13198,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13404,7 +13404,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13610,7 +13610,7 @@
         <v>86</v>
       </c>
       <c r="P61" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q61">
         <v>6.5</v>
@@ -13816,7 +13816,7 @@
         <v>86</v>
       </c>
       <c r="P62" t="s">
-        <v>225</v>
+        <v>193</v>
       </c>
       <c r="Q62">
         <v>7</v>
@@ -15748,7 +15748,7 @@
         <v>2</v>
       </c>
       <c r="AP71">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ71">
         <v>1.27</v>
@@ -16369,7 +16369,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ74">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR74">
         <v>1.27</v>
@@ -17396,7 +17396,7 @@
         <v>1.6</v>
       </c>
       <c r="AP79">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ79">
         <v>1.36</v>
@@ -17730,7 +17730,7 @@
         <v>132</v>
       </c>
       <c r="P81" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -18142,7 +18142,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q83">
         <v>1.67</v>
@@ -19665,7 +19665,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ90">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR90">
         <v>1.18</v>
@@ -20486,7 +20486,7 @@
         <v>3</v>
       </c>
       <c r="AP94">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ94">
         <v>2.36</v>
@@ -22137,7 +22137,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ102">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR102">
         <v>0.91</v>
@@ -23704,7 +23704,7 @@
         <v>149</v>
       </c>
       <c r="P110" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23988,7 +23988,7 @@
         <v>2.57</v>
       </c>
       <c r="AP111">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ111">
         <v>1.91</v>
@@ -25639,7 +25639,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ119">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR119">
         <v>2</v>
@@ -26382,7 +26382,7 @@
         <v>158</v>
       </c>
       <c r="P123" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q123">
         <v>1.73</v>
@@ -27493,7 +27493,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ128">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR128">
         <v>1.33</v>
@@ -27902,7 +27902,7 @@
         <v>1.63</v>
       </c>
       <c r="AP130">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ130">
         <v>1.82</v>
@@ -29884,7 +29884,7 @@
         <v>167</v>
       </c>
       <c r="P140" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q140">
         <v>2.3</v>
@@ -30789,7 +30789,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ144">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR144">
         <v>1.48</v>
@@ -33052,7 +33052,7 @@
         <v>0.44</v>
       </c>
       <c r="AP155">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ155">
         <v>0.45</v>
@@ -33798,7 +33798,7 @@
         <v>182</v>
       </c>
       <c r="P159" t="s">
-        <v>225</v>
+        <v>193</v>
       </c>
       <c r="Q159">
         <v>1.8</v>
@@ -34291,7 +34291,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ161">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR161">
         <v>1.48</v>
@@ -37094,7 +37094,7 @@
         <v>124</v>
       </c>
       <c r="P175" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q175">
         <v>5.5</v>
@@ -37300,7 +37300,7 @@
         <v>86</v>
       </c>
       <c r="P176" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q176">
         <v>3.1</v>
@@ -37457,6 +37457,212 @@
       </c>
       <c r="BP176">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="177" spans="1:68">
+      <c r="A177" s="1">
+        <v>176</v>
+      </c>
+      <c r="B177">
+        <v>7762764</v>
+      </c>
+      <c r="C177" t="s">
+        <v>68</v>
+      </c>
+      <c r="D177" t="s">
+        <v>69</v>
+      </c>
+      <c r="E177" s="2">
+        <v>45712.52083333334</v>
+      </c>
+      <c r="F177">
+        <v>22</v>
+      </c>
+      <c r="G177" t="s">
+        <v>77</v>
+      </c>
+      <c r="H177" t="s">
+        <v>71</v>
+      </c>
+      <c r="I177">
+        <v>1</v>
+      </c>
+      <c r="J177">
+        <v>0</v>
+      </c>
+      <c r="K177">
+        <v>1</v>
+      </c>
+      <c r="L177">
+        <v>1</v>
+      </c>
+      <c r="M177">
+        <v>0</v>
+      </c>
+      <c r="N177">
+        <v>1</v>
+      </c>
+      <c r="O177" t="s">
+        <v>193</v>
+      </c>
+      <c r="P177" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q177">
+        <v>3.25</v>
+      </c>
+      <c r="R177">
+        <v>2</v>
+      </c>
+      <c r="S177">
+        <v>3.6</v>
+      </c>
+      <c r="T177">
+        <v>1.5</v>
+      </c>
+      <c r="U177">
+        <v>2.5</v>
+      </c>
+      <c r="V177">
+        <v>3.4</v>
+      </c>
+      <c r="W177">
+        <v>1.3</v>
+      </c>
+      <c r="X177">
+        <v>10</v>
+      </c>
+      <c r="Y177">
+        <v>1.06</v>
+      </c>
+      <c r="Z177">
+        <v>2.47</v>
+      </c>
+      <c r="AA177">
+        <v>2.92</v>
+      </c>
+      <c r="AB177">
+        <v>3.1</v>
+      </c>
+      <c r="AC177">
+        <v>1.03</v>
+      </c>
+      <c r="AD177">
+        <v>7.6</v>
+      </c>
+      <c r="AE177">
+        <v>1.41</v>
+      </c>
+      <c r="AF177">
+        <v>2.75</v>
+      </c>
+      <c r="AG177">
+        <v>2.2</v>
+      </c>
+      <c r="AH177">
+        <v>1.55</v>
+      </c>
+      <c r="AI177">
+        <v>1.83</v>
+      </c>
+      <c r="AJ177">
+        <v>1.83</v>
+      </c>
+      <c r="AK177">
+        <v>1.38</v>
+      </c>
+      <c r="AL177">
+        <v>1.33</v>
+      </c>
+      <c r="AM177">
+        <v>1.49</v>
+      </c>
+      <c r="AN177">
+        <v>0.8</v>
+      </c>
+      <c r="AO177">
+        <v>1</v>
+      </c>
+      <c r="AP177">
+        <v>1</v>
+      </c>
+      <c r="AQ177">
+        <v>0.91</v>
+      </c>
+      <c r="AR177">
+        <v>1.06</v>
+      </c>
+      <c r="AS177">
+        <v>0.95</v>
+      </c>
+      <c r="AT177">
+        <v>2.01</v>
+      </c>
+      <c r="AU177">
+        <v>2</v>
+      </c>
+      <c r="AV177">
+        <v>4</v>
+      </c>
+      <c r="AW177">
+        <v>1</v>
+      </c>
+      <c r="AX177">
+        <v>3</v>
+      </c>
+      <c r="AY177">
+        <v>3</v>
+      </c>
+      <c r="AZ177">
+        <v>7</v>
+      </c>
+      <c r="BA177">
+        <v>4</v>
+      </c>
+      <c r="BB177">
+        <v>6</v>
+      </c>
+      <c r="BC177">
+        <v>10</v>
+      </c>
+      <c r="BD177">
+        <v>1.81</v>
+      </c>
+      <c r="BE177">
+        <v>6.5</v>
+      </c>
+      <c r="BF177">
+        <v>2.18</v>
+      </c>
+      <c r="BG177">
+        <v>1.32</v>
+      </c>
+      <c r="BH177">
+        <v>3.05</v>
+      </c>
+      <c r="BI177">
+        <v>1.54</v>
+      </c>
+      <c r="BJ177">
+        <v>2.28</v>
+      </c>
+      <c r="BK177">
+        <v>1.9</v>
+      </c>
+      <c r="BL177">
+        <v>1.79</v>
+      </c>
+      <c r="BM177">
+        <v>2.4</v>
+      </c>
+      <c r="BN177">
+        <v>1.49</v>
+      </c>
+      <c r="BO177">
+        <v>3.15</v>
+      </c>
+      <c r="BP177">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="277">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -840,6 +840,12 @@
   <si>
     <t>['8', '47', '60']</t>
   </si>
+  <si>
+    <t>['28', '42']</t>
+  </si>
+  <si>
+    <t>['12', '31', '90']</t>
+  </si>
 </sst>
 </file>
 
@@ -1200,7 +1206,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP177"/>
+  <dimension ref="A1:BP180"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1740,7 +1746,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ3">
         <v>0.73</v>
@@ -1946,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ4">
         <v>1.09</v>
@@ -2979,7 +2985,7 @@
         <v>1</v>
       </c>
       <c r="AQ9">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3391,7 +3397,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ11">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4215,7 +4221,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ15">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4830,7 +4836,7 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ18">
         <v>2</v>
@@ -5036,7 +5042,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ19">
         <v>1.27</v>
@@ -5654,7 +5660,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ22">
         <v>1.91</v>
@@ -5863,7 +5869,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ23">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR23">
         <v>0.91</v>
@@ -6893,7 +6899,7 @@
         <v>1</v>
       </c>
       <c r="AQ28">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR28">
         <v>0.91</v>
@@ -7099,7 +7105,7 @@
         <v>2</v>
       </c>
       <c r="AQ29">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR29">
         <v>2.25</v>
@@ -7302,7 +7308,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ30">
         <v>1.09</v>
@@ -7508,10 +7514,10 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ31">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR31">
         <v>1.36</v>
@@ -8744,7 +8750,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ37">
         <v>1.82</v>
@@ -8953,7 +8959,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ38">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR38">
         <v>0.86</v>
@@ -11216,7 +11222,7 @@
         <v>2</v>
       </c>
       <c r="AP49">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ49">
         <v>2</v>
@@ -11422,7 +11428,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ50">
         <v>1.36</v>
@@ -11628,10 +11634,10 @@
         <v>2</v>
       </c>
       <c r="AP51">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ51">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR51">
         <v>1.13</v>
@@ -11837,7 +11843,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ52">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR52">
         <v>0.93</v>
@@ -12246,7 +12252,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ54">
         <v>0.27</v>
@@ -13482,7 +13488,7 @@
         <v>3</v>
       </c>
       <c r="AP60">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ60">
         <v>2.36</v>
@@ -14100,7 +14106,7 @@
         <v>1.67</v>
       </c>
       <c r="AP63">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ63">
         <v>1.27</v>
@@ -14515,7 +14521,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ65">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR65">
         <v>1.93</v>
@@ -14721,7 +14727,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ66">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR66">
         <v>1.61</v>
@@ -15130,7 +15136,7 @@
         <v>1.33</v>
       </c>
       <c r="AP68">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ68">
         <v>1.82</v>
@@ -15336,10 +15342,10 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ69">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR69">
         <v>1.44</v>
@@ -16366,7 +16372,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ74">
         <v>0.91</v>
@@ -17602,7 +17608,7 @@
         <v>1.8</v>
       </c>
       <c r="AP80">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ80">
         <v>1.27</v>
@@ -17811,7 +17817,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ81">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR81">
         <v>1.3</v>
@@ -18635,7 +18641,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ85">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR85">
         <v>0.85</v>
@@ -18838,10 +18844,10 @@
         <v>1.25</v>
       </c>
       <c r="AP86">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ86">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR86">
         <v>1.23</v>
@@ -20898,7 +20904,7 @@
         <v>1.6</v>
       </c>
       <c r="AP96">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ96">
         <v>1.27</v>
@@ -21107,7 +21113,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ97">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR97">
         <v>1.31</v>
@@ -21313,7 +21319,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ98">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR98">
         <v>1.84</v>
@@ -21931,7 +21937,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ101">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR101">
         <v>1.85</v>
@@ -22958,7 +22964,7 @@
         <v>0.67</v>
       </c>
       <c r="AP106">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ106">
         <v>1.27</v>
@@ -23164,7 +23170,7 @@
         <v>1.57</v>
       </c>
       <c r="AP107">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ107">
         <v>1.36</v>
@@ -23373,7 +23379,7 @@
         <v>1</v>
       </c>
       <c r="AQ108">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR108">
         <v>1.48</v>
@@ -24403,7 +24409,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ113">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR113">
         <v>1.41</v>
@@ -24609,7 +24615,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ114">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR114">
         <v>1.09</v>
@@ -25842,7 +25848,7 @@
         <v>3</v>
       </c>
       <c r="AP120">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ120">
         <v>2.36</v>
@@ -26048,7 +26054,7 @@
         <v>0.29</v>
       </c>
       <c r="AP121">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ121">
         <v>0.27</v>
@@ -26463,7 +26469,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ123">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR123">
         <v>1.29</v>
@@ -26669,7 +26675,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ124">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR124">
         <v>2.17</v>
@@ -27696,7 +27702,7 @@
         <v>1.38</v>
       </c>
       <c r="AP129">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ129">
         <v>1.27</v>
@@ -28111,7 +28117,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ131">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR131">
         <v>1.16</v>
@@ -28726,7 +28732,7 @@
         <v>2.25</v>
       </c>
       <c r="AP134">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ134">
         <v>1.91</v>
@@ -28932,7 +28938,7 @@
         <v>1</v>
       </c>
       <c r="AP135">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ135">
         <v>1.09</v>
@@ -29553,7 +29559,7 @@
         <v>2</v>
       </c>
       <c r="AQ138">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR138">
         <v>1.67</v>
@@ -29965,7 +29971,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ140">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR140">
         <v>1.34</v>
@@ -30992,10 +30998,10 @@
         <v>1.56</v>
       </c>
       <c r="AP145">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ145">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR145">
         <v>1.27</v>
@@ -31816,7 +31822,7 @@
         <v>1.78</v>
       </c>
       <c r="AP149">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ149">
         <v>2</v>
@@ -32434,7 +32440,7 @@
         <v>0.44</v>
       </c>
       <c r="AP152">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ152">
         <v>0.73</v>
@@ -33055,7 +33061,7 @@
         <v>1</v>
       </c>
       <c r="AQ155">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR155">
         <v>1.02</v>
@@ -33673,7 +33679,7 @@
         <v>1</v>
       </c>
       <c r="AQ158">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR158">
         <v>1.62</v>
@@ -34497,7 +34503,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ162">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR162">
         <v>1.31</v>
@@ -34700,7 +34706,7 @@
         <v>1.9</v>
       </c>
       <c r="AP163">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ163">
         <v>1.82</v>
@@ -34906,7 +34912,7 @@
         <v>2.1</v>
       </c>
       <c r="AP164">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ164">
         <v>1.91</v>
@@ -35318,7 +35324,7 @@
         <v>1.2</v>
       </c>
       <c r="AP166">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ166">
         <v>1.36</v>
@@ -35527,7 +35533,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ167">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR167">
         <v>1.7</v>
@@ -36145,7 +36151,7 @@
         <v>1</v>
       </c>
       <c r="AQ170">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR170">
         <v>1.7</v>
@@ -37663,6 +37669,624 @@
       </c>
       <c r="BP177">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="178" spans="1:68">
+      <c r="A178" s="1">
+        <v>177</v>
+      </c>
+      <c r="B178">
+        <v>7762776</v>
+      </c>
+      <c r="C178" t="s">
+        <v>68</v>
+      </c>
+      <c r="D178" t="s">
+        <v>69</v>
+      </c>
+      <c r="E178" s="2">
+        <v>45717.29166666666</v>
+      </c>
+      <c r="F178">
+        <v>23</v>
+      </c>
+      <c r="G178" t="s">
+        <v>71</v>
+      </c>
+      <c r="H178" t="s">
+        <v>73</v>
+      </c>
+      <c r="I178">
+        <v>0</v>
+      </c>
+      <c r="J178">
+        <v>2</v>
+      </c>
+      <c r="K178">
+        <v>2</v>
+      </c>
+      <c r="L178">
+        <v>0</v>
+      </c>
+      <c r="M178">
+        <v>2</v>
+      </c>
+      <c r="N178">
+        <v>2</v>
+      </c>
+      <c r="O178" t="s">
+        <v>86</v>
+      </c>
+      <c r="P178" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q178">
+        <v>3.5</v>
+      </c>
+      <c r="R178">
+        <v>1.95</v>
+      </c>
+      <c r="S178">
+        <v>3.5</v>
+      </c>
+      <c r="T178">
+        <v>1.53</v>
+      </c>
+      <c r="U178">
+        <v>2.38</v>
+      </c>
+      <c r="V178">
+        <v>3.5</v>
+      </c>
+      <c r="W178">
+        <v>1.29</v>
+      </c>
+      <c r="X178">
+        <v>11</v>
+      </c>
+      <c r="Y178">
+        <v>1.05</v>
+      </c>
+      <c r="Z178">
+        <v>2.63</v>
+      </c>
+      <c r="AA178">
+        <v>3.11</v>
+      </c>
+      <c r="AB178">
+        <v>2.71</v>
+      </c>
+      <c r="AC178">
+        <v>1.01</v>
+      </c>
+      <c r="AD178">
+        <v>8.5</v>
+      </c>
+      <c r="AE178">
+        <v>1.42</v>
+      </c>
+      <c r="AF178">
+        <v>2.75</v>
+      </c>
+      <c r="AG178">
+        <v>2.2</v>
+      </c>
+      <c r="AH178">
+        <v>1.55</v>
+      </c>
+      <c r="AI178">
+        <v>2</v>
+      </c>
+      <c r="AJ178">
+        <v>1.73</v>
+      </c>
+      <c r="AK178">
+        <v>1.42</v>
+      </c>
+      <c r="AL178">
+        <v>1.31</v>
+      </c>
+      <c r="AM178">
+        <v>1.46</v>
+      </c>
+      <c r="AN178">
+        <v>1.09</v>
+      </c>
+      <c r="AO178">
+        <v>1</v>
+      </c>
+      <c r="AP178">
+        <v>1</v>
+      </c>
+      <c r="AQ178">
+        <v>1.17</v>
+      </c>
+      <c r="AR178">
+        <v>1.28</v>
+      </c>
+      <c r="AS178">
+        <v>1.3</v>
+      </c>
+      <c r="AT178">
+        <v>2.58</v>
+      </c>
+      <c r="AU178">
+        <v>2</v>
+      </c>
+      <c r="AV178">
+        <v>5</v>
+      </c>
+      <c r="AW178">
+        <v>1</v>
+      </c>
+      <c r="AX178">
+        <v>5</v>
+      </c>
+      <c r="AY178">
+        <v>3</v>
+      </c>
+      <c r="AZ178">
+        <v>10</v>
+      </c>
+      <c r="BA178">
+        <v>4</v>
+      </c>
+      <c r="BB178">
+        <v>5</v>
+      </c>
+      <c r="BC178">
+        <v>9</v>
+      </c>
+      <c r="BD178">
+        <v>1.97</v>
+      </c>
+      <c r="BE178">
+        <v>6.4</v>
+      </c>
+      <c r="BF178">
+        <v>2.02</v>
+      </c>
+      <c r="BG178">
+        <v>1.38</v>
+      </c>
+      <c r="BH178">
+        <v>2.8</v>
+      </c>
+      <c r="BI178">
+        <v>1.64</v>
+      </c>
+      <c r="BJ178">
+        <v>2.1</v>
+      </c>
+      <c r="BK178">
+        <v>2.02</v>
+      </c>
+      <c r="BL178">
+        <v>1.68</v>
+      </c>
+      <c r="BM178">
+        <v>2.55</v>
+      </c>
+      <c r="BN178">
+        <v>1.43</v>
+      </c>
+      <c r="BO178">
+        <v>3.4</v>
+      </c>
+      <c r="BP178">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="179" spans="1:68">
+      <c r="A179" s="1">
+        <v>178</v>
+      </c>
+      <c r="B179">
+        <v>7762777</v>
+      </c>
+      <c r="C179" t="s">
+        <v>68</v>
+      </c>
+      <c r="D179" t="s">
+        <v>69</v>
+      </c>
+      <c r="E179" s="2">
+        <v>45717.39583333334</v>
+      </c>
+      <c r="F179">
+        <v>23</v>
+      </c>
+      <c r="G179" t="s">
+        <v>72</v>
+      </c>
+      <c r="H179" t="s">
+        <v>74</v>
+      </c>
+      <c r="I179">
+        <v>1</v>
+      </c>
+      <c r="J179">
+        <v>0</v>
+      </c>
+      <c r="K179">
+        <v>1</v>
+      </c>
+      <c r="L179">
+        <v>1</v>
+      </c>
+      <c r="M179">
+        <v>0</v>
+      </c>
+      <c r="N179">
+        <v>1</v>
+      </c>
+      <c r="O179" t="s">
+        <v>155</v>
+      </c>
+      <c r="P179" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q179">
+        <v>2.4</v>
+      </c>
+      <c r="R179">
+        <v>2.1</v>
+      </c>
+      <c r="S179">
+        <v>5</v>
+      </c>
+      <c r="T179">
+        <v>1.44</v>
+      </c>
+      <c r="U179">
+        <v>2.63</v>
+      </c>
+      <c r="V179">
+        <v>3</v>
+      </c>
+      <c r="W179">
+        <v>1.36</v>
+      </c>
+      <c r="X179">
+        <v>9</v>
+      </c>
+      <c r="Y179">
+        <v>1.07</v>
+      </c>
+      <c r="Z179">
+        <v>1.75</v>
+      </c>
+      <c r="AA179">
+        <v>3.5</v>
+      </c>
+      <c r="AB179">
+        <v>4.75</v>
+      </c>
+      <c r="AC179">
+        <v>1.02</v>
+      </c>
+      <c r="AD179">
+        <v>7.8</v>
+      </c>
+      <c r="AE179">
+        <v>1.34</v>
+      </c>
+      <c r="AF179">
+        <v>3.1</v>
+      </c>
+      <c r="AG179">
+        <v>1.98</v>
+      </c>
+      <c r="AH179">
+        <v>1.77</v>
+      </c>
+      <c r="AI179">
+        <v>2</v>
+      </c>
+      <c r="AJ179">
+        <v>1.73</v>
+      </c>
+      <c r="AK179">
+        <v>1.18</v>
+      </c>
+      <c r="AL179">
+        <v>1.25</v>
+      </c>
+      <c r="AM179">
+        <v>1.99</v>
+      </c>
+      <c r="AN179">
+        <v>0.55</v>
+      </c>
+      <c r="AO179">
+        <v>0.45</v>
+      </c>
+      <c r="AP179">
+        <v>0.75</v>
+      </c>
+      <c r="AQ179">
+        <v>0.42</v>
+      </c>
+      <c r="AR179">
+        <v>1.32</v>
+      </c>
+      <c r="AS179">
+        <v>0.95</v>
+      </c>
+      <c r="AT179">
+        <v>2.27</v>
+      </c>
+      <c r="AU179">
+        <v>4</v>
+      </c>
+      <c r="AV179">
+        <v>3</v>
+      </c>
+      <c r="AW179">
+        <v>6</v>
+      </c>
+      <c r="AX179">
+        <v>10</v>
+      </c>
+      <c r="AY179">
+        <v>10</v>
+      </c>
+      <c r="AZ179">
+        <v>13</v>
+      </c>
+      <c r="BA179">
+        <v>4</v>
+      </c>
+      <c r="BB179">
+        <v>4</v>
+      </c>
+      <c r="BC179">
+        <v>8</v>
+      </c>
+      <c r="BD179">
+        <v>1.52</v>
+      </c>
+      <c r="BE179">
+        <v>6.75</v>
+      </c>
+      <c r="BF179">
+        <v>2.8</v>
+      </c>
+      <c r="BG179">
+        <v>1.3</v>
+      </c>
+      <c r="BH179">
+        <v>3.05</v>
+      </c>
+      <c r="BI179">
+        <v>1.54</v>
+      </c>
+      <c r="BJ179">
+        <v>2.28</v>
+      </c>
+      <c r="BK179">
+        <v>1.88</v>
+      </c>
+      <c r="BL179">
+        <v>1.81</v>
+      </c>
+      <c r="BM179">
+        <v>2.35</v>
+      </c>
+      <c r="BN179">
+        <v>1.5</v>
+      </c>
+      <c r="BO179">
+        <v>3.05</v>
+      </c>
+      <c r="BP179">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="180" spans="1:68">
+      <c r="A180" s="1">
+        <v>179</v>
+      </c>
+      <c r="B180">
+        <v>7762773</v>
+      </c>
+      <c r="C180" t="s">
+        <v>68</v>
+      </c>
+      <c r="D180" t="s">
+        <v>69</v>
+      </c>
+      <c r="E180" s="2">
+        <v>45717.48958333334</v>
+      </c>
+      <c r="F180">
+        <v>23</v>
+      </c>
+      <c r="G180" t="s">
+        <v>84</v>
+      </c>
+      <c r="H180" t="s">
+        <v>83</v>
+      </c>
+      <c r="I180">
+        <v>0</v>
+      </c>
+      <c r="J180">
+        <v>2</v>
+      </c>
+      <c r="K180">
+        <v>2</v>
+      </c>
+      <c r="L180">
+        <v>0</v>
+      </c>
+      <c r="M180">
+        <v>3</v>
+      </c>
+      <c r="N180">
+        <v>3</v>
+      </c>
+      <c r="O180" t="s">
+        <v>86</v>
+      </c>
+      <c r="P180" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q180">
+        <v>2.88</v>
+      </c>
+      <c r="R180">
+        <v>1.95</v>
+      </c>
+      <c r="S180">
+        <v>4.75</v>
+      </c>
+      <c r="T180">
+        <v>1.44</v>
+      </c>
+      <c r="U180">
+        <v>2.63</v>
+      </c>
+      <c r="V180">
+        <v>3.25</v>
+      </c>
+      <c r="W180">
+        <v>1.33</v>
+      </c>
+      <c r="X180">
+        <v>10</v>
+      </c>
+      <c r="Y180">
+        <v>1.06</v>
+      </c>
+      <c r="Z180">
+        <v>2.08</v>
+      </c>
+      <c r="AA180">
+        <v>2.82</v>
+      </c>
+      <c r="AB180">
+        <v>4.3</v>
+      </c>
+      <c r="AC180">
+        <v>1.04</v>
+      </c>
+      <c r="AD180">
+        <v>6.95</v>
+      </c>
+      <c r="AE180">
+        <v>1.48</v>
+      </c>
+      <c r="AF180">
+        <v>2.55</v>
+      </c>
+      <c r="AG180">
+        <v>2.05</v>
+      </c>
+      <c r="AH180">
+        <v>1.61</v>
+      </c>
+      <c r="AI180">
+        <v>2.2</v>
+      </c>
+      <c r="AJ180">
+        <v>1.62</v>
+      </c>
+      <c r="AK180">
+        <v>1.23</v>
+      </c>
+      <c r="AL180">
+        <v>1.33</v>
+      </c>
+      <c r="AM180">
+        <v>1.71</v>
+      </c>
+      <c r="AN180">
+        <v>1.82</v>
+      </c>
+      <c r="AO180">
+        <v>1.55</v>
+      </c>
+      <c r="AP180">
+        <v>1.67</v>
+      </c>
+      <c r="AQ180">
+        <v>1.67</v>
+      </c>
+      <c r="AR180">
+        <v>1.56</v>
+      </c>
+      <c r="AS180">
+        <v>1.18</v>
+      </c>
+      <c r="AT180">
+        <v>2.74</v>
+      </c>
+      <c r="AU180">
+        <v>4</v>
+      </c>
+      <c r="AV180">
+        <v>7</v>
+      </c>
+      <c r="AW180">
+        <v>9</v>
+      </c>
+      <c r="AX180">
+        <v>3</v>
+      </c>
+      <c r="AY180">
+        <v>13</v>
+      </c>
+      <c r="AZ180">
+        <v>10</v>
+      </c>
+      <c r="BA180">
+        <v>9</v>
+      </c>
+      <c r="BB180">
+        <v>5</v>
+      </c>
+      <c r="BC180">
+        <v>14</v>
+      </c>
+      <c r="BD180">
+        <v>1.61</v>
+      </c>
+      <c r="BE180">
+        <v>6.4</v>
+      </c>
+      <c r="BF180">
+        <v>2.55</v>
+      </c>
+      <c r="BG180">
+        <v>1.54</v>
+      </c>
+      <c r="BH180">
+        <v>2.3</v>
+      </c>
+      <c r="BI180">
+        <v>1.91</v>
+      </c>
+      <c r="BJ180">
+        <v>1.78</v>
+      </c>
+      <c r="BK180">
+        <v>2.45</v>
+      </c>
+      <c r="BL180">
+        <v>1.48</v>
+      </c>
+      <c r="BM180">
+        <v>3.2</v>
+      </c>
+      <c r="BN180">
+        <v>1.29</v>
+      </c>
+      <c r="BO180">
+        <v>4.35</v>
+      </c>
+      <c r="BP180">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="279">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -598,6 +598,9 @@
     <t>['32']</t>
   </si>
   <si>
+    <t>['39', '84']</t>
+  </si>
+  <si>
     <t>['12', '22', '45+1', '45+4', '90+1', '90+8']</t>
   </si>
   <si>
@@ -845,6 +848,9 @@
   </si>
   <si>
     <t>['12', '31', '90']</t>
+  </si>
+  <si>
+    <t>['90+5', '90+13']</t>
   </si>
 </sst>
 </file>
@@ -1206,7 +1212,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP180"/>
+  <dimension ref="A1:BP181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2080,7 +2086,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q5">
         <v>7.5</v>
@@ -2161,7 +2167,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ5">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2286,7 +2292,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2698,7 +2704,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q8">
         <v>4</v>
@@ -3600,7 +3606,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ12">
         <v>0.27</v>
@@ -3728,7 +3734,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3934,7 +3940,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q14">
         <v>2.4</v>
@@ -4758,7 +4764,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -4839,7 +4845,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ18">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AR18">
         <v>1.14</v>
@@ -5170,7 +5176,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -5376,7 +5382,7 @@
         <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5582,7 +5588,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5788,7 +5794,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -5994,7 +6000,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q24">
         <v>3.25</v>
@@ -6200,7 +6206,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q25">
         <v>2.05</v>
@@ -6406,7 +6412,7 @@
         <v>86</v>
       </c>
       <c r="P26" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -7024,7 +7030,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7436,7 +7442,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7642,7 +7648,7 @@
         <v>86</v>
       </c>
       <c r="P32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q32">
         <v>2.05</v>
@@ -7720,7 +7726,7 @@
         <v>0.5</v>
       </c>
       <c r="AP32">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ32">
         <v>0.73</v>
@@ -7929,7 +7935,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ33">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AR33">
         <v>1.4</v>
@@ -8672,7 +8678,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -9496,7 +9502,7 @@
         <v>86</v>
       </c>
       <c r="P41" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q41">
         <v>2.38</v>
@@ -9908,7 +9914,7 @@
         <v>86</v>
       </c>
       <c r="P43" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q43">
         <v>7.5</v>
@@ -10114,7 +10120,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10526,7 +10532,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q46">
         <v>2.5</v>
@@ -10732,7 +10738,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q47">
         <v>4.33</v>
@@ -10938,7 +10944,7 @@
         <v>86</v>
       </c>
       <c r="P48" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q48">
         <v>2.4</v>
@@ -11016,7 +11022,7 @@
         <v>3</v>
       </c>
       <c r="AP48">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ48">
         <v>1.91</v>
@@ -11225,7 +11231,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ49">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AR49">
         <v>1.37</v>
@@ -11556,7 +11562,7 @@
         <v>116</v>
       </c>
       <c r="P51" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11762,7 +11768,7 @@
         <v>118</v>
       </c>
       <c r="P52" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q52">
         <v>5.5</v>
@@ -12174,7 +12180,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -12586,7 +12592,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q56">
         <v>5.5</v>
@@ -12792,7 +12798,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q57">
         <v>5</v>
@@ -12998,7 +13004,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13204,7 +13210,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13285,7 +13291,7 @@
         <v>1</v>
       </c>
       <c r="AQ59">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AR59">
         <v>1.61</v>
@@ -13410,7 +13416,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13616,7 +13622,7 @@
         <v>86</v>
       </c>
       <c r="P61" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q61">
         <v>6.5</v>
@@ -14028,7 +14034,7 @@
         <v>86</v>
       </c>
       <c r="P63" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q63">
         <v>3.5</v>
@@ -14234,7 +14240,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14518,7 +14524,7 @@
         <v>2.25</v>
       </c>
       <c r="AP65">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ65">
         <v>1.67</v>
@@ -14852,7 +14858,7 @@
         <v>86</v>
       </c>
       <c r="P67" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q67">
         <v>6.5</v>
@@ -14933,7 +14939,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ67">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AR67">
         <v>1.17</v>
@@ -15058,7 +15064,7 @@
         <v>86</v>
       </c>
       <c r="P68" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q68">
         <v>4.75</v>
@@ -15676,7 +15682,7 @@
         <v>92</v>
       </c>
       <c r="P71" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q71">
         <v>9.5</v>
@@ -16294,7 +16300,7 @@
         <v>86</v>
       </c>
       <c r="P74" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16912,7 +16918,7 @@
         <v>130</v>
       </c>
       <c r="P77" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q77">
         <v>1.83</v>
@@ -17118,7 +17124,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q78">
         <v>12</v>
@@ -17324,7 +17330,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q79">
         <v>3.75</v>
@@ -17530,7 +17536,7 @@
         <v>131</v>
       </c>
       <c r="P80" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17736,7 +17742,7 @@
         <v>132</v>
       </c>
       <c r="P81" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -18148,7 +18154,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q83">
         <v>1.67</v>
@@ -18226,7 +18232,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ83">
         <v>1.36</v>
@@ -18435,7 +18441,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ84">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AR84">
         <v>1.5</v>
@@ -18766,7 +18772,7 @@
         <v>134</v>
       </c>
       <c r="P86" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q86">
         <v>2.63</v>
@@ -20414,7 +20420,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q94">
         <v>13</v>
@@ -20620,7 +20626,7 @@
         <v>139</v>
       </c>
       <c r="P95" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -21032,7 +21038,7 @@
         <v>140</v>
       </c>
       <c r="P97" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q97">
         <v>2.4</v>
@@ -21316,7 +21322,7 @@
         <v>0.8</v>
       </c>
       <c r="AP98">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ98">
         <v>0.42</v>
@@ -21856,7 +21862,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22474,7 +22480,7 @@
         <v>145</v>
       </c>
       <c r="P104" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22680,7 +22686,7 @@
         <v>86</v>
       </c>
       <c r="P105" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -22886,7 +22892,7 @@
         <v>146</v>
       </c>
       <c r="P106" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q106">
         <v>6</v>
@@ -23298,7 +23304,7 @@
         <v>147</v>
       </c>
       <c r="P108" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23710,7 +23716,7 @@
         <v>149</v>
       </c>
       <c r="P110" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23791,7 +23797,7 @@
         <v>2</v>
       </c>
       <c r="AQ110">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AR110">
         <v>1.77</v>
@@ -24122,7 +24128,7 @@
         <v>143</v>
       </c>
       <c r="P112" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q112">
         <v>4.75</v>
@@ -24946,7 +24952,7 @@
         <v>86</v>
       </c>
       <c r="P116" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q116">
         <v>4.5</v>
@@ -25152,7 +25158,7 @@
         <v>153</v>
       </c>
       <c r="P117" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q117">
         <v>1.53</v>
@@ -25358,7 +25364,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25564,7 +25570,7 @@
         <v>154</v>
       </c>
       <c r="P119" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q119">
         <v>1.8</v>
@@ -25642,7 +25648,7 @@
         <v>0.83</v>
       </c>
       <c r="AP119">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ119">
         <v>0.91</v>
@@ -25770,7 +25776,7 @@
         <v>155</v>
       </c>
       <c r="P120" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q120">
         <v>7.5</v>
@@ -26182,7 +26188,7 @@
         <v>157</v>
       </c>
       <c r="P122" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q122">
         <v>2.63</v>
@@ -26388,7 +26394,7 @@
         <v>158</v>
       </c>
       <c r="P123" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q123">
         <v>1.73</v>
@@ -27006,7 +27012,7 @@
         <v>86</v>
       </c>
       <c r="P126" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27212,7 +27218,7 @@
         <v>161</v>
       </c>
       <c r="P127" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27290,7 +27296,7 @@
         <v>3</v>
       </c>
       <c r="AP127">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ127">
         <v>2.36</v>
@@ -27418,7 +27424,7 @@
         <v>86</v>
       </c>
       <c r="P128" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q128">
         <v>2.4</v>
@@ -27624,7 +27630,7 @@
         <v>138</v>
       </c>
       <c r="P129" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27830,7 +27836,7 @@
         <v>98</v>
       </c>
       <c r="P130" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q130">
         <v>6.5</v>
@@ -28036,7 +28042,7 @@
         <v>162</v>
       </c>
       <c r="P131" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q131">
         <v>4.33</v>
@@ -28242,7 +28248,7 @@
         <v>86</v>
       </c>
       <c r="P132" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q132">
         <v>8</v>
@@ -28323,7 +28329,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ132">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AR132">
         <v>1.32</v>
@@ -29762,7 +29768,7 @@
         <v>1.75</v>
       </c>
       <c r="AP139">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ139">
         <v>1.36</v>
@@ -29890,7 +29896,7 @@
         <v>167</v>
       </c>
       <c r="P140" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q140">
         <v>2.3</v>
@@ -30096,7 +30102,7 @@
         <v>86</v>
       </c>
       <c r="P141" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q141">
         <v>7.5</v>
@@ -30302,7 +30308,7 @@
         <v>168</v>
       </c>
       <c r="P142" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30508,7 +30514,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30920,7 +30926,7 @@
         <v>171</v>
       </c>
       <c r="P145" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q145">
         <v>3.75</v>
@@ -31126,7 +31132,7 @@
         <v>172</v>
       </c>
       <c r="P146" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q146">
         <v>7.5</v>
@@ -31332,7 +31338,7 @@
         <v>173</v>
       </c>
       <c r="P147" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31410,7 +31416,7 @@
         <v>1.33</v>
       </c>
       <c r="AP147">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ147">
         <v>1.27</v>
@@ -31538,7 +31544,7 @@
         <v>174</v>
       </c>
       <c r="P148" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q148">
         <v>2.75</v>
@@ -31744,7 +31750,7 @@
         <v>86</v>
       </c>
       <c r="P149" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q149">
         <v>7.5</v>
@@ -31825,7 +31831,7 @@
         <v>1</v>
       </c>
       <c r="AQ149">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AR149">
         <v>1.37</v>
@@ -32156,7 +32162,7 @@
         <v>86</v>
       </c>
       <c r="P151" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q151">
         <v>6.5</v>
@@ -32362,7 +32368,7 @@
         <v>176</v>
       </c>
       <c r="P152" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q152">
         <v>2.75</v>
@@ -32568,7 +32574,7 @@
         <v>177</v>
       </c>
       <c r="P153" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q153">
         <v>4.75</v>
@@ -32980,7 +32986,7 @@
         <v>179</v>
       </c>
       <c r="P155" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33186,7 +33192,7 @@
         <v>176</v>
       </c>
       <c r="P156" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q156">
         <v>2.2</v>
@@ -33598,7 +33604,7 @@
         <v>181</v>
       </c>
       <c r="P158" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -34422,7 +34428,7 @@
         <v>86</v>
       </c>
       <c r="P162" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q162">
         <v>3.5</v>
@@ -34628,7 +34634,7 @@
         <v>184</v>
       </c>
       <c r="P163" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35040,7 +35046,7 @@
         <v>185</v>
       </c>
       <c r="P165" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q165">
         <v>9.5</v>
@@ -35121,7 +35127,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ165">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AR165">
         <v>1.02</v>
@@ -35736,7 +35742,7 @@
         <v>1.2</v>
       </c>
       <c r="AP168">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ168">
         <v>1.09</v>
@@ -36894,7 +36900,7 @@
         <v>86</v>
       </c>
       <c r="P174" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q174">
         <v>3.75</v>
@@ -37100,7 +37106,7 @@
         <v>124</v>
       </c>
       <c r="P175" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q175">
         <v>5.5</v>
@@ -37306,7 +37312,7 @@
         <v>86</v>
       </c>
       <c r="P176" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q176">
         <v>3.1</v>
@@ -37718,7 +37724,7 @@
         <v>86</v>
       </c>
       <c r="P178" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q178">
         <v>3.5</v>
@@ -38130,7 +38136,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38287,6 +38293,212 @@
       </c>
       <c r="BP180">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="181" spans="1:68">
+      <c r="A181" s="1">
+        <v>180</v>
+      </c>
+      <c r="B181">
+        <v>7762772</v>
+      </c>
+      <c r="C181" t="s">
+        <v>68</v>
+      </c>
+      <c r="D181" t="s">
+        <v>69</v>
+      </c>
+      <c r="E181" s="2">
+        <v>45718.375</v>
+      </c>
+      <c r="F181">
+        <v>23</v>
+      </c>
+      <c r="G181" t="s">
+        <v>80</v>
+      </c>
+      <c r="H181" t="s">
+        <v>79</v>
+      </c>
+      <c r="I181">
+        <v>1</v>
+      </c>
+      <c r="J181">
+        <v>0</v>
+      </c>
+      <c r="K181">
+        <v>1</v>
+      </c>
+      <c r="L181">
+        <v>2</v>
+      </c>
+      <c r="M181">
+        <v>2</v>
+      </c>
+      <c r="N181">
+        <v>4</v>
+      </c>
+      <c r="O181" t="s">
+        <v>194</v>
+      </c>
+      <c r="P181" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q181">
+        <v>3.2</v>
+      </c>
+      <c r="R181">
+        <v>2.05</v>
+      </c>
+      <c r="S181">
+        <v>3.6</v>
+      </c>
+      <c r="T181">
+        <v>1.44</v>
+      </c>
+      <c r="U181">
+        <v>2.63</v>
+      </c>
+      <c r="V181">
+        <v>3.4</v>
+      </c>
+      <c r="W181">
+        <v>1.3</v>
+      </c>
+      <c r="X181">
+        <v>10</v>
+      </c>
+      <c r="Y181">
+        <v>1.06</v>
+      </c>
+      <c r="Z181">
+        <v>2.59</v>
+      </c>
+      <c r="AA181">
+        <v>2.98</v>
+      </c>
+      <c r="AB181">
+        <v>2.88</v>
+      </c>
+      <c r="AC181">
+        <v>1.02</v>
+      </c>
+      <c r="AD181">
+        <v>7.9</v>
+      </c>
+      <c r="AE181">
+        <v>1.38</v>
+      </c>
+      <c r="AF181">
+        <v>2.9</v>
+      </c>
+      <c r="AG181">
+        <v>2.1</v>
+      </c>
+      <c r="AH181">
+        <v>1.6</v>
+      </c>
+      <c r="AI181">
+        <v>1.83</v>
+      </c>
+      <c r="AJ181">
+        <v>1.83</v>
+      </c>
+      <c r="AK181">
+        <v>1.38</v>
+      </c>
+      <c r="AL181">
+        <v>1.31</v>
+      </c>
+      <c r="AM181">
+        <v>1.51</v>
+      </c>
+      <c r="AN181">
+        <v>1.64</v>
+      </c>
+      <c r="AO181">
+        <v>2</v>
+      </c>
+      <c r="AP181">
+        <v>1.58</v>
+      </c>
+      <c r="AQ181">
+        <v>1.92</v>
+      </c>
+      <c r="AR181">
+        <v>2.15</v>
+      </c>
+      <c r="AS181">
+        <v>1.77</v>
+      </c>
+      <c r="AT181">
+        <v>3.92</v>
+      </c>
+      <c r="AU181">
+        <v>5</v>
+      </c>
+      <c r="AV181">
+        <v>9</v>
+      </c>
+      <c r="AW181">
+        <v>1</v>
+      </c>
+      <c r="AX181">
+        <v>3</v>
+      </c>
+      <c r="AY181">
+        <v>6</v>
+      </c>
+      <c r="AZ181">
+        <v>12</v>
+      </c>
+      <c r="BA181">
+        <v>3</v>
+      </c>
+      <c r="BB181">
+        <v>7</v>
+      </c>
+      <c r="BC181">
+        <v>10</v>
+      </c>
+      <c r="BD181">
+        <v>1.83</v>
+      </c>
+      <c r="BE181">
+        <v>6.4</v>
+      </c>
+      <c r="BF181">
+        <v>2.18</v>
+      </c>
+      <c r="BG181">
+        <v>1.35</v>
+      </c>
+      <c r="BH181">
+        <v>2.9</v>
+      </c>
+      <c r="BI181">
+        <v>1.58</v>
+      </c>
+      <c r="BJ181">
+        <v>2.18</v>
+      </c>
+      <c r="BK181">
+        <v>1.95</v>
+      </c>
+      <c r="BL181">
+        <v>1.74</v>
+      </c>
+      <c r="BM181">
+        <v>2.48</v>
+      </c>
+      <c r="BN181">
+        <v>1.47</v>
+      </c>
+      <c r="BO181">
+        <v>3.2</v>
+      </c>
+      <c r="BP181">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="280">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -852,6 +852,9 @@
   <si>
     <t>['90+5', '90+13']</t>
   </si>
+  <si>
+    <t>['90+2']</t>
+  </si>
 </sst>
 </file>
 
@@ -1212,7 +1215,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP181"/>
+  <dimension ref="A1:BP182"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2782,7 +2785,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ8">
         <v>1.36</v>
@@ -4636,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ17">
         <v>0.73</v>
@@ -5463,7 +5466,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ21">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR21">
         <v>0.9</v>
@@ -8344,7 +8347,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ35">
         <v>1.91</v>
@@ -8759,7 +8762,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ37">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR37">
         <v>1.15</v>
@@ -11846,7 +11849,7 @@
         <v>3</v>
       </c>
       <c r="AP52">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ52">
         <v>1.67</v>
@@ -12055,7 +12058,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ53">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR53">
         <v>1.4</v>
@@ -14318,7 +14321,7 @@
         <v>0</v>
       </c>
       <c r="AP64">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ64">
         <v>1.36</v>
@@ -15145,7 +15148,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ68">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR68">
         <v>1.26</v>
@@ -18029,7 +18032,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ82">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR82">
         <v>1.21</v>
@@ -18644,7 +18647,7 @@
         <v>0.75</v>
       </c>
       <c r="AP85">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ85">
         <v>0.42</v>
@@ -21737,7 +21740,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ100">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR100">
         <v>1.22</v>
@@ -22146,7 +22149,7 @@
         <v>0.8</v>
       </c>
       <c r="AP102">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ102">
         <v>0.91</v>
@@ -25033,7 +25036,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ116">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR116">
         <v>1.24</v>
@@ -25442,7 +25445,7 @@
         <v>1.43</v>
       </c>
       <c r="AP118">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ118">
         <v>1.27</v>
@@ -27093,7 +27096,7 @@
         <v>1</v>
       </c>
       <c r="AQ126">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR126">
         <v>1.5</v>
@@ -27917,7 +27920,7 @@
         <v>1</v>
       </c>
       <c r="AQ130">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR130">
         <v>1.03</v>
@@ -28532,7 +28535,7 @@
         <v>1</v>
       </c>
       <c r="AP133">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ133">
         <v>1.27</v>
@@ -31213,7 +31216,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ146">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR146">
         <v>1.29</v>
@@ -32240,7 +32243,7 @@
         <v>1</v>
       </c>
       <c r="AP151">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ151">
         <v>1.09</v>
@@ -34715,7 +34718,7 @@
         <v>1</v>
       </c>
       <c r="AQ163">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR163">
         <v>1.34</v>
@@ -35124,7 +35127,7 @@
         <v>1.9</v>
       </c>
       <c r="AP165">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ165">
         <v>1.92</v>
@@ -38499,6 +38502,212 @@
       </c>
       <c r="BP181">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="182" spans="1:68">
+      <c r="A182" s="1">
+        <v>181</v>
+      </c>
+      <c r="B182">
+        <v>7762774</v>
+      </c>
+      <c r="C182" t="s">
+        <v>68</v>
+      </c>
+      <c r="D182" t="s">
+        <v>69</v>
+      </c>
+      <c r="E182" s="2">
+        <v>45718.51041666666</v>
+      </c>
+      <c r="F182">
+        <v>23</v>
+      </c>
+      <c r="G182" t="s">
+        <v>76</v>
+      </c>
+      <c r="H182" t="s">
+        <v>70</v>
+      </c>
+      <c r="I182">
+        <v>0</v>
+      </c>
+      <c r="J182">
+        <v>0</v>
+      </c>
+      <c r="K182">
+        <v>0</v>
+      </c>
+      <c r="L182">
+        <v>0</v>
+      </c>
+      <c r="M182">
+        <v>1</v>
+      </c>
+      <c r="N182">
+        <v>1</v>
+      </c>
+      <c r="O182" t="s">
+        <v>86</v>
+      </c>
+      <c r="P182" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q182">
+        <v>8.5</v>
+      </c>
+      <c r="R182">
+        <v>2.1</v>
+      </c>
+      <c r="S182">
+        <v>2</v>
+      </c>
+      <c r="T182">
+        <v>1.5</v>
+      </c>
+      <c r="U182">
+        <v>2.5</v>
+      </c>
+      <c r="V182">
+        <v>3.4</v>
+      </c>
+      <c r="W182">
+        <v>1.3</v>
+      </c>
+      <c r="X182">
+        <v>10</v>
+      </c>
+      <c r="Y182">
+        <v>1.06</v>
+      </c>
+      <c r="Z182">
+        <v>8</v>
+      </c>
+      <c r="AA182">
+        <v>4</v>
+      </c>
+      <c r="AB182">
+        <v>1.44</v>
+      </c>
+      <c r="AC182">
+        <v>1</v>
+      </c>
+      <c r="AD182">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE182">
+        <v>1.38</v>
+      </c>
+      <c r="AF182">
+        <v>2.9</v>
+      </c>
+      <c r="AG182">
+        <v>2.05</v>
+      </c>
+      <c r="AH182">
+        <v>1.61</v>
+      </c>
+      <c r="AI182">
+        <v>2.63</v>
+      </c>
+      <c r="AJ182">
+        <v>1.44</v>
+      </c>
+      <c r="AK182">
+        <v>2.6</v>
+      </c>
+      <c r="AL182">
+        <v>1.19</v>
+      </c>
+      <c r="AM182">
+        <v>1.09</v>
+      </c>
+      <c r="AN182">
+        <v>0.64</v>
+      </c>
+      <c r="AO182">
+        <v>1.82</v>
+      </c>
+      <c r="AP182">
+        <v>0.58</v>
+      </c>
+      <c r="AQ182">
+        <v>1.92</v>
+      </c>
+      <c r="AR182">
+        <v>1.01</v>
+      </c>
+      <c r="AS182">
+        <v>1.4</v>
+      </c>
+      <c r="AT182">
+        <v>2.41</v>
+      </c>
+      <c r="AU182">
+        <v>0</v>
+      </c>
+      <c r="AV182">
+        <v>9</v>
+      </c>
+      <c r="AW182">
+        <v>5</v>
+      </c>
+      <c r="AX182">
+        <v>6</v>
+      </c>
+      <c r="AY182">
+        <v>5</v>
+      </c>
+      <c r="AZ182">
+        <v>15</v>
+      </c>
+      <c r="BA182">
+        <v>1</v>
+      </c>
+      <c r="BB182">
+        <v>9</v>
+      </c>
+      <c r="BC182">
+        <v>10</v>
+      </c>
+      <c r="BD182">
+        <v>3.4</v>
+      </c>
+      <c r="BE182">
+        <v>7</v>
+      </c>
+      <c r="BF182">
+        <v>1.38</v>
+      </c>
+      <c r="BG182">
+        <v>1.38</v>
+      </c>
+      <c r="BH182">
+        <v>2.8</v>
+      </c>
+      <c r="BI182">
+        <v>1.64</v>
+      </c>
+      <c r="BJ182">
+        <v>2.1</v>
+      </c>
+      <c r="BK182">
+        <v>2</v>
+      </c>
+      <c r="BL182">
+        <v>1.71</v>
+      </c>
+      <c r="BM182">
+        <v>2.55</v>
+      </c>
+      <c r="BN182">
+        <v>1.45</v>
+      </c>
+      <c r="BO182">
+        <v>3.3</v>
+      </c>
+      <c r="BP182">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="282">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -601,6 +601,9 @@
     <t>['39', '84']</t>
   </si>
   <si>
+    <t>['3', '7', '69']</t>
+  </si>
+  <si>
     <t>['12', '22', '45+1', '45+4', '90+1', '90+8']</t>
   </si>
   <si>
@@ -854,6 +857,9 @@
   </si>
   <si>
     <t>['90+2']</t>
+  </si>
+  <si>
+    <t>['24', '57']</t>
   </si>
 </sst>
 </file>
@@ -1215,7 +1221,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP182"/>
+  <dimension ref="A1:BP184"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1552,7 +1558,7 @@
         <v>2</v>
       </c>
       <c r="AQ2">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2089,7 +2095,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q5">
         <v>7.5</v>
@@ -2295,7 +2301,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2376,7 +2382,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ6">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2707,7 +2713,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q8">
         <v>4</v>
@@ -3197,7 +3203,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ10">
         <v>0.91</v>
@@ -3737,7 +3743,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3943,7 +3949,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q14">
         <v>2.4</v>
@@ -4767,7 +4773,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -5179,7 +5185,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -5385,7 +5391,7 @@
         <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5591,7 +5597,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5672,7 +5678,7 @@
         <v>1</v>
       </c>
       <c r="AQ22">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR22">
         <v>1.34</v>
@@ -5797,7 +5803,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -6003,7 +6009,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q24">
         <v>3.25</v>
@@ -6081,7 +6087,7 @@
         <v>2</v>
       </c>
       <c r="AP24">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ24">
         <v>1.36</v>
@@ -6209,7 +6215,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q25">
         <v>2.05</v>
@@ -6287,7 +6293,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ25">
         <v>0.27</v>
@@ -6415,7 +6421,7 @@
         <v>86</v>
       </c>
       <c r="P26" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -7033,7 +7039,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7445,7 +7451,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7651,7 +7657,7 @@
         <v>86</v>
       </c>
       <c r="P32" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q32">
         <v>2.05</v>
@@ -8144,7 +8150,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ34">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR34">
         <v>0.89</v>
@@ -8350,7 +8356,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ35">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR35">
         <v>0.9399999999999999</v>
@@ -8681,7 +8687,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -9377,7 +9383,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ40">
         <v>1.27</v>
@@ -9505,7 +9511,7 @@
         <v>86</v>
       </c>
       <c r="P41" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q41">
         <v>2.38</v>
@@ -9917,7 +9923,7 @@
         <v>86</v>
       </c>
       <c r="P43" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q43">
         <v>7.5</v>
@@ -10123,7 +10129,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10535,7 +10541,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q46">
         <v>2.5</v>
@@ -10613,7 +10619,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ46">
         <v>1.09</v>
@@ -10741,7 +10747,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q47">
         <v>4.33</v>
@@ -10822,7 +10828,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ47">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR47">
         <v>1.32</v>
@@ -10947,7 +10953,7 @@
         <v>86</v>
       </c>
       <c r="P48" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q48">
         <v>2.4</v>
@@ -11028,7 +11034,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ48">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR48">
         <v>2.19</v>
@@ -11565,7 +11571,7 @@
         <v>116</v>
       </c>
       <c r="P51" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11771,7 +11777,7 @@
         <v>118</v>
       </c>
       <c r="P52" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q52">
         <v>5.5</v>
@@ -12183,7 +12189,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -12595,7 +12601,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q56">
         <v>5.5</v>
@@ -12801,7 +12807,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q57">
         <v>5</v>
@@ -12882,7 +12888,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ57">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR57">
         <v>1.15</v>
@@ -13007,7 +13013,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13213,7 +13219,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13419,7 +13425,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13625,7 +13631,7 @@
         <v>86</v>
       </c>
       <c r="P61" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q61">
         <v>6.5</v>
@@ -13909,7 +13915,7 @@
         <v>3</v>
       </c>
       <c r="AP62">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ62">
         <v>2.36</v>
@@ -14037,7 +14043,7 @@
         <v>86</v>
       </c>
       <c r="P63" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q63">
         <v>3.5</v>
@@ -14118,7 +14124,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ63">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR63">
         <v>1.29</v>
@@ -14243,7 +14249,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14861,7 +14867,7 @@
         <v>86</v>
       </c>
       <c r="P67" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q67">
         <v>6.5</v>
@@ -14939,7 +14945,7 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ67">
         <v>1.92</v>
@@ -15067,7 +15073,7 @@
         <v>86</v>
       </c>
       <c r="P68" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q68">
         <v>4.75</v>
@@ -15557,10 +15563,10 @@
         <v>3</v>
       </c>
       <c r="AP70">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ70">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR70">
         <v>1.49</v>
@@ -15685,7 +15691,7 @@
         <v>92</v>
       </c>
       <c r="P71" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q71">
         <v>9.5</v>
@@ -15766,7 +15772,7 @@
         <v>1</v>
       </c>
       <c r="AQ71">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR71">
         <v>1.26</v>
@@ -16303,7 +16309,7 @@
         <v>86</v>
       </c>
       <c r="P74" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16796,7 +16802,7 @@
         <v>1</v>
       </c>
       <c r="AQ76">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR76">
         <v>1.63</v>
@@ -16921,7 +16927,7 @@
         <v>130</v>
       </c>
       <c r="P77" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q77">
         <v>1.83</v>
@@ -17127,7 +17133,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q78">
         <v>12</v>
@@ -17333,7 +17339,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q79">
         <v>3.75</v>
@@ -17539,7 +17545,7 @@
         <v>131</v>
       </c>
       <c r="P80" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17620,7 +17626,7 @@
         <v>1</v>
       </c>
       <c r="AQ80">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR80">
         <v>1.54</v>
@@ -17745,7 +17751,7 @@
         <v>132</v>
       </c>
       <c r="P81" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -17823,7 +17829,7 @@
         <v>1.8</v>
       </c>
       <c r="AP81">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ81">
         <v>1.67</v>
@@ -18029,7 +18035,7 @@
         <v>1.75</v>
       </c>
       <c r="AP82">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ82">
         <v>1.92</v>
@@ -18157,7 +18163,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q83">
         <v>1.67</v>
@@ -18775,7 +18781,7 @@
         <v>134</v>
       </c>
       <c r="P86" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q86">
         <v>2.63</v>
@@ -20423,7 +20429,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q94">
         <v>13</v>
@@ -20629,7 +20635,7 @@
         <v>139</v>
       </c>
       <c r="P95" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -21041,7 +21047,7 @@
         <v>140</v>
       </c>
       <c r="P97" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q97">
         <v>2.4</v>
@@ -21119,7 +21125,7 @@
         <v>1</v>
       </c>
       <c r="AP97">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ97">
         <v>1.17</v>
@@ -21531,7 +21537,7 @@
         <v>1.2</v>
       </c>
       <c r="AP99">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ99">
         <v>1.36</v>
@@ -21865,7 +21871,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22358,7 +22364,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ103">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR103">
         <v>1.72</v>
@@ -22483,7 +22489,7 @@
         <v>145</v>
       </c>
       <c r="P104" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22689,7 +22695,7 @@
         <v>86</v>
       </c>
       <c r="P105" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -22895,7 +22901,7 @@
         <v>146</v>
       </c>
       <c r="P106" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q106">
         <v>6</v>
@@ -23307,7 +23313,7 @@
         <v>147</v>
       </c>
       <c r="P108" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23719,7 +23725,7 @@
         <v>149</v>
       </c>
       <c r="P110" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -24006,7 +24012,7 @@
         <v>1</v>
       </c>
       <c r="AQ111">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR111">
         <v>1.08</v>
@@ -24131,7 +24137,7 @@
         <v>143</v>
       </c>
       <c r="P112" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q112">
         <v>4.75</v>
@@ -24415,7 +24421,7 @@
         <v>0.67</v>
       </c>
       <c r="AP113">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ113">
         <v>0.42</v>
@@ -24827,7 +24833,7 @@
         <v>1.33</v>
       </c>
       <c r="AP115">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ115">
         <v>1.27</v>
@@ -24955,7 +24961,7 @@
         <v>86</v>
       </c>
       <c r="P116" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q116">
         <v>4.5</v>
@@ -25161,7 +25167,7 @@
         <v>153</v>
       </c>
       <c r="P117" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q117">
         <v>1.53</v>
@@ -25367,7 +25373,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25448,7 +25454,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ118">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR118">
         <v>0.95</v>
@@ -25573,7 +25579,7 @@
         <v>154</v>
       </c>
       <c r="P119" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q119">
         <v>1.8</v>
@@ -25779,7 +25785,7 @@
         <v>155</v>
       </c>
       <c r="P120" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q120">
         <v>7.5</v>
@@ -26191,7 +26197,7 @@
         <v>157</v>
       </c>
       <c r="P122" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q122">
         <v>2.63</v>
@@ -26269,7 +26275,7 @@
         <v>1.14</v>
       </c>
       <c r="AP122">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ122">
         <v>1.27</v>
@@ -26397,7 +26403,7 @@
         <v>158</v>
       </c>
       <c r="P123" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q123">
         <v>1.73</v>
@@ -27015,7 +27021,7 @@
         <v>86</v>
       </c>
       <c r="P126" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27221,7 +27227,7 @@
         <v>161</v>
       </c>
       <c r="P127" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27427,7 +27433,7 @@
         <v>86</v>
       </c>
       <c r="P128" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q128">
         <v>2.4</v>
@@ -27505,7 +27511,7 @@
         <v>0.86</v>
       </c>
       <c r="AP128">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ128">
         <v>0.91</v>
@@ -27633,7 +27639,7 @@
         <v>138</v>
       </c>
       <c r="P129" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27714,7 +27720,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ129">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR129">
         <v>1.45</v>
@@ -27839,7 +27845,7 @@
         <v>98</v>
       </c>
       <c r="P130" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q130">
         <v>6.5</v>
@@ -28045,7 +28051,7 @@
         <v>162</v>
       </c>
       <c r="P131" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q131">
         <v>4.33</v>
@@ -28251,7 +28257,7 @@
         <v>86</v>
       </c>
       <c r="P132" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q132">
         <v>8</v>
@@ -28744,7 +28750,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ134">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR134">
         <v>1.33</v>
@@ -29899,7 +29905,7 @@
         <v>167</v>
       </c>
       <c r="P140" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q140">
         <v>2.3</v>
@@ -30105,7 +30111,7 @@
         <v>86</v>
       </c>
       <c r="P141" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q141">
         <v>7.5</v>
@@ -30183,7 +30189,7 @@
         <v>2.71</v>
       </c>
       <c r="AP141">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ141">
         <v>2.36</v>
@@ -30311,7 +30317,7 @@
         <v>168</v>
       </c>
       <c r="P142" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30517,7 +30523,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30595,7 +30601,7 @@
         <v>0.25</v>
       </c>
       <c r="AP143">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ143">
         <v>0.27</v>
@@ -30929,7 +30935,7 @@
         <v>171</v>
       </c>
       <c r="P145" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q145">
         <v>3.75</v>
@@ -31135,7 +31141,7 @@
         <v>172</v>
       </c>
       <c r="P146" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q146">
         <v>7.5</v>
@@ -31341,7 +31347,7 @@
         <v>173</v>
       </c>
       <c r="P147" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31422,7 +31428,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ147">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR147">
         <v>2.12</v>
@@ -31547,7 +31553,7 @@
         <v>174</v>
       </c>
       <c r="P148" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q148">
         <v>2.75</v>
@@ -31753,7 +31759,7 @@
         <v>86</v>
       </c>
       <c r="P149" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q149">
         <v>7.5</v>
@@ -32040,7 +32046,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ150">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR150">
         <v>1.74</v>
@@ -32165,7 +32171,7 @@
         <v>86</v>
       </c>
       <c r="P151" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q151">
         <v>6.5</v>
@@ -32371,7 +32377,7 @@
         <v>176</v>
       </c>
       <c r="P152" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q152">
         <v>2.75</v>
@@ -32577,7 +32583,7 @@
         <v>177</v>
       </c>
       <c r="P153" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q153">
         <v>4.75</v>
@@ -32861,7 +32867,7 @@
         <v>1.56</v>
       </c>
       <c r="AP154">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ154">
         <v>1.36</v>
@@ -32989,7 +32995,7 @@
         <v>179</v>
       </c>
       <c r="P155" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33195,7 +33201,7 @@
         <v>176</v>
       </c>
       <c r="P156" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q156">
         <v>2.2</v>
@@ -33479,7 +33485,7 @@
         <v>1.22</v>
       </c>
       <c r="AP157">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ157">
         <v>1.27</v>
@@ -33607,7 +33613,7 @@
         <v>181</v>
       </c>
       <c r="P158" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -34431,7 +34437,7 @@
         <v>86</v>
       </c>
       <c r="P162" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q162">
         <v>3.5</v>
@@ -34637,7 +34643,7 @@
         <v>184</v>
       </c>
       <c r="P163" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -34924,7 +34930,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ164">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR164">
         <v>1.55</v>
@@ -35049,7 +35055,7 @@
         <v>185</v>
       </c>
       <c r="P165" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q165">
         <v>9.5</v>
@@ -35951,10 +35957,10 @@
         <v>1.3</v>
       </c>
       <c r="AP169">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ169">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR169">
         <v>1.46</v>
@@ -36775,7 +36781,7 @@
         <v>0.7</v>
       </c>
       <c r="AP173">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ173">
         <v>0.73</v>
@@ -36903,7 +36909,7 @@
         <v>86</v>
       </c>
       <c r="P174" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q174">
         <v>3.75</v>
@@ -37109,7 +37115,7 @@
         <v>124</v>
       </c>
       <c r="P175" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q175">
         <v>5.5</v>
@@ -37315,7 +37321,7 @@
         <v>86</v>
       </c>
       <c r="P176" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q176">
         <v>3.1</v>
@@ -37727,7 +37733,7 @@
         <v>86</v>
       </c>
       <c r="P178" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q178">
         <v>3.5</v>
@@ -38139,7 +38145,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38345,7 +38351,7 @@
         <v>194</v>
       </c>
       <c r="P181" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q181">
         <v>3.2</v>
@@ -38551,7 +38557,7 @@
         <v>86</v>
       </c>
       <c r="P182" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q182">
         <v>8.5</v>
@@ -38708,6 +38714,418 @@
       </c>
       <c r="BP182">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="183" spans="1:68">
+      <c r="A183" s="1">
+        <v>182</v>
+      </c>
+      <c r="B183">
+        <v>7762770</v>
+      </c>
+      <c r="C183" t="s">
+        <v>68</v>
+      </c>
+      <c r="D183" t="s">
+        <v>69</v>
+      </c>
+      <c r="E183" s="2">
+        <v>45719.3125</v>
+      </c>
+      <c r="F183">
+        <v>23</v>
+      </c>
+      <c r="G183" t="s">
+        <v>78</v>
+      </c>
+      <c r="H183" t="s">
+        <v>81</v>
+      </c>
+      <c r="I183">
+        <v>1</v>
+      </c>
+      <c r="J183">
+        <v>0</v>
+      </c>
+      <c r="K183">
+        <v>1</v>
+      </c>
+      <c r="L183">
+        <v>1</v>
+      </c>
+      <c r="M183">
+        <v>0</v>
+      </c>
+      <c r="N183">
+        <v>1</v>
+      </c>
+      <c r="O183" t="s">
+        <v>87</v>
+      </c>
+      <c r="P183" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q183">
+        <v>2.5</v>
+      </c>
+      <c r="R183">
+        <v>2.1</v>
+      </c>
+      <c r="S183">
+        <v>4.5</v>
+      </c>
+      <c r="T183">
+        <v>1.44</v>
+      </c>
+      <c r="U183">
+        <v>2.63</v>
+      </c>
+      <c r="V183">
+        <v>3</v>
+      </c>
+      <c r="W183">
+        <v>1.36</v>
+      </c>
+      <c r="X183">
+        <v>9</v>
+      </c>
+      <c r="Y183">
+        <v>1.07</v>
+      </c>
+      <c r="Z183">
+        <v>1.86</v>
+      </c>
+      <c r="AA183">
+        <v>3.36</v>
+      </c>
+      <c r="AB183">
+        <v>4.3</v>
+      </c>
+      <c r="AC183">
+        <v>1</v>
+      </c>
+      <c r="AD183">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE183">
+        <v>1.35</v>
+      </c>
+      <c r="AF183">
+        <v>3.05</v>
+      </c>
+      <c r="AG183">
+        <v>1.98</v>
+      </c>
+      <c r="AH183">
+        <v>1.77</v>
+      </c>
+      <c r="AI183">
+        <v>1.83</v>
+      </c>
+      <c r="AJ183">
+        <v>1.83</v>
+      </c>
+      <c r="AK183">
+        <v>1.22</v>
+      </c>
+      <c r="AL183">
+        <v>1.28</v>
+      </c>
+      <c r="AM183">
+        <v>1.84</v>
+      </c>
+      <c r="AN183">
+        <v>2.18</v>
+      </c>
+      <c r="AO183">
+        <v>1.27</v>
+      </c>
+      <c r="AP183">
+        <v>2.25</v>
+      </c>
+      <c r="AQ183">
+        <v>1.17</v>
+      </c>
+      <c r="AR183">
+        <v>1.48</v>
+      </c>
+      <c r="AS183">
+        <v>1.53</v>
+      </c>
+      <c r="AT183">
+        <v>3.01</v>
+      </c>
+      <c r="AU183">
+        <v>5</v>
+      </c>
+      <c r="AV183">
+        <v>6</v>
+      </c>
+      <c r="AW183">
+        <v>4</v>
+      </c>
+      <c r="AX183">
+        <v>11</v>
+      </c>
+      <c r="AY183">
+        <v>9</v>
+      </c>
+      <c r="AZ183">
+        <v>17</v>
+      </c>
+      <c r="BA183">
+        <v>1</v>
+      </c>
+      <c r="BB183">
+        <v>6</v>
+      </c>
+      <c r="BC183">
+        <v>7</v>
+      </c>
+      <c r="BD183">
+        <v>1.65</v>
+      </c>
+      <c r="BE183">
+        <v>6.4</v>
+      </c>
+      <c r="BF183">
+        <v>2.55</v>
+      </c>
+      <c r="BG183">
+        <v>1.4</v>
+      </c>
+      <c r="BH183">
+        <v>2.65</v>
+      </c>
+      <c r="BI183">
+        <v>1.68</v>
+      </c>
+      <c r="BJ183">
+        <v>2.05</v>
+      </c>
+      <c r="BK183">
+        <v>2.08</v>
+      </c>
+      <c r="BL183">
+        <v>1.65</v>
+      </c>
+      <c r="BM183">
+        <v>2.65</v>
+      </c>
+      <c r="BN183">
+        <v>1.4</v>
+      </c>
+      <c r="BO183">
+        <v>3.55</v>
+      </c>
+      <c r="BP183">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="184" spans="1:68">
+      <c r="A184" s="1">
+        <v>183</v>
+      </c>
+      <c r="B184">
+        <v>7762771</v>
+      </c>
+      <c r="C184" t="s">
+        <v>68</v>
+      </c>
+      <c r="D184" t="s">
+        <v>69</v>
+      </c>
+      <c r="E184" s="2">
+        <v>45719.41666666666</v>
+      </c>
+      <c r="F184">
+        <v>23</v>
+      </c>
+      <c r="G184" t="s">
+        <v>85</v>
+      </c>
+      <c r="H184" t="s">
+        <v>82</v>
+      </c>
+      <c r="I184">
+        <v>2</v>
+      </c>
+      <c r="J184">
+        <v>1</v>
+      </c>
+      <c r="K184">
+        <v>3</v>
+      </c>
+      <c r="L184">
+        <v>3</v>
+      </c>
+      <c r="M184">
+        <v>2</v>
+      </c>
+      <c r="N184">
+        <v>5</v>
+      </c>
+      <c r="O184" t="s">
+        <v>195</v>
+      </c>
+      <c r="P184" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q184">
+        <v>3.6</v>
+      </c>
+      <c r="R184">
+        <v>2.05</v>
+      </c>
+      <c r="S184">
+        <v>3.1</v>
+      </c>
+      <c r="T184">
+        <v>1.44</v>
+      </c>
+      <c r="U184">
+        <v>2.63</v>
+      </c>
+      <c r="V184">
+        <v>3.25</v>
+      </c>
+      <c r="W184">
+        <v>1.33</v>
+      </c>
+      <c r="X184">
+        <v>10</v>
+      </c>
+      <c r="Y184">
+        <v>1.06</v>
+      </c>
+      <c r="Z184">
+        <v>2.86</v>
+      </c>
+      <c r="AA184">
+        <v>3.02</v>
+      </c>
+      <c r="AB184">
+        <v>2.57</v>
+      </c>
+      <c r="AC184">
+        <v>1.02</v>
+      </c>
+      <c r="AD184">
+        <v>7.8</v>
+      </c>
+      <c r="AE184">
+        <v>1.37</v>
+      </c>
+      <c r="AF184">
+        <v>2.95</v>
+      </c>
+      <c r="AG184">
+        <v>1.98</v>
+      </c>
+      <c r="AH184">
+        <v>1.77</v>
+      </c>
+      <c r="AI184">
+        <v>1.83</v>
+      </c>
+      <c r="AJ184">
+        <v>1.83</v>
+      </c>
+      <c r="AK184">
+        <v>1.49</v>
+      </c>
+      <c r="AL184">
+        <v>1.31</v>
+      </c>
+      <c r="AM184">
+        <v>1.39</v>
+      </c>
+      <c r="AN184">
+        <v>1.82</v>
+      </c>
+      <c r="AO184">
+        <v>1.91</v>
+      </c>
+      <c r="AP184">
+        <v>1.92</v>
+      </c>
+      <c r="AQ184">
+        <v>1.75</v>
+      </c>
+      <c r="AR184">
+        <v>1.43</v>
+      </c>
+      <c r="AS184">
+        <v>1.46</v>
+      </c>
+      <c r="AT184">
+        <v>2.89</v>
+      </c>
+      <c r="AU184">
+        <v>7</v>
+      </c>
+      <c r="AV184">
+        <v>5</v>
+      </c>
+      <c r="AW184">
+        <v>6</v>
+      </c>
+      <c r="AX184">
+        <v>3</v>
+      </c>
+      <c r="AY184">
+        <v>13</v>
+      </c>
+      <c r="AZ184">
+        <v>8</v>
+      </c>
+      <c r="BA184">
+        <v>3</v>
+      </c>
+      <c r="BB184">
+        <v>2</v>
+      </c>
+      <c r="BC184">
+        <v>5</v>
+      </c>
+      <c r="BD184">
+        <v>2.28</v>
+      </c>
+      <c r="BE184">
+        <v>6.75</v>
+      </c>
+      <c r="BF184">
+        <v>1.74</v>
+      </c>
+      <c r="BG184">
+        <v>1.24</v>
+      </c>
+      <c r="BH184">
+        <v>3.65</v>
+      </c>
+      <c r="BI184">
+        <v>1.41</v>
+      </c>
+      <c r="BJ184">
+        <v>2.65</v>
+      </c>
+      <c r="BK184">
+        <v>1.67</v>
+      </c>
+      <c r="BL184">
+        <v>2.07</v>
+      </c>
+      <c r="BM184">
+        <v>2.02</v>
+      </c>
+      <c r="BN184">
+        <v>1.68</v>
+      </c>
+      <c r="BO184">
+        <v>2.55</v>
+      </c>
+      <c r="BP184">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="282">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1221,7 +1221,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP184"/>
+  <dimension ref="A1:BP185"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AQ7">
         <v>1.27</v>
@@ -4442,7 +4442,7 @@
         <v>2</v>
       </c>
       <c r="AQ16">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR16">
         <v>2.14</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AQ20">
         <v>1.09</v>
@@ -7941,7 +7941,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AQ33">
         <v>1.92</v>
@@ -8562,7 +8562,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ36">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR36">
         <v>1.19</v>
@@ -11446,7 +11446,7 @@
         <v>1</v>
       </c>
       <c r="AQ50">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR50">
         <v>1.44</v>
@@ -12061,7 +12061,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AQ53">
         <v>1.92</v>
@@ -14330,7 +14330,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ64">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR64">
         <v>0.92</v>
@@ -14739,7 +14739,7 @@
         <v>1.67</v>
       </c>
       <c r="AP66">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AQ66">
         <v>1.17</v>
@@ -18244,7 +18244,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ83">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR83">
         <v>1.8</v>
@@ -19065,7 +19065,7 @@
         <v>2.33</v>
       </c>
       <c r="AP87">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AQ87">
         <v>1.27</v>
@@ -21540,7 +21540,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ99">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR99">
         <v>1.34</v>
@@ -22361,7 +22361,7 @@
         <v>1.67</v>
       </c>
       <c r="AP103">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AQ103">
         <v>1.17</v>
@@ -23597,7 +23597,7 @@
         <v>0.33</v>
       </c>
       <c r="AP109">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AQ109">
         <v>0.27</v>
@@ -25248,7 +25248,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ117">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR117">
         <v>1.99</v>
@@ -26896,7 +26896,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ125">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR125">
         <v>1.25</v>
@@ -29159,7 +29159,7 @@
         <v>0.5</v>
       </c>
       <c r="AP136">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AQ136">
         <v>0.73</v>
@@ -29368,7 +29368,7 @@
         <v>1</v>
       </c>
       <c r="AQ137">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR137">
         <v>1.54</v>
@@ -31634,7 +31634,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ148">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR148">
         <v>1.13</v>
@@ -32043,7 +32043,7 @@
         <v>2.33</v>
       </c>
       <c r="AP150">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AQ150">
         <v>1.75</v>
@@ -35342,7 +35342,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ166">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR166">
         <v>1.31</v>
@@ -35545,7 +35545,7 @@
         <v>1.7</v>
       </c>
       <c r="AP167">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AQ167">
         <v>1.67</v>
@@ -39126,6 +39126,212 @@
       </c>
       <c r="BP184">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="185" spans="1:68">
+      <c r="A185" s="1">
+        <v>184</v>
+      </c>
+      <c r="B185">
+        <v>7762775</v>
+      </c>
+      <c r="C185" t="s">
+        <v>68</v>
+      </c>
+      <c r="D185" t="s">
+        <v>69</v>
+      </c>
+      <c r="E185" s="2">
+        <v>45719.52083333334</v>
+      </c>
+      <c r="F185">
+        <v>23</v>
+      </c>
+      <c r="G185" t="s">
+        <v>75</v>
+      </c>
+      <c r="H185" t="s">
+        <v>77</v>
+      </c>
+      <c r="I185">
+        <v>0</v>
+      </c>
+      <c r="J185">
+        <v>0</v>
+      </c>
+      <c r="K185">
+        <v>0</v>
+      </c>
+      <c r="L185">
+        <v>0</v>
+      </c>
+      <c r="M185">
+        <v>0</v>
+      </c>
+      <c r="N185">
+        <v>0</v>
+      </c>
+      <c r="O185" t="s">
+        <v>86</v>
+      </c>
+      <c r="P185" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q185">
+        <v>1.36</v>
+      </c>
+      <c r="R185">
+        <v>3.4</v>
+      </c>
+      <c r="S185">
+        <v>17</v>
+      </c>
+      <c r="T185">
+        <v>1.2</v>
+      </c>
+      <c r="U185">
+        <v>4.33</v>
+      </c>
+      <c r="V185">
+        <v>1.91</v>
+      </c>
+      <c r="W185">
+        <v>1.8</v>
+      </c>
+      <c r="X185">
+        <v>4</v>
+      </c>
+      <c r="Y185">
+        <v>1.22</v>
+      </c>
+      <c r="Z185">
+        <v>1.08</v>
+      </c>
+      <c r="AA185">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AB185">
+        <v>23</v>
+      </c>
+      <c r="AC185">
+        <v>1.01</v>
+      </c>
+      <c r="AD185">
+        <v>29</v>
+      </c>
+      <c r="AE185">
+        <v>1.1</v>
+      </c>
+      <c r="AF185">
+        <v>6.2</v>
+      </c>
+      <c r="AG185">
+        <v>1.37</v>
+      </c>
+      <c r="AH185">
+        <v>2.85</v>
+      </c>
+      <c r="AI185">
+        <v>2.63</v>
+      </c>
+      <c r="AJ185">
+        <v>1.44</v>
+      </c>
+      <c r="AK185">
+        <v>1.01</v>
+      </c>
+      <c r="AL185">
+        <v>1.03</v>
+      </c>
+      <c r="AM185">
+        <v>5.8</v>
+      </c>
+      <c r="AN185">
+        <v>2.82</v>
+      </c>
+      <c r="AO185">
+        <v>1.36</v>
+      </c>
+      <c r="AP185">
+        <v>2.67</v>
+      </c>
+      <c r="AQ185">
+        <v>1.33</v>
+      </c>
+      <c r="AR185">
+        <v>1.72</v>
+      </c>
+      <c r="AS185">
+        <v>1.16</v>
+      </c>
+      <c r="AT185">
+        <v>2.88</v>
+      </c>
+      <c r="AU185">
+        <v>10</v>
+      </c>
+      <c r="AV185">
+        <v>2</v>
+      </c>
+      <c r="AW185">
+        <v>13</v>
+      </c>
+      <c r="AX185">
+        <v>2</v>
+      </c>
+      <c r="AY185">
+        <v>23</v>
+      </c>
+      <c r="AZ185">
+        <v>4</v>
+      </c>
+      <c r="BA185">
+        <v>22</v>
+      </c>
+      <c r="BB185">
+        <v>2</v>
+      </c>
+      <c r="BC185">
+        <v>24</v>
+      </c>
+      <c r="BD185">
+        <v>1.09</v>
+      </c>
+      <c r="BE185">
+        <v>11.5</v>
+      </c>
+      <c r="BF185">
+        <v>7</v>
+      </c>
+      <c r="BG185">
+        <v>1.26</v>
+      </c>
+      <c r="BH185">
+        <v>3.4</v>
+      </c>
+      <c r="BI185">
+        <v>1.45</v>
+      </c>
+      <c r="BJ185">
+        <v>2.55</v>
+      </c>
+      <c r="BK185">
+        <v>1.72</v>
+      </c>
+      <c r="BL185">
+        <v>1.98</v>
+      </c>
+      <c r="BM185">
+        <v>2.1</v>
+      </c>
+      <c r="BN185">
+        <v>1.65</v>
+      </c>
+      <c r="BO185">
+        <v>2.65</v>
+      </c>
+      <c r="BP185">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="282">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1221,7 +1221,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP185"/>
+  <dimension ref="A1:BP186"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2379,7 +2379,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ6">
         <v>1.75</v>
@@ -3206,7 +3206,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ10">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -5881,7 +5881,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ23">
         <v>1.67</v>
@@ -6708,7 +6708,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ27">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR27">
         <v>1.64</v>
@@ -8559,7 +8559,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ36">
         <v>1.33</v>
@@ -10416,7 +10416,7 @@
         <v>2</v>
       </c>
       <c r="AQ45">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR45">
         <v>2.07</v>
@@ -10825,7 +10825,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ47">
         <v>1.17</v>
@@ -12473,7 +12473,7 @@
         <v>1.75</v>
       </c>
       <c r="AP55">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ55">
         <v>1.36</v>
@@ -16390,7 +16390,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ74">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR74">
         <v>1.27</v>
@@ -17211,7 +17211,7 @@
         <v>3</v>
       </c>
       <c r="AP78">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ78">
         <v>2.36</v>
@@ -19477,7 +19477,7 @@
         <v>1.75</v>
       </c>
       <c r="AP89">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ89">
         <v>1.27</v>
@@ -19686,7 +19686,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ90">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR90">
         <v>1.18</v>
@@ -22158,7 +22158,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ102">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR102">
         <v>0.91</v>
@@ -22567,7 +22567,7 @@
         <v>0.57</v>
       </c>
       <c r="AP104">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ104">
         <v>0.73</v>
@@ -25660,7 +25660,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ119">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR119">
         <v>2</v>
@@ -27514,7 +27514,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ128">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR128">
         <v>1.33</v>
@@ -28335,7 +28335,7 @@
         <v>1.63</v>
       </c>
       <c r="AP132">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ132">
         <v>1.92</v>
@@ -30810,7 +30810,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ144">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR144">
         <v>1.48</v>
@@ -31219,7 +31219,7 @@
         <v>1.78</v>
       </c>
       <c r="AP146">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ146">
         <v>1.92</v>
@@ -34312,7 +34312,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ161">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR161">
         <v>1.48</v>
@@ -34515,7 +34515,7 @@
         <v>0.8</v>
       </c>
       <c r="AP162">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ162">
         <v>1.17</v>
@@ -37608,7 +37608,7 @@
         <v>1</v>
       </c>
       <c r="AQ177">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR177">
         <v>1.06</v>
@@ -39332,6 +39332,212 @@
       </c>
       <c r="BP185">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="186" spans="1:68">
+      <c r="A186" s="1">
+        <v>185</v>
+      </c>
+      <c r="B186">
+        <v>7762779</v>
+      </c>
+      <c r="C186" t="s">
+        <v>68</v>
+      </c>
+      <c r="D186" t="s">
+        <v>69</v>
+      </c>
+      <c r="E186" s="2">
+        <v>45723.52083333334</v>
+      </c>
+      <c r="F186">
+        <v>24</v>
+      </c>
+      <c r="G186" t="s">
+        <v>74</v>
+      </c>
+      <c r="H186" t="s">
+        <v>71</v>
+      </c>
+      <c r="I186">
+        <v>0</v>
+      </c>
+      <c r="J186">
+        <v>0</v>
+      </c>
+      <c r="K186">
+        <v>0</v>
+      </c>
+      <c r="L186">
+        <v>0</v>
+      </c>
+      <c r="M186">
+        <v>0</v>
+      </c>
+      <c r="N186">
+        <v>0</v>
+      </c>
+      <c r="O186" t="s">
+        <v>86</v>
+      </c>
+      <c r="P186" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q186">
+        <v>3.26</v>
+      </c>
+      <c r="R186">
+        <v>1.93</v>
+      </c>
+      <c r="S186">
+        <v>3.6</v>
+      </c>
+      <c r="T186">
+        <v>1.5</v>
+      </c>
+      <c r="U186">
+        <v>2.5</v>
+      </c>
+      <c r="V186">
+        <v>3.3</v>
+      </c>
+      <c r="W186">
+        <v>1.27</v>
+      </c>
+      <c r="X186">
+        <v>9</v>
+      </c>
+      <c r="Y186">
+        <v>1.03</v>
+      </c>
+      <c r="Z186">
+        <v>2.62</v>
+      </c>
+      <c r="AA186">
+        <v>3.09</v>
+      </c>
+      <c r="AB186">
+        <v>2.74</v>
+      </c>
+      <c r="AC186">
+        <v>1.09</v>
+      </c>
+      <c r="AD186">
+        <v>6.2</v>
+      </c>
+      <c r="AE186">
+        <v>1.44</v>
+      </c>
+      <c r="AF186">
+        <v>2.7</v>
+      </c>
+      <c r="AG186">
+        <v>2.3</v>
+      </c>
+      <c r="AH186">
+        <v>1.5</v>
+      </c>
+      <c r="AI186">
+        <v>2.04</v>
+      </c>
+      <c r="AJ186">
+        <v>1.68</v>
+      </c>
+      <c r="AK186">
+        <v>1.34</v>
+      </c>
+      <c r="AL186">
+        <v>1.32</v>
+      </c>
+      <c r="AM186">
+        <v>1.51</v>
+      </c>
+      <c r="AN186">
+        <v>0.73</v>
+      </c>
+      <c r="AO186">
+        <v>0.91</v>
+      </c>
+      <c r="AP186">
+        <v>0.75</v>
+      </c>
+      <c r="AQ186">
+        <v>0.92</v>
+      </c>
+      <c r="AR186">
+        <v>1.29</v>
+      </c>
+      <c r="AS186">
+        <v>0.96</v>
+      </c>
+      <c r="AT186">
+        <v>2.25</v>
+      </c>
+      <c r="AU186">
+        <v>6</v>
+      </c>
+      <c r="AV186">
+        <v>4</v>
+      </c>
+      <c r="AW186">
+        <v>4</v>
+      </c>
+      <c r="AX186">
+        <v>4</v>
+      </c>
+      <c r="AY186">
+        <v>10</v>
+      </c>
+      <c r="AZ186">
+        <v>8</v>
+      </c>
+      <c r="BA186">
+        <v>6</v>
+      </c>
+      <c r="BB186">
+        <v>1</v>
+      </c>
+      <c r="BC186">
+        <v>7</v>
+      </c>
+      <c r="BD186">
+        <v>1.76</v>
+      </c>
+      <c r="BE186">
+        <v>6.4</v>
+      </c>
+      <c r="BF186">
+        <v>2.3</v>
+      </c>
+      <c r="BG186">
+        <v>1.42</v>
+      </c>
+      <c r="BH186">
+        <v>2.65</v>
+      </c>
+      <c r="BI186">
+        <v>1.72</v>
+      </c>
+      <c r="BJ186">
+        <v>1.98</v>
+      </c>
+      <c r="BK186">
+        <v>2.1</v>
+      </c>
+      <c r="BL186">
+        <v>1.64</v>
+      </c>
+      <c r="BM186">
+        <v>2.7</v>
+      </c>
+      <c r="BN186">
+        <v>1.38</v>
+      </c>
+      <c r="BO186">
+        <v>3.55</v>
+      </c>
+      <c r="BP186">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="285">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -604,6 +604,9 @@
     <t>['3', '7', '69']</t>
   </si>
   <si>
+    <t>['40', '90+2']</t>
+  </si>
+  <si>
     <t>['12', '22', '45+1', '45+4', '90+1', '90+8']</t>
   </si>
   <si>
@@ -860,6 +863,12 @@
   </si>
   <si>
     <t>['24', '57']</t>
+  </si>
+  <si>
+    <t>['53', '72']</t>
+  </si>
+  <si>
+    <t>['72']</t>
   </si>
 </sst>
 </file>
@@ -1221,7 +1230,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP186"/>
+  <dimension ref="A1:BP189"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1555,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ2">
         <v>1.17</v>
@@ -2095,7 +2104,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q5">
         <v>7.5</v>
@@ -2301,7 +2310,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2588,7 +2597,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ7">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2713,7 +2722,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q8">
         <v>4</v>
@@ -2794,7 +2803,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ8">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3743,7 +3752,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3821,10 +3830,10 @@
         <v>3</v>
       </c>
       <c r="AP13">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ13">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3949,7 +3958,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q14">
         <v>2.4</v>
@@ -4030,7 +4039,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ14">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4233,7 +4242,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ15">
         <v>1.17</v>
@@ -4439,7 +4448,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ16">
         <v>1.33</v>
@@ -4773,7 +4782,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -5060,7 +5069,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ19">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5185,7 +5194,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -5391,7 +5400,7 @@
         <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5597,7 +5606,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5803,7 +5812,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -6009,7 +6018,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q24">
         <v>3.25</v>
@@ -6090,7 +6099,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ24">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -6215,7 +6224,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q25">
         <v>2.05</v>
@@ -6421,7 +6430,7 @@
         <v>86</v>
       </c>
       <c r="P26" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6499,10 +6508,10 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ26">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR26">
         <v>1.84</v>
@@ -7039,7 +7048,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7117,7 +7126,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ29">
         <v>0.42</v>
@@ -7451,7 +7460,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7657,7 +7666,7 @@
         <v>86</v>
       </c>
       <c r="P32" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q32">
         <v>2.05</v>
@@ -8687,7 +8696,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -9386,7 +9395,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ40">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR40">
         <v>1.4</v>
@@ -9511,7 +9520,7 @@
         <v>86</v>
       </c>
       <c r="P41" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q41">
         <v>2.38</v>
@@ -9592,7 +9601,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ41">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR41">
         <v>1.88</v>
@@ -9795,7 +9804,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ42">
         <v>0.73</v>
@@ -9923,7 +9932,7 @@
         <v>86</v>
       </c>
       <c r="P43" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q43">
         <v>7.5</v>
@@ -10001,7 +10010,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ43">
         <v>2.36</v>
@@ -10129,7 +10138,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10210,7 +10219,7 @@
         <v>1</v>
       </c>
       <c r="AQ44">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR44">
         <v>0.95</v>
@@ -10413,7 +10422,7 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ45">
         <v>0.92</v>
@@ -10541,7 +10550,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q46">
         <v>2.5</v>
@@ -10747,7 +10756,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q47">
         <v>4.33</v>
@@ -10953,7 +10962,7 @@
         <v>86</v>
       </c>
       <c r="P48" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q48">
         <v>2.4</v>
@@ -11571,7 +11580,7 @@
         <v>116</v>
       </c>
       <c r="P51" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11777,7 +11786,7 @@
         <v>118</v>
       </c>
       <c r="P52" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q52">
         <v>5.5</v>
@@ -12189,7 +12198,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -12476,7 +12485,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ55">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR55">
         <v>1.49</v>
@@ -12601,7 +12610,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q56">
         <v>5.5</v>
@@ -12807,7 +12816,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q57">
         <v>5</v>
@@ -12885,7 +12894,7 @@
         <v>3</v>
       </c>
       <c r="AP57">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ57">
         <v>1.75</v>
@@ -13013,7 +13022,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13091,7 +13100,7 @@
         <v>0.25</v>
       </c>
       <c r="AP58">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ58">
         <v>1.09</v>
@@ -13219,7 +13228,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13297,7 +13306,7 @@
         <v>1.75</v>
       </c>
       <c r="AP59">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ59">
         <v>1.92</v>
@@ -13425,7 +13434,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13631,7 +13640,7 @@
         <v>86</v>
       </c>
       <c r="P61" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q61">
         <v>6.5</v>
@@ -13712,7 +13721,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ61">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR61">
         <v>1.06</v>
@@ -14043,7 +14052,7 @@
         <v>86</v>
       </c>
       <c r="P63" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q63">
         <v>3.5</v>
@@ -14249,7 +14258,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14867,7 +14876,7 @@
         <v>86</v>
       </c>
       <c r="P67" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q67">
         <v>6.5</v>
@@ -15073,7 +15082,7 @@
         <v>86</v>
       </c>
       <c r="P68" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q68">
         <v>4.75</v>
@@ -15691,7 +15700,7 @@
         <v>92</v>
       </c>
       <c r="P71" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q71">
         <v>9.5</v>
@@ -16181,7 +16190,7 @@
         <v>0.8</v>
       </c>
       <c r="AP73">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ73">
         <v>0.73</v>
@@ -16309,7 +16318,7 @@
         <v>86</v>
       </c>
       <c r="P74" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16593,10 +16602,10 @@
         <v>0.75</v>
       </c>
       <c r="AP75">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ75">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR75">
         <v>1.99</v>
@@ -16799,7 +16808,7 @@
         <v>2.5</v>
       </c>
       <c r="AP76">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ76">
         <v>1.75</v>
@@ -16927,7 +16936,7 @@
         <v>130</v>
       </c>
       <c r="P77" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q77">
         <v>1.83</v>
@@ -17133,7 +17142,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q78">
         <v>12</v>
@@ -17339,7 +17348,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q79">
         <v>3.75</v>
@@ -17420,7 +17429,7 @@
         <v>1</v>
       </c>
       <c r="AQ79">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR79">
         <v>1.25</v>
@@ -17545,7 +17554,7 @@
         <v>131</v>
       </c>
       <c r="P80" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17751,7 +17760,7 @@
         <v>132</v>
       </c>
       <c r="P81" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -18163,7 +18172,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q83">
         <v>1.67</v>
@@ -18781,7 +18790,7 @@
         <v>134</v>
       </c>
       <c r="P86" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q86">
         <v>2.63</v>
@@ -19068,7 +19077,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ87">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR87">
         <v>1.66</v>
@@ -19271,10 +19280,10 @@
         <v>1.83</v>
       </c>
       <c r="AP88">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ88">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR88">
         <v>1.18</v>
@@ -19480,7 +19489,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ89">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR89">
         <v>1.32</v>
@@ -19892,7 +19901,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ91">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR91">
         <v>1.91</v>
@@ -20301,7 +20310,7 @@
         <v>0.4</v>
       </c>
       <c r="AP93">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ93">
         <v>0.27</v>
@@ -20429,7 +20438,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q94">
         <v>13</v>
@@ -20635,7 +20644,7 @@
         <v>139</v>
       </c>
       <c r="P95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -20713,7 +20722,7 @@
         <v>0.33</v>
       </c>
       <c r="AP95">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ95">
         <v>1.09</v>
@@ -20922,7 +20931,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ96">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR96">
         <v>1.46</v>
@@ -21047,7 +21056,7 @@
         <v>140</v>
       </c>
       <c r="P97" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q97">
         <v>2.4</v>
@@ -21871,7 +21880,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22489,7 +22498,7 @@
         <v>145</v>
       </c>
       <c r="P104" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22695,7 +22704,7 @@
         <v>86</v>
       </c>
       <c r="P105" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -22901,7 +22910,7 @@
         <v>146</v>
       </c>
       <c r="P106" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q106">
         <v>6</v>
@@ -22982,7 +22991,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ106">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR106">
         <v>1.32</v>
@@ -23188,7 +23197,7 @@
         <v>1</v>
       </c>
       <c r="AQ107">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR107">
         <v>1.46</v>
@@ -23313,7 +23322,7 @@
         <v>147</v>
       </c>
       <c r="P108" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23391,7 +23400,7 @@
         <v>1.86</v>
       </c>
       <c r="AP108">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ108">
         <v>1.67</v>
@@ -23725,7 +23734,7 @@
         <v>149</v>
       </c>
       <c r="P110" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23803,7 +23812,7 @@
         <v>1.86</v>
       </c>
       <c r="AP110">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ110">
         <v>1.92</v>
@@ -24137,7 +24146,7 @@
         <v>143</v>
       </c>
       <c r="P112" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q112">
         <v>4.75</v>
@@ -24215,10 +24224,10 @@
         <v>0.71</v>
       </c>
       <c r="AP112">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ112">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR112">
         <v>1.48</v>
@@ -24836,7 +24845,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ115">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR115">
         <v>1.42</v>
@@ -24961,7 +24970,7 @@
         <v>86</v>
       </c>
       <c r="P116" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q116">
         <v>4.5</v>
@@ -25039,7 +25048,7 @@
         <v>1.17</v>
       </c>
       <c r="AP116">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ116">
         <v>1.92</v>
@@ -25167,7 +25176,7 @@
         <v>153</v>
       </c>
       <c r="P117" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q117">
         <v>1.53</v>
@@ -25373,7 +25382,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25579,7 +25588,7 @@
         <v>154</v>
       </c>
       <c r="P119" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q119">
         <v>1.8</v>
@@ -25785,7 +25794,7 @@
         <v>155</v>
       </c>
       <c r="P120" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q120">
         <v>7.5</v>
@@ -26197,7 +26206,7 @@
         <v>157</v>
       </c>
       <c r="P122" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q122">
         <v>2.63</v>
@@ -26278,7 +26287,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ122">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR122">
         <v>1.43</v>
@@ -26403,7 +26412,7 @@
         <v>158</v>
       </c>
       <c r="P123" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q123">
         <v>1.73</v>
@@ -26893,7 +26902,7 @@
         <v>1.29</v>
       </c>
       <c r="AP125">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ125">
         <v>1.33</v>
@@ -27021,7 +27030,7 @@
         <v>86</v>
       </c>
       <c r="P126" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27099,7 +27108,7 @@
         <v>1.43</v>
       </c>
       <c r="AP126">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ126">
         <v>1.92</v>
@@ -27227,7 +27236,7 @@
         <v>161</v>
       </c>
       <c r="P127" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27433,7 +27442,7 @@
         <v>86</v>
       </c>
       <c r="P128" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q128">
         <v>2.4</v>
@@ -27639,7 +27648,7 @@
         <v>138</v>
       </c>
       <c r="P129" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27845,7 +27854,7 @@
         <v>98</v>
       </c>
       <c r="P130" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q130">
         <v>6.5</v>
@@ -28051,7 +28060,7 @@
         <v>162</v>
       </c>
       <c r="P131" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q131">
         <v>4.33</v>
@@ -28257,7 +28266,7 @@
         <v>86</v>
       </c>
       <c r="P132" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q132">
         <v>8</v>
@@ -28544,7 +28553,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ133">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR133">
         <v>0.99</v>
@@ -29365,7 +29374,7 @@
         <v>1.13</v>
       </c>
       <c r="AP137">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ137">
         <v>1.33</v>
@@ -29571,7 +29580,7 @@
         <v>0.63</v>
       </c>
       <c r="AP138">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ138">
         <v>1.17</v>
@@ -29780,7 +29789,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ139">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR139">
         <v>1.95</v>
@@ -29905,7 +29914,7 @@
         <v>167</v>
       </c>
       <c r="P140" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q140">
         <v>2.3</v>
@@ -29983,7 +29992,7 @@
         <v>0.5</v>
       </c>
       <c r="AP140">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ140">
         <v>0.42</v>
@@ -30111,7 +30120,7 @@
         <v>86</v>
       </c>
       <c r="P141" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q141">
         <v>7.5</v>
@@ -30317,7 +30326,7 @@
         <v>168</v>
       </c>
       <c r="P142" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30398,7 +30407,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ142">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR142">
         <v>2.2</v>
@@ -30523,7 +30532,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30935,7 +30944,7 @@
         <v>171</v>
       </c>
       <c r="P145" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q145">
         <v>3.75</v>
@@ -31141,7 +31150,7 @@
         <v>172</v>
       </c>
       <c r="P146" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q146">
         <v>7.5</v>
@@ -31347,7 +31356,7 @@
         <v>173</v>
       </c>
       <c r="P147" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31553,7 +31562,7 @@
         <v>174</v>
       </c>
       <c r="P148" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q148">
         <v>2.75</v>
@@ -31759,7 +31768,7 @@
         <v>86</v>
       </c>
       <c r="P149" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q149">
         <v>7.5</v>
@@ -32171,7 +32180,7 @@
         <v>86</v>
       </c>
       <c r="P151" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q151">
         <v>6.5</v>
@@ -32377,7 +32386,7 @@
         <v>176</v>
       </c>
       <c r="P152" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q152">
         <v>2.75</v>
@@ -32583,7 +32592,7 @@
         <v>177</v>
       </c>
       <c r="P153" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q153">
         <v>4.75</v>
@@ -32870,7 +32879,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ154">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR154">
         <v>1.41</v>
@@ -32995,7 +33004,7 @@
         <v>179</v>
       </c>
       <c r="P155" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33201,7 +33210,7 @@
         <v>176</v>
       </c>
       <c r="P156" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q156">
         <v>2.2</v>
@@ -33279,10 +33288,10 @@
         <v>0.89</v>
       </c>
       <c r="AP156">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ156">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR156">
         <v>1.7</v>
@@ -33488,7 +33497,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ157">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR157">
         <v>1.48</v>
@@ -33613,7 +33622,7 @@
         <v>181</v>
       </c>
       <c r="P158" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33691,7 +33700,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP158">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ158">
         <v>1.17</v>
@@ -34309,7 +34318,7 @@
         <v>1</v>
       </c>
       <c r="AP161">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ161">
         <v>0.92</v>
@@ -34437,7 +34446,7 @@
         <v>86</v>
       </c>
       <c r="P162" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q162">
         <v>3.5</v>
@@ -34643,7 +34652,7 @@
         <v>184</v>
       </c>
       <c r="P163" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35055,7 +35064,7 @@
         <v>185</v>
       </c>
       <c r="P165" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q165">
         <v>9.5</v>
@@ -36163,7 +36172,7 @@
         <v>0.5</v>
       </c>
       <c r="AP170">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ170">
         <v>0.42</v>
@@ -36369,7 +36378,7 @@
         <v>0.3</v>
       </c>
       <c r="AP171">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ171">
         <v>0.27</v>
@@ -36578,7 +36587,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ172">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR172">
         <v>2.02</v>
@@ -36909,7 +36918,7 @@
         <v>86</v>
       </c>
       <c r="P174" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q174">
         <v>3.75</v>
@@ -36990,7 +36999,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ174">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR174">
         <v>1.58</v>
@@ -37115,7 +37124,7 @@
         <v>124</v>
       </c>
       <c r="P175" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q175">
         <v>5.5</v>
@@ -37193,7 +37202,7 @@
         <v>2.5</v>
       </c>
       <c r="AP175">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ175">
         <v>2.36</v>
@@ -37321,7 +37330,7 @@
         <v>86</v>
       </c>
       <c r="P176" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q176">
         <v>3.1</v>
@@ -37402,7 +37411,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ176">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR176">
         <v>1.29</v>
@@ -37733,7 +37742,7 @@
         <v>86</v>
       </c>
       <c r="P178" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q178">
         <v>3.5</v>
@@ -38145,7 +38154,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38351,7 +38360,7 @@
         <v>194</v>
       </c>
       <c r="P181" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q181">
         <v>3.2</v>
@@ -38557,7 +38566,7 @@
         <v>86</v>
       </c>
       <c r="P182" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q182">
         <v>8.5</v>
@@ -38969,7 +38978,7 @@
         <v>195</v>
       </c>
       <c r="P184" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q184">
         <v>3.6</v>
@@ -39538,6 +39547,624 @@
       </c>
       <c r="BP186">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="187" spans="1:68">
+      <c r="A187" s="1">
+        <v>186</v>
+      </c>
+      <c r="B187">
+        <v>7762778</v>
+      </c>
+      <c r="C187" t="s">
+        <v>68</v>
+      </c>
+      <c r="D187" t="s">
+        <v>69</v>
+      </c>
+      <c r="E187" s="2">
+        <v>45724.3125</v>
+      </c>
+      <c r="F187">
+        <v>24</v>
+      </c>
+      <c r="G187" t="s">
+        <v>81</v>
+      </c>
+      <c r="H187" t="s">
+        <v>72</v>
+      </c>
+      <c r="I187">
+        <v>1</v>
+      </c>
+      <c r="J187">
+        <v>0</v>
+      </c>
+      <c r="K187">
+        <v>1</v>
+      </c>
+      <c r="L187">
+        <v>2</v>
+      </c>
+      <c r="M187">
+        <v>1</v>
+      </c>
+      <c r="N187">
+        <v>3</v>
+      </c>
+      <c r="O187" t="s">
+        <v>196</v>
+      </c>
+      <c r="P187" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q187">
+        <v>2.4</v>
+      </c>
+      <c r="R187">
+        <v>2.1</v>
+      </c>
+      <c r="S187">
+        <v>5</v>
+      </c>
+      <c r="T187">
+        <v>1.44</v>
+      </c>
+      <c r="U187">
+        <v>2.63</v>
+      </c>
+      <c r="V187">
+        <v>3</v>
+      </c>
+      <c r="W187">
+        <v>1.36</v>
+      </c>
+      <c r="X187">
+        <v>9</v>
+      </c>
+      <c r="Y187">
+        <v>1.07</v>
+      </c>
+      <c r="Z187">
+        <v>1.94</v>
+      </c>
+      <c r="AA187">
+        <v>3.29</v>
+      </c>
+      <c r="AB187">
+        <v>3.98</v>
+      </c>
+      <c r="AC187">
+        <v>1.03</v>
+      </c>
+      <c r="AD187">
+        <v>7.4</v>
+      </c>
+      <c r="AE187">
+        <v>1.43</v>
+      </c>
+      <c r="AF187">
+        <v>2.7</v>
+      </c>
+      <c r="AG187">
+        <v>2</v>
+      </c>
+      <c r="AH187">
+        <v>1.67</v>
+      </c>
+      <c r="AI187">
+        <v>1.83</v>
+      </c>
+      <c r="AJ187">
+        <v>1.83</v>
+      </c>
+      <c r="AK187">
+        <v>1.23</v>
+      </c>
+      <c r="AL187">
+        <v>1.29</v>
+      </c>
+      <c r="AM187">
+        <v>1.77</v>
+      </c>
+      <c r="AN187">
+        <v>1</v>
+      </c>
+      <c r="AO187">
+        <v>1.27</v>
+      </c>
+      <c r="AP187">
+        <v>1.17</v>
+      </c>
+      <c r="AQ187">
+        <v>1.17</v>
+      </c>
+      <c r="AR187">
+        <v>1.74</v>
+      </c>
+      <c r="AS187">
+        <v>1.29</v>
+      </c>
+      <c r="AT187">
+        <v>3.03</v>
+      </c>
+      <c r="AU187">
+        <v>8</v>
+      </c>
+      <c r="AV187">
+        <v>4</v>
+      </c>
+      <c r="AW187">
+        <v>5</v>
+      </c>
+      <c r="AX187">
+        <v>4</v>
+      </c>
+      <c r="AY187">
+        <v>13</v>
+      </c>
+      <c r="AZ187">
+        <v>8</v>
+      </c>
+      <c r="BA187">
+        <v>4</v>
+      </c>
+      <c r="BB187">
+        <v>6</v>
+      </c>
+      <c r="BC187">
+        <v>10</v>
+      </c>
+      <c r="BD187">
+        <v>1.55</v>
+      </c>
+      <c r="BE187">
+        <v>6.5</v>
+      </c>
+      <c r="BF187">
+        <v>2.7</v>
+      </c>
+      <c r="BG187">
+        <v>1.43</v>
+      </c>
+      <c r="BH187">
+        <v>2.6</v>
+      </c>
+      <c r="BI187">
+        <v>1.73</v>
+      </c>
+      <c r="BJ187">
+        <v>1.98</v>
+      </c>
+      <c r="BK187">
+        <v>2.17</v>
+      </c>
+      <c r="BL187">
+        <v>1.6</v>
+      </c>
+      <c r="BM187">
+        <v>2.8</v>
+      </c>
+      <c r="BN187">
+        <v>1.37</v>
+      </c>
+      <c r="BO187">
+        <v>3.8</v>
+      </c>
+      <c r="BP187">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="188" spans="1:68">
+      <c r="A188" s="1">
+        <v>187</v>
+      </c>
+      <c r="B188">
+        <v>7762783</v>
+      </c>
+      <c r="C188" t="s">
+        <v>68</v>
+      </c>
+      <c r="D188" t="s">
+        <v>69</v>
+      </c>
+      <c r="E188" s="2">
+        <v>45724.41666666666</v>
+      </c>
+      <c r="F188">
+        <v>24</v>
+      </c>
+      <c r="G188" t="s">
+        <v>83</v>
+      </c>
+      <c r="H188" t="s">
+        <v>80</v>
+      </c>
+      <c r="I188">
+        <v>0</v>
+      </c>
+      <c r="J188">
+        <v>0</v>
+      </c>
+      <c r="K188">
+        <v>0</v>
+      </c>
+      <c r="L188">
+        <v>0</v>
+      </c>
+      <c r="M188">
+        <v>2</v>
+      </c>
+      <c r="N188">
+        <v>2</v>
+      </c>
+      <c r="O188" t="s">
+        <v>86</v>
+      </c>
+      <c r="P188" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q188">
+        <v>6</v>
+      </c>
+      <c r="R188">
+        <v>2.1</v>
+      </c>
+      <c r="S188">
+        <v>2.3</v>
+      </c>
+      <c r="T188">
+        <v>1.44</v>
+      </c>
+      <c r="U188">
+        <v>2.63</v>
+      </c>
+      <c r="V188">
+        <v>3.4</v>
+      </c>
+      <c r="W188">
+        <v>1.3</v>
+      </c>
+      <c r="X188">
+        <v>10</v>
+      </c>
+      <c r="Y188">
+        <v>1.06</v>
+      </c>
+      <c r="Z188">
+        <v>5</v>
+      </c>
+      <c r="AA188">
+        <v>3.58</v>
+      </c>
+      <c r="AB188">
+        <v>1.7</v>
+      </c>
+      <c r="AC188">
+        <v>1.03</v>
+      </c>
+      <c r="AD188">
+        <v>7.5</v>
+      </c>
+      <c r="AE188">
+        <v>1.4</v>
+      </c>
+      <c r="AF188">
+        <v>2.8</v>
+      </c>
+      <c r="AG188">
+        <v>2</v>
+      </c>
+      <c r="AH188">
+        <v>1.75</v>
+      </c>
+      <c r="AI188">
+        <v>2.2</v>
+      </c>
+      <c r="AJ188">
+        <v>1.62</v>
+      </c>
+      <c r="AK188">
+        <v>2.06</v>
+      </c>
+      <c r="AL188">
+        <v>1.24</v>
+      </c>
+      <c r="AM188">
+        <v>1.16</v>
+      </c>
+      <c r="AN188">
+        <v>1.55</v>
+      </c>
+      <c r="AO188">
+        <v>1.27</v>
+      </c>
+      <c r="AP188">
+        <v>1.42</v>
+      </c>
+      <c r="AQ188">
+        <v>1.42</v>
+      </c>
+      <c r="AR188">
+        <v>1.61</v>
+      </c>
+      <c r="AS188">
+        <v>1.66</v>
+      </c>
+      <c r="AT188">
+        <v>3.27</v>
+      </c>
+      <c r="AU188">
+        <v>5</v>
+      </c>
+      <c r="AV188">
+        <v>9</v>
+      </c>
+      <c r="AW188">
+        <v>6</v>
+      </c>
+      <c r="AX188">
+        <v>4</v>
+      </c>
+      <c r="AY188">
+        <v>11</v>
+      </c>
+      <c r="AZ188">
+        <v>13</v>
+      </c>
+      <c r="BA188">
+        <v>2</v>
+      </c>
+      <c r="BB188">
+        <v>1</v>
+      </c>
+      <c r="BC188">
+        <v>3</v>
+      </c>
+      <c r="BD188">
+        <v>2.95</v>
+      </c>
+      <c r="BE188">
+        <v>6.75</v>
+      </c>
+      <c r="BF188">
+        <v>1.48</v>
+      </c>
+      <c r="BG188">
+        <v>1.46</v>
+      </c>
+      <c r="BH188">
+        <v>2.5</v>
+      </c>
+      <c r="BI188">
+        <v>1.75</v>
+      </c>
+      <c r="BJ188">
+        <v>1.95</v>
+      </c>
+      <c r="BK188">
+        <v>2.2</v>
+      </c>
+      <c r="BL188">
+        <v>1.58</v>
+      </c>
+      <c r="BM188">
+        <v>2.8</v>
+      </c>
+      <c r="BN188">
+        <v>1.36</v>
+      </c>
+      <c r="BO188">
+        <v>3.8</v>
+      </c>
+      <c r="BP188">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="189" spans="1:68">
+      <c r="A189" s="1">
+        <v>188</v>
+      </c>
+      <c r="B189">
+        <v>7762782</v>
+      </c>
+      <c r="C189" t="s">
+        <v>68</v>
+      </c>
+      <c r="D189" t="s">
+        <v>69</v>
+      </c>
+      <c r="E189" s="2">
+        <v>45724.52083333334</v>
+      </c>
+      <c r="F189">
+        <v>24</v>
+      </c>
+      <c r="G189" t="s">
+        <v>70</v>
+      </c>
+      <c r="H189" t="s">
+        <v>84</v>
+      </c>
+      <c r="I189">
+        <v>1</v>
+      </c>
+      <c r="J189">
+        <v>0</v>
+      </c>
+      <c r="K189">
+        <v>1</v>
+      </c>
+      <c r="L189">
+        <v>1</v>
+      </c>
+      <c r="M189">
+        <v>1</v>
+      </c>
+      <c r="N189">
+        <v>2</v>
+      </c>
+      <c r="O189" t="s">
+        <v>192</v>
+      </c>
+      <c r="P189" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q189">
+        <v>2.3</v>
+      </c>
+      <c r="R189">
+        <v>2.1</v>
+      </c>
+      <c r="S189">
+        <v>5.5</v>
+      </c>
+      <c r="T189">
+        <v>1.44</v>
+      </c>
+      <c r="U189">
+        <v>2.63</v>
+      </c>
+      <c r="V189">
+        <v>3.25</v>
+      </c>
+      <c r="W189">
+        <v>1.33</v>
+      </c>
+      <c r="X189">
+        <v>9</v>
+      </c>
+      <c r="Y189">
+        <v>1.07</v>
+      </c>
+      <c r="Z189">
+        <v>1.53</v>
+      </c>
+      <c r="AA189">
+        <v>4</v>
+      </c>
+      <c r="AB189">
+        <v>6</v>
+      </c>
+      <c r="AC189">
+        <v>1</v>
+      </c>
+      <c r="AD189">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE189">
+        <v>1.41</v>
+      </c>
+      <c r="AF189">
+        <v>2.75</v>
+      </c>
+      <c r="AG189">
+        <v>1.98</v>
+      </c>
+      <c r="AH189">
+        <v>1.77</v>
+      </c>
+      <c r="AI189">
+        <v>2</v>
+      </c>
+      <c r="AJ189">
+        <v>1.73</v>
+      </c>
+      <c r="AK189">
+        <v>1.11</v>
+      </c>
+      <c r="AL189">
+        <v>1.22</v>
+      </c>
+      <c r="AM189">
+        <v>2.33</v>
+      </c>
+      <c r="AN189">
+        <v>2</v>
+      </c>
+      <c r="AO189">
+        <v>1.36</v>
+      </c>
+      <c r="AP189">
+        <v>1.92</v>
+      </c>
+      <c r="AQ189">
+        <v>1.33</v>
+      </c>
+      <c r="AR189">
+        <v>1.65</v>
+      </c>
+      <c r="AS189">
+        <v>1.15</v>
+      </c>
+      <c r="AT189">
+        <v>2.8</v>
+      </c>
+      <c r="AU189">
+        <v>11</v>
+      </c>
+      <c r="AV189">
+        <v>6</v>
+      </c>
+      <c r="AW189">
+        <v>10</v>
+      </c>
+      <c r="AX189">
+        <v>0</v>
+      </c>
+      <c r="AY189">
+        <v>21</v>
+      </c>
+      <c r="AZ189">
+        <v>6</v>
+      </c>
+      <c r="BA189">
+        <v>7</v>
+      </c>
+      <c r="BB189">
+        <v>3</v>
+      </c>
+      <c r="BC189">
+        <v>10</v>
+      </c>
+      <c r="BD189">
+        <v>1.46</v>
+      </c>
+      <c r="BE189">
+        <v>6.4</v>
+      </c>
+      <c r="BF189">
+        <v>3.15</v>
+      </c>
+      <c r="BG189">
+        <v>1.64</v>
+      </c>
+      <c r="BH189">
+        <v>2.1</v>
+      </c>
+      <c r="BI189">
+        <v>2.02</v>
+      </c>
+      <c r="BJ189">
+        <v>1.7</v>
+      </c>
+      <c r="BK189">
+        <v>2.65</v>
+      </c>
+      <c r="BL189">
+        <v>1.42</v>
+      </c>
+      <c r="BM189">
+        <v>3.55</v>
+      </c>
+      <c r="BN189">
+        <v>1.24</v>
+      </c>
+      <c r="BO189">
+        <v>4.8</v>
+      </c>
+      <c r="BP189">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="289">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -607,6 +607,12 @@
     <t>['40', '90+2']</t>
   </si>
   <si>
+    <t>['2', '90+4', '90+7']</t>
+  </si>
+  <si>
+    <t>['82']</t>
+  </si>
+  <si>
     <t>['12', '22', '45+1', '45+4', '90+1', '90+8']</t>
   </si>
   <si>
@@ -869,6 +875,12 @@
   </si>
   <si>
     <t>['72']</t>
+  </si>
+  <si>
+    <t>['7', '14', '85']</t>
+  </si>
+  <si>
+    <t>['34', '53']</t>
   </si>
 </sst>
 </file>
@@ -1230,7 +1242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP189"/>
+  <dimension ref="A1:BP192"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1773,7 +1785,7 @@
         <v>1</v>
       </c>
       <c r="AQ3">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1979,7 +1991,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ4">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2104,7 +2116,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q5">
         <v>7.5</v>
@@ -2182,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ5">
         <v>1.92</v>
@@ -2310,7 +2322,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2722,7 +2734,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q8">
         <v>4</v>
@@ -3418,7 +3430,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ11">
         <v>0.42</v>
@@ -3752,7 +3764,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3958,7 +3970,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q14">
         <v>2.4</v>
@@ -4036,7 +4048,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ14">
         <v>1.17</v>
@@ -4657,7 +4669,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ17">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR17">
         <v>1.12</v>
@@ -4782,7 +4794,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -5194,7 +5206,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -5275,7 +5287,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ20">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR20">
         <v>0.96</v>
@@ -5400,7 +5412,7 @@
         <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5478,7 +5490,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ21">
         <v>1.92</v>
@@ -5606,7 +5618,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5812,7 +5824,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -6018,7 +6030,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q24">
         <v>3.25</v>
@@ -6224,7 +6236,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q25">
         <v>2.05</v>
@@ -6430,7 +6442,7 @@
         <v>86</v>
       </c>
       <c r="P26" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6714,7 +6726,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ27">
         <v>0.92</v>
@@ -7048,7 +7060,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7335,7 +7347,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ30">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR30">
         <v>1.68</v>
@@ -7460,7 +7472,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7666,7 +7678,7 @@
         <v>86</v>
       </c>
       <c r="P32" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q32">
         <v>2.05</v>
@@ -7747,7 +7759,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ32">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR32">
         <v>2.55</v>
@@ -8156,7 +8168,7 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ34">
         <v>1.17</v>
@@ -8696,7 +8708,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -8980,7 +8992,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ38">
         <v>0.42</v>
@@ -9186,7 +9198,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ39">
         <v>0.27</v>
@@ -9520,7 +9532,7 @@
         <v>86</v>
       </c>
       <c r="P41" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q41">
         <v>2.38</v>
@@ -9598,7 +9610,7 @@
         <v>1.33</v>
       </c>
       <c r="AP41">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ41">
         <v>1.33</v>
@@ -9807,7 +9819,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ42">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR42">
         <v>1.54</v>
@@ -9932,7 +9944,7 @@
         <v>86</v>
       </c>
       <c r="P43" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q43">
         <v>7.5</v>
@@ -10013,7 +10025,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ43">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR43">
         <v>1.51</v>
@@ -10138,7 +10150,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10550,7 +10562,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q46">
         <v>2.5</v>
@@ -10631,7 +10643,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ46">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR46">
         <v>1.81</v>
@@ -10756,7 +10768,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q47">
         <v>4.33</v>
@@ -10962,7 +10974,7 @@
         <v>86</v>
       </c>
       <c r="P48" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q48">
         <v>2.4</v>
@@ -11580,7 +11592,7 @@
         <v>116</v>
       </c>
       <c r="P51" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11786,7 +11798,7 @@
         <v>118</v>
       </c>
       <c r="P52" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q52">
         <v>5.5</v>
@@ -12198,7 +12210,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -12610,7 +12622,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q56">
         <v>5.5</v>
@@ -12691,7 +12703,7 @@
         <v>1</v>
       </c>
       <c r="AQ56">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR56">
         <v>1.1</v>
@@ -12816,7 +12828,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q57">
         <v>5</v>
@@ -13022,7 +13034,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13103,7 +13115,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ58">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR58">
         <v>1.97</v>
@@ -13228,7 +13240,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13434,7 +13446,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13515,7 +13527,7 @@
         <v>1</v>
       </c>
       <c r="AQ60">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR60">
         <v>1.59</v>
@@ -13640,7 +13652,7 @@
         <v>86</v>
       </c>
       <c r="P61" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q61">
         <v>6.5</v>
@@ -13718,7 +13730,7 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ61">
         <v>1.42</v>
@@ -13927,7 +13939,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ62">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR62">
         <v>1.3</v>
@@ -14052,7 +14064,7 @@
         <v>86</v>
       </c>
       <c r="P63" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q63">
         <v>3.5</v>
@@ -14258,7 +14270,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14876,7 +14888,7 @@
         <v>86</v>
       </c>
       <c r="P67" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q67">
         <v>6.5</v>
@@ -15082,7 +15094,7 @@
         <v>86</v>
       </c>
       <c r="P68" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q68">
         <v>4.75</v>
@@ -15700,7 +15712,7 @@
         <v>92</v>
       </c>
       <c r="P71" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q71">
         <v>9.5</v>
@@ -15984,7 +15996,7 @@
         <v>0.25</v>
       </c>
       <c r="AP72">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ72">
         <v>0.27</v>
@@ -16193,7 +16205,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ73">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR73">
         <v>1.15</v>
@@ -16318,7 +16330,7 @@
         <v>86</v>
       </c>
       <c r="P74" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16936,7 +16948,7 @@
         <v>130</v>
       </c>
       <c r="P77" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q77">
         <v>1.83</v>
@@ -17014,10 +17026,10 @@
         <v>0.4</v>
       </c>
       <c r="AP77">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ77">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR77">
         <v>1.79</v>
@@ -17142,7 +17154,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q78">
         <v>12</v>
@@ -17223,7 +17235,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ78">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR78">
         <v>1.46</v>
@@ -17348,7 +17360,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q79">
         <v>3.75</v>
@@ -17554,7 +17566,7 @@
         <v>131</v>
       </c>
       <c r="P80" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17760,7 +17772,7 @@
         <v>132</v>
       </c>
       <c r="P81" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -18172,7 +18184,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q83">
         <v>1.67</v>
@@ -18456,7 +18468,7 @@
         <v>2.17</v>
       </c>
       <c r="AP84">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ84">
         <v>1.92</v>
@@ -18790,7 +18802,7 @@
         <v>134</v>
       </c>
       <c r="P86" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q86">
         <v>2.63</v>
@@ -19692,7 +19704,7 @@
         <v>0.75</v>
       </c>
       <c r="AP90">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ90">
         <v>0.92</v>
@@ -19898,7 +19910,7 @@
         <v>0.8</v>
       </c>
       <c r="AP91">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ91">
         <v>1.42</v>
@@ -20104,10 +20116,10 @@
         <v>0.67</v>
       </c>
       <c r="AP92">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ92">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR92">
         <v>1.22</v>
@@ -20438,7 +20450,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q94">
         <v>13</v>
@@ -20519,7 +20531,7 @@
         <v>1</v>
       </c>
       <c r="AQ94">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR94">
         <v>1.21</v>
@@ -20644,7 +20656,7 @@
         <v>139</v>
       </c>
       <c r="P95" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -20725,7 +20737,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ95">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR95">
         <v>1.49</v>
@@ -21056,7 +21068,7 @@
         <v>140</v>
       </c>
       <c r="P97" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q97">
         <v>2.4</v>
@@ -21752,7 +21764,7 @@
         <v>1.4</v>
       </c>
       <c r="AP100">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ100">
         <v>1.92</v>
@@ -21880,7 +21892,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -21958,7 +21970,7 @@
         <v>1.67</v>
       </c>
       <c r="AP101">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ101">
         <v>1.67</v>
@@ -22498,7 +22510,7 @@
         <v>145</v>
       </c>
       <c r="P104" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22579,7 +22591,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ104">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR104">
         <v>1.26</v>
@@ -22704,7 +22716,7 @@
         <v>86</v>
       </c>
       <c r="P105" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -22782,10 +22794,10 @@
         <v>0.71</v>
       </c>
       <c r="AP105">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ105">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR105">
         <v>1.16</v>
@@ -22910,7 +22922,7 @@
         <v>146</v>
       </c>
       <c r="P106" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q106">
         <v>6</v>
@@ -23322,7 +23334,7 @@
         <v>147</v>
       </c>
       <c r="P108" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23734,7 +23746,7 @@
         <v>149</v>
       </c>
       <c r="P110" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -24146,7 +24158,7 @@
         <v>143</v>
       </c>
       <c r="P112" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q112">
         <v>4.75</v>
@@ -24636,7 +24648,7 @@
         <v>0.83</v>
       </c>
       <c r="AP114">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ114">
         <v>1.17</v>
@@ -24970,7 +24982,7 @@
         <v>86</v>
       </c>
       <c r="P116" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q116">
         <v>4.5</v>
@@ -25176,7 +25188,7 @@
         <v>153</v>
       </c>
       <c r="P117" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q117">
         <v>1.53</v>
@@ -25254,7 +25266,7 @@
         <v>1</v>
       </c>
       <c r="AP117">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ117">
         <v>1.33</v>
@@ -25382,7 +25394,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25588,7 +25600,7 @@
         <v>154</v>
       </c>
       <c r="P119" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q119">
         <v>1.8</v>
@@ -25794,7 +25806,7 @@
         <v>155</v>
       </c>
       <c r="P120" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q120">
         <v>7.5</v>
@@ -25875,7 +25887,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ120">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR120">
         <v>1.46</v>
@@ -26206,7 +26218,7 @@
         <v>157</v>
       </c>
       <c r="P122" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q122">
         <v>2.63</v>
@@ -26412,7 +26424,7 @@
         <v>158</v>
       </c>
       <c r="P123" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q123">
         <v>1.73</v>
@@ -26490,7 +26502,7 @@
         <v>0.57</v>
       </c>
       <c r="AP123">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ123">
         <v>0.42</v>
@@ -26696,7 +26708,7 @@
         <v>0.71</v>
       </c>
       <c r="AP124">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ124">
         <v>1.17</v>
@@ -27030,7 +27042,7 @@
         <v>86</v>
       </c>
       <c r="P126" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27236,7 +27248,7 @@
         <v>161</v>
       </c>
       <c r="P127" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27317,7 +27329,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ127">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR127">
         <v>2.03</v>
@@ -27442,7 +27454,7 @@
         <v>86</v>
       </c>
       <c r="P128" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q128">
         <v>2.4</v>
@@ -27648,7 +27660,7 @@
         <v>138</v>
       </c>
       <c r="P129" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27854,7 +27866,7 @@
         <v>98</v>
       </c>
       <c r="P130" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q130">
         <v>6.5</v>
@@ -28060,7 +28072,7 @@
         <v>162</v>
       </c>
       <c r="P131" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q131">
         <v>4.33</v>
@@ -28138,7 +28150,7 @@
         <v>1.75</v>
       </c>
       <c r="AP131">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ131">
         <v>1.67</v>
@@ -28266,7 +28278,7 @@
         <v>86</v>
       </c>
       <c r="P132" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q132">
         <v>8</v>
@@ -28965,7 +28977,7 @@
         <v>1</v>
       </c>
       <c r="AQ135">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR135">
         <v>1.42</v>
@@ -29171,7 +29183,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ136">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR136">
         <v>1.69</v>
@@ -29914,7 +29926,7 @@
         <v>167</v>
       </c>
       <c r="P140" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q140">
         <v>2.3</v>
@@ -30120,7 +30132,7 @@
         <v>86</v>
       </c>
       <c r="P141" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q141">
         <v>7.5</v>
@@ -30201,7 +30213,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ141">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR141">
         <v>1.45</v>
@@ -30326,7 +30338,7 @@
         <v>168</v>
       </c>
       <c r="P142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30404,7 +30416,7 @@
         <v>1</v>
       </c>
       <c r="AP142">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ142">
         <v>1.17</v>
@@ -30532,7 +30544,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30816,7 +30828,7 @@
         <v>1.13</v>
       </c>
       <c r="AP144">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ144">
         <v>0.92</v>
@@ -30944,7 +30956,7 @@
         <v>171</v>
       </c>
       <c r="P145" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q145">
         <v>3.75</v>
@@ -31150,7 +31162,7 @@
         <v>172</v>
       </c>
       <c r="P146" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q146">
         <v>7.5</v>
@@ -31356,7 +31368,7 @@
         <v>173</v>
       </c>
       <c r="P147" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31562,7 +31574,7 @@
         <v>174</v>
       </c>
       <c r="P148" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q148">
         <v>2.75</v>
@@ -31640,7 +31652,7 @@
         <v>1</v>
       </c>
       <c r="AP148">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ148">
         <v>1.33</v>
@@ -31768,7 +31780,7 @@
         <v>86</v>
       </c>
       <c r="P149" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q149">
         <v>7.5</v>
@@ -32180,7 +32192,7 @@
         <v>86</v>
       </c>
       <c r="P151" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q151">
         <v>6.5</v>
@@ -32261,7 +32273,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ151">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR151">
         <v>0.99</v>
@@ -32386,7 +32398,7 @@
         <v>176</v>
       </c>
       <c r="P152" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q152">
         <v>2.75</v>
@@ -32467,7 +32479,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ152">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR152">
         <v>1.47</v>
@@ -32592,7 +32604,7 @@
         <v>177</v>
       </c>
       <c r="P153" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q153">
         <v>4.75</v>
@@ -32670,10 +32682,10 @@
         <v>2.75</v>
       </c>
       <c r="AP153">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ153">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR153">
         <v>1.54</v>
@@ -33004,7 +33016,7 @@
         <v>179</v>
       </c>
       <c r="P155" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33210,7 +33222,7 @@
         <v>176</v>
       </c>
       <c r="P156" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q156">
         <v>2.2</v>
@@ -33622,7 +33634,7 @@
         <v>181</v>
       </c>
       <c r="P158" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33906,7 +33918,7 @@
         <v>0.22</v>
       </c>
       <c r="AP159">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ159">
         <v>0.27</v>
@@ -34112,10 +34124,10 @@
         <v>2.78</v>
       </c>
       <c r="AP160">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ160">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR160">
         <v>2.11</v>
@@ -34446,7 +34458,7 @@
         <v>86</v>
       </c>
       <c r="P162" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q162">
         <v>3.5</v>
@@ -34652,7 +34664,7 @@
         <v>184</v>
       </c>
       <c r="P163" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35064,7 +35076,7 @@
         <v>185</v>
       </c>
       <c r="P165" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q165">
         <v>9.5</v>
@@ -35763,7 +35775,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ168">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR168">
         <v>2.21</v>
@@ -36584,7 +36596,7 @@
         <v>1.5</v>
       </c>
       <c r="AP172">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ172">
         <v>1.33</v>
@@ -36793,7 +36805,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ173">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR173">
         <v>1.43</v>
@@ -36918,7 +36930,7 @@
         <v>86</v>
       </c>
       <c r="P174" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q174">
         <v>3.75</v>
@@ -36996,7 +37008,7 @@
         <v>1.1</v>
       </c>
       <c r="AP174">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ174">
         <v>1.42</v>
@@ -37124,7 +37136,7 @@
         <v>124</v>
       </c>
       <c r="P175" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q175">
         <v>5.5</v>
@@ -37205,7 +37217,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ175">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR175">
         <v>1.71</v>
@@ -37330,7 +37342,7 @@
         <v>86</v>
       </c>
       <c r="P176" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q176">
         <v>3.1</v>
@@ -37408,7 +37420,7 @@
         <v>1.1</v>
       </c>
       <c r="AP176">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ176">
         <v>1.17</v>
@@ -37742,7 +37754,7 @@
         <v>86</v>
       </c>
       <c r="P178" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q178">
         <v>3.5</v>
@@ -38154,7 +38166,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38360,7 +38372,7 @@
         <v>194</v>
       </c>
       <c r="P181" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q181">
         <v>3.2</v>
@@ -38566,7 +38578,7 @@
         <v>86</v>
       </c>
       <c r="P182" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q182">
         <v>8.5</v>
@@ -38978,7 +38990,7 @@
         <v>195</v>
       </c>
       <c r="P184" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q184">
         <v>3.6</v>
@@ -39596,7 +39608,7 @@
         <v>196</v>
       </c>
       <c r="P187" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -39802,7 +39814,7 @@
         <v>86</v>
       </c>
       <c r="P188" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q188">
         <v>6</v>
@@ -40008,7 +40020,7 @@
         <v>192</v>
       </c>
       <c r="P189" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q189">
         <v>2.3</v>
@@ -40165,6 +40177,624 @@
       </c>
       <c r="BP189">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="190" spans="1:68">
+      <c r="A190" s="1">
+        <v>189</v>
+      </c>
+      <c r="B190">
+        <v>7762785</v>
+      </c>
+      <c r="C190" t="s">
+        <v>68</v>
+      </c>
+      <c r="D190" t="s">
+        <v>69</v>
+      </c>
+      <c r="E190" s="2">
+        <v>45725.29166666666</v>
+      </c>
+      <c r="F190">
+        <v>24</v>
+      </c>
+      <c r="G190" t="s">
+        <v>82</v>
+      </c>
+      <c r="H190" t="s">
+        <v>78</v>
+      </c>
+      <c r="I190">
+        <v>1</v>
+      </c>
+      <c r="J190">
+        <v>0</v>
+      </c>
+      <c r="K190">
+        <v>1</v>
+      </c>
+      <c r="L190">
+        <v>1</v>
+      </c>
+      <c r="M190">
+        <v>1</v>
+      </c>
+      <c r="N190">
+        <v>2</v>
+      </c>
+      <c r="O190" t="s">
+        <v>111</v>
+      </c>
+      <c r="P190" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q190">
+        <v>2.6</v>
+      </c>
+      <c r="R190">
+        <v>2</v>
+      </c>
+      <c r="S190">
+        <v>5</v>
+      </c>
+      <c r="T190">
+        <v>1.53</v>
+      </c>
+      <c r="U190">
+        <v>2.38</v>
+      </c>
+      <c r="V190">
+        <v>3.5</v>
+      </c>
+      <c r="W190">
+        <v>1.29</v>
+      </c>
+      <c r="X190">
+        <v>11</v>
+      </c>
+      <c r="Y190">
+        <v>1.05</v>
+      </c>
+      <c r="Z190">
+        <v>1.94</v>
+      </c>
+      <c r="AA190">
+        <v>3.29</v>
+      </c>
+      <c r="AB190">
+        <v>3.98</v>
+      </c>
+      <c r="AC190">
+        <v>1.03</v>
+      </c>
+      <c r="AD190">
+        <v>7.4</v>
+      </c>
+      <c r="AE190">
+        <v>1.42</v>
+      </c>
+      <c r="AF190">
+        <v>2.7</v>
+      </c>
+      <c r="AG190">
+        <v>2.2</v>
+      </c>
+      <c r="AH190">
+        <v>1.55</v>
+      </c>
+      <c r="AI190">
+        <v>2.1</v>
+      </c>
+      <c r="AJ190">
+        <v>1.67</v>
+      </c>
+      <c r="AK190">
+        <v>1.23</v>
+      </c>
+      <c r="AL190">
+        <v>1.29</v>
+      </c>
+      <c r="AM190">
+        <v>1.77</v>
+      </c>
+      <c r="AN190">
+        <v>1.82</v>
+      </c>
+      <c r="AO190">
+        <v>1.09</v>
+      </c>
+      <c r="AP190">
+        <v>1.75</v>
+      </c>
+      <c r="AQ190">
+        <v>1.08</v>
+      </c>
+      <c r="AR190">
+        <v>1.56</v>
+      </c>
+      <c r="AS190">
+        <v>1.24</v>
+      </c>
+      <c r="AT190">
+        <v>2.8</v>
+      </c>
+      <c r="AU190">
+        <v>7</v>
+      </c>
+      <c r="AV190">
+        <v>5</v>
+      </c>
+      <c r="AW190">
+        <v>6</v>
+      </c>
+      <c r="AX190">
+        <v>4</v>
+      </c>
+      <c r="AY190">
+        <v>13</v>
+      </c>
+      <c r="AZ190">
+        <v>9</v>
+      </c>
+      <c r="BA190">
+        <v>4</v>
+      </c>
+      <c r="BB190">
+        <v>6</v>
+      </c>
+      <c r="BC190">
+        <v>10</v>
+      </c>
+      <c r="BD190">
+        <v>1.52</v>
+      </c>
+      <c r="BE190">
+        <v>7</v>
+      </c>
+      <c r="BF190">
+        <v>2.8</v>
+      </c>
+      <c r="BG190">
+        <v>1.36</v>
+      </c>
+      <c r="BH190">
+        <v>2.85</v>
+      </c>
+      <c r="BI190">
+        <v>1.61</v>
+      </c>
+      <c r="BJ190">
+        <v>2.15</v>
+      </c>
+      <c r="BK190">
+        <v>1.98</v>
+      </c>
+      <c r="BL190">
+        <v>1.72</v>
+      </c>
+      <c r="BM190">
+        <v>2.5</v>
+      </c>
+      <c r="BN190">
+        <v>1.46</v>
+      </c>
+      <c r="BO190">
+        <v>3.3</v>
+      </c>
+      <c r="BP190">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="191" spans="1:68">
+      <c r="A191" s="1">
+        <v>190</v>
+      </c>
+      <c r="B191">
+        <v>7762784</v>
+      </c>
+      <c r="C191" t="s">
+        <v>68</v>
+      </c>
+      <c r="D191" t="s">
+        <v>69</v>
+      </c>
+      <c r="E191" s="2">
+        <v>45725.39583333334</v>
+      </c>
+      <c r="F191">
+        <v>24</v>
+      </c>
+      <c r="G191" t="s">
+        <v>79</v>
+      </c>
+      <c r="H191" t="s">
+        <v>85</v>
+      </c>
+      <c r="I191">
+        <v>1</v>
+      </c>
+      <c r="J191">
+        <v>2</v>
+      </c>
+      <c r="K191">
+        <v>3</v>
+      </c>
+      <c r="L191">
+        <v>3</v>
+      </c>
+      <c r="M191">
+        <v>3</v>
+      </c>
+      <c r="N191">
+        <v>6</v>
+      </c>
+      <c r="O191" t="s">
+        <v>197</v>
+      </c>
+      <c r="P191" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q191">
+        <v>1.95</v>
+      </c>
+      <c r="R191">
+        <v>2.2</v>
+      </c>
+      <c r="S191">
+        <v>8.5</v>
+      </c>
+      <c r="T191">
+        <v>1.44</v>
+      </c>
+      <c r="U191">
+        <v>2.63</v>
+      </c>
+      <c r="V191">
+        <v>3.25</v>
+      </c>
+      <c r="W191">
+        <v>1.33</v>
+      </c>
+      <c r="X191">
+        <v>9</v>
+      </c>
+      <c r="Y191">
+        <v>1.07</v>
+      </c>
+      <c r="Z191">
+        <v>1.32</v>
+      </c>
+      <c r="AA191">
+        <v>4.7</v>
+      </c>
+      <c r="AB191">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC191">
+        <v>1.01</v>
+      </c>
+      <c r="AD191">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE191">
+        <v>1.3</v>
+      </c>
+      <c r="AF191">
+        <v>3.3</v>
+      </c>
+      <c r="AG191">
+        <v>1.94</v>
+      </c>
+      <c r="AH191">
+        <v>1.8</v>
+      </c>
+      <c r="AI191">
+        <v>2.5</v>
+      </c>
+      <c r="AJ191">
+        <v>1.5</v>
+      </c>
+      <c r="AK191">
+        <v>1.07</v>
+      </c>
+      <c r="AL191">
+        <v>1.15</v>
+      </c>
+      <c r="AM191">
+        <v>2.95</v>
+      </c>
+      <c r="AN191">
+        <v>2.45</v>
+      </c>
+      <c r="AO191">
+        <v>0.73</v>
+      </c>
+      <c r="AP191">
+        <v>2.33</v>
+      </c>
+      <c r="AQ191">
+        <v>0.75</v>
+      </c>
+      <c r="AR191">
+        <v>2.07</v>
+      </c>
+      <c r="AS191">
+        <v>1.45</v>
+      </c>
+      <c r="AT191">
+        <v>3.52</v>
+      </c>
+      <c r="AU191">
+        <v>5</v>
+      </c>
+      <c r="AV191">
+        <v>7</v>
+      </c>
+      <c r="AW191">
+        <v>8</v>
+      </c>
+      <c r="AX191">
+        <v>7</v>
+      </c>
+      <c r="AY191">
+        <v>13</v>
+      </c>
+      <c r="AZ191">
+        <v>14</v>
+      </c>
+      <c r="BA191">
+        <v>11</v>
+      </c>
+      <c r="BB191">
+        <v>4</v>
+      </c>
+      <c r="BC191">
+        <v>15</v>
+      </c>
+      <c r="BD191">
+        <v>1.25</v>
+      </c>
+      <c r="BE191">
+        <v>8</v>
+      </c>
+      <c r="BF191">
+        <v>4.1</v>
+      </c>
+      <c r="BG191">
+        <v>1.32</v>
+      </c>
+      <c r="BH191">
+        <v>3.05</v>
+      </c>
+      <c r="BI191">
+        <v>1.54</v>
+      </c>
+      <c r="BJ191">
+        <v>2.28</v>
+      </c>
+      <c r="BK191">
+        <v>1.89</v>
+      </c>
+      <c r="BL191">
+        <v>1.8</v>
+      </c>
+      <c r="BM191">
+        <v>2.38</v>
+      </c>
+      <c r="BN191">
+        <v>1.5</v>
+      </c>
+      <c r="BO191">
+        <v>3.05</v>
+      </c>
+      <c r="BP191">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="192" spans="1:68">
+      <c r="A192" s="1">
+        <v>191</v>
+      </c>
+      <c r="B192">
+        <v>7762780</v>
+      </c>
+      <c r="C192" t="s">
+        <v>68</v>
+      </c>
+      <c r="D192" t="s">
+        <v>69</v>
+      </c>
+      <c r="E192" s="2">
+        <v>45725.5</v>
+      </c>
+      <c r="F192">
+        <v>24</v>
+      </c>
+      <c r="G192" t="s">
+        <v>73</v>
+      </c>
+      <c r="H192" t="s">
+        <v>75</v>
+      </c>
+      <c r="I192">
+        <v>0</v>
+      </c>
+      <c r="J192">
+        <v>1</v>
+      </c>
+      <c r="K192">
+        <v>1</v>
+      </c>
+      <c r="L192">
+        <v>1</v>
+      </c>
+      <c r="M192">
+        <v>2</v>
+      </c>
+      <c r="N192">
+        <v>3</v>
+      </c>
+      <c r="O192" t="s">
+        <v>198</v>
+      </c>
+      <c r="P192" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q192">
+        <v>8.5</v>
+      </c>
+      <c r="R192">
+        <v>2.25</v>
+      </c>
+      <c r="S192">
+        <v>1.91</v>
+      </c>
+      <c r="T192">
+        <v>1.4</v>
+      </c>
+      <c r="U192">
+        <v>2.75</v>
+      </c>
+      <c r="V192">
+        <v>3</v>
+      </c>
+      <c r="W192">
+        <v>1.36</v>
+      </c>
+      <c r="X192">
+        <v>8</v>
+      </c>
+      <c r="Y192">
+        <v>1.08</v>
+      </c>
+      <c r="Z192">
+        <v>8.5</v>
+      </c>
+      <c r="AA192">
+        <v>5</v>
+      </c>
+      <c r="AB192">
+        <v>1.33</v>
+      </c>
+      <c r="AC192">
+        <v>1.01</v>
+      </c>
+      <c r="AD192">
+        <v>11</v>
+      </c>
+      <c r="AE192">
+        <v>1.22</v>
+      </c>
+      <c r="AF192">
+        <v>3.95</v>
+      </c>
+      <c r="AG192">
+        <v>1.92</v>
+      </c>
+      <c r="AH192">
+        <v>1.82</v>
+      </c>
+      <c r="AI192">
+        <v>2.38</v>
+      </c>
+      <c r="AJ192">
+        <v>1.53</v>
+      </c>
+      <c r="AK192">
+        <v>2.95</v>
+      </c>
+      <c r="AL192">
+        <v>1.14</v>
+      </c>
+      <c r="AM192">
+        <v>1.08</v>
+      </c>
+      <c r="AN192">
+        <v>0.82</v>
+      </c>
+      <c r="AO192">
+        <v>2.36</v>
+      </c>
+      <c r="AP192">
+        <v>0.75</v>
+      </c>
+      <c r="AQ192">
+        <v>2.42</v>
+      </c>
+      <c r="AR192">
+        <v>1.34</v>
+      </c>
+      <c r="AS192">
+        <v>1.63</v>
+      </c>
+      <c r="AT192">
+        <v>2.97</v>
+      </c>
+      <c r="AU192">
+        <v>4</v>
+      </c>
+      <c r="AV192">
+        <v>11</v>
+      </c>
+      <c r="AW192">
+        <v>5</v>
+      </c>
+      <c r="AX192">
+        <v>5</v>
+      </c>
+      <c r="AY192">
+        <v>9</v>
+      </c>
+      <c r="AZ192">
+        <v>16</v>
+      </c>
+      <c r="BA192">
+        <v>5</v>
+      </c>
+      <c r="BB192">
+        <v>5</v>
+      </c>
+      <c r="BC192">
+        <v>10</v>
+      </c>
+      <c r="BD192">
+        <v>3.8</v>
+      </c>
+      <c r="BE192">
+        <v>7</v>
+      </c>
+      <c r="BF192">
+        <v>1.32</v>
+      </c>
+      <c r="BG192">
+        <v>1.43</v>
+      </c>
+      <c r="BH192">
+        <v>2.55</v>
+      </c>
+      <c r="BI192">
+        <v>1.73</v>
+      </c>
+      <c r="BJ192">
+        <v>1.98</v>
+      </c>
+      <c r="BK192">
+        <v>2.17</v>
+      </c>
+      <c r="BL192">
+        <v>1.6</v>
+      </c>
+      <c r="BM192">
+        <v>2.8</v>
+      </c>
+      <c r="BN192">
+        <v>1.38</v>
+      </c>
+      <c r="BO192">
+        <v>3.65</v>
+      </c>
+      <c r="BP192">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="290">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -611,6 +611,9 @@
   </si>
   <si>
     <t>['82']</t>
+  </si>
+  <si>
+    <t>['30', '36', '45+1', '47', '57', '60']</t>
   </si>
   <si>
     <t>['12', '22', '45+1', '45+4', '90+1', '90+8']</t>
@@ -1242,7 +1245,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP192"/>
+  <dimension ref="A1:BP193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2116,7 +2119,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q5">
         <v>7.5</v>
@@ -2322,7 +2325,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2734,7 +2737,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q8">
         <v>4</v>
@@ -3018,7 +3021,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ9">
         <v>1.67</v>
@@ -3639,7 +3642,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ12">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3764,7 +3767,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3970,7 +3973,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q14">
         <v>2.4</v>
@@ -4794,7 +4797,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -5206,7 +5209,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -5412,7 +5415,7 @@
         <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5618,7 +5621,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5824,7 +5827,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -6030,7 +6033,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q24">
         <v>3.25</v>
@@ -6236,7 +6239,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q25">
         <v>2.05</v>
@@ -6317,7 +6320,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ25">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR25">
         <v>1.06</v>
@@ -6442,7 +6445,7 @@
         <v>86</v>
       </c>
       <c r="P26" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6932,7 +6935,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ28">
         <v>1.17</v>
@@ -7060,7 +7063,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7472,7 +7475,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7678,7 +7681,7 @@
         <v>86</v>
       </c>
       <c r="P32" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q32">
         <v>2.05</v>
@@ -8708,7 +8711,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -9201,7 +9204,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ39">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR39">
         <v>1.98</v>
@@ -9532,7 +9535,7 @@
         <v>86</v>
       </c>
       <c r="P41" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q41">
         <v>2.38</v>
@@ -9944,7 +9947,7 @@
         <v>86</v>
       </c>
       <c r="P43" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q43">
         <v>7.5</v>
@@ -10150,7 +10153,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10228,7 +10231,7 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ44">
         <v>1.17</v>
@@ -10562,7 +10565,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q46">
         <v>2.5</v>
@@ -10768,7 +10771,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q47">
         <v>4.33</v>
@@ -10974,7 +10977,7 @@
         <v>86</v>
       </c>
       <c r="P48" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q48">
         <v>2.4</v>
@@ -11592,7 +11595,7 @@
         <v>116</v>
       </c>
       <c r="P51" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11798,7 +11801,7 @@
         <v>118</v>
       </c>
       <c r="P52" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q52">
         <v>5.5</v>
@@ -12210,7 +12213,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -12291,7 +12294,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ54">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR54">
         <v>1.14</v>
@@ -12622,7 +12625,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q56">
         <v>5.5</v>
@@ -12700,7 +12703,7 @@
         <v>1</v>
       </c>
       <c r="AP56">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ56">
         <v>0.75</v>
@@ -12828,7 +12831,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q57">
         <v>5</v>
@@ -13034,7 +13037,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13240,7 +13243,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13446,7 +13449,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13652,7 +13655,7 @@
         <v>86</v>
       </c>
       <c r="P61" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q61">
         <v>6.5</v>
@@ -14064,7 +14067,7 @@
         <v>86</v>
       </c>
       <c r="P63" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q63">
         <v>3.5</v>
@@ -14270,7 +14273,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14888,7 +14891,7 @@
         <v>86</v>
       </c>
       <c r="P67" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q67">
         <v>6.5</v>
@@ -15094,7 +15097,7 @@
         <v>86</v>
       </c>
       <c r="P68" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q68">
         <v>4.75</v>
@@ -15712,7 +15715,7 @@
         <v>92</v>
       </c>
       <c r="P71" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q71">
         <v>9.5</v>
@@ -15790,7 +15793,7 @@
         <v>2</v>
       </c>
       <c r="AP71">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ71">
         <v>1.17</v>
@@ -15999,7 +16002,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ72">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR72">
         <v>1.09</v>
@@ -16330,7 +16333,7 @@
         <v>86</v>
       </c>
       <c r="P74" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16948,7 +16951,7 @@
         <v>130</v>
       </c>
       <c r="P77" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q77">
         <v>1.83</v>
@@ -17154,7 +17157,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q78">
         <v>12</v>
@@ -17360,7 +17363,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q79">
         <v>3.75</v>
@@ -17438,7 +17441,7 @@
         <v>1.6</v>
       </c>
       <c r="AP79">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ79">
         <v>1.33</v>
@@ -17566,7 +17569,7 @@
         <v>131</v>
       </c>
       <c r="P80" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17772,7 +17775,7 @@
         <v>132</v>
       </c>
       <c r="P81" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -18184,7 +18187,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q83">
         <v>1.67</v>
@@ -18802,7 +18805,7 @@
         <v>134</v>
       </c>
       <c r="P86" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q86">
         <v>2.63</v>
@@ -20325,7 +20328,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ93">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR93">
         <v>1.8</v>
@@ -20450,7 +20453,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q94">
         <v>13</v>
@@ -20528,7 +20531,7 @@
         <v>3</v>
       </c>
       <c r="AP94">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ94">
         <v>2.42</v>
@@ -20656,7 +20659,7 @@
         <v>139</v>
       </c>
       <c r="P95" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -21068,7 +21071,7 @@
         <v>140</v>
       </c>
       <c r="P97" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q97">
         <v>2.4</v>
@@ -21892,7 +21895,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22510,7 +22513,7 @@
         <v>145</v>
       </c>
       <c r="P104" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22716,7 +22719,7 @@
         <v>86</v>
       </c>
       <c r="P105" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -22922,7 +22925,7 @@
         <v>146</v>
       </c>
       <c r="P106" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q106">
         <v>6</v>
@@ -23334,7 +23337,7 @@
         <v>147</v>
       </c>
       <c r="P108" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23621,7 +23624,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ109">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR109">
         <v>1.64</v>
@@ -23746,7 +23749,7 @@
         <v>149</v>
       </c>
       <c r="P110" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -24030,7 +24033,7 @@
         <v>2.57</v>
       </c>
       <c r="AP111">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ111">
         <v>1.75</v>
@@ -24158,7 +24161,7 @@
         <v>143</v>
       </c>
       <c r="P112" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q112">
         <v>4.75</v>
@@ -24982,7 +24985,7 @@
         <v>86</v>
       </c>
       <c r="P116" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q116">
         <v>4.5</v>
@@ -25188,7 +25191,7 @@
         <v>153</v>
       </c>
       <c r="P117" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q117">
         <v>1.53</v>
@@ -25394,7 +25397,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25600,7 +25603,7 @@
         <v>154</v>
       </c>
       <c r="P119" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q119">
         <v>1.8</v>
@@ -25806,7 +25809,7 @@
         <v>155</v>
       </c>
       <c r="P120" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q120">
         <v>7.5</v>
@@ -26093,7 +26096,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ121">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR121">
         <v>1.4</v>
@@ -26218,7 +26221,7 @@
         <v>157</v>
       </c>
       <c r="P122" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q122">
         <v>2.63</v>
@@ -26424,7 +26427,7 @@
         <v>158</v>
       </c>
       <c r="P123" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q123">
         <v>1.73</v>
@@ -27042,7 +27045,7 @@
         <v>86</v>
       </c>
       <c r="P126" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27248,7 +27251,7 @@
         <v>161</v>
       </c>
       <c r="P127" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27454,7 +27457,7 @@
         <v>86</v>
       </c>
       <c r="P128" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q128">
         <v>2.4</v>
@@ -27660,7 +27663,7 @@
         <v>138</v>
       </c>
       <c r="P129" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27866,7 +27869,7 @@
         <v>98</v>
       </c>
       <c r="P130" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q130">
         <v>6.5</v>
@@ -27944,7 +27947,7 @@
         <v>1.63</v>
       </c>
       <c r="AP130">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ130">
         <v>1.92</v>
@@ -28072,7 +28075,7 @@
         <v>162</v>
       </c>
       <c r="P131" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q131">
         <v>4.33</v>
@@ -28278,7 +28281,7 @@
         <v>86</v>
       </c>
       <c r="P132" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q132">
         <v>8</v>
@@ -29926,7 +29929,7 @@
         <v>167</v>
       </c>
       <c r="P140" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q140">
         <v>2.3</v>
@@ -30132,7 +30135,7 @@
         <v>86</v>
       </c>
       <c r="P141" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q141">
         <v>7.5</v>
@@ -30338,7 +30341,7 @@
         <v>168</v>
       </c>
       <c r="P142" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30544,7 +30547,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30625,7 +30628,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ143">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR143">
         <v>1.42</v>
@@ -30956,7 +30959,7 @@
         <v>171</v>
       </c>
       <c r="P145" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q145">
         <v>3.75</v>
@@ -31162,7 +31165,7 @@
         <v>172</v>
       </c>
       <c r="P146" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q146">
         <v>7.5</v>
@@ -31368,7 +31371,7 @@
         <v>173</v>
       </c>
       <c r="P147" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31574,7 +31577,7 @@
         <v>174</v>
       </c>
       <c r="P148" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q148">
         <v>2.75</v>
@@ -31780,7 +31783,7 @@
         <v>86</v>
       </c>
       <c r="P149" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q149">
         <v>7.5</v>
@@ -32192,7 +32195,7 @@
         <v>86</v>
       </c>
       <c r="P151" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q151">
         <v>6.5</v>
@@ -32398,7 +32401,7 @@
         <v>176</v>
       </c>
       <c r="P152" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q152">
         <v>2.75</v>
@@ -32604,7 +32607,7 @@
         <v>177</v>
       </c>
       <c r="P153" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q153">
         <v>4.75</v>
@@ -33016,7 +33019,7 @@
         <v>179</v>
       </c>
       <c r="P155" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33094,7 +33097,7 @@
         <v>0.44</v>
       </c>
       <c r="AP155">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ155">
         <v>0.42</v>
@@ -33222,7 +33225,7 @@
         <v>176</v>
       </c>
       <c r="P156" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q156">
         <v>2.2</v>
@@ -33634,7 +33637,7 @@
         <v>181</v>
       </c>
       <c r="P158" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33921,7 +33924,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ159">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR159">
         <v>1.57</v>
@@ -34458,7 +34461,7 @@
         <v>86</v>
       </c>
       <c r="P162" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q162">
         <v>3.5</v>
@@ -34664,7 +34667,7 @@
         <v>184</v>
       </c>
       <c r="P163" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35076,7 +35079,7 @@
         <v>185</v>
       </c>
       <c r="P165" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q165">
         <v>9.5</v>
@@ -36393,7 +36396,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ171">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR171">
         <v>1.57</v>
@@ -36930,7 +36933,7 @@
         <v>86</v>
       </c>
       <c r="P174" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q174">
         <v>3.75</v>
@@ -37136,7 +37139,7 @@
         <v>124</v>
       </c>
       <c r="P175" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q175">
         <v>5.5</v>
@@ -37342,7 +37345,7 @@
         <v>86</v>
       </c>
       <c r="P176" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q176">
         <v>3.1</v>
@@ -37626,7 +37629,7 @@
         <v>1</v>
       </c>
       <c r="AP177">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ177">
         <v>0.92</v>
@@ -37754,7 +37757,7 @@
         <v>86</v>
       </c>
       <c r="P178" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q178">
         <v>3.5</v>
@@ -38166,7 +38169,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38372,7 +38375,7 @@
         <v>194</v>
       </c>
       <c r="P181" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q181">
         <v>3.2</v>
@@ -38578,7 +38581,7 @@
         <v>86</v>
       </c>
       <c r="P182" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q182">
         <v>8.5</v>
@@ -38990,7 +38993,7 @@
         <v>195</v>
       </c>
       <c r="P184" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q184">
         <v>3.6</v>
@@ -39608,7 +39611,7 @@
         <v>196</v>
       </c>
       <c r="P187" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -39814,7 +39817,7 @@
         <v>86</v>
       </c>
       <c r="P188" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q188">
         <v>6</v>
@@ -40020,7 +40023,7 @@
         <v>192</v>
       </c>
       <c r="P189" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q189">
         <v>2.3</v>
@@ -40432,7 +40435,7 @@
         <v>197</v>
       </c>
       <c r="P191" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
@@ -40638,7 +40641,7 @@
         <v>198</v>
       </c>
       <c r="P192" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q192">
         <v>8.5</v>
@@ -40795,6 +40798,212 @@
       </c>
       <c r="BP192">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="193" spans="1:68">
+      <c r="A193" s="1">
+        <v>192</v>
+      </c>
+      <c r="B193">
+        <v>7762781</v>
+      </c>
+      <c r="C193" t="s">
+        <v>68</v>
+      </c>
+      <c r="D193" t="s">
+        <v>69</v>
+      </c>
+      <c r="E193" s="2">
+        <v>45726.52083333334</v>
+      </c>
+      <c r="F193">
+        <v>24</v>
+      </c>
+      <c r="G193" t="s">
+        <v>77</v>
+      </c>
+      <c r="H193" t="s">
+        <v>76</v>
+      </c>
+      <c r="I193">
+        <v>3</v>
+      </c>
+      <c r="J193">
+        <v>0</v>
+      </c>
+      <c r="K193">
+        <v>3</v>
+      </c>
+      <c r="L193">
+        <v>6</v>
+      </c>
+      <c r="M193">
+        <v>1</v>
+      </c>
+      <c r="N193">
+        <v>7</v>
+      </c>
+      <c r="O193" t="s">
+        <v>199</v>
+      </c>
+      <c r="P193" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q193">
+        <v>2.6</v>
+      </c>
+      <c r="R193">
+        <v>2.05</v>
+      </c>
+      <c r="S193">
+        <v>4.75</v>
+      </c>
+      <c r="T193">
+        <v>1.44</v>
+      </c>
+      <c r="U193">
+        <v>2.63</v>
+      </c>
+      <c r="V193">
+        <v>3.25</v>
+      </c>
+      <c r="W193">
+        <v>1.33</v>
+      </c>
+      <c r="X193">
+        <v>10</v>
+      </c>
+      <c r="Y193">
+        <v>1.06</v>
+      </c>
+      <c r="Z193">
+        <v>1.83</v>
+      </c>
+      <c r="AA193">
+        <v>3.64</v>
+      </c>
+      <c r="AB193">
+        <v>4</v>
+      </c>
+      <c r="AC193">
+        <v>1.02</v>
+      </c>
+      <c r="AD193">
+        <v>7.9</v>
+      </c>
+      <c r="AE193">
+        <v>1.33</v>
+      </c>
+      <c r="AF193">
+        <v>3.1</v>
+      </c>
+      <c r="AG193">
+        <v>2.05</v>
+      </c>
+      <c r="AH193">
+        <v>1.65</v>
+      </c>
+      <c r="AI193">
+        <v>2</v>
+      </c>
+      <c r="AJ193">
+        <v>1.73</v>
+      </c>
+      <c r="AK193">
+        <v>1.21</v>
+      </c>
+      <c r="AL193">
+        <v>1.31</v>
+      </c>
+      <c r="AM193">
+        <v>1.9</v>
+      </c>
+      <c r="AN193">
+        <v>1</v>
+      </c>
+      <c r="AO193">
+        <v>0.27</v>
+      </c>
+      <c r="AP193">
+        <v>1.17</v>
+      </c>
+      <c r="AQ193">
+        <v>0.25</v>
+      </c>
+      <c r="AR193">
+        <v>1.03</v>
+      </c>
+      <c r="AS193">
+        <v>0.97</v>
+      </c>
+      <c r="AT193">
+        <v>2</v>
+      </c>
+      <c r="AU193">
+        <v>7</v>
+      </c>
+      <c r="AV193">
+        <v>4</v>
+      </c>
+      <c r="AW193">
+        <v>4</v>
+      </c>
+      <c r="AX193">
+        <v>4</v>
+      </c>
+      <c r="AY193">
+        <v>11</v>
+      </c>
+      <c r="AZ193">
+        <v>8</v>
+      </c>
+      <c r="BA193">
+        <v>5</v>
+      </c>
+      <c r="BB193">
+        <v>7</v>
+      </c>
+      <c r="BC193">
+        <v>12</v>
+      </c>
+      <c r="BD193">
+        <v>1.52</v>
+      </c>
+      <c r="BE193">
+        <v>6.75</v>
+      </c>
+      <c r="BF193">
+        <v>2.8</v>
+      </c>
+      <c r="BG193">
+        <v>1.4</v>
+      </c>
+      <c r="BH193">
+        <v>2.7</v>
+      </c>
+      <c r="BI193">
+        <v>1.67</v>
+      </c>
+      <c r="BJ193">
+        <v>2.07</v>
+      </c>
+      <c r="BK193">
+        <v>2.07</v>
+      </c>
+      <c r="BL193">
+        <v>1.67</v>
+      </c>
+      <c r="BM193">
+        <v>2.65</v>
+      </c>
+      <c r="BN193">
+        <v>1.42</v>
+      </c>
+      <c r="BO193">
+        <v>3.45</v>
+      </c>
+      <c r="BP193">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="292">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -616,6 +616,9 @@
     <t>['30', '36', '45+1', '47', '57', '60']</t>
   </si>
   <si>
+    <t>['44', '78']</t>
+  </si>
+  <si>
     <t>['12', '22', '45+1', '45+4', '90+1', '90+8']</t>
   </si>
   <si>
@@ -884,6 +887,9 @@
   </si>
   <si>
     <t>['34', '53']</t>
+  </si>
+  <si>
+    <t>['8']</t>
   </si>
 </sst>
 </file>
@@ -1245,7 +1251,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP193"/>
+  <dimension ref="A1:BP195"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2119,7 +2125,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q5">
         <v>7.5</v>
@@ -2325,7 +2331,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2737,7 +2743,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q8">
         <v>4</v>
@@ -3024,7 +3030,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ9">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3767,7 +3773,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3973,7 +3979,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q14">
         <v>2.4</v>
@@ -4054,7 +4060,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ14">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4797,7 +4803,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -5209,7 +5215,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -5415,7 +5421,7 @@
         <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5621,7 +5627,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5827,7 +5833,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -5908,7 +5914,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ23">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR23">
         <v>0.91</v>
@@ -6033,7 +6039,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q24">
         <v>3.25</v>
@@ -6111,7 +6117,7 @@
         <v>2</v>
       </c>
       <c r="AP24">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ24">
         <v>1.33</v>
@@ -6239,7 +6245,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q25">
         <v>2.05</v>
@@ -6445,7 +6451,7 @@
         <v>86</v>
       </c>
       <c r="P26" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6526,7 +6532,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ26">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR26">
         <v>1.84</v>
@@ -7063,7 +7069,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7475,7 +7481,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7556,7 +7562,7 @@
         <v>1</v>
       </c>
       <c r="AQ31">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR31">
         <v>1.36</v>
@@ -7681,7 +7687,7 @@
         <v>86</v>
       </c>
       <c r="P32" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q32">
         <v>2.05</v>
@@ -8711,7 +8717,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -9535,7 +9541,7 @@
         <v>86</v>
       </c>
       <c r="P41" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q41">
         <v>2.38</v>
@@ -9947,7 +9953,7 @@
         <v>86</v>
       </c>
       <c r="P43" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q43">
         <v>7.5</v>
@@ -10153,7 +10159,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10234,7 +10240,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ44">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR44">
         <v>0.95</v>
@@ -10565,7 +10571,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q46">
         <v>2.5</v>
@@ -10643,7 +10649,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ46">
         <v>1.08</v>
@@ -10771,7 +10777,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q47">
         <v>4.33</v>
@@ -10977,7 +10983,7 @@
         <v>86</v>
       </c>
       <c r="P48" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q48">
         <v>2.4</v>
@@ -11595,7 +11601,7 @@
         <v>116</v>
       </c>
       <c r="P51" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11801,7 +11807,7 @@
         <v>118</v>
       </c>
       <c r="P52" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q52">
         <v>5.5</v>
@@ -11882,7 +11888,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ52">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR52">
         <v>0.93</v>
@@ -12213,7 +12219,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -12625,7 +12631,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q56">
         <v>5.5</v>
@@ -12831,7 +12837,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q57">
         <v>5</v>
@@ -13037,7 +13043,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13243,7 +13249,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13449,7 +13455,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13655,7 +13661,7 @@
         <v>86</v>
       </c>
       <c r="P61" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q61">
         <v>6.5</v>
@@ -13939,7 +13945,7 @@
         <v>3</v>
       </c>
       <c r="AP62">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ62">
         <v>2.42</v>
@@ -14067,7 +14073,7 @@
         <v>86</v>
       </c>
       <c r="P63" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q63">
         <v>3.5</v>
@@ -14273,7 +14279,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14560,7 +14566,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ65">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR65">
         <v>1.93</v>
@@ -14891,7 +14897,7 @@
         <v>86</v>
       </c>
       <c r="P67" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q67">
         <v>6.5</v>
@@ -14969,7 +14975,7 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ67">
         <v>1.92</v>
@@ -15097,7 +15103,7 @@
         <v>86</v>
       </c>
       <c r="P68" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q68">
         <v>4.75</v>
@@ -15715,7 +15721,7 @@
         <v>92</v>
       </c>
       <c r="P71" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q71">
         <v>9.5</v>
@@ -16333,7 +16339,7 @@
         <v>86</v>
       </c>
       <c r="P74" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16951,7 +16957,7 @@
         <v>130</v>
       </c>
       <c r="P77" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q77">
         <v>1.83</v>
@@ -17157,7 +17163,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q78">
         <v>12</v>
@@ -17363,7 +17369,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q79">
         <v>3.75</v>
@@ -17569,7 +17575,7 @@
         <v>131</v>
       </c>
       <c r="P80" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17775,7 +17781,7 @@
         <v>132</v>
       </c>
       <c r="P81" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -17856,7 +17862,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ81">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR81">
         <v>1.3</v>
@@ -18059,7 +18065,7 @@
         <v>1.75</v>
       </c>
       <c r="AP82">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ82">
         <v>1.92</v>
@@ -18187,7 +18193,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q83">
         <v>1.67</v>
@@ -18805,7 +18811,7 @@
         <v>134</v>
       </c>
       <c r="P86" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q86">
         <v>2.63</v>
@@ -19092,7 +19098,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ87">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR87">
         <v>1.66</v>
@@ -19504,7 +19510,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ89">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR89">
         <v>1.32</v>
@@ -20453,7 +20459,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q94">
         <v>13</v>
@@ -20659,7 +20665,7 @@
         <v>139</v>
       </c>
       <c r="P95" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -20946,7 +20952,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ96">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR96">
         <v>1.46</v>
@@ -21071,7 +21077,7 @@
         <v>140</v>
       </c>
       <c r="P97" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q97">
         <v>2.4</v>
@@ -21149,7 +21155,7 @@
         <v>1</v>
       </c>
       <c r="AP97">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ97">
         <v>1.17</v>
@@ -21895,7 +21901,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -21976,7 +21982,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ101">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR101">
         <v>1.85</v>
@@ -22513,7 +22519,7 @@
         <v>145</v>
       </c>
       <c r="P104" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22719,7 +22725,7 @@
         <v>86</v>
       </c>
       <c r="P105" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -22925,7 +22931,7 @@
         <v>146</v>
       </c>
       <c r="P106" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q106">
         <v>6</v>
@@ -23337,7 +23343,7 @@
         <v>147</v>
       </c>
       <c r="P108" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23418,7 +23424,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ108">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR108">
         <v>1.48</v>
@@ -23749,7 +23755,7 @@
         <v>149</v>
       </c>
       <c r="P110" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -24161,7 +24167,7 @@
         <v>143</v>
       </c>
       <c r="P112" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q112">
         <v>4.75</v>
@@ -24857,10 +24863,10 @@
         <v>1.33</v>
       </c>
       <c r="AP115">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ115">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR115">
         <v>1.42</v>
@@ -24985,7 +24991,7 @@
         <v>86</v>
       </c>
       <c r="P116" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q116">
         <v>4.5</v>
@@ -25191,7 +25197,7 @@
         <v>153</v>
       </c>
       <c r="P117" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q117">
         <v>1.53</v>
@@ -25397,7 +25403,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25603,7 +25609,7 @@
         <v>154</v>
       </c>
       <c r="P119" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q119">
         <v>1.8</v>
@@ -25809,7 +25815,7 @@
         <v>155</v>
       </c>
       <c r="P120" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q120">
         <v>7.5</v>
@@ -26221,7 +26227,7 @@
         <v>157</v>
       </c>
       <c r="P122" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q122">
         <v>2.63</v>
@@ -26302,7 +26308,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ122">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR122">
         <v>1.43</v>
@@ -26427,7 +26433,7 @@
         <v>158</v>
       </c>
       <c r="P123" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q123">
         <v>1.73</v>
@@ -27045,7 +27051,7 @@
         <v>86</v>
       </c>
       <c r="P126" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27251,7 +27257,7 @@
         <v>161</v>
       </c>
       <c r="P127" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27457,7 +27463,7 @@
         <v>86</v>
       </c>
       <c r="P128" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q128">
         <v>2.4</v>
@@ -27535,7 +27541,7 @@
         <v>0.86</v>
       </c>
       <c r="AP128">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ128">
         <v>0.92</v>
@@ -27663,7 +27669,7 @@
         <v>138</v>
       </c>
       <c r="P129" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27869,7 +27875,7 @@
         <v>98</v>
       </c>
       <c r="P130" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q130">
         <v>6.5</v>
@@ -28075,7 +28081,7 @@
         <v>162</v>
       </c>
       <c r="P131" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q131">
         <v>4.33</v>
@@ -28156,7 +28162,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ131">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR131">
         <v>1.16</v>
@@ -28281,7 +28287,7 @@
         <v>86</v>
       </c>
       <c r="P132" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q132">
         <v>8</v>
@@ -29929,7 +29935,7 @@
         <v>167</v>
       </c>
       <c r="P140" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q140">
         <v>2.3</v>
@@ -30135,7 +30141,7 @@
         <v>86</v>
       </c>
       <c r="P141" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q141">
         <v>7.5</v>
@@ -30341,7 +30347,7 @@
         <v>168</v>
       </c>
       <c r="P142" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30422,7 +30428,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ142">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR142">
         <v>2.2</v>
@@ -30547,7 +30553,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30625,7 +30631,7 @@
         <v>0.25</v>
       </c>
       <c r="AP143">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ143">
         <v>0.25</v>
@@ -30959,7 +30965,7 @@
         <v>171</v>
       </c>
       <c r="P145" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q145">
         <v>3.75</v>
@@ -31040,7 +31046,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ145">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR145">
         <v>1.27</v>
@@ -31165,7 +31171,7 @@
         <v>172</v>
       </c>
       <c r="P146" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q146">
         <v>7.5</v>
@@ -31371,7 +31377,7 @@
         <v>173</v>
       </c>
       <c r="P147" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31577,7 +31583,7 @@
         <v>174</v>
       </c>
       <c r="P148" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q148">
         <v>2.75</v>
@@ -31783,7 +31789,7 @@
         <v>86</v>
       </c>
       <c r="P149" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q149">
         <v>7.5</v>
@@ -32195,7 +32201,7 @@
         <v>86</v>
       </c>
       <c r="P151" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q151">
         <v>6.5</v>
@@ -32401,7 +32407,7 @@
         <v>176</v>
       </c>
       <c r="P152" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q152">
         <v>2.75</v>
@@ -32607,7 +32613,7 @@
         <v>177</v>
       </c>
       <c r="P153" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q153">
         <v>4.75</v>
@@ -33019,7 +33025,7 @@
         <v>179</v>
       </c>
       <c r="P155" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33225,7 +33231,7 @@
         <v>176</v>
       </c>
       <c r="P156" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q156">
         <v>2.2</v>
@@ -33306,7 +33312,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ156">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR156">
         <v>1.7</v>
@@ -33509,7 +33515,7 @@
         <v>1.22</v>
       </c>
       <c r="AP157">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ157">
         <v>1.42</v>
@@ -33637,7 +33643,7 @@
         <v>181</v>
       </c>
       <c r="P158" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -34461,7 +34467,7 @@
         <v>86</v>
       </c>
       <c r="P162" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q162">
         <v>3.5</v>
@@ -34667,7 +34673,7 @@
         <v>184</v>
       </c>
       <c r="P163" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35079,7 +35085,7 @@
         <v>185</v>
       </c>
       <c r="P165" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q165">
         <v>9.5</v>
@@ -35572,7 +35578,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ167">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR167">
         <v>1.7</v>
@@ -35981,7 +35987,7 @@
         <v>1.3</v>
       </c>
       <c r="AP169">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ169">
         <v>1.17</v>
@@ -36933,7 +36939,7 @@
         <v>86</v>
       </c>
       <c r="P174" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q174">
         <v>3.75</v>
@@ -37139,7 +37145,7 @@
         <v>124</v>
       </c>
       <c r="P175" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q175">
         <v>5.5</v>
@@ -37345,7 +37351,7 @@
         <v>86</v>
       </c>
       <c r="P176" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q176">
         <v>3.1</v>
@@ -37426,7 +37432,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ176">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR176">
         <v>1.29</v>
@@ -37757,7 +37763,7 @@
         <v>86</v>
       </c>
       <c r="P178" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q178">
         <v>3.5</v>
@@ -38169,7 +38175,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38250,7 +38256,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ180">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR180">
         <v>1.56</v>
@@ -38375,7 +38381,7 @@
         <v>194</v>
       </c>
       <c r="P181" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q181">
         <v>3.2</v>
@@ -38581,7 +38587,7 @@
         <v>86</v>
       </c>
       <c r="P182" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q182">
         <v>8.5</v>
@@ -38993,7 +38999,7 @@
         <v>195</v>
       </c>
       <c r="P184" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q184">
         <v>3.6</v>
@@ -39071,7 +39077,7 @@
         <v>1.91</v>
       </c>
       <c r="AP184">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ184">
         <v>1.75</v>
@@ -39611,7 +39617,7 @@
         <v>196</v>
       </c>
       <c r="P187" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -39692,7 +39698,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ187">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR187">
         <v>1.74</v>
@@ -39817,7 +39823,7 @@
         <v>86</v>
       </c>
       <c r="P188" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q188">
         <v>6</v>
@@ -40023,7 +40029,7 @@
         <v>192</v>
       </c>
       <c r="P189" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q189">
         <v>2.3</v>
@@ -40435,7 +40441,7 @@
         <v>197</v>
       </c>
       <c r="P191" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
@@ -40641,7 +40647,7 @@
         <v>198</v>
       </c>
       <c r="P192" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q192">
         <v>8.5</v>
@@ -41004,6 +41010,418 @@
       </c>
       <c r="BP193">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="194" spans="1:68">
+      <c r="A194" s="1">
+        <v>193</v>
+      </c>
+      <c r="B194">
+        <v>7762788</v>
+      </c>
+      <c r="C194" t="s">
+        <v>68</v>
+      </c>
+      <c r="D194" t="s">
+        <v>69</v>
+      </c>
+      <c r="E194" s="2">
+        <v>45730.42708333334</v>
+      </c>
+      <c r="F194">
+        <v>25</v>
+      </c>
+      <c r="G194" t="s">
+        <v>85</v>
+      </c>
+      <c r="H194" t="s">
+        <v>83</v>
+      </c>
+      <c r="I194">
+        <v>1</v>
+      </c>
+      <c r="J194">
+        <v>1</v>
+      </c>
+      <c r="K194">
+        <v>2</v>
+      </c>
+      <c r="L194">
+        <v>2</v>
+      </c>
+      <c r="M194">
+        <v>1</v>
+      </c>
+      <c r="N194">
+        <v>3</v>
+      </c>
+      <c r="O194" t="s">
+        <v>200</v>
+      </c>
+      <c r="P194" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q194">
+        <v>2.75</v>
+      </c>
+      <c r="R194">
+        <v>2.05</v>
+      </c>
+      <c r="S194">
+        <v>4.33</v>
+      </c>
+      <c r="T194">
+        <v>1.5</v>
+      </c>
+      <c r="U194">
+        <v>2.5</v>
+      </c>
+      <c r="V194">
+        <v>3.4</v>
+      </c>
+      <c r="W194">
+        <v>1.3</v>
+      </c>
+      <c r="X194">
+        <v>10</v>
+      </c>
+      <c r="Y194">
+        <v>1.06</v>
+      </c>
+      <c r="Z194">
+        <v>2.25</v>
+      </c>
+      <c r="AA194">
+        <v>3.41</v>
+      </c>
+      <c r="AB194">
+        <v>3.01</v>
+      </c>
+      <c r="AC194">
+        <v>1.01</v>
+      </c>
+      <c r="AD194">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE194">
+        <v>1.34</v>
+      </c>
+      <c r="AF194">
+        <v>2.79</v>
+      </c>
+      <c r="AG194">
+        <v>2.1</v>
+      </c>
+      <c r="AH194">
+        <v>1.61</v>
+      </c>
+      <c r="AI194">
+        <v>1.91</v>
+      </c>
+      <c r="AJ194">
+        <v>1.8</v>
+      </c>
+      <c r="AK194">
+        <v>1.25</v>
+      </c>
+      <c r="AL194">
+        <v>1.3</v>
+      </c>
+      <c r="AM194">
+        <v>1.79</v>
+      </c>
+      <c r="AN194">
+        <v>1.92</v>
+      </c>
+      <c r="AO194">
+        <v>1.67</v>
+      </c>
+      <c r="AP194">
+        <v>2</v>
+      </c>
+      <c r="AQ194">
+        <v>1.54</v>
+      </c>
+      <c r="AR194">
+        <v>1.45</v>
+      </c>
+      <c r="AS194">
+        <v>1.2</v>
+      </c>
+      <c r="AT194">
+        <v>2.65</v>
+      </c>
+      <c r="AU194">
+        <v>4</v>
+      </c>
+      <c r="AV194">
+        <v>3</v>
+      </c>
+      <c r="AW194">
+        <v>6</v>
+      </c>
+      <c r="AX194">
+        <v>3</v>
+      </c>
+      <c r="AY194">
+        <v>10</v>
+      </c>
+      <c r="AZ194">
+        <v>6</v>
+      </c>
+      <c r="BA194">
+        <v>1</v>
+      </c>
+      <c r="BB194">
+        <v>3</v>
+      </c>
+      <c r="BC194">
+        <v>4</v>
+      </c>
+      <c r="BD194">
+        <v>1.71</v>
+      </c>
+      <c r="BE194">
+        <v>6.4</v>
+      </c>
+      <c r="BF194">
+        <v>2.4</v>
+      </c>
+      <c r="BG194">
+        <v>1.36</v>
+      </c>
+      <c r="BH194">
+        <v>2.8</v>
+      </c>
+      <c r="BI194">
+        <v>1.61</v>
+      </c>
+      <c r="BJ194">
+        <v>2.15</v>
+      </c>
+      <c r="BK194">
+        <v>1.98</v>
+      </c>
+      <c r="BL194">
+        <v>1.73</v>
+      </c>
+      <c r="BM194">
+        <v>2.5</v>
+      </c>
+      <c r="BN194">
+        <v>1.46</v>
+      </c>
+      <c r="BO194">
+        <v>3.3</v>
+      </c>
+      <c r="BP194">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="195" spans="1:68">
+      <c r="A195" s="1">
+        <v>194</v>
+      </c>
+      <c r="B195">
+        <v>7762793</v>
+      </c>
+      <c r="C195" t="s">
+        <v>68</v>
+      </c>
+      <c r="D195" t="s">
+        <v>69</v>
+      </c>
+      <c r="E195" s="2">
+        <v>45730.53125</v>
+      </c>
+      <c r="F195">
+        <v>25</v>
+      </c>
+      <c r="G195" t="s">
+        <v>71</v>
+      </c>
+      <c r="H195" t="s">
+        <v>72</v>
+      </c>
+      <c r="I195">
+        <v>0</v>
+      </c>
+      <c r="J195">
+        <v>0</v>
+      </c>
+      <c r="K195">
+        <v>0</v>
+      </c>
+      <c r="L195">
+        <v>0</v>
+      </c>
+      <c r="M195">
+        <v>0</v>
+      </c>
+      <c r="N195">
+        <v>0</v>
+      </c>
+      <c r="O195" t="s">
+        <v>86</v>
+      </c>
+      <c r="P195" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q195">
+        <v>3.6</v>
+      </c>
+      <c r="R195">
+        <v>1.91</v>
+      </c>
+      <c r="S195">
+        <v>3.5</v>
+      </c>
+      <c r="T195">
+        <v>1.57</v>
+      </c>
+      <c r="U195">
+        <v>2.25</v>
+      </c>
+      <c r="V195">
+        <v>3.75</v>
+      </c>
+      <c r="W195">
+        <v>1.25</v>
+      </c>
+      <c r="X195">
+        <v>11</v>
+      </c>
+      <c r="Y195">
+        <v>1.05</v>
+      </c>
+      <c r="Z195">
+        <v>2.61</v>
+      </c>
+      <c r="AA195">
+        <v>3.31</v>
+      </c>
+      <c r="AB195">
+        <v>2.61</v>
+      </c>
+      <c r="AC195">
+        <v>1.05</v>
+      </c>
+      <c r="AD195">
+        <v>6.65</v>
+      </c>
+      <c r="AE195">
+        <v>1.5</v>
+      </c>
+      <c r="AF195">
+        <v>2.4</v>
+      </c>
+      <c r="AG195">
+        <v>2</v>
+      </c>
+      <c r="AH195">
+        <v>1.75</v>
+      </c>
+      <c r="AI195">
+        <v>2.1</v>
+      </c>
+      <c r="AJ195">
+        <v>1.67</v>
+      </c>
+      <c r="AK195">
+        <v>1.46</v>
+      </c>
+      <c r="AL195">
+        <v>1.35</v>
+      </c>
+      <c r="AM195">
+        <v>1.41</v>
+      </c>
+      <c r="AN195">
+        <v>1</v>
+      </c>
+      <c r="AO195">
+        <v>1.17</v>
+      </c>
+      <c r="AP195">
+        <v>1</v>
+      </c>
+      <c r="AQ195">
+        <v>1.15</v>
+      </c>
+      <c r="AR195">
+        <v>1.24</v>
+      </c>
+      <c r="AS195">
+        <v>1.27</v>
+      </c>
+      <c r="AT195">
+        <v>2.51</v>
+      </c>
+      <c r="AU195">
+        <v>2</v>
+      </c>
+      <c r="AV195">
+        <v>6</v>
+      </c>
+      <c r="AW195">
+        <v>2</v>
+      </c>
+      <c r="AX195">
+        <v>7</v>
+      </c>
+      <c r="AY195">
+        <v>4</v>
+      </c>
+      <c r="AZ195">
+        <v>13</v>
+      </c>
+      <c r="BA195">
+        <v>2</v>
+      </c>
+      <c r="BB195">
+        <v>8</v>
+      </c>
+      <c r="BC195">
+        <v>10</v>
+      </c>
+      <c r="BD195">
+        <v>2</v>
+      </c>
+      <c r="BE195">
+        <v>6.1</v>
+      </c>
+      <c r="BF195">
+        <v>1.98</v>
+      </c>
+      <c r="BG195">
+        <v>1.55</v>
+      </c>
+      <c r="BH195">
+        <v>2.25</v>
+      </c>
+      <c r="BI195">
+        <v>1.92</v>
+      </c>
+      <c r="BJ195">
+        <v>1.78</v>
+      </c>
+      <c r="BK195">
+        <v>2.43</v>
+      </c>
+      <c r="BL195">
+        <v>1.48</v>
+      </c>
+      <c r="BM195">
+        <v>3.2</v>
+      </c>
+      <c r="BN195">
+        <v>1.28</v>
+      </c>
+      <c r="BO195">
+        <v>4.35</v>
+      </c>
+      <c r="BP195">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="294">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -619,6 +619,15 @@
     <t>['44', '78']</t>
   </si>
   <si>
+    <t>['45', '90+4']</t>
+  </si>
+  <si>
+    <t>['4', '57', '90+1']</t>
+  </si>
+  <si>
+    <t>['69']</t>
+  </si>
+  <si>
     <t>['12', '22', '45+1', '45+4', '90+1', '90+8']</t>
   </si>
   <si>
@@ -668,9 +677,6 @@
   </si>
   <si>
     <t>['75', '82']</t>
-  </si>
-  <si>
-    <t>['69']</t>
   </si>
   <si>
     <t>['65']</t>
@@ -1251,7 +1257,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP195"/>
+  <dimension ref="A1:BP198"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2125,7 +2131,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q5">
         <v>7.5</v>
@@ -2331,7 +2337,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2615,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ7">
         <v>1.42</v>
@@ -2743,7 +2749,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q8">
         <v>4</v>
@@ -2821,7 +2827,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ8">
         <v>1.33</v>
@@ -3442,7 +3448,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ11">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3645,7 +3651,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ12">
         <v>0.25</v>
@@ -3773,7 +3779,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3979,7 +3985,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q14">
         <v>2.4</v>
@@ -4266,7 +4272,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ15">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4675,7 +4681,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ17">
         <v>0.75</v>
@@ -4803,7 +4809,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -5215,7 +5221,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -5293,7 +5299,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ20">
         <v>1.08</v>
@@ -5421,7 +5427,7 @@
         <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5502,7 +5508,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ21">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR21">
         <v>0.9</v>
@@ -5627,7 +5633,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5833,7 +5839,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -6039,7 +6045,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q24">
         <v>3.25</v>
@@ -6245,7 +6251,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q25">
         <v>2.05</v>
@@ -6451,7 +6457,7 @@
         <v>86</v>
       </c>
       <c r="P26" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6944,7 +6950,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ28">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR28">
         <v>0.91</v>
@@ -7069,7 +7075,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7150,7 +7156,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ29">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR29">
         <v>2.25</v>
@@ -7481,7 +7487,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7687,7 +7693,7 @@
         <v>86</v>
       </c>
       <c r="P32" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q32">
         <v>2.05</v>
@@ -7765,7 +7771,7 @@
         <v>0.5</v>
       </c>
       <c r="AP32">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ32">
         <v>0.75</v>
@@ -7971,7 +7977,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ33">
         <v>1.92</v>
@@ -8383,7 +8389,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ35">
         <v>1.75</v>
@@ -8717,7 +8723,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -8798,7 +8804,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ37">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR37">
         <v>1.15</v>
@@ -9004,7 +9010,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ38">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR38">
         <v>0.86</v>
@@ -9541,7 +9547,7 @@
         <v>86</v>
       </c>
       <c r="P41" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="Q41">
         <v>2.38</v>
@@ -9953,7 +9959,7 @@
         <v>86</v>
       </c>
       <c r="P43" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q43">
         <v>7.5</v>
@@ -10159,7 +10165,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10571,7 +10577,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q46">
         <v>2.5</v>
@@ -10777,7 +10783,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q47">
         <v>4.33</v>
@@ -10983,7 +10989,7 @@
         <v>86</v>
       </c>
       <c r="P48" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q48">
         <v>2.4</v>
@@ -11061,7 +11067,7 @@
         <v>3</v>
       </c>
       <c r="AP48">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ48">
         <v>1.75</v>
@@ -11601,7 +11607,7 @@
         <v>116</v>
       </c>
       <c r="P51" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11682,7 +11688,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ51">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR51">
         <v>1.13</v>
@@ -11807,7 +11813,7 @@
         <v>118</v>
       </c>
       <c r="P52" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q52">
         <v>5.5</v>
@@ -11885,7 +11891,7 @@
         <v>3</v>
       </c>
       <c r="AP52">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ52">
         <v>1.54</v>
@@ -12091,10 +12097,10 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ53">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR53">
         <v>1.4</v>
@@ -12219,7 +12225,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -12631,7 +12637,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q56">
         <v>5.5</v>
@@ -12837,7 +12843,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q57">
         <v>5</v>
@@ -13043,7 +13049,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13249,7 +13255,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13455,7 +13461,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13661,7 +13667,7 @@
         <v>86</v>
       </c>
       <c r="P61" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q61">
         <v>6.5</v>
@@ -14073,7 +14079,7 @@
         <v>86</v>
       </c>
       <c r="P63" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q63">
         <v>3.5</v>
@@ -14279,7 +14285,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14357,7 +14363,7 @@
         <v>0</v>
       </c>
       <c r="AP64">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ64">
         <v>1.33</v>
@@ -14563,7 +14569,7 @@
         <v>2.25</v>
       </c>
       <c r="AP65">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ65">
         <v>1.54</v>
@@ -14769,10 +14775,10 @@
         <v>1.67</v>
       </c>
       <c r="AP66">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ66">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR66">
         <v>1.61</v>
@@ -14897,7 +14903,7 @@
         <v>86</v>
       </c>
       <c r="P67" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q67">
         <v>6.5</v>
@@ -15103,7 +15109,7 @@
         <v>86</v>
       </c>
       <c r="P68" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q68">
         <v>4.75</v>
@@ -15184,7 +15190,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ68">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR68">
         <v>1.26</v>
@@ -15390,7 +15396,7 @@
         <v>1</v>
       </c>
       <c r="AQ69">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR69">
         <v>1.44</v>
@@ -15721,7 +15727,7 @@
         <v>92</v>
       </c>
       <c r="P71" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q71">
         <v>9.5</v>
@@ -16339,7 +16345,7 @@
         <v>86</v>
       </c>
       <c r="P74" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16957,7 +16963,7 @@
         <v>130</v>
       </c>
       <c r="P77" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q77">
         <v>1.83</v>
@@ -17163,7 +17169,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q78">
         <v>12</v>
@@ -17369,7 +17375,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q79">
         <v>3.75</v>
@@ -17575,7 +17581,7 @@
         <v>131</v>
       </c>
       <c r="P80" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17781,7 +17787,7 @@
         <v>132</v>
       </c>
       <c r="P81" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -18068,7 +18074,7 @@
         <v>2</v>
       </c>
       <c r="AQ82">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR82">
         <v>1.21</v>
@@ -18193,7 +18199,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q83">
         <v>1.67</v>
@@ -18271,7 +18277,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ83">
         <v>1.33</v>
@@ -18683,10 +18689,10 @@
         <v>0.75</v>
       </c>
       <c r="AP85">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ85">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR85">
         <v>0.85</v>
@@ -18811,7 +18817,7 @@
         <v>134</v>
       </c>
       <c r="P86" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q86">
         <v>2.63</v>
@@ -18892,7 +18898,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ86">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR86">
         <v>1.23</v>
@@ -19095,7 +19101,7 @@
         <v>2.33</v>
       </c>
       <c r="AP87">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ87">
         <v>1.15</v>
@@ -20459,7 +20465,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q94">
         <v>13</v>
@@ -20665,7 +20671,7 @@
         <v>139</v>
       </c>
       <c r="P95" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -21077,7 +21083,7 @@
         <v>140</v>
       </c>
       <c r="P97" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q97">
         <v>2.4</v>
@@ -21158,7 +21164,7 @@
         <v>2</v>
       </c>
       <c r="AQ97">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR97">
         <v>1.31</v>
@@ -21361,10 +21367,10 @@
         <v>0.8</v>
       </c>
       <c r="AP98">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ98">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR98">
         <v>1.84</v>
@@ -21776,7 +21782,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ100">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR100">
         <v>1.22</v>
@@ -21901,7 +21907,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22185,7 +22191,7 @@
         <v>0.8</v>
       </c>
       <c r="AP102">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ102">
         <v>0.92</v>
@@ -22391,7 +22397,7 @@
         <v>1.67</v>
       </c>
       <c r="AP103">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ103">
         <v>1.17</v>
@@ -22519,7 +22525,7 @@
         <v>145</v>
       </c>
       <c r="P104" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22725,7 +22731,7 @@
         <v>86</v>
       </c>
       <c r="P105" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -22931,7 +22937,7 @@
         <v>146</v>
       </c>
       <c r="P106" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q106">
         <v>6</v>
@@ -23343,7 +23349,7 @@
         <v>147</v>
       </c>
       <c r="P108" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23627,7 +23633,7 @@
         <v>0.33</v>
       </c>
       <c r="AP109">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ109">
         <v>0.25</v>
@@ -23755,7 +23761,7 @@
         <v>149</v>
       </c>
       <c r="P110" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -24167,7 +24173,7 @@
         <v>143</v>
       </c>
       <c r="P112" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q112">
         <v>4.75</v>
@@ -24454,7 +24460,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ113">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR113">
         <v>1.41</v>
@@ -24660,7 +24666,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ114">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR114">
         <v>1.09</v>
@@ -24991,7 +24997,7 @@
         <v>86</v>
       </c>
       <c r="P116" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q116">
         <v>4.5</v>
@@ -25072,7 +25078,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ116">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR116">
         <v>1.24</v>
@@ -25197,7 +25203,7 @@
         <v>153</v>
       </c>
       <c r="P117" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q117">
         <v>1.53</v>
@@ -25403,7 +25409,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25481,7 +25487,7 @@
         <v>1.43</v>
       </c>
       <c r="AP118">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ118">
         <v>1.17</v>
@@ -25609,7 +25615,7 @@
         <v>154</v>
       </c>
       <c r="P119" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q119">
         <v>1.8</v>
@@ -25687,7 +25693,7 @@
         <v>0.83</v>
       </c>
       <c r="AP119">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ119">
         <v>0.92</v>
@@ -25815,7 +25821,7 @@
         <v>155</v>
       </c>
       <c r="P120" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q120">
         <v>7.5</v>
@@ -26227,7 +26233,7 @@
         <v>157</v>
       </c>
       <c r="P122" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q122">
         <v>2.63</v>
@@ -26433,7 +26439,7 @@
         <v>158</v>
       </c>
       <c r="P123" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q123">
         <v>1.73</v>
@@ -26514,7 +26520,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ123">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR123">
         <v>1.29</v>
@@ -26720,7 +26726,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ124">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR124">
         <v>2.17</v>
@@ -27051,7 +27057,7 @@
         <v>86</v>
       </c>
       <c r="P126" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27132,7 +27138,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ126">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR126">
         <v>1.5</v>
@@ -27257,7 +27263,7 @@
         <v>161</v>
       </c>
       <c r="P127" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27335,7 +27341,7 @@
         <v>3</v>
       </c>
       <c r="AP127">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ127">
         <v>2.42</v>
@@ -27463,7 +27469,7 @@
         <v>86</v>
       </c>
       <c r="P128" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q128">
         <v>2.4</v>
@@ -27669,7 +27675,7 @@
         <v>138</v>
       </c>
       <c r="P129" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27875,7 +27881,7 @@
         <v>98</v>
       </c>
       <c r="P130" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q130">
         <v>6.5</v>
@@ -27956,7 +27962,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ130">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR130">
         <v>1.03</v>
@@ -28081,7 +28087,7 @@
         <v>162</v>
       </c>
       <c r="P131" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q131">
         <v>4.33</v>
@@ -28287,7 +28293,7 @@
         <v>86</v>
       </c>
       <c r="P132" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q132">
         <v>8</v>
@@ -28571,7 +28577,7 @@
         <v>1</v>
       </c>
       <c r="AP133">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ133">
         <v>1.42</v>
@@ -29189,7 +29195,7 @@
         <v>0.5</v>
       </c>
       <c r="AP136">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ136">
         <v>0.75</v>
@@ -29604,7 +29610,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ138">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR138">
         <v>1.67</v>
@@ -29807,7 +29813,7 @@
         <v>1.75</v>
       </c>
       <c r="AP139">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ139">
         <v>1.33</v>
@@ -29935,7 +29941,7 @@
         <v>167</v>
       </c>
       <c r="P140" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q140">
         <v>2.3</v>
@@ -30016,7 +30022,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ140">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR140">
         <v>1.34</v>
@@ -30141,7 +30147,7 @@
         <v>86</v>
       </c>
       <c r="P141" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q141">
         <v>7.5</v>
@@ -30347,7 +30353,7 @@
         <v>168</v>
       </c>
       <c r="P142" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30553,7 +30559,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30965,7 +30971,7 @@
         <v>171</v>
       </c>
       <c r="P145" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q145">
         <v>3.75</v>
@@ -31171,7 +31177,7 @@
         <v>172</v>
       </c>
       <c r="P146" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q146">
         <v>7.5</v>
@@ -31252,7 +31258,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ146">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR146">
         <v>1.29</v>
@@ -31377,7 +31383,7 @@
         <v>173</v>
       </c>
       <c r="P147" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31455,7 +31461,7 @@
         <v>1.33</v>
       </c>
       <c r="AP147">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ147">
         <v>1.17</v>
@@ -31583,7 +31589,7 @@
         <v>174</v>
       </c>
       <c r="P148" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q148">
         <v>2.75</v>
@@ -31789,7 +31795,7 @@
         <v>86</v>
       </c>
       <c r="P149" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q149">
         <v>7.5</v>
@@ -32073,7 +32079,7 @@
         <v>2.33</v>
       </c>
       <c r="AP150">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ150">
         <v>1.75</v>
@@ -32201,7 +32207,7 @@
         <v>86</v>
       </c>
       <c r="P151" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q151">
         <v>6.5</v>
@@ -32279,7 +32285,7 @@
         <v>1</v>
       </c>
       <c r="AP151">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ151">
         <v>1.08</v>
@@ -32407,7 +32413,7 @@
         <v>176</v>
       </c>
       <c r="P152" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q152">
         <v>2.75</v>
@@ -32613,7 +32619,7 @@
         <v>177</v>
       </c>
       <c r="P153" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q153">
         <v>4.75</v>
@@ -33025,7 +33031,7 @@
         <v>179</v>
       </c>
       <c r="P155" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33106,7 +33112,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ155">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR155">
         <v>1.02</v>
@@ -33231,7 +33237,7 @@
         <v>176</v>
       </c>
       <c r="P156" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q156">
         <v>2.2</v>
@@ -33643,7 +33649,7 @@
         <v>181</v>
       </c>
       <c r="P158" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33724,7 +33730,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ158">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR158">
         <v>1.62</v>
@@ -34467,7 +34473,7 @@
         <v>86</v>
       </c>
       <c r="P162" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q162">
         <v>3.5</v>
@@ -34548,7 +34554,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ162">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR162">
         <v>1.31</v>
@@ -34673,7 +34679,7 @@
         <v>184</v>
       </c>
       <c r="P163" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -34754,7 +34760,7 @@
         <v>1</v>
       </c>
       <c r="AQ163">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR163">
         <v>1.34</v>
@@ -35085,7 +35091,7 @@
         <v>185</v>
       </c>
       <c r="P165" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q165">
         <v>9.5</v>
@@ -35163,7 +35169,7 @@
         <v>1.9</v>
       </c>
       <c r="AP165">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ165">
         <v>1.92</v>
@@ -35575,7 +35581,7 @@
         <v>1.7</v>
       </c>
       <c r="AP167">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ167">
         <v>1.54</v>
@@ -35781,7 +35787,7 @@
         <v>1.2</v>
       </c>
       <c r="AP168">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ168">
         <v>1.08</v>
@@ -36196,7 +36202,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ170">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR170">
         <v>1.7</v>
@@ -36939,7 +36945,7 @@
         <v>86</v>
       </c>
       <c r="P174" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q174">
         <v>3.75</v>
@@ -37145,7 +37151,7 @@
         <v>124</v>
       </c>
       <c r="P175" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q175">
         <v>5.5</v>
@@ -37351,7 +37357,7 @@
         <v>86</v>
       </c>
       <c r="P176" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q176">
         <v>3.1</v>
@@ -37763,7 +37769,7 @@
         <v>86</v>
       </c>
       <c r="P178" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q178">
         <v>3.5</v>
@@ -37844,7 +37850,7 @@
         <v>1</v>
       </c>
       <c r="AQ178">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR178">
         <v>1.28</v>
@@ -38050,7 +38056,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ179">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR179">
         <v>1.32</v>
@@ -38175,7 +38181,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38381,7 +38387,7 @@
         <v>194</v>
       </c>
       <c r="P181" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q181">
         <v>3.2</v>
@@ -38459,7 +38465,7 @@
         <v>2</v>
       </c>
       <c r="AP181">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ181">
         <v>1.92</v>
@@ -38587,7 +38593,7 @@
         <v>86</v>
       </c>
       <c r="P182" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q182">
         <v>8.5</v>
@@ -38665,10 +38671,10 @@
         <v>1.82</v>
       </c>
       <c r="AP182">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ182">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR182">
         <v>1.01</v>
@@ -38999,7 +39005,7 @@
         <v>195</v>
       </c>
       <c r="P184" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q184">
         <v>3.6</v>
@@ -39283,7 +39289,7 @@
         <v>1.36</v>
       </c>
       <c r="AP185">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ185">
         <v>1.33</v>
@@ -39617,7 +39623,7 @@
         <v>196</v>
       </c>
       <c r="P187" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -39823,7 +39829,7 @@
         <v>86</v>
       </c>
       <c r="P188" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q188">
         <v>6</v>
@@ -40029,7 +40035,7 @@
         <v>192</v>
       </c>
       <c r="P189" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q189">
         <v>2.3</v>
@@ -40441,7 +40447,7 @@
         <v>197</v>
       </c>
       <c r="P191" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
@@ -40647,7 +40653,7 @@
         <v>198</v>
       </c>
       <c r="P192" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q192">
         <v>8.5</v>
@@ -41059,7 +41065,7 @@
         <v>200</v>
       </c>
       <c r="P194" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q194">
         <v>2.75</v>
@@ -41422,6 +41428,624 @@
       </c>
       <c r="BP195">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="196" spans="1:68">
+      <c r="A196" s="1">
+        <v>195</v>
+      </c>
+      <c r="B196">
+        <v>7762791</v>
+      </c>
+      <c r="C196" t="s">
+        <v>68</v>
+      </c>
+      <c r="D196" t="s">
+        <v>69</v>
+      </c>
+      <c r="E196" s="2">
+        <v>45731.3125</v>
+      </c>
+      <c r="F196">
+        <v>25</v>
+      </c>
+      <c r="G196" t="s">
+        <v>76</v>
+      </c>
+      <c r="H196" t="s">
+        <v>73</v>
+      </c>
+      <c r="I196">
+        <v>1</v>
+      </c>
+      <c r="J196">
+        <v>0</v>
+      </c>
+      <c r="K196">
+        <v>1</v>
+      </c>
+      <c r="L196">
+        <v>2</v>
+      </c>
+      <c r="M196">
+        <v>1</v>
+      </c>
+      <c r="N196">
+        <v>3</v>
+      </c>
+      <c r="O196" t="s">
+        <v>201</v>
+      </c>
+      <c r="P196" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q196">
+        <v>4.5</v>
+      </c>
+      <c r="R196">
+        <v>2</v>
+      </c>
+      <c r="S196">
+        <v>2.75</v>
+      </c>
+      <c r="T196">
+        <v>1.5</v>
+      </c>
+      <c r="U196">
+        <v>2.5</v>
+      </c>
+      <c r="V196">
+        <v>3.5</v>
+      </c>
+      <c r="W196">
+        <v>1.29</v>
+      </c>
+      <c r="X196">
+        <v>11</v>
+      </c>
+      <c r="Y196">
+        <v>1.05</v>
+      </c>
+      <c r="Z196">
+        <v>3.99</v>
+      </c>
+      <c r="AA196">
+        <v>3.39</v>
+      </c>
+      <c r="AB196">
+        <v>1.91</v>
+      </c>
+      <c r="AC196">
+        <v>0</v>
+      </c>
+      <c r="AD196">
+        <v>0</v>
+      </c>
+      <c r="AE196">
+        <v>0</v>
+      </c>
+      <c r="AF196">
+        <v>0</v>
+      </c>
+      <c r="AG196">
+        <v>2.28</v>
+      </c>
+      <c r="AH196">
+        <v>1.55</v>
+      </c>
+      <c r="AI196">
+        <v>2.1</v>
+      </c>
+      <c r="AJ196">
+        <v>1.67</v>
+      </c>
+      <c r="AK196">
+        <v>0</v>
+      </c>
+      <c r="AL196">
+        <v>0</v>
+      </c>
+      <c r="AM196">
+        <v>0</v>
+      </c>
+      <c r="AN196">
+        <v>0.58</v>
+      </c>
+      <c r="AO196">
+        <v>1.17</v>
+      </c>
+      <c r="AP196">
+        <v>0.77</v>
+      </c>
+      <c r="AQ196">
+        <v>1.08</v>
+      </c>
+      <c r="AR196">
+        <v>0.97</v>
+      </c>
+      <c r="AS196">
+        <v>1.31</v>
+      </c>
+      <c r="AT196">
+        <v>2.28</v>
+      </c>
+      <c r="AU196">
+        <v>10</v>
+      </c>
+      <c r="AV196">
+        <v>4</v>
+      </c>
+      <c r="AW196">
+        <v>12</v>
+      </c>
+      <c r="AX196">
+        <v>8</v>
+      </c>
+      <c r="AY196">
+        <v>22</v>
+      </c>
+      <c r="AZ196">
+        <v>12</v>
+      </c>
+      <c r="BA196">
+        <v>12</v>
+      </c>
+      <c r="BB196">
+        <v>4</v>
+      </c>
+      <c r="BC196">
+        <v>16</v>
+      </c>
+      <c r="BD196">
+        <v>0</v>
+      </c>
+      <c r="BE196">
+        <v>0</v>
+      </c>
+      <c r="BF196">
+        <v>0</v>
+      </c>
+      <c r="BG196">
+        <v>0</v>
+      </c>
+      <c r="BH196">
+        <v>0</v>
+      </c>
+      <c r="BI196">
+        <v>0</v>
+      </c>
+      <c r="BJ196">
+        <v>0</v>
+      </c>
+      <c r="BK196">
+        <v>0</v>
+      </c>
+      <c r="BL196">
+        <v>0</v>
+      </c>
+      <c r="BM196">
+        <v>0</v>
+      </c>
+      <c r="BN196">
+        <v>0</v>
+      </c>
+      <c r="BO196">
+        <v>0</v>
+      </c>
+      <c r="BP196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:68">
+      <c r="A197" s="1">
+        <v>196</v>
+      </c>
+      <c r="B197">
+        <v>7762792</v>
+      </c>
+      <c r="C197" t="s">
+        <v>68</v>
+      </c>
+      <c r="D197" t="s">
+        <v>69</v>
+      </c>
+      <c r="E197" s="2">
+        <v>45731.41666666666</v>
+      </c>
+      <c r="F197">
+        <v>25</v>
+      </c>
+      <c r="G197" t="s">
+        <v>75</v>
+      </c>
+      <c r="H197" t="s">
+        <v>74</v>
+      </c>
+      <c r="I197">
+        <v>1</v>
+      </c>
+      <c r="J197">
+        <v>0</v>
+      </c>
+      <c r="K197">
+        <v>1</v>
+      </c>
+      <c r="L197">
+        <v>3</v>
+      </c>
+      <c r="M197">
+        <v>0</v>
+      </c>
+      <c r="N197">
+        <v>3</v>
+      </c>
+      <c r="O197" t="s">
+        <v>202</v>
+      </c>
+      <c r="P197" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q197">
+        <v>1.4</v>
+      </c>
+      <c r="R197">
+        <v>3.1</v>
+      </c>
+      <c r="S197">
+        <v>21</v>
+      </c>
+      <c r="T197">
+        <v>1.25</v>
+      </c>
+      <c r="U197">
+        <v>3.75</v>
+      </c>
+      <c r="V197">
+        <v>2.2</v>
+      </c>
+      <c r="W197">
+        <v>1.62</v>
+      </c>
+      <c r="X197">
+        <v>5</v>
+      </c>
+      <c r="Y197">
+        <v>1.17</v>
+      </c>
+      <c r="Z197">
+        <v>1.08</v>
+      </c>
+      <c r="AA197">
+        <v>10</v>
+      </c>
+      <c r="AB197">
+        <v>21</v>
+      </c>
+      <c r="AC197">
+        <v>0</v>
+      </c>
+      <c r="AD197">
+        <v>0</v>
+      </c>
+      <c r="AE197">
+        <v>0</v>
+      </c>
+      <c r="AF197">
+        <v>0</v>
+      </c>
+      <c r="AG197">
+        <v>1.47</v>
+      </c>
+      <c r="AH197">
+        <v>2.5</v>
+      </c>
+      <c r="AI197">
+        <v>3.25</v>
+      </c>
+      <c r="AJ197">
+        <v>1.33</v>
+      </c>
+      <c r="AK197">
+        <v>0</v>
+      </c>
+      <c r="AL197">
+        <v>0</v>
+      </c>
+      <c r="AM197">
+        <v>0</v>
+      </c>
+      <c r="AN197">
+        <v>2.67</v>
+      </c>
+      <c r="AO197">
+        <v>0.42</v>
+      </c>
+      <c r="AP197">
+        <v>2.69</v>
+      </c>
+      <c r="AQ197">
+        <v>0.38</v>
+      </c>
+      <c r="AR197">
+        <v>1.84</v>
+      </c>
+      <c r="AS197">
+        <v>0.99</v>
+      </c>
+      <c r="AT197">
+        <v>2.83</v>
+      </c>
+      <c r="AU197">
+        <v>9</v>
+      </c>
+      <c r="AV197">
+        <v>6</v>
+      </c>
+      <c r="AW197">
+        <v>8</v>
+      </c>
+      <c r="AX197">
+        <v>4</v>
+      </c>
+      <c r="AY197">
+        <v>17</v>
+      </c>
+      <c r="AZ197">
+        <v>10</v>
+      </c>
+      <c r="BA197">
+        <v>6</v>
+      </c>
+      <c r="BB197">
+        <v>3</v>
+      </c>
+      <c r="BC197">
+        <v>9</v>
+      </c>
+      <c r="BD197">
+        <v>0</v>
+      </c>
+      <c r="BE197">
+        <v>0</v>
+      </c>
+      <c r="BF197">
+        <v>0</v>
+      </c>
+      <c r="BG197">
+        <v>0</v>
+      </c>
+      <c r="BH197">
+        <v>0</v>
+      </c>
+      <c r="BI197">
+        <v>0</v>
+      </c>
+      <c r="BJ197">
+        <v>0</v>
+      </c>
+      <c r="BK197">
+        <v>2.25</v>
+      </c>
+      <c r="BL197">
+        <v>0</v>
+      </c>
+      <c r="BM197">
+        <v>0</v>
+      </c>
+      <c r="BN197">
+        <v>0</v>
+      </c>
+      <c r="BO197">
+        <v>0</v>
+      </c>
+      <c r="BP197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:68">
+      <c r="A198" s="1">
+        <v>197</v>
+      </c>
+      <c r="B198">
+        <v>7762789</v>
+      </c>
+      <c r="C198" t="s">
+        <v>68</v>
+      </c>
+      <c r="D198" t="s">
+        <v>69</v>
+      </c>
+      <c r="E198" s="2">
+        <v>45731.52083333334</v>
+      </c>
+      <c r="F198">
+        <v>25</v>
+      </c>
+      <c r="G198" t="s">
+        <v>80</v>
+      </c>
+      <c r="H198" t="s">
+        <v>70</v>
+      </c>
+      <c r="I198">
+        <v>0</v>
+      </c>
+      <c r="J198">
+        <v>1</v>
+      </c>
+      <c r="K198">
+        <v>1</v>
+      </c>
+      <c r="L198">
+        <v>1</v>
+      </c>
+      <c r="M198">
+        <v>1</v>
+      </c>
+      <c r="N198">
+        <v>2</v>
+      </c>
+      <c r="O198" t="s">
+        <v>203</v>
+      </c>
+      <c r="P198" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q198">
+        <v>2.5</v>
+      </c>
+      <c r="R198">
+        <v>2</v>
+      </c>
+      <c r="S198">
+        <v>5.5</v>
+      </c>
+      <c r="T198">
+        <v>1.5</v>
+      </c>
+      <c r="U198">
+        <v>2.5</v>
+      </c>
+      <c r="V198">
+        <v>3.5</v>
+      </c>
+      <c r="W198">
+        <v>1.29</v>
+      </c>
+      <c r="X198">
+        <v>11</v>
+      </c>
+      <c r="Y198">
+        <v>1.05</v>
+      </c>
+      <c r="Z198">
+        <v>1.67</v>
+      </c>
+      <c r="AA198">
+        <v>3.55</v>
+      </c>
+      <c r="AB198">
+        <v>5.3</v>
+      </c>
+      <c r="AC198">
+        <v>0</v>
+      </c>
+      <c r="AD198">
+        <v>0</v>
+      </c>
+      <c r="AE198">
+        <v>0</v>
+      </c>
+      <c r="AF198">
+        <v>0</v>
+      </c>
+      <c r="AG198">
+        <v>2.25</v>
+      </c>
+      <c r="AH198">
+        <v>1.53</v>
+      </c>
+      <c r="AI198">
+        <v>2.1</v>
+      </c>
+      <c r="AJ198">
+        <v>1.67</v>
+      </c>
+      <c r="AK198">
+        <v>0</v>
+      </c>
+      <c r="AL198">
+        <v>0</v>
+      </c>
+      <c r="AM198">
+        <v>0</v>
+      </c>
+      <c r="AN198">
+        <v>1.58</v>
+      </c>
+      <c r="AO198">
+        <v>1.92</v>
+      </c>
+      <c r="AP198">
+        <v>1.54</v>
+      </c>
+      <c r="AQ198">
+        <v>1.85</v>
+      </c>
+      <c r="AR198">
+        <v>2.05</v>
+      </c>
+      <c r="AS198">
+        <v>1.46</v>
+      </c>
+      <c r="AT198">
+        <v>3.51</v>
+      </c>
+      <c r="AU198">
+        <v>4</v>
+      </c>
+      <c r="AV198">
+        <v>4</v>
+      </c>
+      <c r="AW198">
+        <v>6</v>
+      </c>
+      <c r="AX198">
+        <v>2</v>
+      </c>
+      <c r="AY198">
+        <v>10</v>
+      </c>
+      <c r="AZ198">
+        <v>6</v>
+      </c>
+      <c r="BA198">
+        <v>9</v>
+      </c>
+      <c r="BB198">
+        <v>2</v>
+      </c>
+      <c r="BC198">
+        <v>11</v>
+      </c>
+      <c r="BD198">
+        <v>1.52</v>
+      </c>
+      <c r="BE198">
+        <v>6.75</v>
+      </c>
+      <c r="BF198">
+        <v>3.34</v>
+      </c>
+      <c r="BG198">
+        <v>0</v>
+      </c>
+      <c r="BH198">
+        <v>0</v>
+      </c>
+      <c r="BI198">
+        <v>0</v>
+      </c>
+      <c r="BJ198">
+        <v>0</v>
+      </c>
+      <c r="BK198">
+        <v>0</v>
+      </c>
+      <c r="BL198">
+        <v>0</v>
+      </c>
+      <c r="BM198">
+        <v>0</v>
+      </c>
+      <c r="BN198">
+        <v>0</v>
+      </c>
+      <c r="BO198">
+        <v>0</v>
+      </c>
+      <c r="BP198">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -41928,16 +41928,16 @@
         <v>5.3</v>
       </c>
       <c r="AC198">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD198">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AE198">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF198">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG198">
         <v>2.25</v>
@@ -41952,13 +41952,13 @@
         <v>1.67</v>
       </c>
       <c r="AK198">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL198">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AM198">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN198">
         <v>1.58</v>
@@ -42018,34 +42018,34 @@
         <v>3.34</v>
       </c>
       <c r="BG198">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BH198">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="BI198">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BJ198">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BK198">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BL198">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BM198">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BN198">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BO198">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BP198">
-        <v>0</v>
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="298">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -628,6 +628,9 @@
     <t>['69']</t>
   </si>
   <si>
+    <t>['22', '30', '53', '73']</t>
+  </si>
+  <si>
     <t>['12', '22', '45+1', '45+4', '90+1', '90+8']</t>
   </si>
   <si>
@@ -896,6 +899,15 @@
   </si>
   <si>
     <t>['8']</t>
+  </si>
+  <si>
+    <t>['64', '87']</t>
+  </si>
+  <si>
+    <t>['38', '41', '47', '49', '66']</t>
+  </si>
+  <si>
+    <t>['22']</t>
   </si>
 </sst>
 </file>
@@ -1257,7 +1269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP198"/>
+  <dimension ref="A1:BP201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1594,7 +1606,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ2">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2131,7 +2143,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q5">
         <v>7.5</v>
@@ -2212,7 +2224,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ5">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2337,7 +2349,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2749,7 +2761,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q8">
         <v>4</v>
@@ -3239,7 +3251,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ10">
         <v>0.92</v>
@@ -3779,7 +3791,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3985,7 +3997,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q14">
         <v>2.4</v>
@@ -4063,7 +4075,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ14">
         <v>1.15</v>
@@ -4478,7 +4490,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ16">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR16">
         <v>2.14</v>
@@ -4809,7 +4821,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -4890,7 +4902,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ18">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR18">
         <v>1.14</v>
@@ -5093,7 +5105,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ19">
         <v>1.42</v>
@@ -5221,7 +5233,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -5427,7 +5439,7 @@
         <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5633,7 +5645,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5839,7 +5851,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -6045,7 +6057,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q24">
         <v>3.25</v>
@@ -6251,7 +6263,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q25">
         <v>2.05</v>
@@ -6329,7 +6341,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ25">
         <v>0.25</v>
@@ -6457,7 +6469,7 @@
         <v>86</v>
       </c>
       <c r="P26" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -7075,7 +7087,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7359,7 +7371,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ30">
         <v>1.08</v>
@@ -7487,7 +7499,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7693,7 +7705,7 @@
         <v>86</v>
       </c>
       <c r="P32" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q32">
         <v>2.05</v>
@@ -7980,7 +7992,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ33">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR33">
         <v>1.4</v>
@@ -8186,7 +8198,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ34">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR34">
         <v>0.89</v>
@@ -8598,7 +8610,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ36">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR36">
         <v>1.19</v>
@@ -8723,7 +8735,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -9419,7 +9431,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ40">
         <v>1.42</v>
@@ -9625,7 +9637,7 @@
         <v>1.33</v>
       </c>
       <c r="AP41">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ41">
         <v>1.33</v>
@@ -9959,7 +9971,7 @@
         <v>86</v>
       </c>
       <c r="P43" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q43">
         <v>7.5</v>
@@ -10165,7 +10177,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10577,7 +10589,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q46">
         <v>2.5</v>
@@ -10783,7 +10795,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q47">
         <v>4.33</v>
@@ -10864,7 +10876,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ47">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR47">
         <v>1.32</v>
@@ -10989,7 +11001,7 @@
         <v>86</v>
       </c>
       <c r="P48" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q48">
         <v>2.4</v>
@@ -11273,10 +11285,10 @@
         <v>2</v>
       </c>
       <c r="AP49">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ49">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR49">
         <v>1.37</v>
@@ -11482,7 +11494,7 @@
         <v>1</v>
       </c>
       <c r="AQ50">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR50">
         <v>1.44</v>
@@ -11607,7 +11619,7 @@
         <v>116</v>
       </c>
       <c r="P51" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11813,7 +11825,7 @@
         <v>118</v>
       </c>
       <c r="P52" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q52">
         <v>5.5</v>
@@ -12225,7 +12237,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -12637,7 +12649,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q56">
         <v>5.5</v>
@@ -12843,7 +12855,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q57">
         <v>5</v>
@@ -13049,7 +13061,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13255,7 +13267,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13336,7 +13348,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ59">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR59">
         <v>1.61</v>
@@ -13461,7 +13473,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13667,7 +13679,7 @@
         <v>86</v>
       </c>
       <c r="P61" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q61">
         <v>6.5</v>
@@ -14079,7 +14091,7 @@
         <v>86</v>
       </c>
       <c r="P63" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q63">
         <v>3.5</v>
@@ -14160,7 +14172,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ63">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR63">
         <v>1.29</v>
@@ -14285,7 +14297,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14366,7 +14378,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ64">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR64">
         <v>0.92</v>
@@ -14903,7 +14915,7 @@
         <v>86</v>
       </c>
       <c r="P67" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q67">
         <v>6.5</v>
@@ -14984,7 +14996,7 @@
         <v>2</v>
       </c>
       <c r="AQ67">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR67">
         <v>1.17</v>
@@ -15109,7 +15121,7 @@
         <v>86</v>
       </c>
       <c r="P68" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q68">
         <v>4.75</v>
@@ -15187,7 +15199,7 @@
         <v>1.33</v>
       </c>
       <c r="AP68">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ68">
         <v>1.85</v>
@@ -15599,7 +15611,7 @@
         <v>3</v>
       </c>
       <c r="AP70">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ70">
         <v>1.75</v>
@@ -15727,7 +15739,7 @@
         <v>92</v>
       </c>
       <c r="P71" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q71">
         <v>9.5</v>
@@ -15808,7 +15820,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ71">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR71">
         <v>1.26</v>
@@ -16345,7 +16357,7 @@
         <v>86</v>
       </c>
       <c r="P74" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16963,7 +16975,7 @@
         <v>130</v>
       </c>
       <c r="P77" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q77">
         <v>1.83</v>
@@ -17169,7 +17181,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q78">
         <v>12</v>
@@ -17375,7 +17387,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q79">
         <v>3.75</v>
@@ -17581,7 +17593,7 @@
         <v>131</v>
       </c>
       <c r="P80" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17662,7 +17674,7 @@
         <v>1</v>
       </c>
       <c r="AQ80">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR80">
         <v>1.54</v>
@@ -17787,7 +17799,7 @@
         <v>132</v>
       </c>
       <c r="P81" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -17865,7 +17877,7 @@
         <v>1.8</v>
       </c>
       <c r="AP81">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ81">
         <v>1.54</v>
@@ -18199,7 +18211,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q83">
         <v>1.67</v>
@@ -18280,7 +18292,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ83">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR83">
         <v>1.8</v>
@@ -18483,10 +18495,10 @@
         <v>2.17</v>
       </c>
       <c r="AP84">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ84">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR84">
         <v>1.5</v>
@@ -18817,7 +18829,7 @@
         <v>134</v>
       </c>
       <c r="P86" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q86">
         <v>2.63</v>
@@ -18895,7 +18907,7 @@
         <v>1.25</v>
       </c>
       <c r="AP86">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ86">
         <v>1.08</v>
@@ -20131,7 +20143,7 @@
         <v>0.67</v>
       </c>
       <c r="AP92">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ92">
         <v>0.75</v>
@@ -20465,7 +20477,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q94">
         <v>13</v>
@@ -20671,7 +20683,7 @@
         <v>139</v>
       </c>
       <c r="P95" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -20955,7 +20967,7 @@
         <v>1.6</v>
       </c>
       <c r="AP96">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ96">
         <v>1.15</v>
@@ -21083,7 +21095,7 @@
         <v>140</v>
       </c>
       <c r="P97" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q97">
         <v>2.4</v>
@@ -21573,10 +21585,10 @@
         <v>1.2</v>
       </c>
       <c r="AP99">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ99">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR99">
         <v>1.34</v>
@@ -21779,7 +21791,7 @@
         <v>1.4</v>
       </c>
       <c r="AP100">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ100">
         <v>1.85</v>
@@ -21907,7 +21919,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22400,7 +22412,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ103">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR103">
         <v>1.72</v>
@@ -22525,7 +22537,7 @@
         <v>145</v>
       </c>
       <c r="P104" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22731,7 +22743,7 @@
         <v>86</v>
       </c>
       <c r="P105" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -22937,7 +22949,7 @@
         <v>146</v>
       </c>
       <c r="P106" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q106">
         <v>6</v>
@@ -23349,7 +23361,7 @@
         <v>147</v>
       </c>
       <c r="P108" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23761,7 +23773,7 @@
         <v>149</v>
       </c>
       <c r="P110" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23842,7 +23854,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ110">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR110">
         <v>1.77</v>
@@ -24173,7 +24185,7 @@
         <v>143</v>
       </c>
       <c r="P112" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q112">
         <v>4.75</v>
@@ -24457,7 +24469,7 @@
         <v>0.67</v>
       </c>
       <c r="AP113">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ113">
         <v>0.38</v>
@@ -24663,7 +24675,7 @@
         <v>0.83</v>
       </c>
       <c r="AP114">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ114">
         <v>1.08</v>
@@ -24997,7 +25009,7 @@
         <v>86</v>
       </c>
       <c r="P116" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q116">
         <v>4.5</v>
@@ -25203,7 +25215,7 @@
         <v>153</v>
       </c>
       <c r="P117" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q117">
         <v>1.53</v>
@@ -25284,7 +25296,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ117">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR117">
         <v>1.99</v>
@@ -25409,7 +25421,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25490,7 +25502,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ118">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR118">
         <v>0.95</v>
@@ -25615,7 +25627,7 @@
         <v>154</v>
       </c>
       <c r="P119" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q119">
         <v>1.8</v>
@@ -25821,7 +25833,7 @@
         <v>155</v>
       </c>
       <c r="P120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q120">
         <v>7.5</v>
@@ -25899,7 +25911,7 @@
         <v>3</v>
       </c>
       <c r="AP120">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ120">
         <v>2.42</v>
@@ -26105,7 +26117,7 @@
         <v>0.29</v>
       </c>
       <c r="AP121">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ121">
         <v>0.25</v>
@@ -26233,7 +26245,7 @@
         <v>157</v>
       </c>
       <c r="P122" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q122">
         <v>2.63</v>
@@ -26311,7 +26323,7 @@
         <v>1.14</v>
       </c>
       <c r="AP122">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ122">
         <v>1.15</v>
@@ -26439,7 +26451,7 @@
         <v>158</v>
       </c>
       <c r="P123" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q123">
         <v>1.73</v>
@@ -26517,7 +26529,7 @@
         <v>0.57</v>
       </c>
       <c r="AP123">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ123">
         <v>0.38</v>
@@ -26932,7 +26944,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ125">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR125">
         <v>1.25</v>
@@ -27057,7 +27069,7 @@
         <v>86</v>
       </c>
       <c r="P126" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27263,7 +27275,7 @@
         <v>161</v>
       </c>
       <c r="P127" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27469,7 +27481,7 @@
         <v>86</v>
       </c>
       <c r="P128" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q128">
         <v>2.4</v>
@@ -27675,7 +27687,7 @@
         <v>138</v>
       </c>
       <c r="P129" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27753,10 +27765,10 @@
         <v>1.38</v>
       </c>
       <c r="AP129">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ129">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR129">
         <v>1.45</v>
@@ -27881,7 +27893,7 @@
         <v>98</v>
       </c>
       <c r="P130" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q130">
         <v>6.5</v>
@@ -28087,7 +28099,7 @@
         <v>162</v>
       </c>
       <c r="P131" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q131">
         <v>4.33</v>
@@ -28293,7 +28305,7 @@
         <v>86</v>
       </c>
       <c r="P132" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q132">
         <v>8</v>
@@ -28374,7 +28386,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ132">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR132">
         <v>1.32</v>
@@ -29404,7 +29416,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ137">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR137">
         <v>1.54</v>
@@ -29941,7 +29953,7 @@
         <v>167</v>
       </c>
       <c r="P140" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q140">
         <v>2.3</v>
@@ -30147,7 +30159,7 @@
         <v>86</v>
       </c>
       <c r="P141" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q141">
         <v>7.5</v>
@@ -30225,7 +30237,7 @@
         <v>2.71</v>
       </c>
       <c r="AP141">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ141">
         <v>2.42</v>
@@ -30353,7 +30365,7 @@
         <v>168</v>
       </c>
       <c r="P142" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30559,7 +30571,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30843,7 +30855,7 @@
         <v>1.13</v>
       </c>
       <c r="AP144">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ144">
         <v>0.92</v>
@@ -30971,7 +30983,7 @@
         <v>171</v>
       </c>
       <c r="P145" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q145">
         <v>3.75</v>
@@ -31177,7 +31189,7 @@
         <v>172</v>
       </c>
       <c r="P146" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q146">
         <v>7.5</v>
@@ -31383,7 +31395,7 @@
         <v>173</v>
       </c>
       <c r="P147" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31464,7 +31476,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ147">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR147">
         <v>2.12</v>
@@ -31589,7 +31601,7 @@
         <v>174</v>
       </c>
       <c r="P148" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q148">
         <v>2.75</v>
@@ -31670,7 +31682,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ148">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR148">
         <v>1.13</v>
@@ -31795,7 +31807,7 @@
         <v>86</v>
       </c>
       <c r="P149" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q149">
         <v>7.5</v>
@@ -31876,7 +31888,7 @@
         <v>1</v>
       </c>
       <c r="AQ149">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR149">
         <v>1.37</v>
@@ -32207,7 +32219,7 @@
         <v>86</v>
       </c>
       <c r="P151" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q151">
         <v>6.5</v>
@@ -32413,7 +32425,7 @@
         <v>176</v>
       </c>
       <c r="P152" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q152">
         <v>2.75</v>
@@ -32491,7 +32503,7 @@
         <v>0.44</v>
       </c>
       <c r="AP152">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ152">
         <v>0.75</v>
@@ -32619,7 +32631,7 @@
         <v>177</v>
       </c>
       <c r="P153" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q153">
         <v>4.75</v>
@@ -32697,7 +32709,7 @@
         <v>2.75</v>
       </c>
       <c r="AP153">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ153">
         <v>2.42</v>
@@ -32903,7 +32915,7 @@
         <v>1.56</v>
       </c>
       <c r="AP154">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ154">
         <v>1.33</v>
@@ -33031,7 +33043,7 @@
         <v>179</v>
       </c>
       <c r="P155" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33237,7 +33249,7 @@
         <v>176</v>
       </c>
       <c r="P156" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q156">
         <v>2.2</v>
@@ -33649,7 +33661,7 @@
         <v>181</v>
       </c>
       <c r="P158" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33933,7 +33945,7 @@
         <v>0.22</v>
       </c>
       <c r="AP159">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ159">
         <v>0.25</v>
@@ -34473,7 +34485,7 @@
         <v>86</v>
       </c>
       <c r="P162" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q162">
         <v>3.5</v>
@@ -34679,7 +34691,7 @@
         <v>184</v>
       </c>
       <c r="P163" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -34963,7 +34975,7 @@
         <v>2.1</v>
       </c>
       <c r="AP164">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ164">
         <v>1.75</v>
@@ -35091,7 +35103,7 @@
         <v>185</v>
       </c>
       <c r="P165" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q165">
         <v>9.5</v>
@@ -35172,7 +35184,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ165">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR165">
         <v>1.02</v>
@@ -35378,7 +35390,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ166">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR166">
         <v>1.31</v>
@@ -35996,7 +36008,7 @@
         <v>2</v>
       </c>
       <c r="AQ169">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR169">
         <v>1.46</v>
@@ -36817,7 +36829,7 @@
         <v>0.7</v>
       </c>
       <c r="AP173">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ173">
         <v>0.75</v>
@@ -36945,7 +36957,7 @@
         <v>86</v>
       </c>
       <c r="P174" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q174">
         <v>3.75</v>
@@ -37023,7 +37035,7 @@
         <v>1.1</v>
       </c>
       <c r="AP174">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ174">
         <v>1.42</v>
@@ -37151,7 +37163,7 @@
         <v>124</v>
       </c>
       <c r="P175" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q175">
         <v>5.5</v>
@@ -37357,7 +37369,7 @@
         <v>86</v>
       </c>
       <c r="P176" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q176">
         <v>3.1</v>
@@ -37769,7 +37781,7 @@
         <v>86</v>
       </c>
       <c r="P178" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q178">
         <v>3.5</v>
@@ -38181,7 +38193,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38259,7 +38271,7 @@
         <v>1.55</v>
       </c>
       <c r="AP180">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ180">
         <v>1.54</v>
@@ -38387,7 +38399,7 @@
         <v>194</v>
       </c>
       <c r="P181" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q181">
         <v>3.2</v>
@@ -38468,7 +38480,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ181">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR181">
         <v>2.15</v>
@@ -38593,7 +38605,7 @@
         <v>86</v>
       </c>
       <c r="P182" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q182">
         <v>8.5</v>
@@ -38877,10 +38889,10 @@
         <v>1.27</v>
       </c>
       <c r="AP183">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ183">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR183">
         <v>1.48</v>
@@ -39005,7 +39017,7 @@
         <v>195</v>
       </c>
       <c r="P184" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q184">
         <v>3.6</v>
@@ -39292,7 +39304,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ185">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR185">
         <v>1.72</v>
@@ -39623,7 +39635,7 @@
         <v>196</v>
       </c>
       <c r="P187" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -39829,7 +39841,7 @@
         <v>86</v>
       </c>
       <c r="P188" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q188">
         <v>6</v>
@@ -40035,7 +40047,7 @@
         <v>192</v>
       </c>
       <c r="P189" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q189">
         <v>2.3</v>
@@ -40319,7 +40331,7 @@
         <v>1.09</v>
       </c>
       <c r="AP190">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ190">
         <v>1.08</v>
@@ -40447,7 +40459,7 @@
         <v>197</v>
       </c>
       <c r="P191" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
@@ -40653,7 +40665,7 @@
         <v>198</v>
       </c>
       <c r="P192" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q192">
         <v>8.5</v>
@@ -41065,7 +41077,7 @@
         <v>200</v>
       </c>
       <c r="P194" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q194">
         <v>2.75</v>
@@ -41477,7 +41489,7 @@
         <v>201</v>
       </c>
       <c r="P196" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q196">
         <v>4.5</v>
@@ -41889,7 +41901,7 @@
         <v>203</v>
       </c>
       <c r="P198" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q198">
         <v>2.5</v>
@@ -42046,6 +42058,624 @@
       </c>
       <c r="BP198">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="199" spans="1:68">
+      <c r="A199" s="1">
+        <v>198</v>
+      </c>
+      <c r="B199">
+        <v>7762790</v>
+      </c>
+      <c r="C199" t="s">
+        <v>68</v>
+      </c>
+      <c r="D199" t="s">
+        <v>69</v>
+      </c>
+      <c r="E199" s="2">
+        <v>45732.29166666666</v>
+      </c>
+      <c r="F199">
+        <v>25</v>
+      </c>
+      <c r="G199" t="s">
+        <v>84</v>
+      </c>
+      <c r="H199" t="s">
+        <v>77</v>
+      </c>
+      <c r="I199">
+        <v>2</v>
+      </c>
+      <c r="J199">
+        <v>0</v>
+      </c>
+      <c r="K199">
+        <v>2</v>
+      </c>
+      <c r="L199">
+        <v>4</v>
+      </c>
+      <c r="M199">
+        <v>2</v>
+      </c>
+      <c r="N199">
+        <v>6</v>
+      </c>
+      <c r="O199" t="s">
+        <v>204</v>
+      </c>
+      <c r="P199" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q199">
+        <v>2.4</v>
+      </c>
+      <c r="R199">
+        <v>2.1</v>
+      </c>
+      <c r="S199">
+        <v>5</v>
+      </c>
+      <c r="T199">
+        <v>1.44</v>
+      </c>
+      <c r="U199">
+        <v>2.63</v>
+      </c>
+      <c r="V199">
+        <v>3.25</v>
+      </c>
+      <c r="W199">
+        <v>1.33</v>
+      </c>
+      <c r="X199">
+        <v>9</v>
+      </c>
+      <c r="Y199">
+        <v>1.07</v>
+      </c>
+      <c r="Z199">
+        <v>2.11</v>
+      </c>
+      <c r="AA199">
+        <v>3.31</v>
+      </c>
+      <c r="AB199">
+        <v>3.41</v>
+      </c>
+      <c r="AC199">
+        <v>1.01</v>
+      </c>
+      <c r="AD199">
+        <v>8.4</v>
+      </c>
+      <c r="AE199">
+        <v>1.35</v>
+      </c>
+      <c r="AF199">
+        <v>3</v>
+      </c>
+      <c r="AG199">
+        <v>1.89</v>
+      </c>
+      <c r="AH199">
+        <v>1.85</v>
+      </c>
+      <c r="AI199">
+        <v>2</v>
+      </c>
+      <c r="AJ199">
+        <v>1.73</v>
+      </c>
+      <c r="AK199">
+        <v>1.21</v>
+      </c>
+      <c r="AL199">
+        <v>1.28</v>
+      </c>
+      <c r="AM199">
+        <v>1.98</v>
+      </c>
+      <c r="AN199">
+        <v>1.67</v>
+      </c>
+      <c r="AO199">
+        <v>1.33</v>
+      </c>
+      <c r="AP199">
+        <v>1.77</v>
+      </c>
+      <c r="AQ199">
+        <v>1.23</v>
+      </c>
+      <c r="AR199">
+        <v>1.57</v>
+      </c>
+      <c r="AS199">
+        <v>1.11</v>
+      </c>
+      <c r="AT199">
+        <v>2.68</v>
+      </c>
+      <c r="AU199">
+        <v>8</v>
+      </c>
+      <c r="AV199">
+        <v>7</v>
+      </c>
+      <c r="AW199">
+        <v>6</v>
+      </c>
+      <c r="AX199">
+        <v>4</v>
+      </c>
+      <c r="AY199">
+        <v>14</v>
+      </c>
+      <c r="AZ199">
+        <v>11</v>
+      </c>
+      <c r="BA199">
+        <v>6</v>
+      </c>
+      <c r="BB199">
+        <v>9</v>
+      </c>
+      <c r="BC199">
+        <v>15</v>
+      </c>
+      <c r="BD199">
+        <v>1.55</v>
+      </c>
+      <c r="BE199">
+        <v>6.75</v>
+      </c>
+      <c r="BF199">
+        <v>2.7</v>
+      </c>
+      <c r="BG199">
+        <v>1.38</v>
+      </c>
+      <c r="BH199">
+        <v>2.8</v>
+      </c>
+      <c r="BI199">
+        <v>1.63</v>
+      </c>
+      <c r="BJ199">
+        <v>2.15</v>
+      </c>
+      <c r="BK199">
+        <v>1.98</v>
+      </c>
+      <c r="BL199">
+        <v>1.72</v>
+      </c>
+      <c r="BM199">
+        <v>2.5</v>
+      </c>
+      <c r="BN199">
+        <v>1.46</v>
+      </c>
+      <c r="BO199">
+        <v>3.3</v>
+      </c>
+      <c r="BP199">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="200" spans="1:68">
+      <c r="A200" s="1">
+        <v>199</v>
+      </c>
+      <c r="B200">
+        <v>7762786</v>
+      </c>
+      <c r="C200" t="s">
+        <v>68</v>
+      </c>
+      <c r="D200" t="s">
+        <v>69</v>
+      </c>
+      <c r="E200" s="2">
+        <v>45732.39583333334</v>
+      </c>
+      <c r="F200">
+        <v>25</v>
+      </c>
+      <c r="G200" t="s">
+        <v>82</v>
+      </c>
+      <c r="H200" t="s">
+        <v>81</v>
+      </c>
+      <c r="I200">
+        <v>0</v>
+      </c>
+      <c r="J200">
+        <v>2</v>
+      </c>
+      <c r="K200">
+        <v>2</v>
+      </c>
+      <c r="L200">
+        <v>0</v>
+      </c>
+      <c r="M200">
+        <v>5</v>
+      </c>
+      <c r="N200">
+        <v>5</v>
+      </c>
+      <c r="O200" t="s">
+        <v>86</v>
+      </c>
+      <c r="P200" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q200">
+        <v>2.25</v>
+      </c>
+      <c r="R200">
+        <v>2.2</v>
+      </c>
+      <c r="S200">
+        <v>5.5</v>
+      </c>
+      <c r="T200">
+        <v>1.4</v>
+      </c>
+      <c r="U200">
+        <v>2.75</v>
+      </c>
+      <c r="V200">
+        <v>3</v>
+      </c>
+      <c r="W200">
+        <v>1.36</v>
+      </c>
+      <c r="X200">
+        <v>8</v>
+      </c>
+      <c r="Y200">
+        <v>1.08</v>
+      </c>
+      <c r="Z200">
+        <v>1.67</v>
+      </c>
+      <c r="AA200">
+        <v>3.62</v>
+      </c>
+      <c r="AB200">
+        <v>5.1</v>
+      </c>
+      <c r="AC200">
+        <v>1.01</v>
+      </c>
+      <c r="AD200">
+        <v>8.6</v>
+      </c>
+      <c r="AE200">
+        <v>1.3</v>
+      </c>
+      <c r="AF200">
+        <v>3.3</v>
+      </c>
+      <c r="AG200">
+        <v>1.89</v>
+      </c>
+      <c r="AH200">
+        <v>1.85</v>
+      </c>
+      <c r="AI200">
+        <v>1.91</v>
+      </c>
+      <c r="AJ200">
+        <v>1.8</v>
+      </c>
+      <c r="AK200">
+        <v>1.19</v>
+      </c>
+      <c r="AL200">
+        <v>1.27</v>
+      </c>
+      <c r="AM200">
+        <v>2.05</v>
+      </c>
+      <c r="AN200">
+        <v>1.75</v>
+      </c>
+      <c r="AO200">
+        <v>1.17</v>
+      </c>
+      <c r="AP200">
+        <v>1.62</v>
+      </c>
+      <c r="AQ200">
+        <v>1.31</v>
+      </c>
+      <c r="AR200">
+        <v>1.57</v>
+      </c>
+      <c r="AS200">
+        <v>1.57</v>
+      </c>
+      <c r="AT200">
+        <v>3.14</v>
+      </c>
+      <c r="AU200">
+        <v>3</v>
+      </c>
+      <c r="AV200">
+        <v>9</v>
+      </c>
+      <c r="AW200">
+        <v>4</v>
+      </c>
+      <c r="AX200">
+        <v>2</v>
+      </c>
+      <c r="AY200">
+        <v>7</v>
+      </c>
+      <c r="AZ200">
+        <v>11</v>
+      </c>
+      <c r="BA200">
+        <v>7</v>
+      </c>
+      <c r="BB200">
+        <v>1</v>
+      </c>
+      <c r="BC200">
+        <v>8</v>
+      </c>
+      <c r="BD200">
+        <v>1.49</v>
+      </c>
+      <c r="BE200">
+        <v>7</v>
+      </c>
+      <c r="BF200">
+        <v>2.9</v>
+      </c>
+      <c r="BG200">
+        <v>1.32</v>
+      </c>
+      <c r="BH200">
+        <v>3.05</v>
+      </c>
+      <c r="BI200">
+        <v>1.55</v>
+      </c>
+      <c r="BJ200">
+        <v>2.25</v>
+      </c>
+      <c r="BK200">
+        <v>1.9</v>
+      </c>
+      <c r="BL200">
+        <v>1.79</v>
+      </c>
+      <c r="BM200">
+        <v>2.4</v>
+      </c>
+      <c r="BN200">
+        <v>1.49</v>
+      </c>
+      <c r="BO200">
+        <v>3.15</v>
+      </c>
+      <c r="BP200">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="201" spans="1:68">
+      <c r="A201" s="1">
+        <v>200</v>
+      </c>
+      <c r="B201">
+        <v>7762787</v>
+      </c>
+      <c r="C201" t="s">
+        <v>68</v>
+      </c>
+      <c r="D201" t="s">
+        <v>69</v>
+      </c>
+      <c r="E201" s="2">
+        <v>45732.5</v>
+      </c>
+      <c r="F201">
+        <v>25</v>
+      </c>
+      <c r="G201" t="s">
+        <v>78</v>
+      </c>
+      <c r="H201" t="s">
+        <v>79</v>
+      </c>
+      <c r="I201">
+        <v>0</v>
+      </c>
+      <c r="J201">
+        <v>1</v>
+      </c>
+      <c r="K201">
+        <v>1</v>
+      </c>
+      <c r="L201">
+        <v>1</v>
+      </c>
+      <c r="M201">
+        <v>1</v>
+      </c>
+      <c r="N201">
+        <v>2</v>
+      </c>
+      <c r="O201" t="s">
+        <v>198</v>
+      </c>
+      <c r="P201" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q201">
+        <v>4.33</v>
+      </c>
+      <c r="R201">
+        <v>2.1</v>
+      </c>
+      <c r="S201">
+        <v>2.75</v>
+      </c>
+      <c r="T201">
+        <v>1.44</v>
+      </c>
+      <c r="U201">
+        <v>2.63</v>
+      </c>
+      <c r="V201">
+        <v>3.25</v>
+      </c>
+      <c r="W201">
+        <v>1.33</v>
+      </c>
+      <c r="X201">
+        <v>9</v>
+      </c>
+      <c r="Y201">
+        <v>1.07</v>
+      </c>
+      <c r="Z201">
+        <v>4.6</v>
+      </c>
+      <c r="AA201">
+        <v>3.53</v>
+      </c>
+      <c r="AB201">
+        <v>1.76</v>
+      </c>
+      <c r="AC201">
+        <v>1.03</v>
+      </c>
+      <c r="AD201">
+        <v>7.5</v>
+      </c>
+      <c r="AE201">
+        <v>1.36</v>
+      </c>
+      <c r="AF201">
+        <v>2.95</v>
+      </c>
+      <c r="AG201">
+        <v>1.94</v>
+      </c>
+      <c r="AH201">
+        <v>1.8</v>
+      </c>
+      <c r="AI201">
+        <v>1.83</v>
+      </c>
+      <c r="AJ201">
+        <v>1.83</v>
+      </c>
+      <c r="AK201">
+        <v>1.93</v>
+      </c>
+      <c r="AL201">
+        <v>1.29</v>
+      </c>
+      <c r="AM201">
+        <v>1.21</v>
+      </c>
+      <c r="AN201">
+        <v>2.25</v>
+      </c>
+      <c r="AO201">
+        <v>1.92</v>
+      </c>
+      <c r="AP201">
+        <v>2.15</v>
+      </c>
+      <c r="AQ201">
+        <v>1.85</v>
+      </c>
+      <c r="AR201">
+        <v>1.46</v>
+      </c>
+      <c r="AS201">
+        <v>1.77</v>
+      </c>
+      <c r="AT201">
+        <v>3.23</v>
+      </c>
+      <c r="AU201">
+        <v>4</v>
+      </c>
+      <c r="AV201">
+        <v>2</v>
+      </c>
+      <c r="AW201">
+        <v>4</v>
+      </c>
+      <c r="AX201">
+        <v>7</v>
+      </c>
+      <c r="AY201">
+        <v>8</v>
+      </c>
+      <c r="AZ201">
+        <v>9</v>
+      </c>
+      <c r="BA201">
+        <v>3</v>
+      </c>
+      <c r="BB201">
+        <v>7</v>
+      </c>
+      <c r="BC201">
+        <v>10</v>
+      </c>
+      <c r="BD201">
+        <v>2.65</v>
+      </c>
+      <c r="BE201">
+        <v>6.5</v>
+      </c>
+      <c r="BF201">
+        <v>1.58</v>
+      </c>
+      <c r="BG201">
+        <v>1.4</v>
+      </c>
+      <c r="BH201">
+        <v>2.7</v>
+      </c>
+      <c r="BI201">
+        <v>1.68</v>
+      </c>
+      <c r="BJ201">
+        <v>2.05</v>
+      </c>
+      <c r="BK201">
+        <v>2.07</v>
+      </c>
+      <c r="BL201">
+        <v>1.67</v>
+      </c>
+      <c r="BM201">
+        <v>2.65</v>
+      </c>
+      <c r="BN201">
+        <v>1.41</v>
+      </c>
+      <c r="BO201">
+        <v>3.45</v>
+      </c>
+      <c r="BP201">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="301">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -631,6 +631,15 @@
     <t>['22', '30', '53', '73']</t>
   </si>
   <si>
+    <t>['16', '80']</t>
+  </si>
+  <si>
+    <t>['58']</t>
+  </si>
+  <si>
+    <t>['5', '22', '41', '62']</t>
+  </si>
+  <si>
     <t>['12', '22', '45+1', '45+4', '90+1', '90+8']</t>
   </si>
   <si>
@@ -692,9 +701,6 @@
   </si>
   <si>
     <t>['8', '45+1', '68']</t>
-  </si>
-  <si>
-    <t>['58']</t>
   </si>
   <si>
     <t>['1']</t>
@@ -908,6 +914,9 @@
   </si>
   <si>
     <t>['22']</t>
+  </si>
+  <si>
+    <t>['90+6']</t>
   </si>
 </sst>
 </file>
@@ -1269,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP201"/>
+  <dimension ref="A1:BP206"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1603,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ2">
         <v>1.31</v>
@@ -1812,7 +1821,7 @@
         <v>1</v>
       </c>
       <c r="AQ3">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2143,7 +2152,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q5">
         <v>7.5</v>
@@ -2221,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ5">
         <v>1.85</v>
@@ -2349,7 +2358,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2427,7 +2436,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ6">
         <v>1.75</v>
@@ -2636,7 +2645,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ7">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2761,7 +2770,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q8">
         <v>4</v>
@@ -2842,7 +2851,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ8">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3045,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ9">
         <v>1.54</v>
@@ -3254,7 +3263,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ10">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3666,7 +3675,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ12">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3791,7 +3800,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3869,10 +3878,10 @@
         <v>3</v>
       </c>
       <c r="AP13">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ13">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3997,7 +4006,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q14">
         <v>2.4</v>
@@ -4487,7 +4496,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ16">
         <v>1.23</v>
@@ -4696,7 +4705,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ17">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR17">
         <v>1.12</v>
@@ -4821,7 +4830,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -5108,7 +5117,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ19">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5233,7 +5242,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -5439,7 +5448,7 @@
         <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5517,7 +5526,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ21">
         <v>1.85</v>
@@ -5645,7 +5654,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5851,7 +5860,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -5929,7 +5938,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ23">
         <v>1.54</v>
@@ -6057,7 +6066,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q24">
         <v>3.25</v>
@@ -6138,7 +6147,7 @@
         <v>2</v>
       </c>
       <c r="AQ24">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -6263,7 +6272,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q25">
         <v>2.05</v>
@@ -6344,7 +6353,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ25">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR25">
         <v>1.06</v>
@@ -6469,7 +6478,7 @@
         <v>86</v>
       </c>
       <c r="P26" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6756,7 +6765,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ27">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR27">
         <v>1.64</v>
@@ -6959,7 +6968,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ28">
         <v>1.08</v>
@@ -7087,7 +7096,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7165,7 +7174,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ29">
         <v>0.38</v>
@@ -7499,7 +7508,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7705,7 +7714,7 @@
         <v>86</v>
       </c>
       <c r="P32" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q32">
         <v>2.05</v>
@@ -7786,7 +7795,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ32">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR32">
         <v>2.55</v>
@@ -8195,7 +8204,7 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ34">
         <v>1.31</v>
@@ -8607,7 +8616,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ36">
         <v>1.23</v>
@@ -8735,7 +8744,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -9019,7 +9028,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ38">
         <v>0.38</v>
@@ -9228,7 +9237,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ39">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR39">
         <v>1.98</v>
@@ -9434,7 +9443,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ40">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR40">
         <v>1.4</v>
@@ -9640,7 +9649,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ41">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR41">
         <v>1.88</v>
@@ -9843,10 +9852,10 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ42">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR42">
         <v>1.54</v>
@@ -9971,7 +9980,7 @@
         <v>86</v>
       </c>
       <c r="P43" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q43">
         <v>7.5</v>
@@ -10177,7 +10186,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10255,7 +10264,7 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ44">
         <v>1.15</v>
@@ -10461,10 +10470,10 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ45">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR45">
         <v>2.07</v>
@@ -10589,7 +10598,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q46">
         <v>2.5</v>
@@ -10795,7 +10804,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q47">
         <v>4.33</v>
@@ -10873,7 +10882,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ47">
         <v>1.31</v>
@@ -11001,7 +11010,7 @@
         <v>86</v>
       </c>
       <c r="P48" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="Q48">
         <v>2.4</v>
@@ -11619,7 +11628,7 @@
         <v>116</v>
       </c>
       <c r="P51" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11825,7 +11834,7 @@
         <v>118</v>
       </c>
       <c r="P52" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q52">
         <v>5.5</v>
@@ -12237,7 +12246,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -12318,7 +12327,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ54">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR54">
         <v>1.14</v>
@@ -12521,10 +12530,10 @@
         <v>1.75</v>
       </c>
       <c r="AP55">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ55">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR55">
         <v>1.49</v>
@@ -12649,7 +12658,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q56">
         <v>5.5</v>
@@ -12727,10 +12736,10 @@
         <v>1</v>
       </c>
       <c r="AP56">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ56">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR56">
         <v>1.1</v>
@@ -12855,7 +12864,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q57">
         <v>5</v>
@@ -13061,7 +13070,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13139,7 +13148,7 @@
         <v>0.25</v>
       </c>
       <c r="AP58">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ58">
         <v>1.08</v>
@@ -13267,7 +13276,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13345,7 +13354,7 @@
         <v>1.75</v>
       </c>
       <c r="AP59">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ59">
         <v>1.85</v>
@@ -13473,7 +13482,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13679,7 +13688,7 @@
         <v>86</v>
       </c>
       <c r="P61" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q61">
         <v>6.5</v>
@@ -13757,10 +13766,10 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ61">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR61">
         <v>1.06</v>
@@ -14091,7 +14100,7 @@
         <v>86</v>
       </c>
       <c r="P63" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q63">
         <v>3.5</v>
@@ -14297,7 +14306,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14915,7 +14924,7 @@
         <v>86</v>
       </c>
       <c r="P67" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q67">
         <v>6.5</v>
@@ -15121,7 +15130,7 @@
         <v>86</v>
       </c>
       <c r="P68" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q68">
         <v>4.75</v>
@@ -15739,7 +15748,7 @@
         <v>92</v>
       </c>
       <c r="P71" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q71">
         <v>9.5</v>
@@ -15817,7 +15826,7 @@
         <v>2</v>
       </c>
       <c r="AP71">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ71">
         <v>1.31</v>
@@ -16023,10 +16032,10 @@
         <v>0.25</v>
       </c>
       <c r="AP72">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ72">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR72">
         <v>1.09</v>
@@ -16232,7 +16241,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ73">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR73">
         <v>1.15</v>
@@ -16357,7 +16366,7 @@
         <v>86</v>
       </c>
       <c r="P74" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16438,7 +16447,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ74">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR74">
         <v>1.27</v>
@@ -16641,10 +16650,10 @@
         <v>0.75</v>
       </c>
       <c r="AP75">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ75">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR75">
         <v>1.99</v>
@@ -16847,7 +16856,7 @@
         <v>2.5</v>
       </c>
       <c r="AP76">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ76">
         <v>1.75</v>
@@ -16975,7 +16984,7 @@
         <v>130</v>
       </c>
       <c r="P77" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q77">
         <v>1.83</v>
@@ -17181,7 +17190,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q78">
         <v>12</v>
@@ -17259,7 +17268,7 @@
         <v>3</v>
       </c>
       <c r="AP78">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ78">
         <v>2.42</v>
@@ -17387,7 +17396,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q79">
         <v>3.75</v>
@@ -17465,10 +17474,10 @@
         <v>1.6</v>
       </c>
       <c r="AP79">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ79">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR79">
         <v>1.25</v>
@@ -17593,7 +17602,7 @@
         <v>131</v>
       </c>
       <c r="P80" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17799,7 +17808,7 @@
         <v>132</v>
       </c>
       <c r="P81" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -18211,7 +18220,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q83">
         <v>1.67</v>
@@ -18829,7 +18838,7 @@
         <v>134</v>
       </c>
       <c r="P86" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q86">
         <v>2.63</v>
@@ -19322,7 +19331,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ88">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR88">
         <v>1.18</v>
@@ -19525,7 +19534,7 @@
         <v>1.75</v>
       </c>
       <c r="AP89">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ89">
         <v>1.15</v>
@@ -19731,10 +19740,10 @@
         <v>0.75</v>
       </c>
       <c r="AP90">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ90">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR90">
         <v>1.18</v>
@@ -19940,7 +19949,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ91">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR91">
         <v>1.91</v>
@@ -20146,7 +20155,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ92">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR92">
         <v>1.22</v>
@@ -20349,10 +20358,10 @@
         <v>0.4</v>
       </c>
       <c r="AP93">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ93">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR93">
         <v>1.8</v>
@@ -20477,7 +20486,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q94">
         <v>13</v>
@@ -20555,7 +20564,7 @@
         <v>3</v>
       </c>
       <c r="AP94">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ94">
         <v>2.42</v>
@@ -20683,7 +20692,7 @@
         <v>139</v>
       </c>
       <c r="P95" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -20761,7 +20770,7 @@
         <v>0.33</v>
       </c>
       <c r="AP95">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ95">
         <v>1.08</v>
@@ -21095,7 +21104,7 @@
         <v>140</v>
       </c>
       <c r="P97" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q97">
         <v>2.4</v>
@@ -21919,7 +21928,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22206,7 +22215,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ102">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR102">
         <v>0.91</v>
@@ -22537,7 +22546,7 @@
         <v>145</v>
       </c>
       <c r="P104" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22615,10 +22624,10 @@
         <v>0.57</v>
       </c>
       <c r="AP104">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ104">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR104">
         <v>1.26</v>
@@ -22743,7 +22752,7 @@
         <v>86</v>
       </c>
       <c r="P105" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -22821,7 +22830,7 @@
         <v>0.71</v>
       </c>
       <c r="AP105">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ105">
         <v>1.08</v>
@@ -22949,7 +22958,7 @@
         <v>146</v>
       </c>
       <c r="P106" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q106">
         <v>6</v>
@@ -23030,7 +23039,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ106">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR106">
         <v>1.32</v>
@@ -23236,7 +23245,7 @@
         <v>1</v>
       </c>
       <c r="AQ107">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR107">
         <v>1.46</v>
@@ -23361,7 +23370,7 @@
         <v>147</v>
       </c>
       <c r="P108" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23439,7 +23448,7 @@
         <v>1.86</v>
       </c>
       <c r="AP108">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ108">
         <v>1.54</v>
@@ -23648,7 +23657,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ109">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR109">
         <v>1.64</v>
@@ -23773,7 +23782,7 @@
         <v>149</v>
       </c>
       <c r="P110" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23851,7 +23860,7 @@
         <v>1.86</v>
       </c>
       <c r="AP110">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ110">
         <v>1.85</v>
@@ -24057,7 +24066,7 @@
         <v>2.57</v>
       </c>
       <c r="AP111">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ111">
         <v>1.75</v>
@@ -24185,7 +24194,7 @@
         <v>143</v>
       </c>
       <c r="P112" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q112">
         <v>4.75</v>
@@ -24263,10 +24272,10 @@
         <v>0.71</v>
       </c>
       <c r="AP112">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ112">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR112">
         <v>1.48</v>
@@ -25009,7 +25018,7 @@
         <v>86</v>
       </c>
       <c r="P116" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q116">
         <v>4.5</v>
@@ -25215,7 +25224,7 @@
         <v>153</v>
       </c>
       <c r="P117" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q117">
         <v>1.53</v>
@@ -25421,7 +25430,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25627,7 +25636,7 @@
         <v>154</v>
       </c>
       <c r="P119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q119">
         <v>1.8</v>
@@ -25708,7 +25717,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ119">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR119">
         <v>2</v>
@@ -25833,7 +25842,7 @@
         <v>155</v>
       </c>
       <c r="P120" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q120">
         <v>7.5</v>
@@ -26120,7 +26129,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ121">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR121">
         <v>1.4</v>
@@ -26245,7 +26254,7 @@
         <v>157</v>
       </c>
       <c r="P122" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q122">
         <v>2.63</v>
@@ -26451,7 +26460,7 @@
         <v>158</v>
       </c>
       <c r="P123" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="Q123">
         <v>1.73</v>
@@ -27069,7 +27078,7 @@
         <v>86</v>
       </c>
       <c r="P126" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27147,7 +27156,7 @@
         <v>1.43</v>
       </c>
       <c r="AP126">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ126">
         <v>1.85</v>
@@ -27275,7 +27284,7 @@
         <v>161</v>
       </c>
       <c r="P127" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27481,7 +27490,7 @@
         <v>86</v>
       </c>
       <c r="P128" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q128">
         <v>2.4</v>
@@ -27562,7 +27571,7 @@
         <v>2</v>
       </c>
       <c r="AQ128">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR128">
         <v>1.33</v>
@@ -27687,7 +27696,7 @@
         <v>138</v>
       </c>
       <c r="P129" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27893,7 +27902,7 @@
         <v>98</v>
       </c>
       <c r="P130" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q130">
         <v>6.5</v>
@@ -27971,7 +27980,7 @@
         <v>1.63</v>
       </c>
       <c r="AP130">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ130">
         <v>1.85</v>
@@ -28099,7 +28108,7 @@
         <v>162</v>
       </c>
       <c r="P131" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q131">
         <v>4.33</v>
@@ -28177,7 +28186,7 @@
         <v>1.75</v>
       </c>
       <c r="AP131">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ131">
         <v>1.54</v>
@@ -28305,7 +28314,7 @@
         <v>86</v>
       </c>
       <c r="P132" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q132">
         <v>8</v>
@@ -28383,7 +28392,7 @@
         <v>1.63</v>
       </c>
       <c r="AP132">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ132">
         <v>1.85</v>
@@ -28592,7 +28601,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ133">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR133">
         <v>0.99</v>
@@ -29210,7 +29219,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ136">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR136">
         <v>1.69</v>
@@ -29413,7 +29422,7 @@
         <v>1.13</v>
       </c>
       <c r="AP137">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ137">
         <v>1.23</v>
@@ -29619,7 +29628,7 @@
         <v>0.63</v>
       </c>
       <c r="AP138">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ138">
         <v>1.08</v>
@@ -29828,7 +29837,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ139">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR139">
         <v>1.95</v>
@@ -29953,7 +29962,7 @@
         <v>167</v>
       </c>
       <c r="P140" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q140">
         <v>2.3</v>
@@ -30159,7 +30168,7 @@
         <v>86</v>
       </c>
       <c r="P141" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q141">
         <v>7.5</v>
@@ -30365,7 +30374,7 @@
         <v>168</v>
       </c>
       <c r="P142" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30571,7 +30580,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30652,7 +30661,7 @@
         <v>2</v>
       </c>
       <c r="AQ143">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR143">
         <v>1.42</v>
@@ -30858,7 +30867,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ144">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR144">
         <v>1.48</v>
@@ -30983,7 +30992,7 @@
         <v>171</v>
       </c>
       <c r="P145" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q145">
         <v>3.75</v>
@@ -31189,7 +31198,7 @@
         <v>172</v>
       </c>
       <c r="P146" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q146">
         <v>7.5</v>
@@ -31267,7 +31276,7 @@
         <v>1.78</v>
       </c>
       <c r="AP146">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ146">
         <v>1.85</v>
@@ -31395,7 +31404,7 @@
         <v>173</v>
       </c>
       <c r="P147" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31601,7 +31610,7 @@
         <v>174</v>
       </c>
       <c r="P148" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q148">
         <v>2.75</v>
@@ -31679,7 +31688,7 @@
         <v>1</v>
       </c>
       <c r="AP148">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ148">
         <v>1.23</v>
@@ -31807,7 +31816,7 @@
         <v>86</v>
       </c>
       <c r="P149" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q149">
         <v>7.5</v>
@@ -32219,7 +32228,7 @@
         <v>86</v>
       </c>
       <c r="P151" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q151">
         <v>6.5</v>
@@ -32425,7 +32434,7 @@
         <v>176</v>
       </c>
       <c r="P152" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q152">
         <v>2.75</v>
@@ -32506,7 +32515,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ152">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR152">
         <v>1.47</v>
@@ -32631,7 +32640,7 @@
         <v>177</v>
       </c>
       <c r="P153" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q153">
         <v>4.75</v>
@@ -32918,7 +32927,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ154">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR154">
         <v>1.41</v>
@@ -33043,7 +33052,7 @@
         <v>179</v>
       </c>
       <c r="P155" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33121,7 +33130,7 @@
         <v>0.44</v>
       </c>
       <c r="AP155">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ155">
         <v>0.38</v>
@@ -33249,7 +33258,7 @@
         <v>176</v>
       </c>
       <c r="P156" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q156">
         <v>2.2</v>
@@ -33327,7 +33336,7 @@
         <v>0.89</v>
       </c>
       <c r="AP156">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ156">
         <v>1.15</v>
@@ -33536,7 +33545,7 @@
         <v>2</v>
       </c>
       <c r="AQ157">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR157">
         <v>1.48</v>
@@ -33661,7 +33670,7 @@
         <v>181</v>
       </c>
       <c r="P158" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33739,7 +33748,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP158">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ158">
         <v>1.08</v>
@@ -33948,7 +33957,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ159">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR159">
         <v>1.57</v>
@@ -34360,7 +34369,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ161">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR161">
         <v>1.48</v>
@@ -34485,7 +34494,7 @@
         <v>86</v>
       </c>
       <c r="P162" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q162">
         <v>3.5</v>
@@ -34563,7 +34572,7 @@
         <v>0.8</v>
       </c>
       <c r="AP162">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ162">
         <v>1.08</v>
@@ -34691,7 +34700,7 @@
         <v>184</v>
       </c>
       <c r="P163" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35103,7 +35112,7 @@
         <v>185</v>
       </c>
       <c r="P165" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q165">
         <v>9.5</v>
@@ -36211,7 +36220,7 @@
         <v>0.5</v>
       </c>
       <c r="AP170">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ170">
         <v>0.38</v>
@@ -36420,7 +36429,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ171">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR171">
         <v>1.57</v>
@@ -36626,7 +36635,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ172">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR172">
         <v>2.02</v>
@@ -36832,7 +36841,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ173">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR173">
         <v>1.43</v>
@@ -36957,7 +36966,7 @@
         <v>86</v>
       </c>
       <c r="P174" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q174">
         <v>3.75</v>
@@ -37038,7 +37047,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ174">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR174">
         <v>1.58</v>
@@ -37163,7 +37172,7 @@
         <v>124</v>
       </c>
       <c r="P175" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q175">
         <v>5.5</v>
@@ -37241,7 +37250,7 @@
         <v>2.5</v>
       </c>
       <c r="AP175">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ175">
         <v>2.42</v>
@@ -37369,7 +37378,7 @@
         <v>86</v>
       </c>
       <c r="P176" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q176">
         <v>3.1</v>
@@ -37447,7 +37456,7 @@
         <v>1.1</v>
       </c>
       <c r="AP176">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ176">
         <v>1.15</v>
@@ -37653,10 +37662,10 @@
         <v>1</v>
       </c>
       <c r="AP177">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ177">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR177">
         <v>1.06</v>
@@ -37781,7 +37790,7 @@
         <v>86</v>
       </c>
       <c r="P178" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q178">
         <v>3.5</v>
@@ -38193,7 +38202,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38399,7 +38408,7 @@
         <v>194</v>
       </c>
       <c r="P181" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q181">
         <v>3.2</v>
@@ -38605,7 +38614,7 @@
         <v>86</v>
       </c>
       <c r="P182" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q182">
         <v>8.5</v>
@@ -39017,7 +39026,7 @@
         <v>195</v>
       </c>
       <c r="P184" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q184">
         <v>3.6</v>
@@ -39507,10 +39516,10 @@
         <v>0.91</v>
       </c>
       <c r="AP186">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ186">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR186">
         <v>1.29</v>
@@ -39635,7 +39644,7 @@
         <v>196</v>
       </c>
       <c r="P187" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -39713,7 +39722,7 @@
         <v>1.27</v>
       </c>
       <c r="AP187">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ187">
         <v>1.15</v>
@@ -39841,7 +39850,7 @@
         <v>86</v>
       </c>
       <c r="P188" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q188">
         <v>6</v>
@@ -39922,7 +39931,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ188">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR188">
         <v>1.61</v>
@@ -40047,7 +40056,7 @@
         <v>192</v>
       </c>
       <c r="P189" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q189">
         <v>2.3</v>
@@ -40125,10 +40134,10 @@
         <v>1.36</v>
       </c>
       <c r="AP189">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ189">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR189">
         <v>1.65</v>
@@ -40459,7 +40468,7 @@
         <v>197</v>
       </c>
       <c r="P191" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
@@ -40540,7 +40549,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ191">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR191">
         <v>2.07</v>
@@ -40665,7 +40674,7 @@
         <v>198</v>
       </c>
       <c r="P192" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q192">
         <v>8.5</v>
@@ -40743,7 +40752,7 @@
         <v>2.36</v>
       </c>
       <c r="AP192">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ192">
         <v>2.42</v>
@@ -40949,10 +40958,10 @@
         <v>0.27</v>
       </c>
       <c r="AP193">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ193">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR193">
         <v>1.03</v>
@@ -41077,7 +41086,7 @@
         <v>200</v>
       </c>
       <c r="P194" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q194">
         <v>2.75</v>
@@ -41489,7 +41498,7 @@
         <v>201</v>
       </c>
       <c r="P196" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q196">
         <v>4.5</v>
@@ -41901,7 +41910,7 @@
         <v>203</v>
       </c>
       <c r="P198" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q198">
         <v>2.5</v>
@@ -42107,7 +42116,7 @@
         <v>204</v>
       </c>
       <c r="P199" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q199">
         <v>2.4</v>
@@ -42313,7 +42322,7 @@
         <v>86</v>
       </c>
       <c r="P200" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q200">
         <v>2.25</v>
@@ -42519,7 +42528,7 @@
         <v>198</v>
       </c>
       <c r="P201" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q201">
         <v>4.33</v>
@@ -42676,6 +42685,1036 @@
       </c>
       <c r="BP201">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="202" spans="1:68">
+      <c r="A202" s="1">
+        <v>201</v>
+      </c>
+      <c r="B202">
+        <v>7762797</v>
+      </c>
+      <c r="C202" t="s">
+        <v>68</v>
+      </c>
+      <c r="D202" t="s">
+        <v>69</v>
+      </c>
+      <c r="E202" s="2">
+        <v>45744.46875</v>
+      </c>
+      <c r="F202">
+        <v>26</v>
+      </c>
+      <c r="G202" t="s">
+        <v>73</v>
+      </c>
+      <c r="H202" t="s">
+        <v>84</v>
+      </c>
+      <c r="I202">
+        <v>1</v>
+      </c>
+      <c r="J202">
+        <v>0</v>
+      </c>
+      <c r="K202">
+        <v>1</v>
+      </c>
+      <c r="L202">
+        <v>2</v>
+      </c>
+      <c r="M202">
+        <v>1</v>
+      </c>
+      <c r="N202">
+        <v>3</v>
+      </c>
+      <c r="O202" t="s">
+        <v>205</v>
+      </c>
+      <c r="P202" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q202">
+        <v>3</v>
+      </c>
+      <c r="R202">
+        <v>2.05</v>
+      </c>
+      <c r="S202">
+        <v>4</v>
+      </c>
+      <c r="T202">
+        <v>1.5</v>
+      </c>
+      <c r="U202">
+        <v>2.5</v>
+      </c>
+      <c r="V202">
+        <v>3.4</v>
+      </c>
+      <c r="W202">
+        <v>1.3</v>
+      </c>
+      <c r="X202">
+        <v>10</v>
+      </c>
+      <c r="Y202">
+        <v>1.06</v>
+      </c>
+      <c r="Z202">
+        <v>2.3</v>
+      </c>
+      <c r="AA202">
+        <v>3.1</v>
+      </c>
+      <c r="AB202">
+        <v>2.95</v>
+      </c>
+      <c r="AC202">
+        <v>0</v>
+      </c>
+      <c r="AD202">
+        <v>0</v>
+      </c>
+      <c r="AE202">
+        <v>0</v>
+      </c>
+      <c r="AF202">
+        <v>0</v>
+      </c>
+      <c r="AG202">
+        <v>2.1</v>
+      </c>
+      <c r="AH202">
+        <v>1.61</v>
+      </c>
+      <c r="AI202">
+        <v>1.83</v>
+      </c>
+      <c r="AJ202">
+        <v>1.83</v>
+      </c>
+      <c r="AK202">
+        <v>0</v>
+      </c>
+      <c r="AL202">
+        <v>0</v>
+      </c>
+      <c r="AM202">
+        <v>0</v>
+      </c>
+      <c r="AN202">
+        <v>0.75</v>
+      </c>
+      <c r="AO202">
+        <v>1.33</v>
+      </c>
+      <c r="AP202">
+        <v>0.92</v>
+      </c>
+      <c r="AQ202">
+        <v>1.23</v>
+      </c>
+      <c r="AR202">
+        <v>1.33</v>
+      </c>
+      <c r="AS202">
+        <v>1.14</v>
+      </c>
+      <c r="AT202">
+        <v>2.47</v>
+      </c>
+      <c r="AU202">
+        <v>6</v>
+      </c>
+      <c r="AV202">
+        <v>4</v>
+      </c>
+      <c r="AW202">
+        <v>5</v>
+      </c>
+      <c r="AX202">
+        <v>5</v>
+      </c>
+      <c r="AY202">
+        <v>11</v>
+      </c>
+      <c r="AZ202">
+        <v>9</v>
+      </c>
+      <c r="BA202">
+        <v>9</v>
+      </c>
+      <c r="BB202">
+        <v>3</v>
+      </c>
+      <c r="BC202">
+        <v>12</v>
+      </c>
+      <c r="BD202">
+        <v>0</v>
+      </c>
+      <c r="BE202">
+        <v>0</v>
+      </c>
+      <c r="BF202">
+        <v>0</v>
+      </c>
+      <c r="BG202">
+        <v>0</v>
+      </c>
+      <c r="BH202">
+        <v>0</v>
+      </c>
+      <c r="BI202">
+        <v>0</v>
+      </c>
+      <c r="BJ202">
+        <v>0</v>
+      </c>
+      <c r="BK202">
+        <v>0</v>
+      </c>
+      <c r="BL202">
+        <v>0</v>
+      </c>
+      <c r="BM202">
+        <v>0</v>
+      </c>
+      <c r="BN202">
+        <v>0</v>
+      </c>
+      <c r="BO202">
+        <v>0</v>
+      </c>
+      <c r="BP202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:68">
+      <c r="A203" s="1">
+        <v>202</v>
+      </c>
+      <c r="B203">
+        <v>7762796</v>
+      </c>
+      <c r="C203" t="s">
+        <v>68</v>
+      </c>
+      <c r="D203" t="s">
+        <v>69</v>
+      </c>
+      <c r="E203" s="2">
+        <v>45744.57291666666</v>
+      </c>
+      <c r="F203">
+        <v>26</v>
+      </c>
+      <c r="G203" t="s">
+        <v>74</v>
+      </c>
+      <c r="H203" t="s">
+        <v>76</v>
+      </c>
+      <c r="I203">
+        <v>0</v>
+      </c>
+      <c r="J203">
+        <v>0</v>
+      </c>
+      <c r="K203">
+        <v>0</v>
+      </c>
+      <c r="L203">
+        <v>1</v>
+      </c>
+      <c r="M203">
+        <v>0</v>
+      </c>
+      <c r="N203">
+        <v>1</v>
+      </c>
+      <c r="O203" t="s">
+        <v>206</v>
+      </c>
+      <c r="P203" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q203">
+        <v>2.75</v>
+      </c>
+      <c r="R203">
+        <v>2</v>
+      </c>
+      <c r="S203">
+        <v>4.75</v>
+      </c>
+      <c r="T203">
+        <v>1.53</v>
+      </c>
+      <c r="U203">
+        <v>2.38</v>
+      </c>
+      <c r="V203">
+        <v>3.5</v>
+      </c>
+      <c r="W203">
+        <v>1.29</v>
+      </c>
+      <c r="X203">
+        <v>11</v>
+      </c>
+      <c r="Y203">
+        <v>1.05</v>
+      </c>
+      <c r="Z203">
+        <v>1.91</v>
+      </c>
+      <c r="AA203">
+        <v>3.3</v>
+      </c>
+      <c r="AB203">
+        <v>3.8</v>
+      </c>
+      <c r="AC203">
+        <v>0</v>
+      </c>
+      <c r="AD203">
+        <v>0</v>
+      </c>
+      <c r="AE203">
+        <v>2.1</v>
+      </c>
+      <c r="AF203">
+        <v>1.7</v>
+      </c>
+      <c r="AG203">
+        <v>2.2</v>
+      </c>
+      <c r="AH203">
+        <v>1.55</v>
+      </c>
+      <c r="AI203">
+        <v>2.1</v>
+      </c>
+      <c r="AJ203">
+        <v>1.67</v>
+      </c>
+      <c r="AK203">
+        <v>0</v>
+      </c>
+      <c r="AL203">
+        <v>0</v>
+      </c>
+      <c r="AM203">
+        <v>0</v>
+      </c>
+      <c r="AN203">
+        <v>0.75</v>
+      </c>
+      <c r="AO203">
+        <v>0.25</v>
+      </c>
+      <c r="AP203">
+        <v>0.92</v>
+      </c>
+      <c r="AQ203">
+        <v>0.23</v>
+      </c>
+      <c r="AR203">
+        <v>1.32</v>
+      </c>
+      <c r="AS203">
+        <v>0.99</v>
+      </c>
+      <c r="AT203">
+        <v>2.31</v>
+      </c>
+      <c r="AU203">
+        <v>6</v>
+      </c>
+      <c r="AV203">
+        <v>3</v>
+      </c>
+      <c r="AW203">
+        <v>6</v>
+      </c>
+      <c r="AX203">
+        <v>4</v>
+      </c>
+      <c r="AY203">
+        <v>12</v>
+      </c>
+      <c r="AZ203">
+        <v>7</v>
+      </c>
+      <c r="BA203">
+        <v>6</v>
+      </c>
+      <c r="BB203">
+        <v>6</v>
+      </c>
+      <c r="BC203">
+        <v>12</v>
+      </c>
+      <c r="BD203">
+        <v>0</v>
+      </c>
+      <c r="BE203">
+        <v>0</v>
+      </c>
+      <c r="BF203">
+        <v>0</v>
+      </c>
+      <c r="BG203">
+        <v>0</v>
+      </c>
+      <c r="BH203">
+        <v>0</v>
+      </c>
+      <c r="BI203">
+        <v>0</v>
+      </c>
+      <c r="BJ203">
+        <v>0</v>
+      </c>
+      <c r="BK203">
+        <v>0</v>
+      </c>
+      <c r="BL203">
+        <v>0</v>
+      </c>
+      <c r="BM203">
+        <v>0</v>
+      </c>
+      <c r="BN203">
+        <v>0</v>
+      </c>
+      <c r="BO203">
+        <v>0</v>
+      </c>
+      <c r="BP203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:68">
+      <c r="A204" s="1">
+        <v>203</v>
+      </c>
+      <c r="B204">
+        <v>7762794</v>
+      </c>
+      <c r="C204" t="s">
+        <v>68</v>
+      </c>
+      <c r="D204" t="s">
+        <v>69</v>
+      </c>
+      <c r="E204" s="2">
+        <v>45745.30208333334</v>
+      </c>
+      <c r="F204">
+        <v>26</v>
+      </c>
+      <c r="G204" t="s">
+        <v>81</v>
+      </c>
+      <c r="H204" t="s">
+        <v>71</v>
+      </c>
+      <c r="I204">
+        <v>3</v>
+      </c>
+      <c r="J204">
+        <v>1</v>
+      </c>
+      <c r="K204">
+        <v>4</v>
+      </c>
+      <c r="L204">
+        <v>4</v>
+      </c>
+      <c r="M204">
+        <v>1</v>
+      </c>
+      <c r="N204">
+        <v>5</v>
+      </c>
+      <c r="O204" t="s">
+        <v>207</v>
+      </c>
+      <c r="P204" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q204">
+        <v>2.25</v>
+      </c>
+      <c r="R204">
+        <v>2.05</v>
+      </c>
+      <c r="S204">
+        <v>7</v>
+      </c>
+      <c r="T204">
+        <v>1.53</v>
+      </c>
+      <c r="U204">
+        <v>2.38</v>
+      </c>
+      <c r="V204">
+        <v>3.5</v>
+      </c>
+      <c r="W204">
+        <v>1.29</v>
+      </c>
+      <c r="X204">
+        <v>11</v>
+      </c>
+      <c r="Y204">
+        <v>1.05</v>
+      </c>
+      <c r="Z204">
+        <v>1.8</v>
+      </c>
+      <c r="AA204">
+        <v>3.3</v>
+      </c>
+      <c r="AB204">
+        <v>4.3</v>
+      </c>
+      <c r="AC204">
+        <v>0</v>
+      </c>
+      <c r="AD204">
+        <v>0</v>
+      </c>
+      <c r="AE204">
+        <v>0</v>
+      </c>
+      <c r="AF204">
+        <v>0</v>
+      </c>
+      <c r="AG204">
+        <v>2.3</v>
+      </c>
+      <c r="AH204">
+        <v>1.5</v>
+      </c>
+      <c r="AI204">
+        <v>2.5</v>
+      </c>
+      <c r="AJ204">
+        <v>1.5</v>
+      </c>
+      <c r="AK204">
+        <v>0</v>
+      </c>
+      <c r="AL204">
+        <v>0</v>
+      </c>
+      <c r="AM204">
+        <v>0</v>
+      </c>
+      <c r="AN204">
+        <v>1.17</v>
+      </c>
+      <c r="AO204">
+        <v>0.92</v>
+      </c>
+      <c r="AP204">
+        <v>1.31</v>
+      </c>
+      <c r="AQ204">
+        <v>0.85</v>
+      </c>
+      <c r="AR204">
+        <v>1.73</v>
+      </c>
+      <c r="AS204">
+        <v>0.97</v>
+      </c>
+      <c r="AT204">
+        <v>2.7</v>
+      </c>
+      <c r="AU204">
+        <v>10</v>
+      </c>
+      <c r="AV204">
+        <v>4</v>
+      </c>
+      <c r="AW204">
+        <v>11</v>
+      </c>
+      <c r="AX204">
+        <v>1</v>
+      </c>
+      <c r="AY204">
+        <v>21</v>
+      </c>
+      <c r="AZ204">
+        <v>5</v>
+      </c>
+      <c r="BA204">
+        <v>5</v>
+      </c>
+      <c r="BB204">
+        <v>2</v>
+      </c>
+      <c r="BC204">
+        <v>7</v>
+      </c>
+      <c r="BD204">
+        <v>0</v>
+      </c>
+      <c r="BE204">
+        <v>0</v>
+      </c>
+      <c r="BF204">
+        <v>0</v>
+      </c>
+      <c r="BG204">
+        <v>0</v>
+      </c>
+      <c r="BH204">
+        <v>0</v>
+      </c>
+      <c r="BI204">
+        <v>0</v>
+      </c>
+      <c r="BJ204">
+        <v>0</v>
+      </c>
+      <c r="BK204">
+        <v>0</v>
+      </c>
+      <c r="BL204">
+        <v>0</v>
+      </c>
+      <c r="BM204">
+        <v>0</v>
+      </c>
+      <c r="BN204">
+        <v>0</v>
+      </c>
+      <c r="BO204">
+        <v>0</v>
+      </c>
+      <c r="BP204">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:68">
+      <c r="A205" s="1">
+        <v>204</v>
+      </c>
+      <c r="B205">
+        <v>7762799</v>
+      </c>
+      <c r="C205" t="s">
+        <v>68</v>
+      </c>
+      <c r="D205" t="s">
+        <v>69</v>
+      </c>
+      <c r="E205" s="2">
+        <v>45745.40625</v>
+      </c>
+      <c r="F205">
+        <v>26</v>
+      </c>
+      <c r="G205" t="s">
+        <v>70</v>
+      </c>
+      <c r="H205" t="s">
+        <v>85</v>
+      </c>
+      <c r="I205">
+        <v>0</v>
+      </c>
+      <c r="J205">
+        <v>0</v>
+      </c>
+      <c r="K205">
+        <v>0</v>
+      </c>
+      <c r="L205">
+        <v>1</v>
+      </c>
+      <c r="M205">
+        <v>1</v>
+      </c>
+      <c r="N205">
+        <v>2</v>
+      </c>
+      <c r="O205" t="s">
+        <v>135</v>
+      </c>
+      <c r="P205" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q205">
+        <v>2.38</v>
+      </c>
+      <c r="R205">
+        <v>2</v>
+      </c>
+      <c r="S205">
+        <v>6.5</v>
+      </c>
+      <c r="T205">
+        <v>1.53</v>
+      </c>
+      <c r="U205">
+        <v>2.38</v>
+      </c>
+      <c r="V205">
+        <v>3.75</v>
+      </c>
+      <c r="W205">
+        <v>1.25</v>
+      </c>
+      <c r="X205">
+        <v>11</v>
+      </c>
+      <c r="Y205">
+        <v>1.05</v>
+      </c>
+      <c r="Z205">
+        <v>1.62</v>
+      </c>
+      <c r="AA205">
+        <v>3.2</v>
+      </c>
+      <c r="AB205">
+        <v>5.25</v>
+      </c>
+      <c r="AC205">
+        <v>0</v>
+      </c>
+      <c r="AD205">
+        <v>0</v>
+      </c>
+      <c r="AE205">
+        <v>1.5</v>
+      </c>
+      <c r="AF205">
+        <v>2.4</v>
+      </c>
+      <c r="AG205">
+        <v>2.3</v>
+      </c>
+      <c r="AH205">
+        <v>1.5</v>
+      </c>
+      <c r="AI205">
+        <v>2.38</v>
+      </c>
+      <c r="AJ205">
+        <v>1.53</v>
+      </c>
+      <c r="AK205">
+        <v>0</v>
+      </c>
+      <c r="AL205">
+        <v>0</v>
+      </c>
+      <c r="AM205">
+        <v>0</v>
+      </c>
+      <c r="AN205">
+        <v>1.92</v>
+      </c>
+      <c r="AO205">
+        <v>0.75</v>
+      </c>
+      <c r="AP205">
+        <v>1.85</v>
+      </c>
+      <c r="AQ205">
+        <v>0.77</v>
+      </c>
+      <c r="AR205">
+        <v>1.74</v>
+      </c>
+      <c r="AS205">
+        <v>1.46</v>
+      </c>
+      <c r="AT205">
+        <v>3.2</v>
+      </c>
+      <c r="AU205">
+        <v>4</v>
+      </c>
+      <c r="AV205">
+        <v>3</v>
+      </c>
+      <c r="AW205">
+        <v>4</v>
+      </c>
+      <c r="AX205">
+        <v>3</v>
+      </c>
+      <c r="AY205">
+        <v>8</v>
+      </c>
+      <c r="AZ205">
+        <v>6</v>
+      </c>
+      <c r="BA205">
+        <v>4</v>
+      </c>
+      <c r="BB205">
+        <v>3</v>
+      </c>
+      <c r="BC205">
+        <v>7</v>
+      </c>
+      <c r="BD205">
+        <v>0</v>
+      </c>
+      <c r="BE205">
+        <v>0</v>
+      </c>
+      <c r="BF205">
+        <v>0</v>
+      </c>
+      <c r="BG205">
+        <v>0</v>
+      </c>
+      <c r="BH205">
+        <v>0</v>
+      </c>
+      <c r="BI205">
+        <v>0</v>
+      </c>
+      <c r="BJ205">
+        <v>0</v>
+      </c>
+      <c r="BK205">
+        <v>0</v>
+      </c>
+      <c r="BL205">
+        <v>0</v>
+      </c>
+      <c r="BM205">
+        <v>0</v>
+      </c>
+      <c r="BN205">
+        <v>0</v>
+      </c>
+      <c r="BO205">
+        <v>0</v>
+      </c>
+      <c r="BP205">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:68">
+      <c r="A206" s="1">
+        <v>205</v>
+      </c>
+      <c r="B206">
+        <v>7762798</v>
+      </c>
+      <c r="C206" t="s">
+        <v>68</v>
+      </c>
+      <c r="D206" t="s">
+        <v>69</v>
+      </c>
+      <c r="E206" s="2">
+        <v>45745.51041666666</v>
+      </c>
+      <c r="F206">
+        <v>26</v>
+      </c>
+      <c r="G206" t="s">
+        <v>77</v>
+      </c>
+      <c r="H206" t="s">
+        <v>80</v>
+      </c>
+      <c r="I206">
+        <v>0</v>
+      </c>
+      <c r="J206">
+        <v>0</v>
+      </c>
+      <c r="K206">
+        <v>0</v>
+      </c>
+      <c r="L206">
+        <v>0</v>
+      </c>
+      <c r="M206">
+        <v>1</v>
+      </c>
+      <c r="N206">
+        <v>1</v>
+      </c>
+      <c r="O206" t="s">
+        <v>86</v>
+      </c>
+      <c r="P206" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q206">
+        <v>8.5</v>
+      </c>
+      <c r="R206">
+        <v>2.3</v>
+      </c>
+      <c r="S206">
+        <v>1.83</v>
+      </c>
+      <c r="T206">
+        <v>1.4</v>
+      </c>
+      <c r="U206">
+        <v>2.75</v>
+      </c>
+      <c r="V206">
+        <v>2.75</v>
+      </c>
+      <c r="W206">
+        <v>1.4</v>
+      </c>
+      <c r="X206">
+        <v>8</v>
+      </c>
+      <c r="Y206">
+        <v>1.08</v>
+      </c>
+      <c r="Z206">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AA206">
+        <v>4.7</v>
+      </c>
+      <c r="AB206">
+        <v>1.33</v>
+      </c>
+      <c r="AC206">
+        <v>0</v>
+      </c>
+      <c r="AD206">
+        <v>0</v>
+      </c>
+      <c r="AE206">
+        <v>0</v>
+      </c>
+      <c r="AF206">
+        <v>0</v>
+      </c>
+      <c r="AG206">
+        <v>1.82</v>
+      </c>
+      <c r="AH206">
+        <v>1.92</v>
+      </c>
+      <c r="AI206">
+        <v>2.25</v>
+      </c>
+      <c r="AJ206">
+        <v>1.57</v>
+      </c>
+      <c r="AK206">
+        <v>0</v>
+      </c>
+      <c r="AL206">
+        <v>0</v>
+      </c>
+      <c r="AM206">
+        <v>0</v>
+      </c>
+      <c r="AN206">
+        <v>1.17</v>
+      </c>
+      <c r="AO206">
+        <v>1.42</v>
+      </c>
+      <c r="AP206">
+        <v>1.08</v>
+      </c>
+      <c r="AQ206">
+        <v>1.54</v>
+      </c>
+      <c r="AR206">
+        <v>1.07</v>
+      </c>
+      <c r="AS206">
+        <v>1.69</v>
+      </c>
+      <c r="AT206">
+        <v>2.76</v>
+      </c>
+      <c r="AU206">
+        <v>0</v>
+      </c>
+      <c r="AV206">
+        <v>2</v>
+      </c>
+      <c r="AW206">
+        <v>0</v>
+      </c>
+      <c r="AX206">
+        <v>0</v>
+      </c>
+      <c r="AY206">
+        <v>0</v>
+      </c>
+      <c r="AZ206">
+        <v>2</v>
+      </c>
+      <c r="BA206">
+        <v>2</v>
+      </c>
+      <c r="BB206">
+        <v>9</v>
+      </c>
+      <c r="BC206">
+        <v>11</v>
+      </c>
+      <c r="BD206">
+        <v>0</v>
+      </c>
+      <c r="BE206">
+        <v>0</v>
+      </c>
+      <c r="BF206">
+        <v>0</v>
+      </c>
+      <c r="BG206">
+        <v>0</v>
+      </c>
+      <c r="BH206">
+        <v>0</v>
+      </c>
+      <c r="BI206">
+        <v>0</v>
+      </c>
+      <c r="BJ206">
+        <v>0</v>
+      </c>
+      <c r="BK206">
+        <v>1.83</v>
+      </c>
+      <c r="BL206">
+        <v>0</v>
+      </c>
+      <c r="BM206">
+        <v>0</v>
+      </c>
+      <c r="BN206">
+        <v>0</v>
+      </c>
+      <c r="BO206">
+        <v>0</v>
+      </c>
+      <c r="BP206">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="304">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -640,6 +640,12 @@
     <t>['5', '22', '41', '62']</t>
   </si>
   <si>
+    <t>['23']</t>
+  </si>
+  <si>
+    <t>['12']</t>
+  </si>
+  <si>
     <t>['12', '22', '45+1', '45+4', '90+1', '90+8']</t>
   </si>
   <si>
@@ -917,6 +923,9 @@
   </si>
   <si>
     <t>['90+6']</t>
+  </si>
+  <si>
+    <t>['31', '59', '68', '90+1']</t>
   </si>
 </sst>
 </file>
@@ -1278,7 +1287,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP206"/>
+  <dimension ref="A1:BP209"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2024,10 +2033,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ4">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2152,7 +2161,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q5">
         <v>7.5</v>
@@ -2358,7 +2367,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2439,7 +2448,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ6">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2770,7 +2779,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q8">
         <v>4</v>
@@ -3466,7 +3475,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ11">
         <v>0.38</v>
@@ -3800,7 +3809,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4006,7 +4015,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q14">
         <v>2.4</v>
@@ -4290,7 +4299,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ15">
         <v>1.08</v>
@@ -4830,7 +4839,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -4908,7 +4917,7 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ18">
         <v>1.85</v>
@@ -5242,7 +5251,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -5323,7 +5332,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ20">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR20">
         <v>0.96</v>
@@ -5448,7 +5457,7 @@
         <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5654,7 +5663,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5735,7 +5744,7 @@
         <v>1</v>
       </c>
       <c r="AQ22">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR22">
         <v>1.34</v>
@@ -5860,7 +5869,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -6066,7 +6075,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q24">
         <v>3.25</v>
@@ -6272,7 +6281,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q25">
         <v>2.05</v>
@@ -6478,7 +6487,7 @@
         <v>86</v>
       </c>
       <c r="P26" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6556,7 +6565,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ26">
         <v>1.15</v>
@@ -6762,7 +6771,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ27">
         <v>0.85</v>
@@ -7096,7 +7105,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7383,7 +7392,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ30">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR30">
         <v>1.68</v>
@@ -7508,7 +7517,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7714,7 +7723,7 @@
         <v>86</v>
       </c>
       <c r="P32" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q32">
         <v>2.05</v>
@@ -8413,7 +8422,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ35">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR35">
         <v>0.9399999999999999</v>
@@ -8744,7 +8753,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -8822,7 +8831,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ37">
         <v>1.85</v>
@@ -9234,7 +9243,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ39">
         <v>0.23</v>
@@ -9980,7 +9989,7 @@
         <v>86</v>
       </c>
       <c r="P43" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q43">
         <v>7.5</v>
@@ -10058,10 +10067,10 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ43">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AR43">
         <v>1.51</v>
@@ -10186,7 +10195,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10598,7 +10607,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q46">
         <v>2.5</v>
@@ -10679,7 +10688,7 @@
         <v>2</v>
       </c>
       <c r="AQ46">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR46">
         <v>1.81</v>
@@ -10804,7 +10813,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q47">
         <v>4.33</v>
@@ -11091,7 +11100,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ48">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR48">
         <v>2.19</v>
@@ -11628,7 +11637,7 @@
         <v>116</v>
       </c>
       <c r="P51" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11706,7 +11715,7 @@
         <v>2</v>
       </c>
       <c r="AP51">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ51">
         <v>1.08</v>
@@ -11834,7 +11843,7 @@
         <v>118</v>
       </c>
       <c r="P52" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q52">
         <v>5.5</v>
@@ -12246,7 +12255,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -12324,7 +12333,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ54">
         <v>0.23</v>
@@ -12658,7 +12667,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q56">
         <v>5.5</v>
@@ -12864,7 +12873,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q57">
         <v>5</v>
@@ -12942,10 +12951,10 @@
         <v>3</v>
       </c>
       <c r="AP57">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ57">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR57">
         <v>1.15</v>
@@ -13070,7 +13079,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13151,7 +13160,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ58">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR58">
         <v>1.97</v>
@@ -13276,7 +13285,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13482,7 +13491,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13563,7 +13572,7 @@
         <v>1</v>
       </c>
       <c r="AQ60">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AR60">
         <v>1.59</v>
@@ -13688,7 +13697,7 @@
         <v>86</v>
       </c>
       <c r="P61" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q61">
         <v>6.5</v>
@@ -13975,7 +13984,7 @@
         <v>2</v>
       </c>
       <c r="AQ62">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AR62">
         <v>1.3</v>
@@ -14100,7 +14109,7 @@
         <v>86</v>
       </c>
       <c r="P63" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q63">
         <v>3.5</v>
@@ -14178,7 +14187,7 @@
         <v>1.67</v>
       </c>
       <c r="AP63">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ63">
         <v>1.31</v>
@@ -14306,7 +14315,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14924,7 +14933,7 @@
         <v>86</v>
       </c>
       <c r="P67" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q67">
         <v>6.5</v>
@@ -15130,7 +15139,7 @@
         <v>86</v>
       </c>
       <c r="P68" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q68">
         <v>4.75</v>
@@ -15623,7 +15632,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ70">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR70">
         <v>1.49</v>
@@ -15748,7 +15757,7 @@
         <v>92</v>
       </c>
       <c r="P71" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q71">
         <v>9.5</v>
@@ -16238,7 +16247,7 @@
         <v>0.8</v>
       </c>
       <c r="AP73">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ73">
         <v>0.77</v>
@@ -16366,7 +16375,7 @@
         <v>86</v>
       </c>
       <c r="P74" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16444,7 +16453,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ74">
         <v>0.85</v>
@@ -16859,7 +16868,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ76">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR76">
         <v>1.63</v>
@@ -16984,7 +16993,7 @@
         <v>130</v>
       </c>
       <c r="P77" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q77">
         <v>1.83</v>
@@ -17062,10 +17071,10 @@
         <v>0.4</v>
       </c>
       <c r="AP77">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ77">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR77">
         <v>1.79</v>
@@ -17190,7 +17199,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q78">
         <v>12</v>
@@ -17271,7 +17280,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ78">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AR78">
         <v>1.46</v>
@@ -17396,7 +17405,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q79">
         <v>3.75</v>
@@ -17602,7 +17611,7 @@
         <v>131</v>
       </c>
       <c r="P80" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17808,7 +17817,7 @@
         <v>132</v>
       </c>
       <c r="P81" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -18220,7 +18229,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q83">
         <v>1.67</v>
@@ -18838,7 +18847,7 @@
         <v>134</v>
       </c>
       <c r="P86" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q86">
         <v>2.63</v>
@@ -19328,7 +19337,7 @@
         <v>1.83</v>
       </c>
       <c r="AP88">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ88">
         <v>1.23</v>
@@ -19946,7 +19955,7 @@
         <v>0.8</v>
       </c>
       <c r="AP91">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ91">
         <v>1.54</v>
@@ -20486,7 +20495,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q94">
         <v>13</v>
@@ -20567,7 +20576,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ94">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AR94">
         <v>1.21</v>
@@ -20692,7 +20701,7 @@
         <v>139</v>
       </c>
       <c r="P95" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -20773,7 +20782,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ95">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR95">
         <v>1.49</v>
@@ -21104,7 +21113,7 @@
         <v>140</v>
       </c>
       <c r="P97" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q97">
         <v>2.4</v>
@@ -21928,7 +21937,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22006,7 +22015,7 @@
         <v>1.67</v>
       </c>
       <c r="AP101">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ101">
         <v>1.54</v>
@@ -22546,7 +22555,7 @@
         <v>145</v>
       </c>
       <c r="P104" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22752,7 +22761,7 @@
         <v>86</v>
       </c>
       <c r="P105" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -22833,7 +22842,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ105">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR105">
         <v>1.16</v>
@@ -22958,7 +22967,7 @@
         <v>146</v>
       </c>
       <c r="P106" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q106">
         <v>6</v>
@@ -23036,7 +23045,7 @@
         <v>0.67</v>
       </c>
       <c r="AP106">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ106">
         <v>1.54</v>
@@ -23370,7 +23379,7 @@
         <v>147</v>
       </c>
       <c r="P108" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23782,7 +23791,7 @@
         <v>149</v>
       </c>
       <c r="P110" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -24069,7 +24078,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ111">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR111">
         <v>1.08</v>
@@ -24194,7 +24203,7 @@
         <v>143</v>
       </c>
       <c r="P112" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q112">
         <v>4.75</v>
@@ -25018,7 +25027,7 @@
         <v>86</v>
       </c>
       <c r="P116" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q116">
         <v>4.5</v>
@@ -25096,7 +25105,7 @@
         <v>1.17</v>
       </c>
       <c r="AP116">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ116">
         <v>1.85</v>
@@ -25224,7 +25233,7 @@
         <v>153</v>
       </c>
       <c r="P117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q117">
         <v>1.53</v>
@@ -25302,7 +25311,7 @@
         <v>1</v>
       </c>
       <c r="AP117">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ117">
         <v>1.23</v>
@@ -25430,7 +25439,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25636,7 +25645,7 @@
         <v>154</v>
       </c>
       <c r="P119" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q119">
         <v>1.8</v>
@@ -25842,7 +25851,7 @@
         <v>155</v>
       </c>
       <c r="P120" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q120">
         <v>7.5</v>
@@ -25923,7 +25932,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ120">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AR120">
         <v>1.46</v>
@@ -26254,7 +26263,7 @@
         <v>157</v>
       </c>
       <c r="P122" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q122">
         <v>2.63</v>
@@ -26744,7 +26753,7 @@
         <v>0.71</v>
       </c>
       <c r="AP124">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ124">
         <v>1.08</v>
@@ -26950,7 +26959,7 @@
         <v>1.29</v>
       </c>
       <c r="AP125">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ125">
         <v>1.23</v>
@@ -27078,7 +27087,7 @@
         <v>86</v>
       </c>
       <c r="P126" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27284,7 +27293,7 @@
         <v>161</v>
       </c>
       <c r="P127" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27365,7 +27374,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ127">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AR127">
         <v>2.03</v>
@@ -27490,7 +27499,7 @@
         <v>86</v>
       </c>
       <c r="P128" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q128">
         <v>2.4</v>
@@ -27696,7 +27705,7 @@
         <v>138</v>
       </c>
       <c r="P129" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27902,7 +27911,7 @@
         <v>98</v>
       </c>
       <c r="P130" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q130">
         <v>6.5</v>
@@ -28108,7 +28117,7 @@
         <v>162</v>
       </c>
       <c r="P131" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q131">
         <v>4.33</v>
@@ -28314,7 +28323,7 @@
         <v>86</v>
       </c>
       <c r="P132" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q132">
         <v>8</v>
@@ -28804,10 +28813,10 @@
         <v>2.25</v>
       </c>
       <c r="AP134">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ134">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR134">
         <v>1.33</v>
@@ -29013,7 +29022,7 @@
         <v>1</v>
       </c>
       <c r="AQ135">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR135">
         <v>1.42</v>
@@ -29962,7 +29971,7 @@
         <v>167</v>
       </c>
       <c r="P140" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q140">
         <v>2.3</v>
@@ -30040,7 +30049,7 @@
         <v>0.5</v>
       </c>
       <c r="AP140">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ140">
         <v>0.38</v>
@@ -30168,7 +30177,7 @@
         <v>86</v>
       </c>
       <c r="P141" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q141">
         <v>7.5</v>
@@ -30249,7 +30258,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ141">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AR141">
         <v>1.45</v>
@@ -30374,7 +30383,7 @@
         <v>168</v>
       </c>
       <c r="P142" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30452,7 +30461,7 @@
         <v>1</v>
       </c>
       <c r="AP142">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ142">
         <v>1.15</v>
@@ -30580,7 +30589,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30992,7 +31001,7 @@
         <v>171</v>
       </c>
       <c r="P145" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q145">
         <v>3.75</v>
@@ -31070,7 +31079,7 @@
         <v>1.56</v>
       </c>
       <c r="AP145">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ145">
         <v>1.54</v>
@@ -31198,7 +31207,7 @@
         <v>172</v>
       </c>
       <c r="P146" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q146">
         <v>7.5</v>
@@ -31404,7 +31413,7 @@
         <v>173</v>
       </c>
       <c r="P147" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31610,7 +31619,7 @@
         <v>174</v>
       </c>
       <c r="P148" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q148">
         <v>2.75</v>
@@ -31816,7 +31825,7 @@
         <v>86</v>
       </c>
       <c r="P149" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q149">
         <v>7.5</v>
@@ -32103,7 +32112,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ150">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR150">
         <v>1.74</v>
@@ -32228,7 +32237,7 @@
         <v>86</v>
       </c>
       <c r="P151" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q151">
         <v>6.5</v>
@@ -32309,7 +32318,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ151">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR151">
         <v>0.99</v>
@@ -32434,7 +32443,7 @@
         <v>176</v>
       </c>
       <c r="P152" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q152">
         <v>2.75</v>
@@ -32640,7 +32649,7 @@
         <v>177</v>
       </c>
       <c r="P153" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q153">
         <v>4.75</v>
@@ -32721,7 +32730,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ153">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AR153">
         <v>1.54</v>
@@ -33052,7 +33061,7 @@
         <v>179</v>
       </c>
       <c r="P155" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33258,7 +33267,7 @@
         <v>176</v>
       </c>
       <c r="P156" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q156">
         <v>2.2</v>
@@ -33670,7 +33679,7 @@
         <v>181</v>
       </c>
       <c r="P158" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -34160,10 +34169,10 @@
         <v>2.78</v>
       </c>
       <c r="AP160">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ160">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AR160">
         <v>2.11</v>
@@ -34366,7 +34375,7 @@
         <v>1</v>
       </c>
       <c r="AP161">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ161">
         <v>0.85</v>
@@ -34494,7 +34503,7 @@
         <v>86</v>
       </c>
       <c r="P162" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q162">
         <v>3.5</v>
@@ -34700,7 +34709,7 @@
         <v>184</v>
       </c>
       <c r="P163" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -34987,7 +34996,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ164">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR164">
         <v>1.55</v>
@@ -35112,7 +35121,7 @@
         <v>185</v>
       </c>
       <c r="P165" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q165">
         <v>9.5</v>
@@ -35396,7 +35405,7 @@
         <v>1.2</v>
       </c>
       <c r="AP166">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ166">
         <v>1.23</v>
@@ -35811,7 +35820,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ168">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR168">
         <v>2.21</v>
@@ -36426,7 +36435,7 @@
         <v>0.3</v>
       </c>
       <c r="AP171">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ171">
         <v>0.23</v>
@@ -36632,7 +36641,7 @@
         <v>1.5</v>
       </c>
       <c r="AP172">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ172">
         <v>1.23</v>
@@ -36966,7 +36975,7 @@
         <v>86</v>
       </c>
       <c r="P174" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q174">
         <v>3.75</v>
@@ -37172,7 +37181,7 @@
         <v>124</v>
       </c>
       <c r="P175" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q175">
         <v>5.5</v>
@@ -37253,7 +37262,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ175">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AR175">
         <v>1.71</v>
@@ -37378,7 +37387,7 @@
         <v>86</v>
       </c>
       <c r="P176" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q176">
         <v>3.1</v>
@@ -37790,7 +37799,7 @@
         <v>86</v>
       </c>
       <c r="P178" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q178">
         <v>3.5</v>
@@ -38074,7 +38083,7 @@
         <v>0.45</v>
       </c>
       <c r="AP179">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ179">
         <v>0.38</v>
@@ -38202,7 +38211,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38408,7 +38417,7 @@
         <v>194</v>
       </c>
       <c r="P181" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q181">
         <v>3.2</v>
@@ -38614,7 +38623,7 @@
         <v>86</v>
       </c>
       <c r="P182" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q182">
         <v>8.5</v>
@@ -39026,7 +39035,7 @@
         <v>195</v>
       </c>
       <c r="P184" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q184">
         <v>3.6</v>
@@ -39107,7 +39116,7 @@
         <v>2</v>
       </c>
       <c r="AQ184">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR184">
         <v>1.43</v>
@@ -39644,7 +39653,7 @@
         <v>196</v>
       </c>
       <c r="P187" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -39850,7 +39859,7 @@
         <v>86</v>
       </c>
       <c r="P188" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q188">
         <v>6</v>
@@ -39928,7 +39937,7 @@
         <v>1.27</v>
       </c>
       <c r="AP188">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ188">
         <v>1.54</v>
@@ -40056,7 +40065,7 @@
         <v>192</v>
       </c>
       <c r="P189" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q189">
         <v>2.3</v>
@@ -40343,7 +40352,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ190">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR190">
         <v>1.56</v>
@@ -40468,7 +40477,7 @@
         <v>197</v>
       </c>
       <c r="P191" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
@@ -40546,7 +40555,7 @@
         <v>0.73</v>
       </c>
       <c r="AP191">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ191">
         <v>0.77</v>
@@ -40674,7 +40683,7 @@
         <v>198</v>
       </c>
       <c r="P192" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q192">
         <v>8.5</v>
@@ -40755,7 +40764,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ192">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AR192">
         <v>1.34</v>
@@ -41086,7 +41095,7 @@
         <v>200</v>
       </c>
       <c r="P194" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q194">
         <v>2.75</v>
@@ -41498,7 +41507,7 @@
         <v>201</v>
       </c>
       <c r="P196" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q196">
         <v>4.5</v>
@@ -41910,7 +41919,7 @@
         <v>203</v>
       </c>
       <c r="P198" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q198">
         <v>2.5</v>
@@ -42116,7 +42125,7 @@
         <v>204</v>
       </c>
       <c r="P199" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q199">
         <v>2.4</v>
@@ -42322,7 +42331,7 @@
         <v>86</v>
       </c>
       <c r="P200" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q200">
         <v>2.25</v>
@@ -42528,7 +42537,7 @@
         <v>198</v>
       </c>
       <c r="P201" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q201">
         <v>4.33</v>
@@ -43146,7 +43155,7 @@
         <v>207</v>
       </c>
       <c r="P204" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q204">
         <v>2.25</v>
@@ -43558,7 +43567,7 @@
         <v>86</v>
       </c>
       <c r="P206" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q206">
         <v>8.5</v>
@@ -43714,6 +43723,624 @@
         <v>0</v>
       </c>
       <c r="BP206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:68">
+      <c r="A207" s="1">
+        <v>206</v>
+      </c>
+      <c r="B207">
+        <v>7762800</v>
+      </c>
+      <c r="C207" t="s">
+        <v>68</v>
+      </c>
+      <c r="D207" t="s">
+        <v>69</v>
+      </c>
+      <c r="E207" s="2">
+        <v>45746.3125</v>
+      </c>
+      <c r="F207">
+        <v>26</v>
+      </c>
+      <c r="G207" t="s">
+        <v>83</v>
+      </c>
+      <c r="H207" t="s">
+        <v>78</v>
+      </c>
+      <c r="I207">
+        <v>1</v>
+      </c>
+      <c r="J207">
+        <v>1</v>
+      </c>
+      <c r="K207">
+        <v>2</v>
+      </c>
+      <c r="L207">
+        <v>1</v>
+      </c>
+      <c r="M207">
+        <v>4</v>
+      </c>
+      <c r="N207">
+        <v>5</v>
+      </c>
+      <c r="O207" t="s">
+        <v>208</v>
+      </c>
+      <c r="P207" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q207">
+        <v>4</v>
+      </c>
+      <c r="R207">
+        <v>1.83</v>
+      </c>
+      <c r="S207">
+        <v>3.4</v>
+      </c>
+      <c r="T207">
+        <v>1.62</v>
+      </c>
+      <c r="U207">
+        <v>2.2</v>
+      </c>
+      <c r="V207">
+        <v>4</v>
+      </c>
+      <c r="W207">
+        <v>1.22</v>
+      </c>
+      <c r="X207">
+        <v>13</v>
+      </c>
+      <c r="Y207">
+        <v>1.04</v>
+      </c>
+      <c r="Z207">
+        <v>3.04</v>
+      </c>
+      <c r="AA207">
+        <v>2.78</v>
+      </c>
+      <c r="AB207">
+        <v>2.62</v>
+      </c>
+      <c r="AC207">
+        <v>0</v>
+      </c>
+      <c r="AD207">
+        <v>0</v>
+      </c>
+      <c r="AE207">
+        <v>1.53</v>
+      </c>
+      <c r="AF207">
+        <v>2.25</v>
+      </c>
+      <c r="AG207">
+        <v>2.75</v>
+      </c>
+      <c r="AH207">
+        <v>1.39</v>
+      </c>
+      <c r="AI207">
+        <v>2.2</v>
+      </c>
+      <c r="AJ207">
+        <v>1.62</v>
+      </c>
+      <c r="AK207">
+        <v>0</v>
+      </c>
+      <c r="AL207">
+        <v>0</v>
+      </c>
+      <c r="AM207">
+        <v>0</v>
+      </c>
+      <c r="AN207">
+        <v>1.42</v>
+      </c>
+      <c r="AO207">
+        <v>1.08</v>
+      </c>
+      <c r="AP207">
+        <v>1.31</v>
+      </c>
+      <c r="AQ207">
+        <v>1.23</v>
+      </c>
+      <c r="AR207">
+        <v>1.6</v>
+      </c>
+      <c r="AS207">
+        <v>1.25</v>
+      </c>
+      <c r="AT207">
+        <v>2.85</v>
+      </c>
+      <c r="AU207">
+        <v>8</v>
+      </c>
+      <c r="AV207">
+        <v>8</v>
+      </c>
+      <c r="AW207">
+        <v>4</v>
+      </c>
+      <c r="AX207">
+        <v>6</v>
+      </c>
+      <c r="AY207">
+        <v>12</v>
+      </c>
+      <c r="AZ207">
+        <v>14</v>
+      </c>
+      <c r="BA207">
+        <v>6</v>
+      </c>
+      <c r="BB207">
+        <v>6</v>
+      </c>
+      <c r="BC207">
+        <v>12</v>
+      </c>
+      <c r="BD207">
+        <v>0</v>
+      </c>
+      <c r="BE207">
+        <v>0</v>
+      </c>
+      <c r="BF207">
+        <v>0</v>
+      </c>
+      <c r="BG207">
+        <v>0</v>
+      </c>
+      <c r="BH207">
+        <v>0</v>
+      </c>
+      <c r="BI207">
+        <v>0</v>
+      </c>
+      <c r="BJ207">
+        <v>0</v>
+      </c>
+      <c r="BK207">
+        <v>0</v>
+      </c>
+      <c r="BL207">
+        <v>0</v>
+      </c>
+      <c r="BM207">
+        <v>0</v>
+      </c>
+      <c r="BN207">
+        <v>0</v>
+      </c>
+      <c r="BO207">
+        <v>0</v>
+      </c>
+      <c r="BP207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:68">
+      <c r="A208" s="1">
+        <v>207</v>
+      </c>
+      <c r="B208">
+        <v>7762795</v>
+      </c>
+      <c r="C208" t="s">
+        <v>68</v>
+      </c>
+      <c r="D208" t="s">
+        <v>69</v>
+      </c>
+      <c r="E208" s="2">
+        <v>45746.41666666666</v>
+      </c>
+      <c r="F208">
+        <v>26</v>
+      </c>
+      <c r="G208" t="s">
+        <v>72</v>
+      </c>
+      <c r="H208" t="s">
+        <v>75</v>
+      </c>
+      <c r="I208">
+        <v>1</v>
+      </c>
+      <c r="J208">
+        <v>0</v>
+      </c>
+      <c r="K208">
+        <v>1</v>
+      </c>
+      <c r="L208">
+        <v>1</v>
+      </c>
+      <c r="M208">
+        <v>0</v>
+      </c>
+      <c r="N208">
+        <v>1</v>
+      </c>
+      <c r="O208" t="s">
+        <v>209</v>
+      </c>
+      <c r="P208" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q208">
+        <v>7.5</v>
+      </c>
+      <c r="R208">
+        <v>2.3</v>
+      </c>
+      <c r="S208">
+        <v>1.95</v>
+      </c>
+      <c r="T208">
+        <v>1.4</v>
+      </c>
+      <c r="U208">
+        <v>2.75</v>
+      </c>
+      <c r="V208">
+        <v>2.75</v>
+      </c>
+      <c r="W208">
+        <v>1.4</v>
+      </c>
+      <c r="X208">
+        <v>8</v>
+      </c>
+      <c r="Y208">
+        <v>1.08</v>
+      </c>
+      <c r="Z208">
+        <v>7.8</v>
+      </c>
+      <c r="AA208">
+        <v>4.2</v>
+      </c>
+      <c r="AB208">
+        <v>1.42</v>
+      </c>
+      <c r="AC208">
+        <v>0</v>
+      </c>
+      <c r="AD208">
+        <v>0</v>
+      </c>
+      <c r="AE208">
+        <v>2.47</v>
+      </c>
+      <c r="AF208">
+        <v>1.52</v>
+      </c>
+      <c r="AG208">
+        <v>1.94</v>
+      </c>
+      <c r="AH208">
+        <v>1.8</v>
+      </c>
+      <c r="AI208">
+        <v>2.2</v>
+      </c>
+      <c r="AJ208">
+        <v>1.62</v>
+      </c>
+      <c r="AK208">
+        <v>0</v>
+      </c>
+      <c r="AL208">
+        <v>0</v>
+      </c>
+      <c r="AM208">
+        <v>0</v>
+      </c>
+      <c r="AN208">
+        <v>0.75</v>
+      </c>
+      <c r="AO208">
+        <v>2.42</v>
+      </c>
+      <c r="AP208">
+        <v>0.92</v>
+      </c>
+      <c r="AQ208">
+        <v>2.23</v>
+      </c>
+      <c r="AR208">
+        <v>1.32</v>
+      </c>
+      <c r="AS208">
+        <v>1.69</v>
+      </c>
+      <c r="AT208">
+        <v>3.01</v>
+      </c>
+      <c r="AU208">
+        <v>5</v>
+      </c>
+      <c r="AV208">
+        <v>4</v>
+      </c>
+      <c r="AW208">
+        <v>4</v>
+      </c>
+      <c r="AX208">
+        <v>15</v>
+      </c>
+      <c r="AY208">
+        <v>9</v>
+      </c>
+      <c r="AZ208">
+        <v>19</v>
+      </c>
+      <c r="BA208">
+        <v>3</v>
+      </c>
+      <c r="BB208">
+        <v>7</v>
+      </c>
+      <c r="BC208">
+        <v>10</v>
+      </c>
+      <c r="BD208">
+        <v>0</v>
+      </c>
+      <c r="BE208">
+        <v>0</v>
+      </c>
+      <c r="BF208">
+        <v>0</v>
+      </c>
+      <c r="BG208">
+        <v>0</v>
+      </c>
+      <c r="BH208">
+        <v>0</v>
+      </c>
+      <c r="BI208">
+        <v>0</v>
+      </c>
+      <c r="BJ208">
+        <v>0</v>
+      </c>
+      <c r="BK208">
+        <v>0</v>
+      </c>
+      <c r="BL208">
+        <v>0</v>
+      </c>
+      <c r="BM208">
+        <v>0</v>
+      </c>
+      <c r="BN208">
+        <v>0</v>
+      </c>
+      <c r="BO208">
+        <v>0</v>
+      </c>
+      <c r="BP208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:68">
+      <c r="A209" s="1">
+        <v>208</v>
+      </c>
+      <c r="B209">
+        <v>7762801</v>
+      </c>
+      <c r="C209" t="s">
+        <v>68</v>
+      </c>
+      <c r="D209" t="s">
+        <v>69</v>
+      </c>
+      <c r="E209" s="2">
+        <v>45746.52083333334</v>
+      </c>
+      <c r="F209">
+        <v>26</v>
+      </c>
+      <c r="G209" t="s">
+        <v>79</v>
+      </c>
+      <c r="H209" t="s">
+        <v>82</v>
+      </c>
+      <c r="I209">
+        <v>0</v>
+      </c>
+      <c r="J209">
+        <v>0</v>
+      </c>
+      <c r="K209">
+        <v>0</v>
+      </c>
+      <c r="L209">
+        <v>1</v>
+      </c>
+      <c r="M209">
+        <v>1</v>
+      </c>
+      <c r="N209">
+        <v>2</v>
+      </c>
+      <c r="O209" t="s">
+        <v>184</v>
+      </c>
+      <c r="P209" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q209">
+        <v>2.1</v>
+      </c>
+      <c r="R209">
+        <v>2.25</v>
+      </c>
+      <c r="S209">
+        <v>6</v>
+      </c>
+      <c r="T209">
+        <v>1.4</v>
+      </c>
+      <c r="U209">
+        <v>2.75</v>
+      </c>
+      <c r="V209">
+        <v>2.75</v>
+      </c>
+      <c r="W209">
+        <v>1.4</v>
+      </c>
+      <c r="X209">
+        <v>8</v>
+      </c>
+      <c r="Y209">
+        <v>1.08</v>
+      </c>
+      <c r="Z209">
+        <v>1.5</v>
+      </c>
+      <c r="AA209">
+        <v>4.1</v>
+      </c>
+      <c r="AB209">
+        <v>6.3</v>
+      </c>
+      <c r="AC209">
+        <v>0</v>
+      </c>
+      <c r="AD209">
+        <v>0</v>
+      </c>
+      <c r="AE209">
+        <v>0</v>
+      </c>
+      <c r="AF209">
+        <v>0</v>
+      </c>
+      <c r="AG209">
+        <v>1.87</v>
+      </c>
+      <c r="AH209">
+        <v>1.87</v>
+      </c>
+      <c r="AI209">
+        <v>2</v>
+      </c>
+      <c r="AJ209">
+        <v>1.73</v>
+      </c>
+      <c r="AK209">
+        <v>0</v>
+      </c>
+      <c r="AL209">
+        <v>0</v>
+      </c>
+      <c r="AM209">
+        <v>0</v>
+      </c>
+      <c r="AN209">
+        <v>2.33</v>
+      </c>
+      <c r="AO209">
+        <v>1.75</v>
+      </c>
+      <c r="AP209">
+        <v>2.23</v>
+      </c>
+      <c r="AQ209">
+        <v>1.69</v>
+      </c>
+      <c r="AR209">
+        <v>2.05</v>
+      </c>
+      <c r="AS209">
+        <v>1.44</v>
+      </c>
+      <c r="AT209">
+        <v>3.49</v>
+      </c>
+      <c r="AU209">
+        <v>8</v>
+      </c>
+      <c r="AV209">
+        <v>3</v>
+      </c>
+      <c r="AW209">
+        <v>13</v>
+      </c>
+      <c r="AX209">
+        <v>2</v>
+      </c>
+      <c r="AY209">
+        <v>21</v>
+      </c>
+      <c r="AZ209">
+        <v>5</v>
+      </c>
+      <c r="BA209">
+        <v>9</v>
+      </c>
+      <c r="BB209">
+        <v>3</v>
+      </c>
+      <c r="BC209">
+        <v>12</v>
+      </c>
+      <c r="BD209">
+        <v>0</v>
+      </c>
+      <c r="BE209">
+        <v>0</v>
+      </c>
+      <c r="BF209">
+        <v>0</v>
+      </c>
+      <c r="BG209">
+        <v>0</v>
+      </c>
+      <c r="BH209">
+        <v>0</v>
+      </c>
+      <c r="BI209">
+        <v>0</v>
+      </c>
+      <c r="BJ209">
+        <v>0</v>
+      </c>
+      <c r="BK209">
+        <v>2.1</v>
+      </c>
+      <c r="BL209">
+        <v>0</v>
+      </c>
+      <c r="BM209">
+        <v>0</v>
+      </c>
+      <c r="BN209">
+        <v>0</v>
+      </c>
+      <c r="BO209">
+        <v>0</v>
+      </c>
+      <c r="BP209">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="305">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -927,6 +927,9 @@
   <si>
     <t>['31', '59', '68', '90+1']</t>
   </si>
+  <si>
+    <t>['36', '62', '78']</t>
+  </si>
 </sst>
 </file>
 
@@ -1287,7 +1290,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP209"/>
+  <dimension ref="A1:BP211"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3478,7 +3481,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ11">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4508,7 +4511,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ16">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR16">
         <v>2.14</v>
@@ -5123,7 +5126,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ19">
         <v>1.54</v>
@@ -6153,7 +6156,7 @@
         <v>2</v>
       </c>
       <c r="AP24">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ24">
         <v>1.23</v>
@@ -7186,7 +7189,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ29">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR29">
         <v>2.25</v>
@@ -7389,7 +7392,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ30">
         <v>1.23</v>
@@ -8628,7 +8631,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ36">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR36">
         <v>1.19</v>
@@ -9040,7 +9043,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ38">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR38">
         <v>0.86</v>
@@ -10685,7 +10688,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ46">
         <v>1.23</v>
@@ -11303,7 +11306,7 @@
         <v>2</v>
       </c>
       <c r="AP49">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ49">
         <v>1.85</v>
@@ -11512,7 +11515,7 @@
         <v>1</v>
       </c>
       <c r="AQ50">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR50">
         <v>1.44</v>
@@ -13981,7 +13984,7 @@
         <v>3</v>
       </c>
       <c r="AP62">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ62">
         <v>2.23</v>
@@ -14396,7 +14399,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ64">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR64">
         <v>0.92</v>
@@ -15011,7 +15014,7 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ67">
         <v>1.85</v>
@@ -15217,7 +15220,7 @@
         <v>1.33</v>
       </c>
       <c r="AP68">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ68">
         <v>1.85</v>
@@ -15426,7 +15429,7 @@
         <v>1</v>
       </c>
       <c r="AQ69">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR69">
         <v>1.44</v>
@@ -18101,7 +18104,7 @@
         <v>1.75</v>
       </c>
       <c r="AP82">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ82">
         <v>1.85</v>
@@ -18310,7 +18313,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ83">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR83">
         <v>1.8</v>
@@ -18722,7 +18725,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ85">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR85">
         <v>0.85</v>
@@ -18925,7 +18928,7 @@
         <v>1.25</v>
       </c>
       <c r="AP86">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ86">
         <v>1.08</v>
@@ -20985,7 +20988,7 @@
         <v>1.6</v>
       </c>
       <c r="AP96">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ96">
         <v>1.15</v>
@@ -21191,7 +21194,7 @@
         <v>1</v>
       </c>
       <c r="AP97">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ97">
         <v>1.08</v>
@@ -21400,7 +21403,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ98">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR98">
         <v>1.84</v>
@@ -21606,7 +21609,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ99">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR99">
         <v>1.34</v>
@@ -24490,7 +24493,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ113">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR113">
         <v>1.41</v>
@@ -24899,7 +24902,7 @@
         <v>1.33</v>
       </c>
       <c r="AP115">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ115">
         <v>1.15</v>
@@ -25314,7 +25317,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ117">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR117">
         <v>1.99</v>
@@ -25929,7 +25932,7 @@
         <v>3</v>
       </c>
       <c r="AP120">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ120">
         <v>2.23</v>
@@ -26135,7 +26138,7 @@
         <v>0.29</v>
       </c>
       <c r="AP121">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ121">
         <v>0.23</v>
@@ -26550,7 +26553,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ123">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR123">
         <v>1.29</v>
@@ -26962,7 +26965,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ125">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR125">
         <v>1.25</v>
@@ -27577,7 +27580,7 @@
         <v>0.86</v>
       </c>
       <c r="AP128">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ128">
         <v>0.85</v>
@@ -27783,7 +27786,7 @@
         <v>1.38</v>
       </c>
       <c r="AP129">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ129">
         <v>1.31</v>
@@ -29434,7 +29437,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ137">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR137">
         <v>1.54</v>
@@ -30052,7 +30055,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ140">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR140">
         <v>1.34</v>
@@ -30667,7 +30670,7 @@
         <v>0.25</v>
       </c>
       <c r="AP143">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ143">
         <v>0.23</v>
@@ -31700,7 +31703,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ148">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR148">
         <v>1.13</v>
@@ -32521,7 +32524,7 @@
         <v>0.44</v>
       </c>
       <c r="AP152">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ152">
         <v>0.77</v>
@@ -33142,7 +33145,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ155">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR155">
         <v>1.02</v>
@@ -33551,7 +33554,7 @@
         <v>1.22</v>
       </c>
       <c r="AP157">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ157">
         <v>1.54</v>
@@ -34993,7 +34996,7 @@
         <v>2.1</v>
       </c>
       <c r="AP164">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ164">
         <v>1.69</v>
@@ -35408,7 +35411,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ166">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR166">
         <v>1.31</v>
@@ -36023,7 +36026,7 @@
         <v>1.3</v>
       </c>
       <c r="AP169">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ169">
         <v>1.31</v>
@@ -36232,7 +36235,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ170">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR170">
         <v>1.7</v>
@@ -38086,7 +38089,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ179">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR179">
         <v>1.32</v>
@@ -38289,7 +38292,7 @@
         <v>1.55</v>
       </c>
       <c r="AP180">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ180">
         <v>1.54</v>
@@ -39113,7 +39116,7 @@
         <v>1.91</v>
       </c>
       <c r="AP184">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ184">
         <v>1.69</v>
@@ -39322,7 +39325,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ185">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR185">
         <v>1.72</v>
@@ -41173,7 +41176,7 @@
         <v>1.67</v>
       </c>
       <c r="AP194">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ194">
         <v>1.54</v>
@@ -41794,7 +41797,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ197">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR197">
         <v>1.84</v>
@@ -42203,10 +42206,10 @@
         <v>1.33</v>
       </c>
       <c r="AP199">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ199">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR199">
         <v>1.57</v>
@@ -44342,6 +44345,418 @@
       </c>
       <c r="BP209">
         <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:68">
+      <c r="A210" s="1">
+        <v>209</v>
+      </c>
+      <c r="B210">
+        <v>7762807</v>
+      </c>
+      <c r="C210" t="s">
+        <v>68</v>
+      </c>
+      <c r="D210" t="s">
+        <v>69</v>
+      </c>
+      <c r="E210" s="2">
+        <v>45748.42708333334</v>
+      </c>
+      <c r="F210">
+        <v>27</v>
+      </c>
+      <c r="G210" t="s">
+        <v>84</v>
+      </c>
+      <c r="H210" t="s">
+        <v>74</v>
+      </c>
+      <c r="I210">
+        <v>1</v>
+      </c>
+      <c r="J210">
+        <v>0</v>
+      </c>
+      <c r="K210">
+        <v>1</v>
+      </c>
+      <c r="L210">
+        <v>1</v>
+      </c>
+      <c r="M210">
+        <v>0</v>
+      </c>
+      <c r="N210">
+        <v>1</v>
+      </c>
+      <c r="O210" t="s">
+        <v>102</v>
+      </c>
+      <c r="P210" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q210">
+        <v>2.25</v>
+      </c>
+      <c r="R210">
+        <v>2.2</v>
+      </c>
+      <c r="S210">
+        <v>5.5</v>
+      </c>
+      <c r="T210">
+        <v>1.4</v>
+      </c>
+      <c r="U210">
+        <v>2.75</v>
+      </c>
+      <c r="V210">
+        <v>3</v>
+      </c>
+      <c r="W210">
+        <v>1.36</v>
+      </c>
+      <c r="X210">
+        <v>8</v>
+      </c>
+      <c r="Y210">
+        <v>1.08</v>
+      </c>
+      <c r="Z210">
+        <v>1.66</v>
+      </c>
+      <c r="AA210">
+        <v>3.69</v>
+      </c>
+      <c r="AB210">
+        <v>5.1</v>
+      </c>
+      <c r="AC210">
+        <v>1.06</v>
+      </c>
+      <c r="AD210">
+        <v>8.75</v>
+      </c>
+      <c r="AE210">
+        <v>1.3</v>
+      </c>
+      <c r="AF210">
+        <v>3.35</v>
+      </c>
+      <c r="AG210">
+        <v>2.03</v>
+      </c>
+      <c r="AH210">
+        <v>1.72</v>
+      </c>
+      <c r="AI210">
+        <v>1.91</v>
+      </c>
+      <c r="AJ210">
+        <v>1.8</v>
+      </c>
+      <c r="AK210">
+        <v>1.14</v>
+      </c>
+      <c r="AL210">
+        <v>1.25</v>
+      </c>
+      <c r="AM210">
+        <v>2.25</v>
+      </c>
+      <c r="AN210">
+        <v>1.77</v>
+      </c>
+      <c r="AO210">
+        <v>0.38</v>
+      </c>
+      <c r="AP210">
+        <v>1.86</v>
+      </c>
+      <c r="AQ210">
+        <v>0.36</v>
+      </c>
+      <c r="AR210">
+        <v>1.59</v>
+      </c>
+      <c r="AS210">
+        <v>1.02</v>
+      </c>
+      <c r="AT210">
+        <v>2.61</v>
+      </c>
+      <c r="AU210">
+        <v>4</v>
+      </c>
+      <c r="AV210">
+        <v>6</v>
+      </c>
+      <c r="AW210">
+        <v>5</v>
+      </c>
+      <c r="AX210">
+        <v>2</v>
+      </c>
+      <c r="AY210">
+        <v>9</v>
+      </c>
+      <c r="AZ210">
+        <v>8</v>
+      </c>
+      <c r="BA210">
+        <v>11</v>
+      </c>
+      <c r="BB210">
+        <v>6</v>
+      </c>
+      <c r="BC210">
+        <v>17</v>
+      </c>
+      <c r="BD210">
+        <v>1.45</v>
+      </c>
+      <c r="BE210">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF210">
+        <v>3.32</v>
+      </c>
+      <c r="BG210">
+        <v>1.29</v>
+      </c>
+      <c r="BH210">
+        <v>3.04</v>
+      </c>
+      <c r="BI210">
+        <v>1.56</v>
+      </c>
+      <c r="BJ210">
+        <v>2.21</v>
+      </c>
+      <c r="BK210">
+        <v>1.98</v>
+      </c>
+      <c r="BL210">
+        <v>1.74</v>
+      </c>
+      <c r="BM210">
+        <v>2.57</v>
+      </c>
+      <c r="BN210">
+        <v>1.42</v>
+      </c>
+      <c r="BO210">
+        <v>3.5</v>
+      </c>
+      <c r="BP210">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="211" spans="1:68">
+      <c r="A211" s="1">
+        <v>210</v>
+      </c>
+      <c r="B211">
+        <v>7762805</v>
+      </c>
+      <c r="C211" t="s">
+        <v>68</v>
+      </c>
+      <c r="D211" t="s">
+        <v>69</v>
+      </c>
+      <c r="E211" s="2">
+        <v>45748.53125</v>
+      </c>
+      <c r="F211">
+        <v>27</v>
+      </c>
+      <c r="G211" t="s">
+        <v>85</v>
+      </c>
+      <c r="H211" t="s">
+        <v>77</v>
+      </c>
+      <c r="I211">
+        <v>1</v>
+      </c>
+      <c r="J211">
+        <v>1</v>
+      </c>
+      <c r="K211">
+        <v>2</v>
+      </c>
+      <c r="L211">
+        <v>2</v>
+      </c>
+      <c r="M211">
+        <v>3</v>
+      </c>
+      <c r="N211">
+        <v>5</v>
+      </c>
+      <c r="O211" t="s">
+        <v>141</v>
+      </c>
+      <c r="P211" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q211">
+        <v>2.3</v>
+      </c>
+      <c r="R211">
+        <v>2.1</v>
+      </c>
+      <c r="S211">
+        <v>6</v>
+      </c>
+      <c r="T211">
+        <v>1.44</v>
+      </c>
+      <c r="U211">
+        <v>2.63</v>
+      </c>
+      <c r="V211">
+        <v>3.25</v>
+      </c>
+      <c r="W211">
+        <v>1.33</v>
+      </c>
+      <c r="X211">
+        <v>10</v>
+      </c>
+      <c r="Y211">
+        <v>1.06</v>
+      </c>
+      <c r="Z211">
+        <v>1.76</v>
+      </c>
+      <c r="AA211">
+        <v>3.58</v>
+      </c>
+      <c r="AB211">
+        <v>4.5</v>
+      </c>
+      <c r="AC211">
+        <v>1</v>
+      </c>
+      <c r="AD211">
+        <v>9.4</v>
+      </c>
+      <c r="AE211">
+        <v>1.36</v>
+      </c>
+      <c r="AF211">
+        <v>3</v>
+      </c>
+      <c r="AG211">
+        <v>2.05</v>
+      </c>
+      <c r="AH211">
+        <v>1.7</v>
+      </c>
+      <c r="AI211">
+        <v>2.1</v>
+      </c>
+      <c r="AJ211">
+        <v>1.67</v>
+      </c>
+      <c r="AK211">
+        <v>1.15</v>
+      </c>
+      <c r="AL211">
+        <v>1.27</v>
+      </c>
+      <c r="AM211">
+        <v>2.15</v>
+      </c>
+      <c r="AN211">
+        <v>2</v>
+      </c>
+      <c r="AO211">
+        <v>1.23</v>
+      </c>
+      <c r="AP211">
+        <v>1.86</v>
+      </c>
+      <c r="AQ211">
+        <v>1.36</v>
+      </c>
+      <c r="AR211">
+        <v>1.45</v>
+      </c>
+      <c r="AS211">
+        <v>1.14</v>
+      </c>
+      <c r="AT211">
+        <v>2.59</v>
+      </c>
+      <c r="AU211">
+        <v>5</v>
+      </c>
+      <c r="AV211">
+        <v>6</v>
+      </c>
+      <c r="AW211">
+        <v>4</v>
+      </c>
+      <c r="AX211">
+        <v>5</v>
+      </c>
+      <c r="AY211">
+        <v>9</v>
+      </c>
+      <c r="AZ211">
+        <v>11</v>
+      </c>
+      <c r="BA211">
+        <v>4</v>
+      </c>
+      <c r="BB211">
+        <v>3</v>
+      </c>
+      <c r="BC211">
+        <v>7</v>
+      </c>
+      <c r="BD211">
+        <v>1.36</v>
+      </c>
+      <c r="BE211">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF211">
+        <v>3.7</v>
+      </c>
+      <c r="BG211">
+        <v>1.25</v>
+      </c>
+      <c r="BH211">
+        <v>3.45</v>
+      </c>
+      <c r="BI211">
+        <v>1.3</v>
+      </c>
+      <c r="BJ211">
+        <v>2.97</v>
+      </c>
+      <c r="BK211">
+        <v>1.55</v>
+      </c>
+      <c r="BL211">
+        <v>2.23</v>
+      </c>
+      <c r="BM211">
+        <v>1.94</v>
+      </c>
+      <c r="BN211">
+        <v>1.77</v>
+      </c>
+      <c r="BO211">
+        <v>2.48</v>
+      </c>
+      <c r="BP211">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="306">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -644,6 +644,9 @@
   </si>
   <si>
     <t>['12']</t>
+  </si>
+  <si>
+    <t>['22', '39', '41', '48']</t>
   </si>
   <si>
     <t>['12', '22', '45+1', '45+4', '90+1', '90+8']</t>
@@ -1290,7 +1293,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP211"/>
+  <dimension ref="A1:BP214"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2164,7 +2167,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q5">
         <v>7.5</v>
@@ -2370,7 +2373,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2782,7 +2785,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q8">
         <v>4</v>
@@ -3069,7 +3072,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ9">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3272,7 +3275,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ10">
         <v>0.85</v>
@@ -3684,7 +3687,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ12">
         <v>0.23</v>
@@ -3812,7 +3815,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4018,7 +4021,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q14">
         <v>2.4</v>
@@ -4096,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ14">
         <v>1.15</v>
@@ -4305,7 +4308,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ15">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4842,7 +4845,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -5254,7 +5257,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -5460,7 +5463,7 @@
         <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5541,7 +5544,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ21">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR21">
         <v>0.9</v>
@@ -5666,7 +5669,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5872,7 +5875,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -5953,7 +5956,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ23">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR23">
         <v>0.91</v>
@@ -6078,7 +6081,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q24">
         <v>3.25</v>
@@ -6284,7 +6287,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q25">
         <v>2.05</v>
@@ -6362,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ25">
         <v>0.23</v>
@@ -6490,7 +6493,7 @@
         <v>86</v>
       </c>
       <c r="P26" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6983,7 +6986,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ28">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR28">
         <v>0.91</v>
@@ -7108,7 +7111,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7520,7 +7523,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7601,7 +7604,7 @@
         <v>1</v>
       </c>
       <c r="AQ31">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR31">
         <v>1.36</v>
@@ -7726,7 +7729,7 @@
         <v>86</v>
       </c>
       <c r="P32" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q32">
         <v>2.05</v>
@@ -7804,7 +7807,7 @@
         <v>0.5</v>
       </c>
       <c r="AP32">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ32">
         <v>0.77</v>
@@ -8756,7 +8759,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -8837,7 +8840,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ37">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR37">
         <v>1.15</v>
@@ -9452,7 +9455,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ40">
         <v>1.54</v>
@@ -9658,7 +9661,7 @@
         <v>1.33</v>
       </c>
       <c r="AP41">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ41">
         <v>1.23</v>
@@ -9992,7 +9995,7 @@
         <v>86</v>
       </c>
       <c r="P43" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q43">
         <v>7.5</v>
@@ -10198,7 +10201,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10610,7 +10613,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q46">
         <v>2.5</v>
@@ -10816,7 +10819,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q47">
         <v>4.33</v>
@@ -11100,7 +11103,7 @@
         <v>3</v>
       </c>
       <c r="AP48">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ48">
         <v>1.69</v>
@@ -11640,7 +11643,7 @@
         <v>116</v>
       </c>
       <c r="P51" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11721,7 +11724,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ51">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR51">
         <v>1.13</v>
@@ -11846,7 +11849,7 @@
         <v>118</v>
       </c>
       <c r="P52" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q52">
         <v>5.5</v>
@@ -11927,7 +11930,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ52">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR52">
         <v>0.93</v>
@@ -12133,7 +12136,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ53">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR53">
         <v>1.4</v>
@@ -12258,7 +12261,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -12670,7 +12673,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q56">
         <v>5.5</v>
@@ -12876,7 +12879,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q57">
         <v>5</v>
@@ -13082,7 +13085,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13288,7 +13291,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13494,7 +13497,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13700,7 +13703,7 @@
         <v>86</v>
       </c>
       <c r="P61" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q61">
         <v>6.5</v>
@@ -14112,7 +14115,7 @@
         <v>86</v>
       </c>
       <c r="P63" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q63">
         <v>3.5</v>
@@ -14318,7 +14321,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14602,10 +14605,10 @@
         <v>2.25</v>
       </c>
       <c r="AP65">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ65">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR65">
         <v>1.93</v>
@@ -14811,7 +14814,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ66">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR66">
         <v>1.61</v>
@@ -14936,7 +14939,7 @@
         <v>86</v>
       </c>
       <c r="P67" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q67">
         <v>6.5</v>
@@ -15142,7 +15145,7 @@
         <v>86</v>
       </c>
       <c r="P68" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q68">
         <v>4.75</v>
@@ -15223,7 +15226,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ68">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR68">
         <v>1.26</v>
@@ -15632,7 +15635,7 @@
         <v>3</v>
       </c>
       <c r="AP70">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ70">
         <v>1.69</v>
@@ -15760,7 +15763,7 @@
         <v>92</v>
       </c>
       <c r="P71" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q71">
         <v>9.5</v>
@@ -16378,7 +16381,7 @@
         <v>86</v>
       </c>
       <c r="P74" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16996,7 +16999,7 @@
         <v>130</v>
       </c>
       <c r="P77" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q77">
         <v>1.83</v>
@@ -17202,7 +17205,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q78">
         <v>12</v>
@@ -17408,7 +17411,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q79">
         <v>3.75</v>
@@ -17614,7 +17617,7 @@
         <v>131</v>
       </c>
       <c r="P80" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17820,7 +17823,7 @@
         <v>132</v>
       </c>
       <c r="P81" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -17898,10 +17901,10 @@
         <v>1.8</v>
       </c>
       <c r="AP81">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ81">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR81">
         <v>1.3</v>
@@ -18107,7 +18110,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ82">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR82">
         <v>1.21</v>
@@ -18232,7 +18235,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q83">
         <v>1.67</v>
@@ -18310,7 +18313,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ83">
         <v>1.36</v>
@@ -18516,7 +18519,7 @@
         <v>2.17</v>
       </c>
       <c r="AP84">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ84">
         <v>1.85</v>
@@ -18850,7 +18853,7 @@
         <v>134</v>
       </c>
       <c r="P86" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q86">
         <v>2.63</v>
@@ -18931,7 +18934,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ86">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR86">
         <v>1.23</v>
@@ -20164,7 +20167,7 @@
         <v>0.67</v>
       </c>
       <c r="AP92">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ92">
         <v>0.77</v>
@@ -20498,7 +20501,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q94">
         <v>13</v>
@@ -20704,7 +20707,7 @@
         <v>139</v>
       </c>
       <c r="P95" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -21116,7 +21119,7 @@
         <v>140</v>
       </c>
       <c r="P97" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q97">
         <v>2.4</v>
@@ -21197,7 +21200,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ97">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR97">
         <v>1.31</v>
@@ -21400,7 +21403,7 @@
         <v>0.8</v>
       </c>
       <c r="AP98">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ98">
         <v>0.36</v>
@@ -21606,7 +21609,7 @@
         <v>1.2</v>
       </c>
       <c r="AP99">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ99">
         <v>1.36</v>
@@ -21812,10 +21815,10 @@
         <v>1.4</v>
       </c>
       <c r="AP100">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ100">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR100">
         <v>1.22</v>
@@ -21940,7 +21943,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22021,7 +22024,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ101">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR101">
         <v>1.85</v>
@@ -22558,7 +22561,7 @@
         <v>145</v>
       </c>
       <c r="P104" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22764,7 +22767,7 @@
         <v>86</v>
       </c>
       <c r="P105" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -22970,7 +22973,7 @@
         <v>146</v>
       </c>
       <c r="P106" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q106">
         <v>6</v>
@@ -23382,7 +23385,7 @@
         <v>147</v>
       </c>
       <c r="P108" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23463,7 +23466,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ108">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR108">
         <v>1.48</v>
@@ -23794,7 +23797,7 @@
         <v>149</v>
       </c>
       <c r="P110" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -24206,7 +24209,7 @@
         <v>143</v>
       </c>
       <c r="P112" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q112">
         <v>4.75</v>
@@ -24490,7 +24493,7 @@
         <v>0.67</v>
       </c>
       <c r="AP113">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ113">
         <v>0.36</v>
@@ -24696,10 +24699,10 @@
         <v>0.83</v>
       </c>
       <c r="AP114">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ114">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR114">
         <v>1.09</v>
@@ -25030,7 +25033,7 @@
         <v>86</v>
       </c>
       <c r="P116" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q116">
         <v>4.5</v>
@@ -25111,7 +25114,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ116">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR116">
         <v>1.24</v>
@@ -25236,7 +25239,7 @@
         <v>153</v>
       </c>
       <c r="P117" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q117">
         <v>1.53</v>
@@ -25442,7 +25445,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25648,7 +25651,7 @@
         <v>154</v>
       </c>
       <c r="P119" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q119">
         <v>1.8</v>
@@ -25726,7 +25729,7 @@
         <v>0.83</v>
       </c>
       <c r="AP119">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ119">
         <v>0.85</v>
@@ -25854,7 +25857,7 @@
         <v>155</v>
       </c>
       <c r="P120" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q120">
         <v>7.5</v>
@@ -26266,7 +26269,7 @@
         <v>157</v>
       </c>
       <c r="P122" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q122">
         <v>2.63</v>
@@ -26344,7 +26347,7 @@
         <v>1.14</v>
       </c>
       <c r="AP122">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ122">
         <v>1.15</v>
@@ -26550,7 +26553,7 @@
         <v>0.57</v>
       </c>
       <c r="AP123">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ123">
         <v>0.36</v>
@@ -26759,7 +26762,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ124">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR124">
         <v>2.17</v>
@@ -27090,7 +27093,7 @@
         <v>86</v>
       </c>
       <c r="P126" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27171,7 +27174,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ126">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR126">
         <v>1.5</v>
@@ -27296,7 +27299,7 @@
         <v>161</v>
       </c>
       <c r="P127" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27374,7 +27377,7 @@
         <v>3</v>
       </c>
       <c r="AP127">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ127">
         <v>2.23</v>
@@ -27502,7 +27505,7 @@
         <v>86</v>
       </c>
       <c r="P128" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q128">
         <v>2.4</v>
@@ -27708,7 +27711,7 @@
         <v>138</v>
       </c>
       <c r="P129" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27914,7 +27917,7 @@
         <v>98</v>
       </c>
       <c r="P130" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q130">
         <v>6.5</v>
@@ -27995,7 +27998,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ130">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR130">
         <v>1.03</v>
@@ -28120,7 +28123,7 @@
         <v>162</v>
       </c>
       <c r="P131" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q131">
         <v>4.33</v>
@@ -28201,7 +28204,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ131">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR131">
         <v>1.16</v>
@@ -28326,7 +28329,7 @@
         <v>86</v>
       </c>
       <c r="P132" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q132">
         <v>8</v>
@@ -29643,7 +29646,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ138">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR138">
         <v>1.67</v>
@@ -29846,7 +29849,7 @@
         <v>1.75</v>
       </c>
       <c r="AP139">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ139">
         <v>1.23</v>
@@ -29974,7 +29977,7 @@
         <v>167</v>
       </c>
       <c r="P140" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q140">
         <v>2.3</v>
@@ -30180,7 +30183,7 @@
         <v>86</v>
       </c>
       <c r="P141" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q141">
         <v>7.5</v>
@@ -30258,7 +30261,7 @@
         <v>2.71</v>
       </c>
       <c r="AP141">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ141">
         <v>2.23</v>
@@ -30386,7 +30389,7 @@
         <v>168</v>
       </c>
       <c r="P142" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30592,7 +30595,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30876,7 +30879,7 @@
         <v>1.13</v>
       </c>
       <c r="AP144">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ144">
         <v>0.85</v>
@@ -31004,7 +31007,7 @@
         <v>171</v>
       </c>
       <c r="P145" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q145">
         <v>3.75</v>
@@ -31085,7 +31088,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ145">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR145">
         <v>1.27</v>
@@ -31210,7 +31213,7 @@
         <v>172</v>
       </c>
       <c r="P146" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q146">
         <v>7.5</v>
@@ -31291,7 +31294,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ146">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR146">
         <v>1.29</v>
@@ -31416,7 +31419,7 @@
         <v>173</v>
       </c>
       <c r="P147" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31494,7 +31497,7 @@
         <v>1.33</v>
       </c>
       <c r="AP147">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ147">
         <v>1.31</v>
@@ -31622,7 +31625,7 @@
         <v>174</v>
       </c>
       <c r="P148" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q148">
         <v>2.75</v>
@@ -31828,7 +31831,7 @@
         <v>86</v>
       </c>
       <c r="P149" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q149">
         <v>7.5</v>
@@ -32240,7 +32243,7 @@
         <v>86</v>
       </c>
       <c r="P151" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q151">
         <v>6.5</v>
@@ -32446,7 +32449,7 @@
         <v>176</v>
       </c>
       <c r="P152" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q152">
         <v>2.75</v>
@@ -32652,7 +32655,7 @@
         <v>177</v>
       </c>
       <c r="P153" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q153">
         <v>4.75</v>
@@ -32730,7 +32733,7 @@
         <v>2.75</v>
       </c>
       <c r="AP153">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ153">
         <v>2.23</v>
@@ -32936,7 +32939,7 @@
         <v>1.56</v>
       </c>
       <c r="AP154">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ154">
         <v>1.23</v>
@@ -33064,7 +33067,7 @@
         <v>179</v>
       </c>
       <c r="P155" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33270,7 +33273,7 @@
         <v>176</v>
       </c>
       <c r="P156" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q156">
         <v>2.2</v>
@@ -33682,7 +33685,7 @@
         <v>181</v>
       </c>
       <c r="P158" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33763,7 +33766,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ158">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR158">
         <v>1.62</v>
@@ -33966,7 +33969,7 @@
         <v>0.22</v>
       </c>
       <c r="AP159">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ159">
         <v>0.23</v>
@@ -34506,7 +34509,7 @@
         <v>86</v>
       </c>
       <c r="P162" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q162">
         <v>3.5</v>
@@ -34587,7 +34590,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ162">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR162">
         <v>1.31</v>
@@ -34712,7 +34715,7 @@
         <v>184</v>
       </c>
       <c r="P163" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -34793,7 +34796,7 @@
         <v>1</v>
       </c>
       <c r="AQ163">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR163">
         <v>1.34</v>
@@ -35124,7 +35127,7 @@
         <v>185</v>
       </c>
       <c r="P165" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q165">
         <v>9.5</v>
@@ -35617,7 +35620,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ167">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR167">
         <v>1.7</v>
@@ -35820,7 +35823,7 @@
         <v>1.2</v>
       </c>
       <c r="AP168">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ168">
         <v>1.23</v>
@@ -36850,7 +36853,7 @@
         <v>0.7</v>
       </c>
       <c r="AP173">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ173">
         <v>0.77</v>
@@ -36978,7 +36981,7 @@
         <v>86</v>
       </c>
       <c r="P174" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q174">
         <v>3.75</v>
@@ -37056,7 +37059,7 @@
         <v>1.1</v>
       </c>
       <c r="AP174">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ174">
         <v>1.54</v>
@@ -37184,7 +37187,7 @@
         <v>124</v>
       </c>
       <c r="P175" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q175">
         <v>5.5</v>
@@ -37390,7 +37393,7 @@
         <v>86</v>
       </c>
       <c r="P176" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q176">
         <v>3.1</v>
@@ -37802,7 +37805,7 @@
         <v>86</v>
       </c>
       <c r="P178" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q178">
         <v>3.5</v>
@@ -37883,7 +37886,7 @@
         <v>1</v>
       </c>
       <c r="AQ178">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR178">
         <v>1.28</v>
@@ -38214,7 +38217,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38295,7 +38298,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ180">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR180">
         <v>1.56</v>
@@ -38420,7 +38423,7 @@
         <v>194</v>
       </c>
       <c r="P181" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q181">
         <v>3.2</v>
@@ -38498,7 +38501,7 @@
         <v>2</v>
       </c>
       <c r="AP181">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ181">
         <v>1.85</v>
@@ -38626,7 +38629,7 @@
         <v>86</v>
       </c>
       <c r="P182" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q182">
         <v>8.5</v>
@@ -38707,7 +38710,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ182">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR182">
         <v>1.01</v>
@@ -38910,7 +38913,7 @@
         <v>1.27</v>
       </c>
       <c r="AP183">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ183">
         <v>1.31</v>
@@ -39038,7 +39041,7 @@
         <v>195</v>
       </c>
       <c r="P184" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q184">
         <v>3.6</v>
@@ -39656,7 +39659,7 @@
         <v>196</v>
       </c>
       <c r="P187" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -39862,7 +39865,7 @@
         <v>86</v>
       </c>
       <c r="P188" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q188">
         <v>6</v>
@@ -40068,7 +40071,7 @@
         <v>192</v>
       </c>
       <c r="P189" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q189">
         <v>2.3</v>
@@ -40352,7 +40355,7 @@
         <v>1.09</v>
       </c>
       <c r="AP190">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ190">
         <v>1.23</v>
@@ -40480,7 +40483,7 @@
         <v>197</v>
       </c>
       <c r="P191" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
@@ -40686,7 +40689,7 @@
         <v>198</v>
       </c>
       <c r="P192" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q192">
         <v>8.5</v>
@@ -41098,7 +41101,7 @@
         <v>200</v>
       </c>
       <c r="P194" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q194">
         <v>2.75</v>
@@ -41179,7 +41182,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ194">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR194">
         <v>1.45</v>
@@ -41510,7 +41513,7 @@
         <v>201</v>
       </c>
       <c r="P196" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q196">
         <v>4.5</v>
@@ -41591,7 +41594,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ196">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR196">
         <v>0.97</v>
@@ -41922,7 +41925,7 @@
         <v>203</v>
       </c>
       <c r="P198" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q198">
         <v>2.5</v>
@@ -42000,10 +42003,10 @@
         <v>1.92</v>
       </c>
       <c r="AP198">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ198">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR198">
         <v>2.05</v>
@@ -42128,7 +42131,7 @@
         <v>204</v>
       </c>
       <c r="P199" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q199">
         <v>2.4</v>
@@ -42334,7 +42337,7 @@
         <v>86</v>
       </c>
       <c r="P200" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q200">
         <v>2.25</v>
@@ -42412,7 +42415,7 @@
         <v>1.17</v>
       </c>
       <c r="AP200">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ200">
         <v>1.31</v>
@@ -42540,7 +42543,7 @@
         <v>198</v>
       </c>
       <c r="P201" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q201">
         <v>4.33</v>
@@ -42618,7 +42621,7 @@
         <v>1.92</v>
       </c>
       <c r="AP201">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ201">
         <v>1.85</v>
@@ -43158,7 +43161,7 @@
         <v>207</v>
       </c>
       <c r="P204" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q204">
         <v>2.25</v>
@@ -43570,7 +43573,7 @@
         <v>86</v>
       </c>
       <c r="P206" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q206">
         <v>8.5</v>
@@ -43776,7 +43779,7 @@
         <v>208</v>
       </c>
       <c r="P207" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q207">
         <v>4</v>
@@ -44600,7 +44603,7 @@
         <v>141</v>
       </c>
       <c r="P211" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q211">
         <v>2.3</v>
@@ -44757,6 +44760,624 @@
       </c>
       <c r="BP211">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="212" spans="1:68">
+      <c r="A212" s="1">
+        <v>211</v>
+      </c>
+      <c r="B212">
+        <v>7762804</v>
+      </c>
+      <c r="C212" t="s">
+        <v>68</v>
+      </c>
+      <c r="D212" t="s">
+        <v>69</v>
+      </c>
+      <c r="E212" s="2">
+        <v>45749.34375</v>
+      </c>
+      <c r="F212">
+        <v>27</v>
+      </c>
+      <c r="G212" t="s">
+        <v>78</v>
+      </c>
+      <c r="H212" t="s">
+        <v>70</v>
+      </c>
+      <c r="I212">
+        <v>3</v>
+      </c>
+      <c r="J212">
+        <v>0</v>
+      </c>
+      <c r="K212">
+        <v>3</v>
+      </c>
+      <c r="L212">
+        <v>4</v>
+      </c>
+      <c r="M212">
+        <v>0</v>
+      </c>
+      <c r="N212">
+        <v>4</v>
+      </c>
+      <c r="O212" t="s">
+        <v>210</v>
+      </c>
+      <c r="P212" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q212">
+        <v>3.75</v>
+      </c>
+      <c r="R212">
+        <v>1.91</v>
+      </c>
+      <c r="S212">
+        <v>3.4</v>
+      </c>
+      <c r="T212">
+        <v>1.57</v>
+      </c>
+      <c r="U212">
+        <v>2.25</v>
+      </c>
+      <c r="V212">
+        <v>3.75</v>
+      </c>
+      <c r="W212">
+        <v>1.25</v>
+      </c>
+      <c r="X212">
+        <v>13</v>
+      </c>
+      <c r="Y212">
+        <v>1.04</v>
+      </c>
+      <c r="Z212">
+        <v>2.81</v>
+      </c>
+      <c r="AA212">
+        <v>3.04</v>
+      </c>
+      <c r="AB212">
+        <v>2.6</v>
+      </c>
+      <c r="AC212">
+        <v>1.05</v>
+      </c>
+      <c r="AD212">
+        <v>6.4</v>
+      </c>
+      <c r="AE212">
+        <v>1.57</v>
+      </c>
+      <c r="AF212">
+        <v>2.25</v>
+      </c>
+      <c r="AG212">
+        <v>2.3</v>
+      </c>
+      <c r="AH212">
+        <v>1.5</v>
+      </c>
+      <c r="AI212">
+        <v>2.1</v>
+      </c>
+      <c r="AJ212">
+        <v>1.67</v>
+      </c>
+      <c r="AK212">
+        <v>1.49</v>
+      </c>
+      <c r="AL212">
+        <v>1.39</v>
+      </c>
+      <c r="AM212">
+        <v>1.37</v>
+      </c>
+      <c r="AN212">
+        <v>2.15</v>
+      </c>
+      <c r="AO212">
+        <v>1.85</v>
+      </c>
+      <c r="AP212">
+        <v>2.21</v>
+      </c>
+      <c r="AQ212">
+        <v>1.71</v>
+      </c>
+      <c r="AR212">
+        <v>1.44</v>
+      </c>
+      <c r="AS212">
+        <v>1.42</v>
+      </c>
+      <c r="AT212">
+        <v>2.86</v>
+      </c>
+      <c r="AU212">
+        <v>9</v>
+      </c>
+      <c r="AV212">
+        <v>5</v>
+      </c>
+      <c r="AW212">
+        <v>2</v>
+      </c>
+      <c r="AX212">
+        <v>4</v>
+      </c>
+      <c r="AY212">
+        <v>11</v>
+      </c>
+      <c r="AZ212">
+        <v>9</v>
+      </c>
+      <c r="BA212">
+        <v>2</v>
+      </c>
+      <c r="BB212">
+        <v>2</v>
+      </c>
+      <c r="BC212">
+        <v>4</v>
+      </c>
+      <c r="BD212">
+        <v>2.05</v>
+      </c>
+      <c r="BE212">
+        <v>6.25</v>
+      </c>
+      <c r="BF212">
+        <v>1.98</v>
+      </c>
+      <c r="BG212">
+        <v>1.52</v>
+      </c>
+      <c r="BH212">
+        <v>2.33</v>
+      </c>
+      <c r="BI212">
+        <v>1.86</v>
+      </c>
+      <c r="BJ212">
+        <v>1.82</v>
+      </c>
+      <c r="BK212">
+        <v>2.38</v>
+      </c>
+      <c r="BL212">
+        <v>1.5</v>
+      </c>
+      <c r="BM212">
+        <v>3.15</v>
+      </c>
+      <c r="BN212">
+        <v>1.3</v>
+      </c>
+      <c r="BO212">
+        <v>4.1</v>
+      </c>
+      <c r="BP212">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="213" spans="1:68">
+      <c r="A213" s="1">
+        <v>212</v>
+      </c>
+      <c r="B213">
+        <v>7762803</v>
+      </c>
+      <c r="C213" t="s">
+        <v>68</v>
+      </c>
+      <c r="D213" t="s">
+        <v>69</v>
+      </c>
+      <c r="E213" s="2">
+        <v>45749.44791666666</v>
+      </c>
+      <c r="F213">
+        <v>27</v>
+      </c>
+      <c r="G213" t="s">
+        <v>82</v>
+      </c>
+      <c r="H213" t="s">
+        <v>83</v>
+      </c>
+      <c r="I213">
+        <v>0</v>
+      </c>
+      <c r="J213">
+        <v>0</v>
+      </c>
+      <c r="K213">
+        <v>0</v>
+      </c>
+      <c r="L213">
+        <v>0</v>
+      </c>
+      <c r="M213">
+        <v>0</v>
+      </c>
+      <c r="N213">
+        <v>0</v>
+      </c>
+      <c r="O213" t="s">
+        <v>86</v>
+      </c>
+      <c r="P213" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q213">
+        <v>2.38</v>
+      </c>
+      <c r="R213">
+        <v>2.1</v>
+      </c>
+      <c r="S213">
+        <v>5.5</v>
+      </c>
+      <c r="T213">
+        <v>1.44</v>
+      </c>
+      <c r="U213">
+        <v>2.63</v>
+      </c>
+      <c r="V213">
+        <v>3.25</v>
+      </c>
+      <c r="W213">
+        <v>1.33</v>
+      </c>
+      <c r="X213">
+        <v>10</v>
+      </c>
+      <c r="Y213">
+        <v>1.06</v>
+      </c>
+      <c r="Z213">
+        <v>1.84</v>
+      </c>
+      <c r="AA213">
+        <v>3.5</v>
+      </c>
+      <c r="AB213">
+        <v>4.2</v>
+      </c>
+      <c r="AC213">
+        <v>1.02</v>
+      </c>
+      <c r="AD213">
+        <v>7.7</v>
+      </c>
+      <c r="AE213">
+        <v>1.33</v>
+      </c>
+      <c r="AF213">
+        <v>2.84</v>
+      </c>
+      <c r="AG213">
+        <v>2.2</v>
+      </c>
+      <c r="AH213">
+        <v>1.57</v>
+      </c>
+      <c r="AI213">
+        <v>2.1</v>
+      </c>
+      <c r="AJ213">
+        <v>1.67</v>
+      </c>
+      <c r="AK213">
+        <v>1.15</v>
+      </c>
+      <c r="AL213">
+        <v>1.26</v>
+      </c>
+      <c r="AM213">
+        <v>2.2</v>
+      </c>
+      <c r="AN213">
+        <v>1.62</v>
+      </c>
+      <c r="AO213">
+        <v>1.54</v>
+      </c>
+      <c r="AP213">
+        <v>1.57</v>
+      </c>
+      <c r="AQ213">
+        <v>1.5</v>
+      </c>
+      <c r="AR213">
+        <v>1.54</v>
+      </c>
+      <c r="AS213">
+        <v>1.18</v>
+      </c>
+      <c r="AT213">
+        <v>2.72</v>
+      </c>
+      <c r="AU213">
+        <v>9</v>
+      </c>
+      <c r="AV213">
+        <v>3</v>
+      </c>
+      <c r="AW213">
+        <v>12</v>
+      </c>
+      <c r="AX213">
+        <v>6</v>
+      </c>
+      <c r="AY213">
+        <v>21</v>
+      </c>
+      <c r="AZ213">
+        <v>9</v>
+      </c>
+      <c r="BA213">
+        <v>10</v>
+      </c>
+      <c r="BB213">
+        <v>4</v>
+      </c>
+      <c r="BC213">
+        <v>14</v>
+      </c>
+      <c r="BD213">
+        <v>1.48</v>
+      </c>
+      <c r="BE213">
+        <v>6.75</v>
+      </c>
+      <c r="BF213">
+        <v>2.9</v>
+      </c>
+      <c r="BG213">
+        <v>1.36</v>
+      </c>
+      <c r="BH213">
+        <v>2.8</v>
+      </c>
+      <c r="BI213">
+        <v>1.6</v>
+      </c>
+      <c r="BJ213">
+        <v>2.17</v>
+      </c>
+      <c r="BK213">
+        <v>1.98</v>
+      </c>
+      <c r="BL213">
+        <v>1.72</v>
+      </c>
+      <c r="BM213">
+        <v>2.55</v>
+      </c>
+      <c r="BN213">
+        <v>1.45</v>
+      </c>
+      <c r="BO213">
+        <v>3.3</v>
+      </c>
+      <c r="BP213">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="214" spans="1:68">
+      <c r="A214" s="1">
+        <v>213</v>
+      </c>
+      <c r="B214">
+        <v>7762806</v>
+      </c>
+      <c r="C214" t="s">
+        <v>68</v>
+      </c>
+      <c r="D214" t="s">
+        <v>69</v>
+      </c>
+      <c r="E214" s="2">
+        <v>45749.55208333334</v>
+      </c>
+      <c r="F214">
+        <v>27</v>
+      </c>
+      <c r="G214" t="s">
+        <v>80</v>
+      </c>
+      <c r="H214" t="s">
+        <v>73</v>
+      </c>
+      <c r="I214">
+        <v>1</v>
+      </c>
+      <c r="J214">
+        <v>0</v>
+      </c>
+      <c r="K214">
+        <v>1</v>
+      </c>
+      <c r="L214">
+        <v>1</v>
+      </c>
+      <c r="M214">
+        <v>0</v>
+      </c>
+      <c r="N214">
+        <v>1</v>
+      </c>
+      <c r="O214" t="s">
+        <v>208</v>
+      </c>
+      <c r="P214" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q214">
+        <v>1.83</v>
+      </c>
+      <c r="R214">
+        <v>2.38</v>
+      </c>
+      <c r="S214">
+        <v>9</v>
+      </c>
+      <c r="T214">
+        <v>1.36</v>
+      </c>
+      <c r="U214">
+        <v>3</v>
+      </c>
+      <c r="V214">
+        <v>2.75</v>
+      </c>
+      <c r="W214">
+        <v>1.4</v>
+      </c>
+      <c r="X214">
+        <v>7</v>
+      </c>
+      <c r="Y214">
+        <v>1.1</v>
+      </c>
+      <c r="Z214">
+        <v>1.36</v>
+      </c>
+      <c r="AA214">
+        <v>4.8</v>
+      </c>
+      <c r="AB214">
+        <v>8.1</v>
+      </c>
+      <c r="AC214">
+        <v>1</v>
+      </c>
+      <c r="AD214">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE214">
+        <v>1.24</v>
+      </c>
+      <c r="AF214">
+        <v>3.36</v>
+      </c>
+      <c r="AG214">
+        <v>1.8</v>
+      </c>
+      <c r="AH214">
+        <v>1.94</v>
+      </c>
+      <c r="AI214">
+        <v>2.25</v>
+      </c>
+      <c r="AJ214">
+        <v>1.57</v>
+      </c>
+      <c r="AK214">
+        <v>1.06</v>
+      </c>
+      <c r="AL214">
+        <v>1.17</v>
+      </c>
+      <c r="AM214">
+        <v>3.2</v>
+      </c>
+      <c r="AN214">
+        <v>1.54</v>
+      </c>
+      <c r="AO214">
+        <v>1.08</v>
+      </c>
+      <c r="AP214">
+        <v>1.64</v>
+      </c>
+      <c r="AQ214">
+        <v>1</v>
+      </c>
+      <c r="AR214">
+        <v>2</v>
+      </c>
+      <c r="AS214">
+        <v>1.32</v>
+      </c>
+      <c r="AT214">
+        <v>3.32</v>
+      </c>
+      <c r="AU214">
+        <v>4</v>
+      </c>
+      <c r="AV214">
+        <v>0</v>
+      </c>
+      <c r="AW214">
+        <v>8</v>
+      </c>
+      <c r="AX214">
+        <v>0</v>
+      </c>
+      <c r="AY214">
+        <v>12</v>
+      </c>
+      <c r="AZ214">
+        <v>0</v>
+      </c>
+      <c r="BA214">
+        <v>7</v>
+      </c>
+      <c r="BB214">
+        <v>2</v>
+      </c>
+      <c r="BC214">
+        <v>9</v>
+      </c>
+      <c r="BD214">
+        <v>1.25</v>
+      </c>
+      <c r="BE214">
+        <v>8</v>
+      </c>
+      <c r="BF214">
+        <v>4.3</v>
+      </c>
+      <c r="BG214">
+        <v>1.3</v>
+      </c>
+      <c r="BH214">
+        <v>3.05</v>
+      </c>
+      <c r="BI214">
+        <v>1.53</v>
+      </c>
+      <c r="BJ214">
+        <v>2.32</v>
+      </c>
+      <c r="BK214">
+        <v>1.85</v>
+      </c>
+      <c r="BL214">
+        <v>1.83</v>
+      </c>
+      <c r="BM214">
+        <v>2.3</v>
+      </c>
+      <c r="BN214">
+        <v>1.53</v>
+      </c>
+      <c r="BO214">
+        <v>2.9</v>
+      </c>
+      <c r="BP214">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="308">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -647,6 +647,12 @@
   </si>
   <si>
     <t>['22', '39', '41', '48']</t>
+  </si>
+  <si>
+    <t>['22', '51', '82']</t>
+  </si>
+  <si>
+    <t>['9', '23']</t>
   </si>
   <si>
     <t>['12', '22', '45+1', '45+4', '90+1', '90+8']</t>
@@ -1293,7 +1299,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP214"/>
+  <dimension ref="A1:BP217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1630,7 +1636,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ2">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2167,7 +2173,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q5">
         <v>7.5</v>
@@ -2373,7 +2379,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2657,7 +2663,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ7">
         <v>1.54</v>
@@ -2785,7 +2791,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q8">
         <v>4</v>
@@ -2863,7 +2869,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ8">
         <v>1.23</v>
@@ -3278,7 +3284,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ10">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3481,7 +3487,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ11">
         <v>0.36</v>
@@ -3815,7 +3821,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4021,7 +4027,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q14">
         <v>2.4</v>
@@ -4102,7 +4108,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ14">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4717,7 +4723,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ17">
         <v>0.77</v>
@@ -4845,7 +4851,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -5257,7 +5263,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -5335,7 +5341,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ20">
         <v>1.23</v>
@@ -5463,7 +5469,7 @@
         <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5669,7 +5675,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5875,7 +5881,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -6081,7 +6087,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q24">
         <v>3.25</v>
@@ -6287,7 +6293,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q25">
         <v>2.05</v>
@@ -6493,7 +6499,7 @@
         <v>86</v>
       </c>
       <c r="P26" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6574,7 +6580,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ26">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR26">
         <v>1.84</v>
@@ -6777,10 +6783,10 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ27">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR27">
         <v>1.64</v>
@@ -7111,7 +7117,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7523,7 +7529,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7729,7 +7735,7 @@
         <v>86</v>
       </c>
       <c r="P32" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q32">
         <v>2.05</v>
@@ -8013,7 +8019,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ33">
         <v>1.85</v>
@@ -8222,7 +8228,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ34">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR34">
         <v>0.89</v>
@@ -8425,7 +8431,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ35">
         <v>1.69</v>
@@ -8759,7 +8765,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -9249,7 +9255,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ39">
         <v>0.23</v>
@@ -9995,7 +10001,7 @@
         <v>86</v>
       </c>
       <c r="P43" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q43">
         <v>7.5</v>
@@ -10201,7 +10207,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10282,7 +10288,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ44">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR44">
         <v>0.95</v>
@@ -10488,7 +10494,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ45">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR45">
         <v>2.07</v>
@@ -10613,7 +10619,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q46">
         <v>2.5</v>
@@ -10819,7 +10825,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q47">
         <v>4.33</v>
@@ -10900,7 +10906,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ47">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR47">
         <v>1.32</v>
@@ -11643,7 +11649,7 @@
         <v>116</v>
       </c>
       <c r="P51" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11849,7 +11855,7 @@
         <v>118</v>
       </c>
       <c r="P52" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q52">
         <v>5.5</v>
@@ -11927,7 +11933,7 @@
         <v>3</v>
       </c>
       <c r="AP52">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ52">
         <v>1.5</v>
@@ -12133,7 +12139,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ53">
         <v>1.71</v>
@@ -12261,7 +12267,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -12673,7 +12679,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q56">
         <v>5.5</v>
@@ -12879,7 +12885,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q57">
         <v>5</v>
@@ -13085,7 +13091,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13291,7 +13297,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13497,7 +13503,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13703,7 +13709,7 @@
         <v>86</v>
       </c>
       <c r="P61" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q61">
         <v>6.5</v>
@@ -14115,7 +14121,7 @@
         <v>86</v>
       </c>
       <c r="P63" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q63">
         <v>3.5</v>
@@ -14196,7 +14202,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ63">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR63">
         <v>1.29</v>
@@ -14321,7 +14327,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14399,7 +14405,7 @@
         <v>0</v>
       </c>
       <c r="AP64">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ64">
         <v>1.36</v>
@@ -14811,7 +14817,7 @@
         <v>1.67</v>
       </c>
       <c r="AP66">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ66">
         <v>1</v>
@@ -14939,7 +14945,7 @@
         <v>86</v>
       </c>
       <c r="P67" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q67">
         <v>6.5</v>
@@ -15145,7 +15151,7 @@
         <v>86</v>
       </c>
       <c r="P68" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q68">
         <v>4.75</v>
@@ -15763,7 +15769,7 @@
         <v>92</v>
       </c>
       <c r="P71" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q71">
         <v>9.5</v>
@@ -15844,7 +15850,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ71">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR71">
         <v>1.26</v>
@@ -16381,7 +16387,7 @@
         <v>86</v>
       </c>
       <c r="P74" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16462,7 +16468,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ74">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR74">
         <v>1.27</v>
@@ -16999,7 +17005,7 @@
         <v>130</v>
       </c>
       <c r="P77" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q77">
         <v>1.83</v>
@@ -17077,7 +17083,7 @@
         <v>0.4</v>
       </c>
       <c r="AP77">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ77">
         <v>1.23</v>
@@ -17205,7 +17211,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q78">
         <v>12</v>
@@ -17411,7 +17417,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q79">
         <v>3.75</v>
@@ -17617,7 +17623,7 @@
         <v>131</v>
       </c>
       <c r="P80" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17698,7 +17704,7 @@
         <v>1</v>
       </c>
       <c r="AQ80">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR80">
         <v>1.54</v>
@@ -17823,7 +17829,7 @@
         <v>132</v>
       </c>
       <c r="P81" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -18235,7 +18241,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q83">
         <v>1.67</v>
@@ -18725,7 +18731,7 @@
         <v>0.75</v>
       </c>
       <c r="AP85">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ85">
         <v>0.36</v>
@@ -18853,7 +18859,7 @@
         <v>134</v>
       </c>
       <c r="P86" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q86">
         <v>2.63</v>
@@ -19137,10 +19143,10 @@
         <v>2.33</v>
       </c>
       <c r="AP87">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ87">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR87">
         <v>1.66</v>
@@ -19552,7 +19558,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ89">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR89">
         <v>1.32</v>
@@ -19758,7 +19764,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ90">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR90">
         <v>1.18</v>
@@ -19961,7 +19967,7 @@
         <v>0.8</v>
       </c>
       <c r="AP91">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ91">
         <v>1.54</v>
@@ -20501,7 +20507,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q94">
         <v>13</v>
@@ -20707,7 +20713,7 @@
         <v>139</v>
       </c>
       <c r="P95" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -20994,7 +21000,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ96">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR96">
         <v>1.46</v>
@@ -21119,7 +21125,7 @@
         <v>140</v>
       </c>
       <c r="P97" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q97">
         <v>2.4</v>
@@ -21943,7 +21949,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22021,7 +22027,7 @@
         <v>1.67</v>
       </c>
       <c r="AP101">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ101">
         <v>1.5</v>
@@ -22227,10 +22233,10 @@
         <v>0.8</v>
       </c>
       <c r="AP102">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ102">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR102">
         <v>0.91</v>
@@ -22433,10 +22439,10 @@
         <v>1.67</v>
       </c>
       <c r="AP103">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ103">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR103">
         <v>1.72</v>
@@ -22561,7 +22567,7 @@
         <v>145</v>
       </c>
       <c r="P104" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22767,7 +22773,7 @@
         <v>86</v>
       </c>
       <c r="P105" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -22973,7 +22979,7 @@
         <v>146</v>
       </c>
       <c r="P106" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q106">
         <v>6</v>
@@ -23385,7 +23391,7 @@
         <v>147</v>
       </c>
       <c r="P108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23669,7 +23675,7 @@
         <v>0.33</v>
       </c>
       <c r="AP109">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ109">
         <v>0.23</v>
@@ -23797,7 +23803,7 @@
         <v>149</v>
       </c>
       <c r="P110" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -24209,7 +24215,7 @@
         <v>143</v>
       </c>
       <c r="P112" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q112">
         <v>4.75</v>
@@ -24908,7 +24914,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ115">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR115">
         <v>1.42</v>
@@ -25033,7 +25039,7 @@
         <v>86</v>
       </c>
       <c r="P116" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q116">
         <v>4.5</v>
@@ -25239,7 +25245,7 @@
         <v>153</v>
       </c>
       <c r="P117" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q117">
         <v>1.53</v>
@@ -25317,7 +25323,7 @@
         <v>1</v>
       </c>
       <c r="AP117">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ117">
         <v>1.36</v>
@@ -25445,7 +25451,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25523,10 +25529,10 @@
         <v>1.43</v>
       </c>
       <c r="AP118">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ118">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR118">
         <v>0.95</v>
@@ -25651,7 +25657,7 @@
         <v>154</v>
       </c>
       <c r="P119" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q119">
         <v>1.8</v>
@@ -25732,7 +25738,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ119">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR119">
         <v>2</v>
@@ -25857,7 +25863,7 @@
         <v>155</v>
       </c>
       <c r="P120" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q120">
         <v>7.5</v>
@@ -26269,7 +26275,7 @@
         <v>157</v>
       </c>
       <c r="P122" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q122">
         <v>2.63</v>
@@ -26350,7 +26356,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ122">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR122">
         <v>1.43</v>
@@ -26759,7 +26765,7 @@
         <v>0.71</v>
       </c>
       <c r="AP124">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ124">
         <v>1</v>
@@ -27093,7 +27099,7 @@
         <v>86</v>
       </c>
       <c r="P126" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27299,7 +27305,7 @@
         <v>161</v>
       </c>
       <c r="P127" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27505,7 +27511,7 @@
         <v>86</v>
       </c>
       <c r="P128" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q128">
         <v>2.4</v>
@@ -27586,7 +27592,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ128">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR128">
         <v>1.33</v>
@@ -27711,7 +27717,7 @@
         <v>138</v>
       </c>
       <c r="P129" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27792,7 +27798,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ129">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR129">
         <v>1.45</v>
@@ -27917,7 +27923,7 @@
         <v>98</v>
       </c>
       <c r="P130" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q130">
         <v>6.5</v>
@@ -28123,7 +28129,7 @@
         <v>162</v>
       </c>
       <c r="P131" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q131">
         <v>4.33</v>
@@ -28329,7 +28335,7 @@
         <v>86</v>
       </c>
       <c r="P132" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q132">
         <v>8</v>
@@ -28613,7 +28619,7 @@
         <v>1</v>
       </c>
       <c r="AP133">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ133">
         <v>1.54</v>
@@ -29231,7 +29237,7 @@
         <v>0.5</v>
       </c>
       <c r="AP136">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ136">
         <v>0.77</v>
@@ -29977,7 +29983,7 @@
         <v>167</v>
       </c>
       <c r="P140" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q140">
         <v>2.3</v>
@@ -30183,7 +30189,7 @@
         <v>86</v>
       </c>
       <c r="P141" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q141">
         <v>7.5</v>
@@ -30389,7 +30395,7 @@
         <v>168</v>
       </c>
       <c r="P142" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30467,10 +30473,10 @@
         <v>1</v>
       </c>
       <c r="AP142">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ142">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR142">
         <v>2.2</v>
@@ -30595,7 +30601,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30882,7 +30888,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ144">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR144">
         <v>1.48</v>
@@ -31007,7 +31013,7 @@
         <v>171</v>
       </c>
       <c r="P145" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q145">
         <v>3.75</v>
@@ -31213,7 +31219,7 @@
         <v>172</v>
       </c>
       <c r="P146" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q146">
         <v>7.5</v>
@@ -31419,7 +31425,7 @@
         <v>173</v>
       </c>
       <c r="P147" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31500,7 +31506,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ147">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR147">
         <v>2.12</v>
@@ -31625,7 +31631,7 @@
         <v>174</v>
       </c>
       <c r="P148" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q148">
         <v>2.75</v>
@@ -31831,7 +31837,7 @@
         <v>86</v>
       </c>
       <c r="P149" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q149">
         <v>7.5</v>
@@ -32115,7 +32121,7 @@
         <v>2.33</v>
       </c>
       <c r="AP150">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ150">
         <v>1.69</v>
@@ -32243,7 +32249,7 @@
         <v>86</v>
       </c>
       <c r="P151" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q151">
         <v>6.5</v>
@@ -32321,7 +32327,7 @@
         <v>1</v>
       </c>
       <c r="AP151">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ151">
         <v>1.23</v>
@@ -32449,7 +32455,7 @@
         <v>176</v>
       </c>
       <c r="P152" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q152">
         <v>2.75</v>
@@ -32655,7 +32661,7 @@
         <v>177</v>
       </c>
       <c r="P153" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q153">
         <v>4.75</v>
@@ -33067,7 +33073,7 @@
         <v>179</v>
       </c>
       <c r="P155" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33273,7 +33279,7 @@
         <v>176</v>
       </c>
       <c r="P156" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q156">
         <v>2.2</v>
@@ -33354,7 +33360,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ156">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR156">
         <v>1.7</v>
@@ -33685,7 +33691,7 @@
         <v>181</v>
       </c>
       <c r="P158" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -34175,7 +34181,7 @@
         <v>2.78</v>
       </c>
       <c r="AP160">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ160">
         <v>2.23</v>
@@ -34384,7 +34390,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ161">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR161">
         <v>1.48</v>
@@ -34509,7 +34515,7 @@
         <v>86</v>
       </c>
       <c r="P162" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q162">
         <v>3.5</v>
@@ -34715,7 +34721,7 @@
         <v>184</v>
       </c>
       <c r="P163" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35127,7 +35133,7 @@
         <v>185</v>
       </c>
       <c r="P165" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q165">
         <v>9.5</v>
@@ -35205,7 +35211,7 @@
         <v>1.9</v>
       </c>
       <c r="AP165">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ165">
         <v>1.85</v>
@@ -35617,7 +35623,7 @@
         <v>1.7</v>
       </c>
       <c r="AP167">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ167">
         <v>1.5</v>
@@ -36032,7 +36038,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ169">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR169">
         <v>1.46</v>
@@ -36647,7 +36653,7 @@
         <v>1.5</v>
       </c>
       <c r="AP172">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ172">
         <v>1.23</v>
@@ -36981,7 +36987,7 @@
         <v>86</v>
       </c>
       <c r="P174" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q174">
         <v>3.75</v>
@@ -37187,7 +37193,7 @@
         <v>124</v>
       </c>
       <c r="P175" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q175">
         <v>5.5</v>
@@ -37393,7 +37399,7 @@
         <v>86</v>
       </c>
       <c r="P176" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q176">
         <v>3.1</v>
@@ -37474,7 +37480,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ176">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR176">
         <v>1.29</v>
@@ -37680,7 +37686,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ177">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR177">
         <v>1.06</v>
@@ -37805,7 +37811,7 @@
         <v>86</v>
       </c>
       <c r="P178" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q178">
         <v>3.5</v>
@@ -38217,7 +38223,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38423,7 +38429,7 @@
         <v>194</v>
       </c>
       <c r="P181" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q181">
         <v>3.2</v>
@@ -38629,7 +38635,7 @@
         <v>86</v>
       </c>
       <c r="P182" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q182">
         <v>8.5</v>
@@ -38707,7 +38713,7 @@
         <v>1.82</v>
       </c>
       <c r="AP182">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ182">
         <v>1.71</v>
@@ -38916,7 +38922,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ183">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR183">
         <v>1.48</v>
@@ -39041,7 +39047,7 @@
         <v>195</v>
       </c>
       <c r="P184" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q184">
         <v>3.6</v>
@@ -39325,7 +39331,7 @@
         <v>1.36</v>
       </c>
       <c r="AP185">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ185">
         <v>1.36</v>
@@ -39534,7 +39540,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ186">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR186">
         <v>1.29</v>
@@ -39659,7 +39665,7 @@
         <v>196</v>
       </c>
       <c r="P187" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -39740,7 +39746,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ187">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR187">
         <v>1.74</v>
@@ -39865,7 +39871,7 @@
         <v>86</v>
       </c>
       <c r="P188" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q188">
         <v>6</v>
@@ -40071,7 +40077,7 @@
         <v>192</v>
       </c>
       <c r="P189" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q189">
         <v>2.3</v>
@@ -40483,7 +40489,7 @@
         <v>197</v>
       </c>
       <c r="P191" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
@@ -40561,7 +40567,7 @@
         <v>0.73</v>
       </c>
       <c r="AP191">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ191">
         <v>0.77</v>
@@ -40689,7 +40695,7 @@
         <v>198</v>
       </c>
       <c r="P192" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q192">
         <v>8.5</v>
@@ -41101,7 +41107,7 @@
         <v>200</v>
       </c>
       <c r="P194" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q194">
         <v>2.75</v>
@@ -41388,7 +41394,7 @@
         <v>1</v>
       </c>
       <c r="AQ195">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR195">
         <v>1.24</v>
@@ -41513,7 +41519,7 @@
         <v>201</v>
       </c>
       <c r="P196" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q196">
         <v>4.5</v>
@@ -41591,7 +41597,7 @@
         <v>1.17</v>
       </c>
       <c r="AP196">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ196">
         <v>1</v>
@@ -41797,7 +41803,7 @@
         <v>0.42</v>
       </c>
       <c r="AP197">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ197">
         <v>0.36</v>
@@ -41925,7 +41931,7 @@
         <v>203</v>
       </c>
       <c r="P198" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q198">
         <v>2.5</v>
@@ -42131,7 +42137,7 @@
         <v>204</v>
       </c>
       <c r="P199" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q199">
         <v>2.4</v>
@@ -42337,7 +42343,7 @@
         <v>86</v>
       </c>
       <c r="P200" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q200">
         <v>2.25</v>
@@ -42418,7 +42424,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ200">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR200">
         <v>1.57</v>
@@ -42543,7 +42549,7 @@
         <v>198</v>
       </c>
       <c r="P201" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q201">
         <v>4.33</v>
@@ -43161,7 +43167,7 @@
         <v>207</v>
       </c>
       <c r="P204" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q204">
         <v>2.25</v>
@@ -43242,7 +43248,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ204">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR204">
         <v>1.73</v>
@@ -43573,7 +43579,7 @@
         <v>86</v>
       </c>
       <c r="P206" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q206">
         <v>8.5</v>
@@ -43779,7 +43785,7 @@
         <v>208</v>
       </c>
       <c r="P207" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q207">
         <v>4</v>
@@ -44269,7 +44275,7 @@
         <v>1.75</v>
       </c>
       <c r="AP209">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ209">
         <v>1.69</v>
@@ -44603,7 +44609,7 @@
         <v>141</v>
       </c>
       <c r="P211" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q211">
         <v>2.3</v>
@@ -45332,13 +45338,13 @@
         <v>0</v>
       </c>
       <c r="BA214">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="BB214">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BC214">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="BD214">
         <v>1.25</v>
@@ -45378,6 +45384,624 @@
       </c>
       <c r="BP214">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="215" spans="1:68">
+      <c r="A215" s="1">
+        <v>214</v>
+      </c>
+      <c r="B215">
+        <v>7762808</v>
+      </c>
+      <c r="C215" t="s">
+        <v>68</v>
+      </c>
+      <c r="D215" t="s">
+        <v>69</v>
+      </c>
+      <c r="E215" s="2">
+        <v>45750.35416666666</v>
+      </c>
+      <c r="F215">
+        <v>27</v>
+      </c>
+      <c r="G215" t="s">
+        <v>76</v>
+      </c>
+      <c r="H215" t="s">
+        <v>72</v>
+      </c>
+      <c r="I215">
+        <v>0</v>
+      </c>
+      <c r="J215">
+        <v>0</v>
+      </c>
+      <c r="K215">
+        <v>0</v>
+      </c>
+      <c r="L215">
+        <v>0</v>
+      </c>
+      <c r="M215">
+        <v>0</v>
+      </c>
+      <c r="N215">
+        <v>0</v>
+      </c>
+      <c r="O215" t="s">
+        <v>86</v>
+      </c>
+      <c r="P215" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q215">
+        <v>4.5</v>
+      </c>
+      <c r="R215">
+        <v>2.05</v>
+      </c>
+      <c r="S215">
+        <v>2.63</v>
+      </c>
+      <c r="T215">
+        <v>1.44</v>
+      </c>
+      <c r="U215">
+        <v>2.63</v>
+      </c>
+      <c r="V215">
+        <v>3.25</v>
+      </c>
+      <c r="W215">
+        <v>1.33</v>
+      </c>
+      <c r="X215">
+        <v>10</v>
+      </c>
+      <c r="Y215">
+        <v>1.06</v>
+      </c>
+      <c r="Z215">
+        <v>3.41</v>
+      </c>
+      <c r="AA215">
+        <v>3.28</v>
+      </c>
+      <c r="AB215">
+        <v>2.11</v>
+      </c>
+      <c r="AC215">
+        <v>1.03</v>
+      </c>
+      <c r="AD215">
+        <v>7.2</v>
+      </c>
+      <c r="AE215">
+        <v>1.33</v>
+      </c>
+      <c r="AF215">
+        <v>2.84</v>
+      </c>
+      <c r="AG215">
+        <v>2.15</v>
+      </c>
+      <c r="AH215">
+        <v>1.57</v>
+      </c>
+      <c r="AI215">
+        <v>1.91</v>
+      </c>
+      <c r="AJ215">
+        <v>1.8</v>
+      </c>
+      <c r="AK215">
+        <v>1.77</v>
+      </c>
+      <c r="AL215">
+        <v>1.33</v>
+      </c>
+      <c r="AM215">
+        <v>1.24</v>
+      </c>
+      <c r="AN215">
+        <v>0.77</v>
+      </c>
+      <c r="AO215">
+        <v>1.15</v>
+      </c>
+      <c r="AP215">
+        <v>0.79</v>
+      </c>
+      <c r="AQ215">
+        <v>1.14</v>
+      </c>
+      <c r="AR215">
+        <v>1.1</v>
+      </c>
+      <c r="AS215">
+        <v>1.32</v>
+      </c>
+      <c r="AT215">
+        <v>2.42</v>
+      </c>
+      <c r="AU215">
+        <v>7</v>
+      </c>
+      <c r="AV215">
+        <v>2</v>
+      </c>
+      <c r="AW215">
+        <v>7</v>
+      </c>
+      <c r="AX215">
+        <v>4</v>
+      </c>
+      <c r="AY215">
+        <v>14</v>
+      </c>
+      <c r="AZ215">
+        <v>6</v>
+      </c>
+      <c r="BA215">
+        <v>11</v>
+      </c>
+      <c r="BB215">
+        <v>4</v>
+      </c>
+      <c r="BC215">
+        <v>15</v>
+      </c>
+      <c r="BD215">
+        <v>2.18</v>
+      </c>
+      <c r="BE215">
+        <v>6.4</v>
+      </c>
+      <c r="BF215">
+        <v>1.84</v>
+      </c>
+      <c r="BG215">
+        <v>1.48</v>
+      </c>
+      <c r="BH215">
+        <v>2.45</v>
+      </c>
+      <c r="BI215">
+        <v>1.79</v>
+      </c>
+      <c r="BJ215">
+        <v>1.9</v>
+      </c>
+      <c r="BK215">
+        <v>2.25</v>
+      </c>
+      <c r="BL215">
+        <v>1.55</v>
+      </c>
+      <c r="BM215">
+        <v>2.9</v>
+      </c>
+      <c r="BN215">
+        <v>1.34</v>
+      </c>
+      <c r="BO215">
+        <v>3.9</v>
+      </c>
+      <c r="BP215">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="216" spans="1:68">
+      <c r="A216" s="1">
+        <v>215</v>
+      </c>
+      <c r="B216">
+        <v>7762809</v>
+      </c>
+      <c r="C216" t="s">
+        <v>68</v>
+      </c>
+      <c r="D216" t="s">
+        <v>69</v>
+      </c>
+      <c r="E216" s="2">
+        <v>45750.45833333334</v>
+      </c>
+      <c r="F216">
+        <v>27</v>
+      </c>
+      <c r="G216" t="s">
+        <v>75</v>
+      </c>
+      <c r="H216" t="s">
+        <v>71</v>
+      </c>
+      <c r="I216">
+        <v>1</v>
+      </c>
+      <c r="J216">
+        <v>0</v>
+      </c>
+      <c r="K216">
+        <v>1</v>
+      </c>
+      <c r="L216">
+        <v>3</v>
+      </c>
+      <c r="M216">
+        <v>0</v>
+      </c>
+      <c r="N216">
+        <v>3</v>
+      </c>
+      <c r="O216" t="s">
+        <v>211</v>
+      </c>
+      <c r="P216" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q216">
+        <v>1.53</v>
+      </c>
+      <c r="R216">
+        <v>2.63</v>
+      </c>
+      <c r="S216">
+        <v>17</v>
+      </c>
+      <c r="T216">
+        <v>1.33</v>
+      </c>
+      <c r="U216">
+        <v>3.25</v>
+      </c>
+      <c r="V216">
+        <v>2.5</v>
+      </c>
+      <c r="W216">
+        <v>1.5</v>
+      </c>
+      <c r="X216">
+        <v>6.5</v>
+      </c>
+      <c r="Y216">
+        <v>1.11</v>
+      </c>
+      <c r="Z216">
+        <v>1.19</v>
+      </c>
+      <c r="AA216">
+        <v>6.2</v>
+      </c>
+      <c r="AB216">
+        <v>15</v>
+      </c>
+      <c r="AC216">
+        <v>1.01</v>
+      </c>
+      <c r="AD216">
+        <v>11</v>
+      </c>
+      <c r="AE216">
+        <v>1.16</v>
+      </c>
+      <c r="AF216">
+        <v>4.2</v>
+      </c>
+      <c r="AG216">
+        <v>1.67</v>
+      </c>
+      <c r="AH216">
+        <v>2</v>
+      </c>
+      <c r="AI216">
+        <v>3.25</v>
+      </c>
+      <c r="AJ216">
+        <v>1.33</v>
+      </c>
+      <c r="AK216">
+        <v>1.01</v>
+      </c>
+      <c r="AL216">
+        <v>1.08</v>
+      </c>
+      <c r="AM216">
+        <v>5.75</v>
+      </c>
+      <c r="AN216">
+        <v>2.69</v>
+      </c>
+      <c r="AO216">
+        <v>0.85</v>
+      </c>
+      <c r="AP216">
+        <v>2.71</v>
+      </c>
+      <c r="AQ216">
+        <v>0.79</v>
+      </c>
+      <c r="AR216">
+        <v>1.87</v>
+      </c>
+      <c r="AS216">
+        <v>0.96</v>
+      </c>
+      <c r="AT216">
+        <v>2.83</v>
+      </c>
+      <c r="AU216">
+        <v>7</v>
+      </c>
+      <c r="AV216">
+        <v>4</v>
+      </c>
+      <c r="AW216">
+        <v>5</v>
+      </c>
+      <c r="AX216">
+        <v>1</v>
+      </c>
+      <c r="AY216">
+        <v>12</v>
+      </c>
+      <c r="AZ216">
+        <v>5</v>
+      </c>
+      <c r="BA216">
+        <v>8</v>
+      </c>
+      <c r="BB216">
+        <v>0</v>
+      </c>
+      <c r="BC216">
+        <v>8</v>
+      </c>
+      <c r="BD216">
+        <v>1.11</v>
+      </c>
+      <c r="BE216">
+        <v>10</v>
+      </c>
+      <c r="BF216">
+        <v>6.75</v>
+      </c>
+      <c r="BG216">
+        <v>1.47</v>
+      </c>
+      <c r="BH216">
+        <v>2.48</v>
+      </c>
+      <c r="BI216">
+        <v>1.76</v>
+      </c>
+      <c r="BJ216">
+        <v>1.94</v>
+      </c>
+      <c r="BK216">
+        <v>2.2</v>
+      </c>
+      <c r="BL216">
+        <v>1.58</v>
+      </c>
+      <c r="BM216">
+        <v>2.8</v>
+      </c>
+      <c r="BN216">
+        <v>1.36</v>
+      </c>
+      <c r="BO216">
+        <v>3.7</v>
+      </c>
+      <c r="BP216">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="217" spans="1:68">
+      <c r="A217" s="1">
+        <v>216</v>
+      </c>
+      <c r="B217">
+        <v>7762802</v>
+      </c>
+      <c r="C217" t="s">
+        <v>68</v>
+      </c>
+      <c r="D217" t="s">
+        <v>69</v>
+      </c>
+      <c r="E217" s="2">
+        <v>45750.5625</v>
+      </c>
+      <c r="F217">
+        <v>27</v>
+      </c>
+      <c r="G217" t="s">
+        <v>79</v>
+      </c>
+      <c r="H217" t="s">
+        <v>81</v>
+      </c>
+      <c r="I217">
+        <v>2</v>
+      </c>
+      <c r="J217">
+        <v>0</v>
+      </c>
+      <c r="K217">
+        <v>2</v>
+      </c>
+      <c r="L217">
+        <v>2</v>
+      </c>
+      <c r="M217">
+        <v>0</v>
+      </c>
+      <c r="N217">
+        <v>2</v>
+      </c>
+      <c r="O217" t="s">
+        <v>212</v>
+      </c>
+      <c r="P217" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q217">
+        <v>2</v>
+      </c>
+      <c r="R217">
+        <v>2.3</v>
+      </c>
+      <c r="S217">
+        <v>7</v>
+      </c>
+      <c r="T217">
+        <v>1.36</v>
+      </c>
+      <c r="U217">
+        <v>3</v>
+      </c>
+      <c r="V217">
+        <v>2.75</v>
+      </c>
+      <c r="W217">
+        <v>1.4</v>
+      </c>
+      <c r="X217">
+        <v>7</v>
+      </c>
+      <c r="Y217">
+        <v>1.1</v>
+      </c>
+      <c r="Z217">
+        <v>1.51</v>
+      </c>
+      <c r="AA217">
+        <v>4.1</v>
+      </c>
+      <c r="AB217">
+        <v>6</v>
+      </c>
+      <c r="AC217">
+        <v>1</v>
+      </c>
+      <c r="AD217">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE217">
+        <v>1.28</v>
+      </c>
+      <c r="AF217">
+        <v>3.1</v>
+      </c>
+      <c r="AG217">
+        <v>1.89</v>
+      </c>
+      <c r="AH217">
+        <v>1.85</v>
+      </c>
+      <c r="AI217">
+        <v>2</v>
+      </c>
+      <c r="AJ217">
+        <v>1.73</v>
+      </c>
+      <c r="AK217">
+        <v>1.09</v>
+      </c>
+      <c r="AL217">
+        <v>1.2</v>
+      </c>
+      <c r="AM217">
+        <v>2.75</v>
+      </c>
+      <c r="AN217">
+        <v>2.23</v>
+      </c>
+      <c r="AO217">
+        <v>1.31</v>
+      </c>
+      <c r="AP217">
+        <v>2.29</v>
+      </c>
+      <c r="AQ217">
+        <v>1.21</v>
+      </c>
+      <c r="AR217">
+        <v>2.09</v>
+      </c>
+      <c r="AS217">
+        <v>1.57</v>
+      </c>
+      <c r="AT217">
+        <v>3.66</v>
+      </c>
+      <c r="AU217">
+        <v>6</v>
+      </c>
+      <c r="AV217">
+        <v>5</v>
+      </c>
+      <c r="AW217">
+        <v>8</v>
+      </c>
+      <c r="AX217">
+        <v>3</v>
+      </c>
+      <c r="AY217">
+        <v>14</v>
+      </c>
+      <c r="AZ217">
+        <v>8</v>
+      </c>
+      <c r="BA217">
+        <v>8</v>
+      </c>
+      <c r="BB217">
+        <v>2</v>
+      </c>
+      <c r="BC217">
+        <v>10</v>
+      </c>
+      <c r="BD217">
+        <v>1.38</v>
+      </c>
+      <c r="BE217">
+        <v>7</v>
+      </c>
+      <c r="BF217">
+        <v>3.4</v>
+      </c>
+      <c r="BG217">
+        <v>1.42</v>
+      </c>
+      <c r="BH217">
+        <v>2.65</v>
+      </c>
+      <c r="BI217">
+        <v>1.71</v>
+      </c>
+      <c r="BJ217">
+        <v>2</v>
+      </c>
+      <c r="BK217">
+        <v>2.15</v>
+      </c>
+      <c r="BL217">
+        <v>1.63</v>
+      </c>
+      <c r="BM217">
+        <v>2.7</v>
+      </c>
+      <c r="BN217">
+        <v>1.38</v>
+      </c>
+      <c r="BO217">
+        <v>3.55</v>
+      </c>
+      <c r="BP217">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="308">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1299,7 +1299,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP217"/>
+  <dimension ref="A1:BP219"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ2">
         <v>1.21</v>
@@ -2457,10 +2457,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ6">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2666,7 +2666,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ7">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -4517,7 +4517,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ16">
         <v>1.36</v>
@@ -5138,7 +5138,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ19">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5756,7 +5756,7 @@
         <v>1</v>
       </c>
       <c r="AQ22">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR22">
         <v>1.34</v>
@@ -5959,7 +5959,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ23">
         <v>1.5</v>
@@ -7195,7 +7195,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ29">
         <v>0.36</v>
@@ -8434,7 +8434,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ35">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR35">
         <v>0.9399999999999999</v>
@@ -8637,7 +8637,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ36">
         <v>1.36</v>
@@ -9464,7 +9464,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ40">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR40">
         <v>1.4</v>
@@ -10491,7 +10491,7 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ45">
         <v>0.79</v>
@@ -10903,7 +10903,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ47">
         <v>1.21</v>
@@ -11112,7 +11112,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ48">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR48">
         <v>2.19</v>
@@ -12551,7 +12551,7 @@
         <v>1.75</v>
       </c>
       <c r="AP55">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ55">
         <v>1.23</v>
@@ -12966,7 +12966,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ57">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR57">
         <v>1.15</v>
@@ -13169,7 +13169,7 @@
         <v>0.25</v>
       </c>
       <c r="AP58">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ58">
         <v>1.23</v>
@@ -13790,7 +13790,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ61">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR61">
         <v>1.06</v>
@@ -15644,7 +15644,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ70">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR70">
         <v>1.49</v>
@@ -16671,10 +16671,10 @@
         <v>0.75</v>
       </c>
       <c r="AP75">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ75">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR75">
         <v>1.99</v>
@@ -16880,7 +16880,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ76">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR76">
         <v>1.63</v>
@@ -17289,7 +17289,7 @@
         <v>3</v>
       </c>
       <c r="AP78">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ78">
         <v>2.23</v>
@@ -19555,7 +19555,7 @@
         <v>1.75</v>
       </c>
       <c r="AP89">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ89">
         <v>1.14</v>
@@ -19970,7 +19970,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ91">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR91">
         <v>1.91</v>
@@ -20379,7 +20379,7 @@
         <v>0.4</v>
       </c>
       <c r="AP93">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ93">
         <v>0.23</v>
@@ -22645,7 +22645,7 @@
         <v>0.57</v>
       </c>
       <c r="AP104">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ104">
         <v>0.77</v>
@@ -23060,7 +23060,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ106">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR106">
         <v>1.32</v>
@@ -23881,7 +23881,7 @@
         <v>1.86</v>
       </c>
       <c r="AP110">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ110">
         <v>1.85</v>
@@ -24090,7 +24090,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ111">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR111">
         <v>1.08</v>
@@ -24296,7 +24296,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ112">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR112">
         <v>1.48</v>
@@ -28413,7 +28413,7 @@
         <v>1.63</v>
       </c>
       <c r="AP132">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ132">
         <v>1.85</v>
@@ -28622,7 +28622,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ133">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR133">
         <v>0.99</v>
@@ -28828,7 +28828,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ134">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR134">
         <v>1.33</v>
@@ -29649,7 +29649,7 @@
         <v>0.63</v>
       </c>
       <c r="AP138">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ138">
         <v>1</v>
@@ -31297,7 +31297,7 @@
         <v>1.78</v>
       </c>
       <c r="AP146">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ146">
         <v>1.71</v>
@@ -32124,7 +32124,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ150">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR150">
         <v>1.74</v>
@@ -33357,7 +33357,7 @@
         <v>0.89</v>
       </c>
       <c r="AP156">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ156">
         <v>1.14</v>
@@ -33566,7 +33566,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ157">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR157">
         <v>1.48</v>
@@ -34593,7 +34593,7 @@
         <v>0.8</v>
       </c>
       <c r="AP162">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ162">
         <v>1</v>
@@ -35008,7 +35008,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ164">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR164">
         <v>1.55</v>
@@ -37068,7 +37068,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ174">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR174">
         <v>1.58</v>
@@ -37271,7 +37271,7 @@
         <v>2.5</v>
       </c>
       <c r="AP175">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ175">
         <v>2.23</v>
@@ -39128,7 +39128,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ184">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR184">
         <v>1.43</v>
@@ -39537,7 +39537,7 @@
         <v>0.91</v>
       </c>
       <c r="AP186">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ186">
         <v>0.79</v>
@@ -39952,7 +39952,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ188">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR188">
         <v>1.61</v>
@@ -40155,7 +40155,7 @@
         <v>1.36</v>
       </c>
       <c r="AP189">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ189">
         <v>1.23</v>
@@ -43039,7 +43039,7 @@
         <v>0.25</v>
       </c>
       <c r="AP203">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ203">
         <v>0.23</v>
@@ -43451,7 +43451,7 @@
         <v>0.75</v>
       </c>
       <c r="AP205">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ205">
         <v>0.77</v>
@@ -43660,7 +43660,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ206">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR206">
         <v>1.07</v>
@@ -44278,7 +44278,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ209">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR209">
         <v>2.05</v>
@@ -46002,6 +46002,418 @@
       </c>
       <c r="BP217">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="218" spans="1:68">
+      <c r="A218" s="1">
+        <v>217</v>
+      </c>
+      <c r="B218">
+        <v>7762816</v>
+      </c>
+      <c r="C218" t="s">
+        <v>68</v>
+      </c>
+      <c r="D218" t="s">
+        <v>69</v>
+      </c>
+      <c r="E218" s="2">
+        <v>45752.4375</v>
+      </c>
+      <c r="F218">
+        <v>28</v>
+      </c>
+      <c r="G218" t="s">
+        <v>70</v>
+      </c>
+      <c r="H218" t="s">
+        <v>82</v>
+      </c>
+      <c r="I218">
+        <v>0</v>
+      </c>
+      <c r="J218">
+        <v>0</v>
+      </c>
+      <c r="K218">
+        <v>0</v>
+      </c>
+      <c r="L218">
+        <v>1</v>
+      </c>
+      <c r="M218">
+        <v>1</v>
+      </c>
+      <c r="N218">
+        <v>2</v>
+      </c>
+      <c r="O218" t="s">
+        <v>188</v>
+      </c>
+      <c r="P218" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q218">
+        <v>2.4</v>
+      </c>
+      <c r="R218">
+        <v>2.1</v>
+      </c>
+      <c r="S218">
+        <v>5.5</v>
+      </c>
+      <c r="T218">
+        <v>1.44</v>
+      </c>
+      <c r="U218">
+        <v>2.63</v>
+      </c>
+      <c r="V218">
+        <v>3.25</v>
+      </c>
+      <c r="W218">
+        <v>1.33</v>
+      </c>
+      <c r="X218">
+        <v>10</v>
+      </c>
+      <c r="Y218">
+        <v>1.06</v>
+      </c>
+      <c r="Z218">
+        <v>1.9</v>
+      </c>
+      <c r="AA218">
+        <v>3.4</v>
+      </c>
+      <c r="AB218">
+        <v>4</v>
+      </c>
+      <c r="AC218">
+        <v>1.12</v>
+      </c>
+      <c r="AD218">
+        <v>6.17</v>
+      </c>
+      <c r="AE218">
+        <v>1.53</v>
+      </c>
+      <c r="AF218">
+        <v>2.52</v>
+      </c>
+      <c r="AG218">
+        <v>1.91</v>
+      </c>
+      <c r="AH218">
+        <v>1.83</v>
+      </c>
+      <c r="AI218">
+        <v>2</v>
+      </c>
+      <c r="AJ218">
+        <v>1.73</v>
+      </c>
+      <c r="AK218">
+        <v>1.14</v>
+      </c>
+      <c r="AL218">
+        <v>1.3</v>
+      </c>
+      <c r="AM218">
+        <v>2.29</v>
+      </c>
+      <c r="AN218">
+        <v>1.85</v>
+      </c>
+      <c r="AO218">
+        <v>1.69</v>
+      </c>
+      <c r="AP218">
+        <v>1.79</v>
+      </c>
+      <c r="AQ218">
+        <v>1.64</v>
+      </c>
+      <c r="AR218">
+        <v>1.69</v>
+      </c>
+      <c r="AS218">
+        <v>1.39</v>
+      </c>
+      <c r="AT218">
+        <v>3.08</v>
+      </c>
+      <c r="AU218">
+        <v>6</v>
+      </c>
+      <c r="AV218">
+        <v>3</v>
+      </c>
+      <c r="AW218">
+        <v>12</v>
+      </c>
+      <c r="AX218">
+        <v>5</v>
+      </c>
+      <c r="AY218">
+        <v>18</v>
+      </c>
+      <c r="AZ218">
+        <v>8</v>
+      </c>
+      <c r="BA218">
+        <v>3</v>
+      </c>
+      <c r="BB218">
+        <v>4</v>
+      </c>
+      <c r="BC218">
+        <v>7</v>
+      </c>
+      <c r="BD218">
+        <v>1.43</v>
+      </c>
+      <c r="BE218">
+        <v>8.9</v>
+      </c>
+      <c r="BF218">
+        <v>3.4</v>
+      </c>
+      <c r="BG218">
+        <v>1.27</v>
+      </c>
+      <c r="BH218">
+        <v>3.14</v>
+      </c>
+      <c r="BI218">
+        <v>1.57</v>
+      </c>
+      <c r="BJ218">
+        <v>2.33</v>
+      </c>
+      <c r="BK218">
+        <v>1.97</v>
+      </c>
+      <c r="BL218">
+        <v>1.83</v>
+      </c>
+      <c r="BM218">
+        <v>2.51</v>
+      </c>
+      <c r="BN218">
+        <v>1.5</v>
+      </c>
+      <c r="BO218">
+        <v>3.34</v>
+      </c>
+      <c r="BP218">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="219" spans="1:68">
+      <c r="A219" s="1">
+        <v>218</v>
+      </c>
+      <c r="B219">
+        <v>7762813</v>
+      </c>
+      <c r="C219" t="s">
+        <v>68</v>
+      </c>
+      <c r="D219" t="s">
+        <v>69</v>
+      </c>
+      <c r="E219" s="2">
+        <v>45752.54166666666</v>
+      </c>
+      <c r="F219">
+        <v>28</v>
+      </c>
+      <c r="G219" t="s">
+        <v>74</v>
+      </c>
+      <c r="H219" t="s">
+        <v>80</v>
+      </c>
+      <c r="I219">
+        <v>1</v>
+      </c>
+      <c r="J219">
+        <v>0</v>
+      </c>
+      <c r="K219">
+        <v>1</v>
+      </c>
+      <c r="L219">
+        <v>1</v>
+      </c>
+      <c r="M219">
+        <v>1</v>
+      </c>
+      <c r="N219">
+        <v>2</v>
+      </c>
+      <c r="O219" t="s">
+        <v>102</v>
+      </c>
+      <c r="P219" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q219">
+        <v>8.5</v>
+      </c>
+      <c r="R219">
+        <v>2.5</v>
+      </c>
+      <c r="S219">
+        <v>1.8</v>
+      </c>
+      <c r="T219">
+        <v>1.33</v>
+      </c>
+      <c r="U219">
+        <v>3.25</v>
+      </c>
+      <c r="V219">
+        <v>2.63</v>
+      </c>
+      <c r="W219">
+        <v>1.44</v>
+      </c>
+      <c r="X219">
+        <v>6.5</v>
+      </c>
+      <c r="Y219">
+        <v>1.11</v>
+      </c>
+      <c r="Z219">
+        <v>7.4</v>
+      </c>
+      <c r="AA219">
+        <v>4.4</v>
+      </c>
+      <c r="AB219">
+        <v>1.42</v>
+      </c>
+      <c r="AC219">
+        <v>0</v>
+      </c>
+      <c r="AD219">
+        <v>0</v>
+      </c>
+      <c r="AE219">
+        <v>1.25</v>
+      </c>
+      <c r="AF219">
+        <v>3.92</v>
+      </c>
+      <c r="AG219">
+        <v>1.86</v>
+      </c>
+      <c r="AH219">
+        <v>1.84</v>
+      </c>
+      <c r="AI219">
+        <v>2.1</v>
+      </c>
+      <c r="AJ219">
+        <v>1.67</v>
+      </c>
+      <c r="AK219">
+        <v>3.58</v>
+      </c>
+      <c r="AL219">
+        <v>1.17</v>
+      </c>
+      <c r="AM219">
+        <v>1.07</v>
+      </c>
+      <c r="AN219">
+        <v>0.92</v>
+      </c>
+      <c r="AO219">
+        <v>1.54</v>
+      </c>
+      <c r="AP219">
+        <v>0.93</v>
+      </c>
+      <c r="AQ219">
+        <v>1.5</v>
+      </c>
+      <c r="AR219">
+        <v>1.35</v>
+      </c>
+      <c r="AS219">
+        <v>1.69</v>
+      </c>
+      <c r="AT219">
+        <v>3.04</v>
+      </c>
+      <c r="AU219">
+        <v>2</v>
+      </c>
+      <c r="AV219">
+        <v>2</v>
+      </c>
+      <c r="AW219">
+        <v>0</v>
+      </c>
+      <c r="AX219">
+        <v>0</v>
+      </c>
+      <c r="AY219">
+        <v>2</v>
+      </c>
+      <c r="AZ219">
+        <v>2</v>
+      </c>
+      <c r="BA219">
+        <v>0</v>
+      </c>
+      <c r="BB219">
+        <v>10</v>
+      </c>
+      <c r="BC219">
+        <v>10</v>
+      </c>
+      <c r="BD219">
+        <v>4.7</v>
+      </c>
+      <c r="BE219">
+        <v>10.25</v>
+      </c>
+      <c r="BF219">
+        <v>1.26</v>
+      </c>
+      <c r="BG219">
+        <v>1.25</v>
+      </c>
+      <c r="BH219">
+        <v>3.28</v>
+      </c>
+      <c r="BI219">
+        <v>1.56</v>
+      </c>
+      <c r="BJ219">
+        <v>2.34</v>
+      </c>
+      <c r="BK219">
+        <v>1.94</v>
+      </c>
+      <c r="BL219">
+        <v>1.85</v>
+      </c>
+      <c r="BM219">
+        <v>2.38</v>
+      </c>
+      <c r="BN219">
+        <v>1.54</v>
+      </c>
+      <c r="BO219">
+        <v>3.2</v>
+      </c>
+      <c r="BP219">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="311">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -655,6 +655,9 @@
     <t>['9', '23']</t>
   </si>
   <si>
+    <t>['4', '23', '90+8']</t>
+  </si>
+  <si>
     <t>['12', '22', '45+1', '45+4', '90+1', '90+8']</t>
   </si>
   <si>
@@ -938,6 +941,12 @@
   </si>
   <si>
     <t>['36', '62', '78']</t>
+  </si>
+  <si>
+    <t>['76', '86']</t>
+  </si>
+  <si>
+    <t>['73']</t>
   </si>
 </sst>
 </file>
@@ -1299,7 +1308,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP219"/>
+  <dimension ref="A1:BP222"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1839,10 +1848,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ3">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2173,7 +2182,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q5">
         <v>7.5</v>
@@ -2251,10 +2260,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ5">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2379,7 +2388,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2791,7 +2800,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q8">
         <v>4</v>
@@ -3696,7 +3705,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ12">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3821,7 +3830,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4027,7 +4036,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q14">
         <v>2.4</v>
@@ -4311,7 +4320,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ15">
         <v>1</v>
@@ -4726,7 +4735,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ17">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR17">
         <v>1.12</v>
@@ -4851,7 +4860,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -4932,7 +4941,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ18">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR18">
         <v>1.14</v>
@@ -5263,7 +5272,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -5469,7 +5478,7 @@
         <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5547,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ21">
         <v>1.71</v>
@@ -5675,7 +5684,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5753,7 +5762,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ22">
         <v>1.64</v>
@@ -5881,7 +5890,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -6087,7 +6096,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q24">
         <v>3.25</v>
@@ -6293,7 +6302,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q25">
         <v>2.05</v>
@@ -6374,7 +6383,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ25">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR25">
         <v>1.06</v>
@@ -6499,7 +6508,7 @@
         <v>86</v>
       </c>
       <c r="P26" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6577,7 +6586,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ26">
         <v>1.14</v>
@@ -7117,7 +7126,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7529,7 +7538,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7607,7 +7616,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ31">
         <v>1.5</v>
@@ -7735,7 +7744,7 @@
         <v>86</v>
       </c>
       <c r="P32" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q32">
         <v>2.05</v>
@@ -7816,7 +7825,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ32">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR32">
         <v>2.55</v>
@@ -8022,7 +8031,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ33">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR33">
         <v>1.4</v>
@@ -8225,7 +8234,7 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ34">
         <v>1.21</v>
@@ -8765,7 +8774,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -9049,7 +9058,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ38">
         <v>0.36</v>
@@ -9258,7 +9267,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ39">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR39">
         <v>1.98</v>
@@ -9876,7 +9885,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ42">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR42">
         <v>1.54</v>
@@ -10001,7 +10010,7 @@
         <v>86</v>
       </c>
       <c r="P43" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q43">
         <v>7.5</v>
@@ -10079,7 +10088,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ43">
         <v>2.23</v>
@@ -10207,7 +10216,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10619,7 +10628,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q46">
         <v>2.5</v>
@@ -10825,7 +10834,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q47">
         <v>4.33</v>
@@ -11318,7 +11327,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ49">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR49">
         <v>1.37</v>
@@ -11521,7 +11530,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ50">
         <v>1.36</v>
@@ -11649,7 +11658,7 @@
         <v>116</v>
       </c>
       <c r="P51" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11855,7 +11864,7 @@
         <v>118</v>
       </c>
       <c r="P52" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q52">
         <v>5.5</v>
@@ -12267,7 +12276,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -12348,7 +12357,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ54">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR54">
         <v>1.14</v>
@@ -12679,7 +12688,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q56">
         <v>5.5</v>
@@ -12760,7 +12769,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ56">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR56">
         <v>1.1</v>
@@ -12885,7 +12894,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q57">
         <v>5</v>
@@ -12963,7 +12972,7 @@
         <v>3</v>
       </c>
       <c r="AP57">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ57">
         <v>1.64</v>
@@ -13091,7 +13100,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13297,7 +13306,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13378,7 +13387,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ59">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR59">
         <v>1.61</v>
@@ -13503,7 +13512,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q60">
         <v>8.5</v>
@@ -13581,7 +13590,7 @@
         <v>3</v>
       </c>
       <c r="AP60">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ60">
         <v>2.23</v>
@@ -13709,7 +13718,7 @@
         <v>86</v>
       </c>
       <c r="P61" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q61">
         <v>6.5</v>
@@ -13787,7 +13796,7 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ61">
         <v>1.5</v>
@@ -14121,7 +14130,7 @@
         <v>86</v>
       </c>
       <c r="P63" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q63">
         <v>3.5</v>
@@ -14327,7 +14336,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14945,7 +14954,7 @@
         <v>86</v>
       </c>
       <c r="P67" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q67">
         <v>6.5</v>
@@ -15026,7 +15035,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ67">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR67">
         <v>1.17</v>
@@ -15151,7 +15160,7 @@
         <v>86</v>
       </c>
       <c r="P68" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q68">
         <v>4.75</v>
@@ -15435,7 +15444,7 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ69">
         <v>0.36</v>
@@ -15769,7 +15778,7 @@
         <v>92</v>
       </c>
       <c r="P71" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q71">
         <v>9.5</v>
@@ -16053,10 +16062,10 @@
         <v>0.25</v>
       </c>
       <c r="AP72">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ72">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR72">
         <v>1.09</v>
@@ -16259,10 +16268,10 @@
         <v>0.8</v>
       </c>
       <c r="AP73">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ73">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR73">
         <v>1.15</v>
@@ -16387,7 +16396,7 @@
         <v>86</v>
       </c>
       <c r="P74" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -17005,7 +17014,7 @@
         <v>130</v>
       </c>
       <c r="P77" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q77">
         <v>1.83</v>
@@ -17211,7 +17220,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q78">
         <v>12</v>
@@ -17417,7 +17426,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q79">
         <v>3.75</v>
@@ -17623,7 +17632,7 @@
         <v>131</v>
       </c>
       <c r="P80" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -17701,7 +17710,7 @@
         <v>1.8</v>
       </c>
       <c r="AP80">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ80">
         <v>1.21</v>
@@ -17829,7 +17838,7 @@
         <v>132</v>
       </c>
       <c r="P81" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -18241,7 +18250,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q83">
         <v>1.67</v>
@@ -18528,7 +18537,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ84">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR84">
         <v>1.5</v>
@@ -18859,7 +18868,7 @@
         <v>134</v>
       </c>
       <c r="P86" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q86">
         <v>2.63</v>
@@ -19349,7 +19358,7 @@
         <v>1.83</v>
       </c>
       <c r="AP88">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ88">
         <v>1.23</v>
@@ -19761,7 +19770,7 @@
         <v>0.75</v>
       </c>
       <c r="AP90">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ90">
         <v>0.79</v>
@@ -20176,7 +20185,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ92">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR92">
         <v>1.22</v>
@@ -20382,7 +20391,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ93">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR93">
         <v>1.8</v>
@@ -20507,7 +20516,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q94">
         <v>13</v>
@@ -20713,7 +20722,7 @@
         <v>139</v>
       </c>
       <c r="P95" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q95">
         <v>2.88</v>
@@ -21125,7 +21134,7 @@
         <v>140</v>
       </c>
       <c r="P97" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q97">
         <v>2.4</v>
@@ -21949,7 +21958,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22567,7 +22576,7 @@
         <v>145</v>
       </c>
       <c r="P104" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22648,7 +22657,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ104">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR104">
         <v>1.26</v>
@@ -22773,7 +22782,7 @@
         <v>86</v>
       </c>
       <c r="P105" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -22851,7 +22860,7 @@
         <v>0.71</v>
       </c>
       <c r="AP105">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ105">
         <v>1.23</v>
@@ -22979,7 +22988,7 @@
         <v>146</v>
       </c>
       <c r="P106" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q106">
         <v>6</v>
@@ -23263,7 +23272,7 @@
         <v>1.57</v>
       </c>
       <c r="AP107">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ107">
         <v>1.23</v>
@@ -23391,7 +23400,7 @@
         <v>147</v>
       </c>
       <c r="P108" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23678,7 +23687,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ109">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR109">
         <v>1.64</v>
@@ -23803,7 +23812,7 @@
         <v>149</v>
       </c>
       <c r="P110" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23884,7 +23893,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ110">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR110">
         <v>1.77</v>
@@ -24215,7 +24224,7 @@
         <v>143</v>
       </c>
       <c r="P112" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q112">
         <v>4.75</v>
@@ -25039,7 +25048,7 @@
         <v>86</v>
       </c>
       <c r="P116" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q116">
         <v>4.5</v>
@@ -25117,7 +25126,7 @@
         <v>1.17</v>
       </c>
       <c r="AP116">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ116">
         <v>1.71</v>
@@ -25245,7 +25254,7 @@
         <v>153</v>
       </c>
       <c r="P117" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q117">
         <v>1.53</v>
@@ -25451,7 +25460,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25657,7 +25666,7 @@
         <v>154</v>
       </c>
       <c r="P119" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q119">
         <v>1.8</v>
@@ -25863,7 +25872,7 @@
         <v>155</v>
       </c>
       <c r="P120" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q120">
         <v>7.5</v>
@@ -26150,7 +26159,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ121">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR121">
         <v>1.4</v>
@@ -26275,7 +26284,7 @@
         <v>157</v>
       </c>
       <c r="P122" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q122">
         <v>2.63</v>
@@ -26971,7 +26980,7 @@
         <v>1.29</v>
       </c>
       <c r="AP125">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ125">
         <v>1.36</v>
@@ -27099,7 +27108,7 @@
         <v>86</v>
       </c>
       <c r="P126" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q126">
         <v>3.75</v>
@@ -27305,7 +27314,7 @@
         <v>161</v>
       </c>
       <c r="P127" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27511,7 +27520,7 @@
         <v>86</v>
       </c>
       <c r="P128" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q128">
         <v>2.4</v>
@@ -27717,7 +27726,7 @@
         <v>138</v>
       </c>
       <c r="P129" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27923,7 +27932,7 @@
         <v>98</v>
       </c>
       <c r="P130" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q130">
         <v>6.5</v>
@@ -28129,7 +28138,7 @@
         <v>162</v>
       </c>
       <c r="P131" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q131">
         <v>4.33</v>
@@ -28207,7 +28216,7 @@
         <v>1.75</v>
       </c>
       <c r="AP131">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ131">
         <v>1.5</v>
@@ -28335,7 +28344,7 @@
         <v>86</v>
       </c>
       <c r="P132" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q132">
         <v>8</v>
@@ -28416,7 +28425,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ132">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR132">
         <v>1.32</v>
@@ -29031,7 +29040,7 @@
         <v>1</v>
       </c>
       <c r="AP135">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ135">
         <v>1.23</v>
@@ -29240,7 +29249,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ136">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR136">
         <v>1.69</v>
@@ -29983,7 +29992,7 @@
         <v>167</v>
       </c>
       <c r="P140" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q140">
         <v>2.3</v>
@@ -30061,7 +30070,7 @@
         <v>0.5</v>
       </c>
       <c r="AP140">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ140">
         <v>0.36</v>
@@ -30189,7 +30198,7 @@
         <v>86</v>
       </c>
       <c r="P141" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q141">
         <v>7.5</v>
@@ -30395,7 +30404,7 @@
         <v>168</v>
       </c>
       <c r="P142" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q142">
         <v>1.8</v>
@@ -30601,7 +30610,7 @@
         <v>169</v>
       </c>
       <c r="P143" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30682,7 +30691,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ143">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR143">
         <v>1.42</v>
@@ -31013,7 +31022,7 @@
         <v>171</v>
       </c>
       <c r="P145" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q145">
         <v>3.75</v>
@@ -31219,7 +31228,7 @@
         <v>172</v>
       </c>
       <c r="P146" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q146">
         <v>7.5</v>
@@ -31425,7 +31434,7 @@
         <v>173</v>
       </c>
       <c r="P147" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q147">
         <v>2</v>
@@ -31631,7 +31640,7 @@
         <v>174</v>
       </c>
       <c r="P148" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q148">
         <v>2.75</v>
@@ -31709,7 +31718,7 @@
         <v>1</v>
       </c>
       <c r="AP148">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ148">
         <v>1.36</v>
@@ -31837,7 +31846,7 @@
         <v>86</v>
       </c>
       <c r="P149" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q149">
         <v>7.5</v>
@@ -31915,10 +31924,10 @@
         <v>1.78</v>
       </c>
       <c r="AP149">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ149">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR149">
         <v>1.37</v>
@@ -32249,7 +32258,7 @@
         <v>86</v>
       </c>
       <c r="P151" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q151">
         <v>6.5</v>
@@ -32455,7 +32464,7 @@
         <v>176</v>
       </c>
       <c r="P152" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q152">
         <v>2.75</v>
@@ -32536,7 +32545,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ152">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR152">
         <v>1.47</v>
@@ -32661,7 +32670,7 @@
         <v>177</v>
       </c>
       <c r="P153" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q153">
         <v>4.75</v>
@@ -33073,7 +33082,7 @@
         <v>179</v>
       </c>
       <c r="P155" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33279,7 +33288,7 @@
         <v>176</v>
       </c>
       <c r="P156" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q156">
         <v>2.2</v>
@@ -33691,7 +33700,7 @@
         <v>181</v>
       </c>
       <c r="P158" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33978,7 +33987,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ159">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR159">
         <v>1.57</v>
@@ -34387,7 +34396,7 @@
         <v>1</v>
       </c>
       <c r="AP161">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ161">
         <v>0.79</v>
@@ -34515,7 +34524,7 @@
         <v>86</v>
       </c>
       <c r="P162" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q162">
         <v>3.5</v>
@@ -34721,7 +34730,7 @@
         <v>184</v>
       </c>
       <c r="P163" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -34799,7 +34808,7 @@
         <v>1.9</v>
       </c>
       <c r="AP163">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ163">
         <v>1.71</v>
@@ -35133,7 +35142,7 @@
         <v>185</v>
       </c>
       <c r="P165" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q165">
         <v>9.5</v>
@@ -35214,7 +35223,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ165">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR165">
         <v>1.02</v>
@@ -36447,10 +36456,10 @@
         <v>0.3</v>
       </c>
       <c r="AP171">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ171">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR171">
         <v>1.57</v>
@@ -36862,7 +36871,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ173">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR173">
         <v>1.43</v>
@@ -36987,7 +36996,7 @@
         <v>86</v>
       </c>
       <c r="P174" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q174">
         <v>3.75</v>
@@ -37193,7 +37202,7 @@
         <v>124</v>
       </c>
       <c r="P175" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q175">
         <v>5.5</v>
@@ -37399,7 +37408,7 @@
         <v>86</v>
       </c>
       <c r="P176" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q176">
         <v>3.1</v>
@@ -37477,7 +37486,7 @@
         <v>1.1</v>
       </c>
       <c r="AP176">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ176">
         <v>1.14</v>
@@ -37811,7 +37820,7 @@
         <v>86</v>
       </c>
       <c r="P178" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q178">
         <v>3.5</v>
@@ -37889,7 +37898,7 @@
         <v>1</v>
       </c>
       <c r="AP178">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ178">
         <v>1</v>
@@ -38223,7 +38232,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q180">
         <v>2.88</v>
@@ -38429,7 +38438,7 @@
         <v>194</v>
       </c>
       <c r="P181" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q181">
         <v>3.2</v>
@@ -38510,7 +38519,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ181">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR181">
         <v>2.15</v>
@@ -38635,7 +38644,7 @@
         <v>86</v>
       </c>
       <c r="P182" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q182">
         <v>8.5</v>
@@ -39047,7 +39056,7 @@
         <v>195</v>
       </c>
       <c r="P184" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q184">
         <v>3.6</v>
@@ -39665,7 +39674,7 @@
         <v>196</v>
       </c>
       <c r="P187" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -39871,7 +39880,7 @@
         <v>86</v>
       </c>
       <c r="P188" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q188">
         <v>6</v>
@@ -39949,7 +39958,7 @@
         <v>1.27</v>
       </c>
       <c r="AP188">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ188">
         <v>1.5</v>
@@ -40077,7 +40086,7 @@
         <v>192</v>
       </c>
       <c r="P189" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q189">
         <v>2.3</v>
@@ -40489,7 +40498,7 @@
         <v>197</v>
       </c>
       <c r="P191" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
@@ -40570,7 +40579,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ191">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR191">
         <v>2.07</v>
@@ -40695,7 +40704,7 @@
         <v>198</v>
       </c>
       <c r="P192" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q192">
         <v>8.5</v>
@@ -40773,7 +40782,7 @@
         <v>2.36</v>
       </c>
       <c r="AP192">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ192">
         <v>2.23</v>
@@ -40982,7 +40991,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ193">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR193">
         <v>1.03</v>
@@ -41107,7 +41116,7 @@
         <v>200</v>
       </c>
       <c r="P194" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q194">
         <v>2.75</v>
@@ -41391,7 +41400,7 @@
         <v>1.17</v>
       </c>
       <c r="AP195">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ195">
         <v>1.14</v>
@@ -41519,7 +41528,7 @@
         <v>201</v>
       </c>
       <c r="P196" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q196">
         <v>4.5</v>
@@ -41931,7 +41940,7 @@
         <v>203</v>
       </c>
       <c r="P198" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q198">
         <v>2.5</v>
@@ -42137,7 +42146,7 @@
         <v>204</v>
       </c>
       <c r="P199" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q199">
         <v>2.4</v>
@@ -42343,7 +42352,7 @@
         <v>86</v>
       </c>
       <c r="P200" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q200">
         <v>2.25</v>
@@ -42549,7 +42558,7 @@
         <v>198</v>
       </c>
       <c r="P201" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q201">
         <v>4.33</v>
@@ -42630,7 +42639,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ201">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AR201">
         <v>1.46</v>
@@ -42833,7 +42842,7 @@
         <v>1.33</v>
       </c>
       <c r="AP202">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ202">
         <v>1.23</v>
@@ -43042,7 +43051,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ203">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR203">
         <v>1.32</v>
@@ -43167,7 +43176,7 @@
         <v>207</v>
       </c>
       <c r="P204" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q204">
         <v>2.25</v>
@@ -43454,7 +43463,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ205">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR205">
         <v>1.74</v>
@@ -43579,7 +43588,7 @@
         <v>86</v>
       </c>
       <c r="P206" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q206">
         <v>8.5</v>
@@ -43785,7 +43794,7 @@
         <v>208</v>
       </c>
       <c r="P207" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q207">
         <v>4</v>
@@ -43863,7 +43872,7 @@
         <v>1.08</v>
       </c>
       <c r="AP207">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ207">
         <v>1.23</v>
@@ -44609,7 +44618,7 @@
         <v>141</v>
       </c>
       <c r="P211" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q211">
         <v>2.3</v>
@@ -46018,7 +46027,7 @@
         <v>69</v>
       </c>
       <c r="E218" s="2">
-        <v>45752.4375</v>
+        <v>45752.52083333334</v>
       </c>
       <c r="F218">
         <v>28</v>
@@ -46033,10 +46042,10 @@
         <v>0</v>
       </c>
       <c r="J218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L218">
         <v>1</v>
@@ -46048,10 +46057,10 @@
         <v>2</v>
       </c>
       <c r="O218" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="P218" t="s">
-        <v>188</v>
+        <v>92</v>
       </c>
       <c r="Q218">
         <v>2.4</v>
@@ -46257,7 +46266,7 @@
         <v>102</v>
       </c>
       <c r="P219" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q219">
         <v>8.5</v>
@@ -46414,6 +46423,624 @@
       </c>
       <c r="BP219">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="220" spans="1:68">
+      <c r="A220" s="1">
+        <v>219</v>
+      </c>
+      <c r="B220">
+        <v>7762811</v>
+      </c>
+      <c r="C220" t="s">
+        <v>68</v>
+      </c>
+      <c r="D220" t="s">
+        <v>69</v>
+      </c>
+      <c r="E220" s="2">
+        <v>45753.26041666666</v>
+      </c>
+      <c r="F220">
+        <v>28</v>
+      </c>
+      <c r="G220" t="s">
+        <v>71</v>
+      </c>
+      <c r="H220" t="s">
+        <v>76</v>
+      </c>
+      <c r="I220">
+        <v>1</v>
+      </c>
+      <c r="J220">
+        <v>0</v>
+      </c>
+      <c r="K220">
+        <v>1</v>
+      </c>
+      <c r="L220">
+        <v>1</v>
+      </c>
+      <c r="M220">
+        <v>0</v>
+      </c>
+      <c r="N220">
+        <v>1</v>
+      </c>
+      <c r="O220" t="s">
+        <v>89</v>
+      </c>
+      <c r="P220" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q220">
+        <v>3</v>
+      </c>
+      <c r="R220">
+        <v>1.91</v>
+      </c>
+      <c r="S220">
+        <v>4.5</v>
+      </c>
+      <c r="T220">
+        <v>1.57</v>
+      </c>
+      <c r="U220">
+        <v>2.25</v>
+      </c>
+      <c r="V220">
+        <v>3.75</v>
+      </c>
+      <c r="W220">
+        <v>1.25</v>
+      </c>
+      <c r="X220">
+        <v>13</v>
+      </c>
+      <c r="Y220">
+        <v>1.04</v>
+      </c>
+      <c r="Z220">
+        <v>1.76</v>
+      </c>
+      <c r="AA220">
+        <v>3.53</v>
+      </c>
+      <c r="AB220">
+        <v>4.6</v>
+      </c>
+      <c r="AC220">
+        <v>1.1</v>
+      </c>
+      <c r="AD220">
+        <v>6.75</v>
+      </c>
+      <c r="AE220">
+        <v>1.5</v>
+      </c>
+      <c r="AF220">
+        <v>2.4</v>
+      </c>
+      <c r="AG220">
+        <v>2.2</v>
+      </c>
+      <c r="AH220">
+        <v>1.55</v>
+      </c>
+      <c r="AI220">
+        <v>2.2</v>
+      </c>
+      <c r="AJ220">
+        <v>1.62</v>
+      </c>
+      <c r="AK220">
+        <v>1.27</v>
+      </c>
+      <c r="AL220">
+        <v>1.32</v>
+      </c>
+      <c r="AM220">
+        <v>1.78</v>
+      </c>
+      <c r="AN220">
+        <v>1</v>
+      </c>
+      <c r="AO220">
+        <v>0.23</v>
+      </c>
+      <c r="AP220">
+        <v>1.14</v>
+      </c>
+      <c r="AQ220">
+        <v>0.21</v>
+      </c>
+      <c r="AR220">
+        <v>1.2</v>
+      </c>
+      <c r="AS220">
+        <v>0.99</v>
+      </c>
+      <c r="AT220">
+        <v>2.19</v>
+      </c>
+      <c r="AU220">
+        <v>6</v>
+      </c>
+      <c r="AV220">
+        <v>8</v>
+      </c>
+      <c r="AW220">
+        <v>5</v>
+      </c>
+      <c r="AX220">
+        <v>9</v>
+      </c>
+      <c r="AY220">
+        <v>11</v>
+      </c>
+      <c r="AZ220">
+        <v>17</v>
+      </c>
+      <c r="BA220">
+        <v>5</v>
+      </c>
+      <c r="BB220">
+        <v>10</v>
+      </c>
+      <c r="BC220">
+        <v>15</v>
+      </c>
+      <c r="BD220">
+        <v>1.78</v>
+      </c>
+      <c r="BE220">
+        <v>8</v>
+      </c>
+      <c r="BF220">
+        <v>2.39</v>
+      </c>
+      <c r="BG220">
+        <v>1.32</v>
+      </c>
+      <c r="BH220">
+        <v>2.88</v>
+      </c>
+      <c r="BI220">
+        <v>1.61</v>
+      </c>
+      <c r="BJ220">
+        <v>2.12</v>
+      </c>
+      <c r="BK220">
+        <v>2.06</v>
+      </c>
+      <c r="BL220">
+        <v>1.68</v>
+      </c>
+      <c r="BM220">
+        <v>2.71</v>
+      </c>
+      <c r="BN220">
+        <v>1.38</v>
+      </c>
+      <c r="BO220">
+        <v>3.72</v>
+      </c>
+      <c r="BP220">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="221" spans="1:68">
+      <c r="A221" s="1">
+        <v>220</v>
+      </c>
+      <c r="B221">
+        <v>7762814</v>
+      </c>
+      <c r="C221" t="s">
+        <v>68</v>
+      </c>
+      <c r="D221" t="s">
+        <v>69</v>
+      </c>
+      <c r="E221" s="2">
+        <v>45753.36458333334</v>
+      </c>
+      <c r="F221">
+        <v>28</v>
+      </c>
+      <c r="G221" t="s">
+        <v>73</v>
+      </c>
+      <c r="H221" t="s">
+        <v>85</v>
+      </c>
+      <c r="I221">
+        <v>2</v>
+      </c>
+      <c r="J221">
+        <v>0</v>
+      </c>
+      <c r="K221">
+        <v>2</v>
+      </c>
+      <c r="L221">
+        <v>3</v>
+      </c>
+      <c r="M221">
+        <v>2</v>
+      </c>
+      <c r="N221">
+        <v>5</v>
+      </c>
+      <c r="O221" t="s">
+        <v>213</v>
+      </c>
+      <c r="P221" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q221">
+        <v>3.14</v>
+      </c>
+      <c r="R221">
+        <v>2.05</v>
+      </c>
+      <c r="S221">
+        <v>3.34</v>
+      </c>
+      <c r="T221">
+        <v>1.42</v>
+      </c>
+      <c r="U221">
+        <v>2.65</v>
+      </c>
+      <c r="V221">
+        <v>2.94</v>
+      </c>
+      <c r="W221">
+        <v>1.35</v>
+      </c>
+      <c r="X221">
+        <v>7.1</v>
+      </c>
+      <c r="Y221">
+        <v>1.04</v>
+      </c>
+      <c r="Z221">
+        <v>2.75</v>
+      </c>
+      <c r="AA221">
+        <v>3.05</v>
+      </c>
+      <c r="AB221">
+        <v>2.65</v>
+      </c>
+      <c r="AC221">
+        <v>1.02</v>
+      </c>
+      <c r="AD221">
+        <v>8</v>
+      </c>
+      <c r="AE221">
+        <v>1.3</v>
+      </c>
+      <c r="AF221">
+        <v>2.98</v>
+      </c>
+      <c r="AG221">
+        <v>1.95</v>
+      </c>
+      <c r="AH221">
+        <v>1.7</v>
+      </c>
+      <c r="AI221">
+        <v>1.79</v>
+      </c>
+      <c r="AJ221">
+        <v>1.92</v>
+      </c>
+      <c r="AK221">
+        <v>1.45</v>
+      </c>
+      <c r="AL221">
+        <v>1.32</v>
+      </c>
+      <c r="AM221">
+        <v>1.49</v>
+      </c>
+      <c r="AN221">
+        <v>0.92</v>
+      </c>
+      <c r="AO221">
+        <v>0.77</v>
+      </c>
+      <c r="AP221">
+        <v>1.07</v>
+      </c>
+      <c r="AQ221">
+        <v>0.71</v>
+      </c>
+      <c r="AR221">
+        <v>1.35</v>
+      </c>
+      <c r="AS221">
+        <v>1.4</v>
+      </c>
+      <c r="AT221">
+        <v>2.75</v>
+      </c>
+      <c r="AU221">
+        <v>6</v>
+      </c>
+      <c r="AV221">
+        <v>6</v>
+      </c>
+      <c r="AW221">
+        <v>5</v>
+      </c>
+      <c r="AX221">
+        <v>5</v>
+      </c>
+      <c r="AY221">
+        <v>11</v>
+      </c>
+      <c r="AZ221">
+        <v>11</v>
+      </c>
+      <c r="BA221">
+        <v>3</v>
+      </c>
+      <c r="BB221">
+        <v>8</v>
+      </c>
+      <c r="BC221">
+        <v>11</v>
+      </c>
+      <c r="BD221">
+        <v>1.8</v>
+      </c>
+      <c r="BE221">
+        <v>6.75</v>
+      </c>
+      <c r="BF221">
+        <v>2.18</v>
+      </c>
+      <c r="BG221">
+        <v>1.27</v>
+      </c>
+      <c r="BH221">
+        <v>3.3</v>
+      </c>
+      <c r="BI221">
+        <v>1.47</v>
+      </c>
+      <c r="BJ221">
+        <v>2.48</v>
+      </c>
+      <c r="BK221">
+        <v>1.75</v>
+      </c>
+      <c r="BL221">
+        <v>1.95</v>
+      </c>
+      <c r="BM221">
+        <v>2.17</v>
+      </c>
+      <c r="BN221">
+        <v>1.6</v>
+      </c>
+      <c r="BO221">
+        <v>2.8</v>
+      </c>
+      <c r="BP221">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="222" spans="1:68">
+      <c r="A222" s="1">
+        <v>221</v>
+      </c>
+      <c r="B222">
+        <v>7762817</v>
+      </c>
+      <c r="C222" t="s">
+        <v>68</v>
+      </c>
+      <c r="D222" t="s">
+        <v>69</v>
+      </c>
+      <c r="E222" s="2">
+        <v>45753.46875</v>
+      </c>
+      <c r="F222">
+        <v>28</v>
+      </c>
+      <c r="G222" t="s">
+        <v>83</v>
+      </c>
+      <c r="H222" t="s">
+        <v>79</v>
+      </c>
+      <c r="I222">
+        <v>0</v>
+      </c>
+      <c r="J222">
+        <v>0</v>
+      </c>
+      <c r="K222">
+        <v>0</v>
+      </c>
+      <c r="L222">
+        <v>0</v>
+      </c>
+      <c r="M222">
+        <v>1</v>
+      </c>
+      <c r="N222">
+        <v>1</v>
+      </c>
+      <c r="O222" t="s">
+        <v>86</v>
+      </c>
+      <c r="P222" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q222">
+        <v>6.1</v>
+      </c>
+      <c r="R222">
+        <v>2.25</v>
+      </c>
+      <c r="S222">
+        <v>2.01</v>
+      </c>
+      <c r="T222">
+        <v>1.33</v>
+      </c>
+      <c r="U222">
+        <v>3.04</v>
+      </c>
+      <c r="V222">
+        <v>2.73</v>
+      </c>
+      <c r="W222">
+        <v>1.4</v>
+      </c>
+      <c r="X222">
+        <v>7.1</v>
+      </c>
+      <c r="Y222">
+        <v>1.04</v>
+      </c>
+      <c r="Z222">
+        <v>4.75</v>
+      </c>
+      <c r="AA222">
+        <v>3.64</v>
+      </c>
+      <c r="AB222">
+        <v>1.71</v>
+      </c>
+      <c r="AC222">
+        <v>1.02</v>
+      </c>
+      <c r="AD222">
+        <v>10</v>
+      </c>
+      <c r="AE222">
+        <v>1.21</v>
+      </c>
+      <c r="AF222">
+        <v>3.6</v>
+      </c>
+      <c r="AG222">
+        <v>2.13</v>
+      </c>
+      <c r="AH222">
+        <v>1.63</v>
+      </c>
+      <c r="AI222">
+        <v>1.92</v>
+      </c>
+      <c r="AJ222">
+        <v>1.79</v>
+      </c>
+      <c r="AK222">
+        <v>2.55</v>
+      </c>
+      <c r="AL222">
+        <v>1.21</v>
+      </c>
+      <c r="AM222">
+        <v>1.1</v>
+      </c>
+      <c r="AN222">
+        <v>1.31</v>
+      </c>
+      <c r="AO222">
+        <v>1.85</v>
+      </c>
+      <c r="AP222">
+        <v>1.21</v>
+      </c>
+      <c r="AQ222">
+        <v>1.93</v>
+      </c>
+      <c r="AR222">
+        <v>1.61</v>
+      </c>
+      <c r="AS222">
+        <v>1.72</v>
+      </c>
+      <c r="AT222">
+        <v>3.33</v>
+      </c>
+      <c r="AU222">
+        <v>0</v>
+      </c>
+      <c r="AV222">
+        <v>8</v>
+      </c>
+      <c r="AW222">
+        <v>6</v>
+      </c>
+      <c r="AX222">
+        <v>6</v>
+      </c>
+      <c r="AY222">
+        <v>6</v>
+      </c>
+      <c r="AZ222">
+        <v>14</v>
+      </c>
+      <c r="BA222">
+        <v>1</v>
+      </c>
+      <c r="BB222">
+        <v>9</v>
+      </c>
+      <c r="BC222">
+        <v>10</v>
+      </c>
+      <c r="BD222">
+        <v>3.05</v>
+      </c>
+      <c r="BE222">
+        <v>6.75</v>
+      </c>
+      <c r="BF222">
+        <v>1.46</v>
+      </c>
+      <c r="BG222">
+        <v>1.38</v>
+      </c>
+      <c r="BH222">
+        <v>2.7</v>
+      </c>
+      <c r="BI222">
+        <v>1.65</v>
+      </c>
+      <c r="BJ222">
+        <v>2.08</v>
+      </c>
+      <c r="BK222">
+        <v>2.05</v>
+      </c>
+      <c r="BL222">
+        <v>1.68</v>
+      </c>
+      <c r="BM222">
+        <v>2.63</v>
+      </c>
+      <c r="BN222">
+        <v>1.43</v>
+      </c>
+      <c r="BO222">
+        <v>3.4</v>
+      </c>
+      <c r="BP222">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="314">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -658,6 +658,9 @@
     <t>['4', '23', '90+8']</t>
   </si>
   <si>
+    <t>['66']</t>
+  </si>
+  <si>
     <t>['12', '22', '45+1', '45+4', '90+1', '90+8']</t>
   </si>
   <si>
@@ -722,9 +725,6 @@
   </si>
   <si>
     <t>['1']</t>
-  </si>
-  <si>
-    <t>['66']</t>
   </si>
   <si>
     <t>['3', '90+1', '90+7']</t>
@@ -947,6 +947,15 @@
   </si>
   <si>
     <t>['73']</t>
+  </si>
+  <si>
+    <t>['16', '43', '61', '90+3']</t>
+  </si>
+  <si>
+    <t>['7', '32']</t>
+  </si>
+  <si>
+    <t>['39', '82', '90+5']</t>
   </si>
 </sst>
 </file>
@@ -1308,7 +1317,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP222"/>
+  <dimension ref="A1:BP225"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2054,10 +2063,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ4">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2182,7 +2191,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q5">
         <v>7.5</v>
@@ -2388,7 +2397,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2800,7 +2809,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q8">
         <v>4</v>
@@ -2881,7 +2890,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ8">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3084,7 +3093,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ9">
         <v>1.5</v>
@@ -3830,7 +3839,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3908,10 +3917,10 @@
         <v>3</v>
       </c>
       <c r="AP13">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ13">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4036,7 +4045,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q14">
         <v>2.4</v>
@@ -4860,7 +4869,7 @@
         <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -4938,7 +4947,7 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ18">
         <v>1.93</v>
@@ -5272,7 +5281,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -5353,7 +5362,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ20">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR20">
         <v>0.96</v>
@@ -5478,7 +5487,7 @@
         <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5684,7 +5693,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5890,7 +5899,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -6096,7 +6105,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q24">
         <v>3.25</v>
@@ -6177,7 +6186,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ24">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -6302,7 +6311,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q25">
         <v>2.05</v>
@@ -6508,7 +6517,7 @@
         <v>86</v>
       </c>
       <c r="P26" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6998,7 +7007,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ28">
         <v>1</v>
@@ -7126,7 +7135,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q29">
         <v>1.83</v>
@@ -7413,7 +7422,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ30">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR30">
         <v>1.68</v>
@@ -7538,7 +7547,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7744,7 +7753,7 @@
         <v>86</v>
       </c>
       <c r="P32" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q32">
         <v>2.05</v>
@@ -8774,7 +8783,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -8852,7 +8861,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ37">
         <v>1.71</v>
@@ -9679,7 +9688,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ41">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR41">
         <v>1.88</v>
@@ -9882,7 +9891,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ42">
         <v>0.71</v>
@@ -10010,7 +10019,7 @@
         <v>86</v>
       </c>
       <c r="P43" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q43">
         <v>7.5</v>
@@ -10091,7 +10100,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ43">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR43">
         <v>1.51</v>
@@ -10216,7 +10225,7 @@
         <v>114</v>
       </c>
       <c r="P44" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -10294,7 +10303,7 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ44">
         <v>1.14</v>
@@ -10628,7 +10637,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q46">
         <v>2.5</v>
@@ -10709,7 +10718,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ46">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR46">
         <v>1.81</v>
@@ -10834,7 +10843,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q47">
         <v>4.33</v>
@@ -11658,7 +11667,7 @@
         <v>116</v>
       </c>
       <c r="P51" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11736,7 +11745,7 @@
         <v>2</v>
       </c>
       <c r="AP51">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ51">
         <v>1</v>
@@ -11864,7 +11873,7 @@
         <v>118</v>
       </c>
       <c r="P52" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="Q52">
         <v>5.5</v>
@@ -12354,7 +12363,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ54">
         <v>0.21</v>
@@ -12563,7 +12572,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ55">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR55">
         <v>1.49</v>
@@ -12766,7 +12775,7 @@
         <v>1</v>
       </c>
       <c r="AP56">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ56">
         <v>0.71</v>
@@ -13181,7 +13190,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ58">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR58">
         <v>1.97</v>
@@ -13384,7 +13393,7 @@
         <v>1.75</v>
       </c>
       <c r="AP59">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ59">
         <v>1.93</v>
@@ -13593,7 +13602,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ60">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR60">
         <v>1.59</v>
@@ -14005,7 +14014,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ62">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR62">
         <v>1.3</v>
@@ -14208,7 +14217,7 @@
         <v>1.67</v>
       </c>
       <c r="AP63">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ63">
         <v>1.21</v>
@@ -15856,7 +15865,7 @@
         <v>2</v>
       </c>
       <c r="AP71">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ71">
         <v>1.21</v>
@@ -16474,7 +16483,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ74">
         <v>0.79</v>
@@ -16886,7 +16895,7 @@
         <v>2.5</v>
       </c>
       <c r="AP76">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ76">
         <v>1.64</v>
@@ -17095,7 +17104,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ77">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR77">
         <v>1.79</v>
@@ -17301,7 +17310,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ78">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR78">
         <v>1.46</v>
@@ -17504,10 +17513,10 @@
         <v>1.6</v>
       </c>
       <c r="AP79">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ79">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR79">
         <v>1.25</v>
@@ -17838,7 +17847,7 @@
         <v>132</v>
       </c>
       <c r="P81" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -19361,7 +19370,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ88">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR88">
         <v>1.18</v>
@@ -20594,10 +20603,10 @@
         <v>3</v>
       </c>
       <c r="AP94">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ94">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR94">
         <v>1.21</v>
@@ -20800,10 +20809,10 @@
         <v>0.33</v>
       </c>
       <c r="AP95">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ95">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR95">
         <v>1.49</v>
@@ -22863,7 +22872,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ105">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR105">
         <v>1.16</v>
@@ -23066,7 +23075,7 @@
         <v>0.67</v>
       </c>
       <c r="AP106">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ106">
         <v>1.5</v>
@@ -23275,7 +23284,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ107">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR107">
         <v>1.46</v>
@@ -23478,7 +23487,7 @@
         <v>1.86</v>
       </c>
       <c r="AP108">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ108">
         <v>1.5</v>
@@ -23812,7 +23821,7 @@
         <v>149</v>
       </c>
       <c r="P110" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -24096,7 +24105,7 @@
         <v>2.57</v>
       </c>
       <c r="AP111">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ111">
         <v>1.64</v>
@@ -24302,7 +24311,7 @@
         <v>0.71</v>
       </c>
       <c r="AP112">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ112">
         <v>1.5</v>
@@ -25953,7 +25962,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ120">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR120">
         <v>1.46</v>
@@ -27186,7 +27195,7 @@
         <v>1.43</v>
       </c>
       <c r="AP126">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ126">
         <v>1.71</v>
@@ -27395,7 +27404,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ127">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR127">
         <v>2.03</v>
@@ -28010,7 +28019,7 @@
         <v>1.63</v>
       </c>
       <c r="AP130">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ130">
         <v>1.71</v>
@@ -28834,7 +28843,7 @@
         <v>2.25</v>
       </c>
       <c r="AP134">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ134">
         <v>1.64</v>
@@ -29043,7 +29052,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ135">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR135">
         <v>1.42</v>
@@ -29452,7 +29461,7 @@
         <v>1.13</v>
       </c>
       <c r="AP137">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ137">
         <v>1.36</v>
@@ -29867,7 +29876,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ139">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR139">
         <v>1.95</v>
@@ -29992,7 +30001,7 @@
         <v>167</v>
       </c>
       <c r="P140" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q140">
         <v>2.3</v>
@@ -30279,7 +30288,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ141">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR141">
         <v>1.45</v>
@@ -31100,7 +31109,7 @@
         <v>1.56</v>
       </c>
       <c r="AP145">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ145">
         <v>1.5</v>
@@ -32339,7 +32348,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ151">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR151">
         <v>0.99</v>
@@ -32751,7 +32760,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ153">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR153">
         <v>1.54</v>
@@ -32957,7 +32966,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ154">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR154">
         <v>1.41</v>
@@ -33160,7 +33169,7 @@
         <v>0.44</v>
       </c>
       <c r="AP155">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ155">
         <v>0.36</v>
@@ -33778,7 +33787,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP158">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ158">
         <v>1</v>
@@ -34193,7 +34202,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ160">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR160">
         <v>2.11</v>
@@ -35426,7 +35435,7 @@
         <v>1.2</v>
       </c>
       <c r="AP166">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ166">
         <v>1.36</v>
@@ -35841,7 +35850,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ168">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR168">
         <v>2.21</v>
@@ -36250,7 +36259,7 @@
         <v>0.5</v>
       </c>
       <c r="AP170">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ170">
         <v>0.36</v>
@@ -36665,7 +36674,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ172">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR172">
         <v>2.02</v>
@@ -37202,7 +37211,7 @@
         <v>124</v>
       </c>
       <c r="P175" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q175">
         <v>5.5</v>
@@ -37283,7 +37292,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ175">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR175">
         <v>1.71</v>
@@ -37408,7 +37417,7 @@
         <v>86</v>
       </c>
       <c r="P176" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q176">
         <v>3.1</v>
@@ -37692,7 +37701,7 @@
         <v>1</v>
       </c>
       <c r="AP177">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ177">
         <v>0.79</v>
@@ -38104,7 +38113,7 @@
         <v>0.45</v>
       </c>
       <c r="AP179">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ179">
         <v>0.36</v>
@@ -39674,7 +39683,7 @@
         <v>196</v>
       </c>
       <c r="P187" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -39752,7 +39761,7 @@
         <v>1.27</v>
       </c>
       <c r="AP187">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ187">
         <v>1.14</v>
@@ -40167,7 +40176,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ189">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR189">
         <v>1.65</v>
@@ -40373,7 +40382,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ190">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR190">
         <v>1.56</v>
@@ -40785,7 +40794,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ192">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR192">
         <v>1.34</v>
@@ -40988,7 +40997,7 @@
         <v>0.27</v>
       </c>
       <c r="AP193">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ193">
         <v>0.21</v>
@@ -42845,7 +42854,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ202">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR202">
         <v>1.33</v>
@@ -43254,7 +43263,7 @@
         <v>0.92</v>
       </c>
       <c r="AP204">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ204">
         <v>0.79</v>
@@ -43666,7 +43675,7 @@
         <v>1.42</v>
       </c>
       <c r="AP206">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ206">
         <v>1.5</v>
@@ -43875,7 +43884,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ207">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR207">
         <v>1.6</v>
@@ -44078,10 +44087,10 @@
         <v>2.42</v>
       </c>
       <c r="AP208">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ208">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR208">
         <v>1.32</v>
@@ -47041,6 +47050,624 @@
       </c>
       <c r="BP222">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="223" spans="1:68">
+      <c r="A223" s="1">
+        <v>222</v>
+      </c>
+      <c r="B223">
+        <v>7762815</v>
+      </c>
+      <c r="C223" t="s">
+        <v>68</v>
+      </c>
+      <c r="D223" t="s">
+        <v>69</v>
+      </c>
+      <c r="E223" s="2">
+        <v>45754.375</v>
+      </c>
+      <c r="F223">
+        <v>28</v>
+      </c>
+      <c r="G223" t="s">
+        <v>77</v>
+      </c>
+      <c r="H223" t="s">
+        <v>78</v>
+      </c>
+      <c r="I223">
+        <v>0</v>
+      </c>
+      <c r="J223">
+        <v>2</v>
+      </c>
+      <c r="K223">
+        <v>2</v>
+      </c>
+      <c r="L223">
+        <v>0</v>
+      </c>
+      <c r="M223">
+        <v>4</v>
+      </c>
+      <c r="N223">
+        <v>4</v>
+      </c>
+      <c r="O223" t="s">
+        <v>86</v>
+      </c>
+      <c r="P223" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q223">
+        <v>4.78</v>
+      </c>
+      <c r="R223">
+        <v>2.16</v>
+      </c>
+      <c r="S223">
+        <v>2.49</v>
+      </c>
+      <c r="T223">
+        <v>1.41</v>
+      </c>
+      <c r="U223">
+        <v>2.78</v>
+      </c>
+      <c r="V223">
+        <v>3.1</v>
+      </c>
+      <c r="W223">
+        <v>1.34</v>
+      </c>
+      <c r="X223">
+        <v>9</v>
+      </c>
+      <c r="Y223">
+        <v>1.07</v>
+      </c>
+      <c r="Z223">
+        <v>3.26</v>
+      </c>
+      <c r="AA223">
+        <v>3.45</v>
+      </c>
+      <c r="AB223">
+        <v>2.12</v>
+      </c>
+      <c r="AC223">
+        <v>1.03</v>
+      </c>
+      <c r="AD223">
+        <v>7.7</v>
+      </c>
+      <c r="AE223">
+        <v>1.35</v>
+      </c>
+      <c r="AF223">
+        <v>3.06</v>
+      </c>
+      <c r="AG223">
+        <v>2</v>
+      </c>
+      <c r="AH223">
+        <v>1.67</v>
+      </c>
+      <c r="AI223">
+        <v>1.91</v>
+      </c>
+      <c r="AJ223">
+        <v>1.8</v>
+      </c>
+      <c r="AK223">
+        <v>1.92</v>
+      </c>
+      <c r="AL223">
+        <v>1.3</v>
+      </c>
+      <c r="AM223">
+        <v>1.21</v>
+      </c>
+      <c r="AN223">
+        <v>1.08</v>
+      </c>
+      <c r="AO223">
+        <v>1.23</v>
+      </c>
+      <c r="AP223">
+        <v>1</v>
+      </c>
+      <c r="AQ223">
+        <v>1.36</v>
+      </c>
+      <c r="AR223">
+        <v>1.07</v>
+      </c>
+      <c r="AS223">
+        <v>1.3</v>
+      </c>
+      <c r="AT223">
+        <v>2.37</v>
+      </c>
+      <c r="AU223">
+        <v>7</v>
+      </c>
+      <c r="AV223">
+        <v>10</v>
+      </c>
+      <c r="AW223">
+        <v>4</v>
+      </c>
+      <c r="AX223">
+        <v>5</v>
+      </c>
+      <c r="AY223">
+        <v>11</v>
+      </c>
+      <c r="AZ223">
+        <v>15</v>
+      </c>
+      <c r="BA223">
+        <v>7</v>
+      </c>
+      <c r="BB223">
+        <v>5</v>
+      </c>
+      <c r="BC223">
+        <v>12</v>
+      </c>
+      <c r="BD223">
+        <v>2.4</v>
+      </c>
+      <c r="BE223">
+        <v>6.4</v>
+      </c>
+      <c r="BF223">
+        <v>1.7</v>
+      </c>
+      <c r="BG223">
+        <v>1.35</v>
+      </c>
+      <c r="BH223">
+        <v>2.9</v>
+      </c>
+      <c r="BI223">
+        <v>1.6</v>
+      </c>
+      <c r="BJ223">
+        <v>2.17</v>
+      </c>
+      <c r="BK223">
+        <v>1.98</v>
+      </c>
+      <c r="BL223">
+        <v>1.74</v>
+      </c>
+      <c r="BM223">
+        <v>2.5</v>
+      </c>
+      <c r="BN223">
+        <v>1.46</v>
+      </c>
+      <c r="BO223">
+        <v>3.3</v>
+      </c>
+      <c r="BP223">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="224" spans="1:68">
+      <c r="A224" s="1">
+        <v>223</v>
+      </c>
+      <c r="B224">
+        <v>7762812</v>
+      </c>
+      <c r="C224" t="s">
+        <v>68</v>
+      </c>
+      <c r="D224" t="s">
+        <v>69</v>
+      </c>
+      <c r="E224" s="2">
+        <v>45754.47916666666</v>
+      </c>
+      <c r="F224">
+        <v>28</v>
+      </c>
+      <c r="G224" t="s">
+        <v>72</v>
+      </c>
+      <c r="H224" t="s">
+        <v>84</v>
+      </c>
+      <c r="I224">
+        <v>0</v>
+      </c>
+      <c r="J224">
+        <v>2</v>
+      </c>
+      <c r="K224">
+        <v>2</v>
+      </c>
+      <c r="L224">
+        <v>1</v>
+      </c>
+      <c r="M224">
+        <v>2</v>
+      </c>
+      <c r="N224">
+        <v>3</v>
+      </c>
+      <c r="O224" t="s">
+        <v>214</v>
+      </c>
+      <c r="P224" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q224">
+        <v>3.25</v>
+      </c>
+      <c r="R224">
+        <v>2</v>
+      </c>
+      <c r="S224">
+        <v>3.75</v>
+      </c>
+      <c r="T224">
+        <v>1.5</v>
+      </c>
+      <c r="U224">
+        <v>2.5</v>
+      </c>
+      <c r="V224">
+        <v>3.5</v>
+      </c>
+      <c r="W224">
+        <v>1.29</v>
+      </c>
+      <c r="X224">
+        <v>11</v>
+      </c>
+      <c r="Y224">
+        <v>1.05</v>
+      </c>
+      <c r="Z224">
+        <v>2.14</v>
+      </c>
+      <c r="AA224">
+        <v>3.41</v>
+      </c>
+      <c r="AB224">
+        <v>3.23</v>
+      </c>
+      <c r="AC224">
+        <v>1.01</v>
+      </c>
+      <c r="AD224">
+        <v>8.5</v>
+      </c>
+      <c r="AE224">
+        <v>1.36</v>
+      </c>
+      <c r="AF224">
+        <v>2.99</v>
+      </c>
+      <c r="AG224">
+        <v>2.1</v>
+      </c>
+      <c r="AH224">
+        <v>1.6</v>
+      </c>
+      <c r="AI224">
+        <v>1.91</v>
+      </c>
+      <c r="AJ224">
+        <v>1.8</v>
+      </c>
+      <c r="AK224">
+        <v>1.35</v>
+      </c>
+      <c r="AL224">
+        <v>1.34</v>
+      </c>
+      <c r="AM224">
+        <v>1.57</v>
+      </c>
+      <c r="AN224">
+        <v>0.92</v>
+      </c>
+      <c r="AO224">
+        <v>1.23</v>
+      </c>
+      <c r="AP224">
+        <v>0.86</v>
+      </c>
+      <c r="AQ224">
+        <v>1.36</v>
+      </c>
+      <c r="AR224">
+        <v>1.32</v>
+      </c>
+      <c r="AS224">
+        <v>1.15</v>
+      </c>
+      <c r="AT224">
+        <v>2.47</v>
+      </c>
+      <c r="AU224">
+        <v>6</v>
+      </c>
+      <c r="AV224">
+        <v>4</v>
+      </c>
+      <c r="AW224">
+        <v>4</v>
+      </c>
+      <c r="AX224">
+        <v>3</v>
+      </c>
+      <c r="AY224">
+        <v>10</v>
+      </c>
+      <c r="AZ224">
+        <v>7</v>
+      </c>
+      <c r="BA224">
+        <v>8</v>
+      </c>
+      <c r="BB224">
+        <v>2</v>
+      </c>
+      <c r="BC224">
+        <v>10</v>
+      </c>
+      <c r="BD224">
+        <v>1.82</v>
+      </c>
+      <c r="BE224">
+        <v>6.25</v>
+      </c>
+      <c r="BF224">
+        <v>2.23</v>
+      </c>
+      <c r="BG224">
+        <v>1.56</v>
+      </c>
+      <c r="BH224">
+        <v>2.23</v>
+      </c>
+      <c r="BI224">
+        <v>1.95</v>
+      </c>
+      <c r="BJ224">
+        <v>1.75</v>
+      </c>
+      <c r="BK224">
+        <v>2.55</v>
+      </c>
+      <c r="BL224">
+        <v>1.45</v>
+      </c>
+      <c r="BM224">
+        <v>3.3</v>
+      </c>
+      <c r="BN224">
+        <v>1.27</v>
+      </c>
+      <c r="BO224">
+        <v>4.5</v>
+      </c>
+      <c r="BP224">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="225" spans="1:68">
+      <c r="A225" s="1">
+        <v>224</v>
+      </c>
+      <c r="B225">
+        <v>7762810</v>
+      </c>
+      <c r="C225" t="s">
+        <v>68</v>
+      </c>
+      <c r="D225" t="s">
+        <v>69</v>
+      </c>
+      <c r="E225" s="2">
+        <v>45754.58333333334</v>
+      </c>
+      <c r="F225">
+        <v>28</v>
+      </c>
+      <c r="G225" t="s">
+        <v>81</v>
+      </c>
+      <c r="H225" t="s">
+        <v>75</v>
+      </c>
+      <c r="I225">
+        <v>0</v>
+      </c>
+      <c r="J225">
+        <v>1</v>
+      </c>
+      <c r="K225">
+        <v>1</v>
+      </c>
+      <c r="L225">
+        <v>1</v>
+      </c>
+      <c r="M225">
+        <v>3</v>
+      </c>
+      <c r="N225">
+        <v>4</v>
+      </c>
+      <c r="O225" t="s">
+        <v>129</v>
+      </c>
+      <c r="P225" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q225">
+        <v>5</v>
+      </c>
+      <c r="R225">
+        <v>2.25</v>
+      </c>
+      <c r="S225">
+        <v>2.25</v>
+      </c>
+      <c r="T225">
+        <v>1.36</v>
+      </c>
+      <c r="U225">
+        <v>3</v>
+      </c>
+      <c r="V225">
+        <v>2.75</v>
+      </c>
+      <c r="W225">
+        <v>1.4</v>
+      </c>
+      <c r="X225">
+        <v>7</v>
+      </c>
+      <c r="Y225">
+        <v>1.1</v>
+      </c>
+      <c r="Z225">
+        <v>5.6</v>
+      </c>
+      <c r="AA225">
+        <v>4</v>
+      </c>
+      <c r="AB225">
+        <v>1.56</v>
+      </c>
+      <c r="AC225">
+        <v>1.06</v>
+      </c>
+      <c r="AD225">
+        <v>9</v>
+      </c>
+      <c r="AE225">
+        <v>1.31</v>
+      </c>
+      <c r="AF225">
+        <v>3.26</v>
+      </c>
+      <c r="AG225">
+        <v>1.81</v>
+      </c>
+      <c r="AH225">
+        <v>1.89</v>
+      </c>
+      <c r="AI225">
+        <v>1.83</v>
+      </c>
+      <c r="AJ225">
+        <v>1.83</v>
+      </c>
+      <c r="AK225">
+        <v>2.27</v>
+      </c>
+      <c r="AL225">
+        <v>1.26</v>
+      </c>
+      <c r="AM225">
+        <v>1.15</v>
+      </c>
+      <c r="AN225">
+        <v>1.31</v>
+      </c>
+      <c r="AO225">
+        <v>2.23</v>
+      </c>
+      <c r="AP225">
+        <v>1.21</v>
+      </c>
+      <c r="AQ225">
+        <v>2.29</v>
+      </c>
+      <c r="AR225">
+        <v>1.8</v>
+      </c>
+      <c r="AS225">
+        <v>1.72</v>
+      </c>
+      <c r="AT225">
+        <v>3.52</v>
+      </c>
+      <c r="AU225">
+        <v>4</v>
+      </c>
+      <c r="AV225">
+        <v>5</v>
+      </c>
+      <c r="AW225">
+        <v>7</v>
+      </c>
+      <c r="AX225">
+        <v>2</v>
+      </c>
+      <c r="AY225">
+        <v>11</v>
+      </c>
+      <c r="AZ225">
+        <v>7</v>
+      </c>
+      <c r="BA225">
+        <v>4</v>
+      </c>
+      <c r="BB225">
+        <v>1</v>
+      </c>
+      <c r="BC225">
+        <v>5</v>
+      </c>
+      <c r="BD225">
+        <v>2.9</v>
+      </c>
+      <c r="BE225">
+        <v>6.4</v>
+      </c>
+      <c r="BF225">
+        <v>1.52</v>
+      </c>
+      <c r="BG225">
+        <v>1.53</v>
+      </c>
+      <c r="BH225">
+        <v>2.3</v>
+      </c>
+      <c r="BI225">
+        <v>1.91</v>
+      </c>
+      <c r="BJ225">
+        <v>1.78</v>
+      </c>
+      <c r="BK225">
+        <v>2.43</v>
+      </c>
+      <c r="BL225">
+        <v>1.48</v>
+      </c>
+      <c r="BM225">
+        <v>3.2</v>
+      </c>
+      <c r="BN225">
+        <v>1.29</v>
+      </c>
+      <c r="BO225">
+        <v>4.35</v>
+      </c>
+      <c r="BP225">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -46577,19 +46577,19 @@
         <v>6</v>
       </c>
       <c r="AV220">
+        <v>7</v>
+      </c>
+      <c r="AW220">
+        <v>0</v>
+      </c>
+      <c r="AX220">
+        <v>3</v>
+      </c>
+      <c r="AY220">
         <v>8</v>
       </c>
-      <c r="AW220">
-        <v>5</v>
-      </c>
-      <c r="AX220">
-        <v>9</v>
-      </c>
-      <c r="AY220">
-        <v>11</v>
-      </c>
       <c r="AZ220">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA220">
         <v>5</v>
@@ -46989,19 +46989,19 @@
         <v>0</v>
       </c>
       <c r="AV222">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AW222">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX222">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY222">
         <v>6</v>
       </c>
       <c r="AZ222">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA222">
         <v>1</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Bulgaria First League_20242025.xlsx
@@ -47192,22 +47192,22 @@
         <v>2.37</v>
       </c>
       <c r="AU223">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV223">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AW223">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AX223">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY223">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ223">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BA223">
         <v>7</v>
@@ -47398,22 +47398,22 @@
         <v>2.47</v>
       </c>
       <c r="AU224">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV224">
+        <v>3</v>
+      </c>
+      <c r="AW224">
+        <v>7</v>
+      </c>
+      <c r="AX224">
         <v>4</v>
       </c>
-      <c r="AW224">
-        <v>4</v>
-      </c>
-      <c r="AX224">
-        <v>3</v>
-      </c>
       <c r="AY224">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AZ224">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA224">
         <v>8</v>
@@ -47604,22 +47604,22 @@
         <v>3.52</v>
       </c>
       <c r="AU225">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV225">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW225">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AX225">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY225">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ225">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA225">
         <v>4</v>
